--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="644">
   <si>
     <t>IDSocio</t>
   </si>
@@ -106,6 +106,12 @@
     <t>332845</t>
   </si>
   <si>
+    <t>339174</t>
+  </si>
+  <si>
+    <t>233666</t>
+  </si>
+  <si>
     <t>236785</t>
   </si>
   <si>
@@ -118,114 +124,132 @@
     <t>339256</t>
   </si>
   <si>
-    <t>339174</t>
+    <t>340216</t>
   </si>
   <si>
     <t>339258</t>
   </si>
   <si>
+    <t>340315</t>
+  </si>
+  <si>
+    <t>340512</t>
+  </si>
+  <si>
     <t>338953</t>
   </si>
   <si>
-    <t>340216</t>
-  </si>
-  <si>
-    <t>340315</t>
-  </si>
-  <si>
-    <t>340512</t>
-  </si>
-  <si>
     <t>340516</t>
   </si>
   <si>
     <t>340960</t>
   </si>
   <si>
+    <t>341357</t>
+  </si>
+  <si>
     <t>341101</t>
   </si>
   <si>
+    <t>341889</t>
+  </si>
+  <si>
+    <t>341952</t>
+  </si>
+  <si>
+    <t>341951</t>
+  </si>
+  <si>
+    <t>341922</t>
+  </si>
+  <si>
+    <t>342184</t>
+  </si>
+  <si>
+    <t>342375</t>
+  </si>
+  <si>
+    <t>342048</t>
+  </si>
+  <si>
+    <t>342192</t>
+  </si>
+  <si>
     <t>341099</t>
   </si>
   <si>
-    <t>341357</t>
-  </si>
-  <si>
-    <t>341889</t>
-  </si>
-  <si>
-    <t>341951</t>
+    <t>342287</t>
+  </si>
+  <si>
+    <t>341617</t>
+  </si>
+  <si>
+    <t>342536</t>
+  </si>
+  <si>
+    <t>342380</t>
   </si>
   <si>
     <t>341894</t>
   </si>
   <si>
-    <t>341952</t>
-  </si>
-  <si>
-    <t>341617</t>
-  </si>
-  <si>
-    <t>342184</t>
-  </si>
-  <si>
-    <t>342287</t>
-  </si>
-  <si>
-    <t>341922</t>
-  </si>
-  <si>
-    <t>342048</t>
-  </si>
-  <si>
-    <t>342380</t>
-  </si>
-  <si>
     <t>342227</t>
   </si>
   <si>
-    <t>342192</t>
-  </si>
-  <si>
-    <t>342375</t>
+    <t>343301</t>
+  </si>
+  <si>
+    <t>343539</t>
+  </si>
+  <si>
+    <t>344626</t>
+  </si>
+  <si>
+    <t>343505</t>
+  </si>
+  <si>
+    <t>343544</t>
   </si>
   <si>
     <t>342750</t>
   </si>
   <si>
-    <t>342536</t>
+    <t>343824</t>
+  </si>
+  <si>
+    <t>344676</t>
   </si>
   <si>
     <t>343503</t>
   </si>
   <si>
-    <t>343301</t>
-  </si>
-  <si>
     <t>343838</t>
   </si>
   <si>
+    <t>344233</t>
+  </si>
+  <si>
+    <t>344432</t>
+  </si>
+  <si>
+    <t>344433</t>
+  </si>
+  <si>
     <t>342745</t>
   </si>
   <si>
-    <t>343824</t>
-  </si>
-  <si>
-    <t>343505</t>
-  </si>
-  <si>
-    <t>343544</t>
-  </si>
-  <si>
-    <t>343539</t>
-  </si>
-  <si>
     <t>343831</t>
   </si>
   <si>
     <t>16712</t>
   </si>
   <si>
+    <t>16992</t>
+  </si>
+  <si>
+    <t>31171</t>
+  </si>
+  <si>
     <t>34290</t>
   </si>
   <si>
@@ -238,108 +262,120 @@
     <t>17074</t>
   </si>
   <si>
-    <t>16992</t>
+    <t>18034</t>
   </si>
   <si>
     <t>17076</t>
   </si>
   <si>
+    <t>18133</t>
+  </si>
+  <si>
+    <t>18330</t>
+  </si>
+  <si>
     <t>16771</t>
   </si>
   <si>
-    <t>18034</t>
-  </si>
-  <si>
-    <t>18133</t>
-  </si>
-  <si>
-    <t>18330</t>
-  </si>
-  <si>
     <t>18334</t>
   </si>
   <si>
     <t>18778</t>
   </si>
   <si>
+    <t>19175</t>
+  </si>
+  <si>
     <t>18919</t>
   </si>
   <si>
+    <t>19707</t>
+  </si>
+  <si>
+    <t>19770</t>
+  </si>
+  <si>
+    <t>19769</t>
+  </si>
+  <si>
+    <t>19740</t>
+  </si>
+  <si>
+    <t>20002</t>
+  </si>
+  <si>
+    <t>20193</t>
+  </si>
+  <si>
+    <t>19866</t>
+  </si>
+  <si>
+    <t>20010</t>
+  </si>
+  <si>
     <t>18917</t>
   </si>
   <si>
-    <t>19175</t>
-  </si>
-  <si>
-    <t>19707</t>
-  </si>
-  <si>
-    <t>19769</t>
+    <t>20105</t>
+  </si>
+  <si>
+    <t>19435</t>
+  </si>
+  <si>
+    <t>20353</t>
+  </si>
+  <si>
+    <t>20198</t>
   </si>
   <si>
     <t>19712</t>
   </si>
   <si>
-    <t>19770</t>
-  </si>
-  <si>
-    <t>19435</t>
-  </si>
-  <si>
-    <t>20002</t>
-  </si>
-  <si>
-    <t>20105</t>
-  </si>
-  <si>
-    <t>19740</t>
-  </si>
-  <si>
-    <t>19866</t>
-  </si>
-  <si>
-    <t>20198</t>
-  </si>
-  <si>
     <t>20045</t>
   </si>
   <si>
-    <t>20010</t>
-  </si>
-  <si>
-    <t>20193</t>
+    <t>21118</t>
+  </si>
+  <si>
+    <t>21356</t>
+  </si>
+  <si>
+    <t>22443</t>
+  </si>
+  <si>
+    <t>21322</t>
+  </si>
+  <si>
+    <t>21361</t>
   </si>
   <si>
     <t>20567</t>
   </si>
   <si>
-    <t>20353</t>
+    <t>21641</t>
+  </si>
+  <si>
+    <t>22493</t>
   </si>
   <si>
     <t>21320</t>
   </si>
   <si>
-    <t>21118</t>
-  </si>
-  <si>
     <t>21655</t>
   </si>
   <si>
+    <t>22050</t>
+  </si>
+  <si>
+    <t>22249</t>
+  </si>
+  <si>
+    <t>22250</t>
+  </si>
+  <si>
     <t>20562</t>
   </si>
   <si>
-    <t>21641</t>
-  </si>
-  <si>
-    <t>21322</t>
-  </si>
-  <si>
-    <t>21361</t>
-  </si>
-  <si>
-    <t>21356</t>
-  </si>
-  <si>
     <t>21648</t>
   </si>
   <si>
@@ -349,6 +385,12 @@
     <t>MIRSHA ASERET</t>
   </si>
   <si>
+    <t>DAVID ISAAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATALY </t>
+  </si>
+  <si>
     <t>MARIA DEL ROSARIO</t>
   </si>
   <si>
@@ -361,114 +403,132 @@
     <t>CARLOS EDUARDO</t>
   </si>
   <si>
-    <t>DAVID ISAAC</t>
+    <t>AXEL ZADKYEL</t>
   </si>
   <si>
     <t>PAOLA</t>
   </si>
   <si>
+    <t>MAYRA JAZMIN</t>
+  </si>
+  <si>
+    <t>ROSA LIDIA</t>
+  </si>
+  <si>
     <t xml:space="preserve">FABIOLA </t>
   </si>
   <si>
-    <t>AXEL ZADKYEL</t>
-  </si>
-  <si>
-    <t>MAYRA JAZMIN</t>
-  </si>
-  <si>
-    <t>ROSA LIDIA</t>
-  </si>
-  <si>
     <t>CARLOS ENRIQUE</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
     <t>CHRISTIAN OWEN</t>
   </si>
   <si>
+    <t>LUCIA</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIANA </t>
+  </si>
+  <si>
+    <t>YANNEVY ARIADNE</t>
+  </si>
+  <si>
+    <t>LUIS FERNANDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIANA AMELIA </t>
+  </si>
+  <si>
+    <t>DULCE IVONNE</t>
+  </si>
+  <si>
+    <t>JESUS ZAID</t>
+  </si>
+  <si>
     <t>AXEL KALID</t>
   </si>
   <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>LUCIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADRIANA </t>
+    <t>IRVING DONNOVAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDILBERTO </t>
+  </si>
+  <si>
+    <t>HANNIA ATZIRY</t>
+  </si>
+  <si>
+    <t>DIANA ALINE</t>
   </si>
   <si>
     <t xml:space="preserve">JONATHAN </t>
   </si>
   <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDILBERTO </t>
-  </si>
-  <si>
-    <t>LUIS FERNANDO</t>
-  </si>
-  <si>
-    <t>IRVING DONNOVAN</t>
-  </si>
-  <si>
-    <t>YANNEVY ARIADNE</t>
-  </si>
-  <si>
-    <t>DULCE IVONNE</t>
-  </si>
-  <si>
-    <t>DIANA ALINE</t>
-  </si>
-  <si>
     <t>YORDI JESUS</t>
   </si>
   <si>
-    <t>JESUS ZAID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIANA AMELIA </t>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ROCIO</t>
+  </si>
+  <si>
+    <t>IXCHEL YARELI</t>
+  </si>
+  <si>
+    <t>ALVARO O BRIAN</t>
+  </si>
+  <si>
+    <t>LAURA AMAYRANI</t>
   </si>
   <si>
     <t>MANUEL RAFAEL</t>
   </si>
   <si>
-    <t>HANNIA ATZIRY</t>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>JESSICA BERENICE</t>
   </si>
   <si>
     <t>DIANA VIANEY</t>
   </si>
   <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
     <t>ALBERTO</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ALFREDO</t>
+  </si>
+  <si>
+    <t>IRIS MONTSERRAT</t>
+  </si>
+  <si>
     <t>ITZEL STEPHANY</t>
   </si>
   <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ALVARO O BRIAN</t>
-  </si>
-  <si>
-    <t>LAURA AMAYRANI</t>
-  </si>
-  <si>
-    <t>ROCIO</t>
-  </si>
-  <si>
     <t>JESSICA</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>CRISOSTOMO</t>
+  </si>
+  <si>
+    <t>VILLALPANDO</t>
+  </si>
+  <si>
     <t>ROBLES</t>
   </si>
   <si>
@@ -481,15 +541,12 @@
     <t xml:space="preserve">HERNANDEZ </t>
   </si>
   <si>
-    <t>CRISOSTOMO</t>
+    <t>VALDEZ</t>
   </si>
   <si>
     <t>ARTEAGA</t>
   </si>
   <si>
-    <t>VALDEZ</t>
-  </si>
-  <si>
     <t>KURY</t>
   </si>
   <si>
@@ -502,81 +559,102 @@
     <t>AYALA</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>CERVANTES</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>BORREGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRAVO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GONZALEZ </t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GONZALEZ </t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRAVO </t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>ROCHA</t>
   </si>
   <si>
-    <t>BORREGO</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
+    <t>TOVAR</t>
+  </si>
+  <si>
+    <t>JAIMEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIN </t>
+  </si>
+  <si>
+    <t>VALADEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>SANDOVAL</t>
+    <t>PONCE</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t xml:space="preserve">CARREON </t>
   </si>
   <si>
-    <t>TOVAR</t>
-  </si>
-  <si>
     <t xml:space="preserve">MORAN </t>
   </si>
   <si>
+    <t xml:space="preserve">JEREZ </t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>CHAVARIN</t>
+  </si>
+  <si>
     <t>VERDE</t>
   </si>
   <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>VALADEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>JAIMEZ</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
+    <t>CARDOSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CADENA </t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -586,9 +664,6 @@
     <t>PLATA</t>
   </si>
   <si>
-    <t>CARDOSO</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
@@ -598,78 +673,84 @@
     <t>ANZALDO</t>
   </si>
   <si>
+    <t xml:space="preserve">QUINTERO </t>
+  </si>
+  <si>
     <t>GUERRERO</t>
   </si>
   <si>
-    <t xml:space="preserve">QUINTERO </t>
-  </si>
-  <si>
     <t>BELLO</t>
   </si>
   <si>
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>SIERNA</t>
+  </si>
+  <si>
+    <t>ZARCO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t xml:space="preserve">URBAN </t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ZARCO</t>
-  </si>
-  <si>
     <t>PADRON</t>
   </si>
   <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>SIERNA</t>
+    <t>ESPEJEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGUEZ </t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>BLANCA</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>MORALES</t>
+    <t>GUEVARA</t>
   </si>
   <si>
     <t>YAÑEZ</t>
   </si>
   <si>
-    <t>ESPEJEL</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>SERVIN</t>
   </si>
   <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>BLANCA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RODRIGUEZ </t>
-  </si>
-  <si>
     <t>52</t>
   </si>
   <si>
     <t>5574210862</t>
   </si>
   <si>
+    <t>5550539848</t>
+  </si>
+  <si>
+    <t>5564992033</t>
+  </si>
+  <si>
     <t>5573035144</t>
   </si>
   <si>
@@ -682,114 +763,132 @@
     <t>5528464677</t>
   </si>
   <si>
-    <t>5550539848</t>
+    <t>5591647693</t>
   </si>
   <si>
     <t>5512421794</t>
   </si>
   <si>
+    <t>5561248221</t>
+  </si>
+  <si>
+    <t>5521196367</t>
+  </si>
+  <si>
     <t>5582314058</t>
   </si>
   <si>
-    <t>5591647693</t>
-  </si>
-  <si>
-    <t>5561248221</t>
-  </si>
-  <si>
-    <t>5521196367</t>
-  </si>
-  <si>
     <t>5619885190</t>
   </si>
   <si>
     <t>5669156876</t>
   </si>
   <si>
+    <t>5634592607</t>
+  </si>
+  <si>
     <t>5643127118</t>
   </si>
   <si>
+    <t>5574445968</t>
+  </si>
+  <si>
+    <t>5520734799</t>
+  </si>
+  <si>
+    <t>5641136687</t>
+  </si>
+  <si>
+    <t>5580261394</t>
+  </si>
+  <si>
+    <t>5537110647</t>
+  </si>
+  <si>
+    <t>5532857495</t>
+  </si>
+  <si>
+    <t>5519303247</t>
+  </si>
+  <si>
+    <t>4055882651</t>
+  </si>
+  <si>
     <t>5635122950</t>
   </si>
   <si>
-    <t>5634592607</t>
-  </si>
-  <si>
-    <t>5574445968</t>
-  </si>
-  <si>
-    <t>5641136687</t>
+    <t>5564343538</t>
+  </si>
+  <si>
+    <t>5540185856</t>
+  </si>
+  <si>
+    <t>5541561912</t>
+  </si>
+  <si>
+    <t>5625435058</t>
   </si>
   <si>
     <t>5574445964</t>
   </si>
   <si>
-    <t>5520734799</t>
-  </si>
-  <si>
-    <t>5540185856</t>
-  </si>
-  <si>
-    <t>5537110647</t>
-  </si>
-  <si>
-    <t>5564343538</t>
-  </si>
-  <si>
-    <t>5580261394</t>
-  </si>
-  <si>
-    <t>5519303247</t>
-  </si>
-  <si>
-    <t>5625435058</t>
-  </si>
-  <si>
     <t>5613711355</t>
   </si>
   <si>
-    <t>4055882651</t>
-  </si>
-  <si>
-    <t>5532857495</t>
+    <t>5516346350</t>
+  </si>
+  <si>
+    <t>5534063877</t>
+  </si>
+  <si>
+    <t>5579912763</t>
+  </si>
+  <si>
+    <t>5591919598</t>
+  </si>
+  <si>
+    <t>5546447212</t>
   </si>
   <si>
     <t>5574265455</t>
   </si>
   <si>
-    <t>5541561912</t>
+    <t>5531971979</t>
+  </si>
+  <si>
+    <t>2219009457</t>
   </si>
   <si>
     <t>5614816775</t>
   </si>
   <si>
-    <t>5516346350</t>
-  </si>
-  <si>
     <t>2206073345</t>
   </si>
   <si>
+    <t>5611753742</t>
+  </si>
+  <si>
+    <t>5515226715</t>
+  </si>
+  <si>
+    <t>5564692994</t>
+  </si>
+  <si>
     <t>5584585348</t>
   </si>
   <si>
-    <t>5531971979</t>
-  </si>
-  <si>
-    <t>5591919598</t>
-  </si>
-  <si>
-    <t>5546447212</t>
-  </si>
-  <si>
-    <t>5534063877</t>
-  </si>
-  <si>
     <t>2217041181</t>
   </si>
   <si>
     <t>C IGNACIO ZARAGOZA MZ 25</t>
   </si>
   <si>
+    <t>CDA 21 DE MARZO 12</t>
+  </si>
+  <si>
+    <t>AV LOS PINOS MZ 37 LT 17</t>
+  </si>
+  <si>
     <t>CDA BOSQUE DE EUCALIPTOS MZA 29</t>
   </si>
   <si>
@@ -802,24 +901,21 @@
     <t xml:space="preserve">AV. JOSE MARIA MARTINEZ MZA 24 LT 19 </t>
   </si>
   <si>
-    <t>CDA 21 DE MARZO 12</t>
+    <t>SAN BUENAVENTURA</t>
   </si>
   <si>
     <t>AV. JOSE MARIA MARTINEZ MZA 24 LY 19</t>
   </si>
   <si>
+    <t>IXTAP</t>
+  </si>
+  <si>
+    <t>IXTA</t>
+  </si>
+  <si>
     <t>CDA DE JAZMINES MZ 20 LT 10</t>
   </si>
   <si>
-    <t>SAN BUENAVENTURA</t>
-  </si>
-  <si>
-    <t>IXTAP</t>
-  </si>
-  <si>
-    <t>IXTA</t>
-  </si>
-  <si>
     <t>C TONATICO 197</t>
   </si>
   <si>
@@ -829,25 +925,34 @@
     <t>LOTOS</t>
   </si>
   <si>
+    <t>RANCHOO</t>
+  </si>
+  <si>
     <t>RANCHO</t>
   </si>
   <si>
-    <t>RANCHOO</t>
+    <t>HEROES</t>
+  </si>
+  <si>
+    <t>COL SANTA CRUZ TLAPACOYA</t>
+  </si>
+  <si>
+    <t>AV DEL POPO MZA 56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. LA CIGARRA COL. ESPERANZA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C MELCHOR OCAMPO S/N COL. LA ESPERANZA </t>
+  </si>
+  <si>
+    <t>C PERA SAN MARCOS</t>
   </si>
   <si>
     <t>ACACIA 80</t>
   </si>
   <si>
-    <t>COL SANTA CRUZ TLAPACOYA</t>
-  </si>
-  <si>
-    <t>C PERA SAN MARCOS</t>
-  </si>
-  <si>
-    <t>HEROES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C. LA CIGARRA COL. ESPERANZA </t>
+    <t>TEJALPA</t>
   </si>
   <si>
     <t xml:space="preserve">C CASTILLO DE CHAPULTEPEC </t>
@@ -856,42 +961,45 @@
     <t>CDA HACIENDA DE JALPA MZ 19 LT 115C</t>
   </si>
   <si>
-    <t xml:space="preserve">C MELCHOR OCAMPO S/N COL. LA ESPERANZA </t>
-  </si>
-  <si>
-    <t>AV DEL POPO MZA 56</t>
+    <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
+  </si>
+  <si>
+    <t>C CUAUTZINGO MZA 34</t>
+  </si>
+  <si>
+    <t>C DZILAM MZ 814 LT 4</t>
+  </si>
+  <si>
+    <t>AV NUEVO MEXICO 301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
   </si>
   <si>
     <t>C CEBADA MZ 6 LT 3</t>
   </si>
   <si>
-    <t>TEJALPA</t>
+    <t>COL CENTRO CDMX</t>
+  </si>
+  <si>
+    <t>C CIPRECES MZ 3</t>
   </si>
   <si>
     <t>C TEPOYAN 5</t>
   </si>
   <si>
-    <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
-  </si>
-  <si>
     <t>CALLE MAGNOLIA 242</t>
   </si>
   <si>
+    <t xml:space="preserve">FRACC LOS HEROES </t>
+  </si>
+  <si>
+    <t>ALFREDIO</t>
+  </si>
+  <si>
     <t>CDA BARRANCA DE MEZQUITE MZ 56</t>
   </si>
   <si>
-    <t>COL CENTRO CDMX</t>
-  </si>
-  <si>
-    <t>AV NUEVO MEXICO 301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
-  </si>
-  <si>
-    <t>C CUAUTZINGO MZA 34</t>
-  </si>
-  <si>
     <t>Femenino</t>
   </si>
   <si>
@@ -901,6 +1009,12 @@
     <t>11-02-2000</t>
   </si>
   <si>
+    <t>03-06-1998</t>
+  </si>
+  <si>
+    <t>30-11-1985</t>
+  </si>
+  <si>
     <t>24-06-1985</t>
   </si>
   <si>
@@ -913,114 +1027,132 @@
     <t>12-01-1990</t>
   </si>
   <si>
-    <t>03-06-1998</t>
+    <t>24-05-2006</t>
   </si>
   <si>
     <t>07-04-1992</t>
   </si>
   <si>
+    <t>13-08-1980</t>
+  </si>
+  <si>
+    <t>14-04-1993</t>
+  </si>
+  <si>
     <t>11-04-1991</t>
   </si>
   <si>
-    <t>24-05-2006</t>
-  </si>
-  <si>
-    <t>13-08-1980</t>
-  </si>
-  <si>
-    <t>14-04-1993</t>
-  </si>
-  <si>
     <t>05-08-1991</t>
   </si>
   <si>
     <t>19-02-1993</t>
   </si>
   <si>
+    <t>25-11-2010</t>
+  </si>
+  <si>
     <t>18-06-2011</t>
   </si>
   <si>
+    <t>06-03-1990</t>
+  </si>
+  <si>
+    <t>31-08-1964</t>
+  </si>
+  <si>
+    <t>05-03-1965</t>
+  </si>
+  <si>
+    <t>25-11-1994</t>
+  </si>
+  <si>
+    <t>25-07-2017</t>
+  </si>
+  <si>
+    <t>10-08-1975</t>
+  </si>
+  <si>
+    <t>01-08-1991</t>
+  </si>
+  <si>
+    <t>23-12-1999</t>
+  </si>
+  <si>
     <t>23-07-2004</t>
   </si>
   <si>
-    <t>25-11-2010</t>
-  </si>
-  <si>
-    <t>06-03-1990</t>
-  </si>
-  <si>
-    <t>05-03-1965</t>
+    <t>06-09-1992</t>
+  </si>
+  <si>
+    <t>13-08-1979</t>
+  </si>
+  <si>
+    <t>22-01-1997</t>
+  </si>
+  <si>
+    <t>22-12-1996</t>
   </si>
   <si>
     <t>06-12-1990</t>
   </si>
   <si>
-    <t>31-08-1964</t>
-  </si>
-  <si>
-    <t>13-08-1979</t>
-  </si>
-  <si>
-    <t>25-07-2017</t>
-  </si>
-  <si>
-    <t>06-09-1992</t>
-  </si>
-  <si>
-    <t>25-11-1994</t>
-  </si>
-  <si>
-    <t>01-08-1991</t>
-  </si>
-  <si>
-    <t>22-12-1996</t>
-  </si>
-  <si>
     <t>23-10-2002</t>
   </si>
   <si>
-    <t>23-12-1999</t>
-  </si>
-  <si>
-    <t>10-08-1975</t>
+    <t>06-07-1995</t>
+  </si>
+  <si>
+    <t>12-01-1998</t>
+  </si>
+  <si>
+    <t>31-01-1989</t>
+  </si>
+  <si>
+    <t>12-09-1993</t>
+  </si>
+  <si>
+    <t>13-03-2007</t>
   </si>
   <si>
     <t>23-11-1999</t>
   </si>
   <si>
-    <t>22-01-1997</t>
+    <t>02-03-1973</t>
+  </si>
+  <si>
+    <t>02-04-1995</t>
   </si>
   <si>
     <t>16-10-1986</t>
   </si>
   <si>
-    <t>06-07-1995</t>
-  </si>
-  <si>
     <t>26-02-1995</t>
   </si>
   <si>
+    <t>07-08-1998</t>
+  </si>
+  <si>
+    <t>23-08-1991</t>
+  </si>
+  <si>
+    <t>29-08-1994</t>
+  </si>
+  <si>
     <t>21-12-1995</t>
   </si>
   <si>
-    <t>02-03-1973</t>
-  </si>
-  <si>
-    <t>12-09-1993</t>
-  </si>
-  <si>
-    <t>13-03-2007</t>
-  </si>
-  <si>
-    <t>12-01-1998</t>
-  </si>
-  <si>
     <t>14-12-1998</t>
   </si>
   <si>
     <t>MIRSHA@GMAIL.COM</t>
   </si>
   <si>
+    <t>DEIVID.AYD.CRI98@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>NATYVILLALPANDO6@GMAIL.COM</t>
+  </si>
+  <si>
     <t>PRINCESS_CHAIN@HOTMAIL.COM</t>
   </si>
   <si>
@@ -1033,114 +1165,132 @@
     <t>ELDA.SOLRAC@GMAIL.COM</t>
   </si>
   <si>
-    <t>DEIVID.AYD.CRI98@GMAIL.COM</t>
+    <t>AXELVALDEZ099@GMAL.COM</t>
   </si>
   <si>
     <t>LOOPZY_9797@HOTMAIL.COM</t>
   </si>
   <si>
+    <t>MAYRACGT@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ROSYN_N@HOTMAIL.COM</t>
+  </si>
+  <si>
     <t>FALIZEE004@GMAIL.COM</t>
   </si>
   <si>
-    <t>AXELVALDEZ099@GMAL.COM</t>
-  </si>
-  <si>
-    <t>MAYRACGT@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ROSYN_N@HOTMAIL.COM</t>
-  </si>
-  <si>
     <t>ENRIQUE-RUEDA@OUTLOOK.COM</t>
   </si>
   <si>
     <t>BUICKGOLIFE856@GMAIL.COM</t>
   </si>
   <si>
+    <t>DENI.QUINTERO2010@GMAIL.COM</t>
+  </si>
+  <si>
     <t>CHRISTIAN09MENDEZ1234@GMAIL.COM</t>
   </si>
   <si>
+    <t>LUCYCOSA06039@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MONN.64KAISER@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ADRIANA.CERVANT.AL@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>YENNEVY@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>KARINAFLORESVICENTE@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>DIANAALINE10@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>DULCEIVONNETORRESZARCO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SAIDD.BST@GMAIL.COM</t>
+  </si>
+  <si>
     <t>GUERREROAXEL190@GMAIL.COM</t>
   </si>
   <si>
-    <t>DENI.QUINTERO2010@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>LUCYCOSA06039@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ADRIANA.CERVANT.AL@GMAIL.COM</t>
+    <t>DONNOVANBR@OUTLOOK.COM</t>
+  </si>
+  <si>
+    <t>GONZALEZCRUZEDILBERTO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>HANNIA_22_SANDOVAL@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>DIGTZ15@GMAIL.COM</t>
   </si>
   <si>
     <t>SOLDADO.DE.DIOS@HOTMAIL.COM</t>
   </si>
   <si>
-    <t>MONN.64KAISER@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>GONZALEZCRUZEDILBERTO@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>KARINAFLORESVICENTE@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>DONNOVANBR@OUTLOOK.COM</t>
-  </si>
-  <si>
-    <t>YENNEVY@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>DULCEIVONNETORRESZARCO@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>DIGTZ15@GMAIL.COM</t>
-  </si>
-  <si>
     <t>TREYOI.1023.ROCHA@GMAIL.COM</t>
   </si>
   <si>
-    <t>SAIDD.BST@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>DIANAALINE10@HOTMAIL.COM</t>
+    <t>DIEGOLUPUS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IXCHELMARIN@OUTLOOK.COM</t>
+  </si>
+  <si>
+    <t>POSEIDONBALA93@OUTLOOK.COM</t>
+  </si>
+  <si>
+    <t>LAUPRD25@GMAIL.COM</t>
   </si>
   <si>
     <t>MANUEL_LVNA@HOTMAIL.COM</t>
   </si>
   <si>
-    <t>HANNIA_22_SANDOVAL@HOTMAIL.COM</t>
+    <t>MAPGUE2@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JEBER18@YAHOO.COM.MX</t>
   </si>
   <si>
     <t>DIANACARREON995@GMAIL.COM</t>
   </si>
   <si>
-    <t>DIEGOLUPUS@GMAIL.COM</t>
-  </si>
-  <si>
     <t>TRILLISO_BET@HOTMAIL.COM</t>
   </si>
   <si>
+    <t>CASTROMARIAFERNANDA57@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>LIC.ALFREDO.91@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MONTSERRAT_94@HOTMAIL.COM</t>
+  </si>
+  <si>
     <t>ITZEL_VERDE95@ICLOUD.COM</t>
   </si>
   <si>
-    <t>MAPGUE2@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>POSEIDONBALA93@OUTLOOK.COM</t>
-  </si>
-  <si>
-    <t>LAUPRD25@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
-  </si>
-  <si>
     <t>JESSICAHERNANDEZVAZQUEZ@OUTLOOK.COM</t>
   </si>
   <si>
     <t>07-01-2026 14:07:05</t>
   </si>
   <si>
+    <t>29-01-2026 19:21:28</t>
+  </si>
+  <si>
+    <t>09-05-2024 07:51:19</t>
+  </si>
+  <si>
     <t>28-05-2024 18:11:53</t>
   </si>
   <si>
@@ -1153,111 +1303,126 @@
     <t>30-01-2026 09:16:32</t>
   </si>
   <si>
-    <t>29-01-2026 19:21:28</t>
+    <t>02-02-2026 15:29:08</t>
   </si>
   <si>
     <t>30-01-2026 09:21:25</t>
   </si>
   <si>
+    <t>02-02-2026 17:44:11</t>
+  </si>
+  <si>
+    <t>03-02-2026 10:51:49</t>
+  </si>
+  <si>
     <t>29-01-2026 08:24:12</t>
   </si>
   <si>
-    <t>02-02-2026 15:29:08</t>
-  </si>
-  <si>
-    <t>02-02-2026 17:44:11</t>
-  </si>
-  <si>
-    <t>03-02-2026 10:51:49</t>
-  </si>
-  <si>
     <t>03-02-2026 10:59:53</t>
   </si>
   <si>
     <t>04-02-2026 12:16:09</t>
   </si>
   <si>
+    <t>05-02-2026 16:04:32</t>
+  </si>
+  <si>
     <t>04-02-2026 17:18:13</t>
   </si>
   <si>
+    <t>08-02-2026 09:58:42</t>
+  </si>
+  <si>
+    <t>08-02-2026 13:27:30</t>
+  </si>
+  <si>
+    <t>08-02-2026 13:24:14</t>
+  </si>
+  <si>
+    <t>08-02-2026 11:53:18</t>
+  </si>
+  <si>
+    <t>09-02-2026 14:42:03</t>
+  </si>
+  <si>
+    <t>09-02-2026 18:11:48</t>
+  </si>
+  <si>
+    <t>09-02-2026 08:22:24</t>
+  </si>
+  <si>
+    <t>09-02-2026 14:52:50</t>
+  </si>
+  <si>
     <t>04-02-2026 17:15:27</t>
   </si>
   <si>
-    <t>05-02-2026 16:04:32</t>
-  </si>
-  <si>
-    <t>08-02-2026 09:58:42</t>
-  </si>
-  <si>
-    <t>08-02-2026 13:24:14</t>
+    <t>09-02-2026 16:52:02</t>
+  </si>
+  <si>
+    <t>06-02-2026 16:14:24</t>
+  </si>
+  <si>
+    <t>10-02-2026 07:49:10</t>
+  </si>
+  <si>
+    <t>09-02-2026 18:16:13</t>
   </si>
   <si>
     <t>08-02-2026 10:05:09</t>
   </si>
   <si>
-    <t>08-02-2026 13:27:30</t>
-  </si>
-  <si>
-    <t>06-02-2026 16:14:24</t>
-  </si>
-  <si>
-    <t>09-02-2026 14:42:03</t>
-  </si>
-  <si>
-    <t>09-02-2026 16:52:02</t>
-  </si>
-  <si>
-    <t>08-02-2026 11:53:18</t>
-  </si>
-  <si>
-    <t>09-02-2026 08:22:24</t>
-  </si>
-  <si>
-    <t>09-02-2026 18:16:13</t>
-  </si>
-  <si>
     <t>09-02-2026 15:55:59</t>
   </si>
   <si>
-    <t>09-02-2026 14:52:50</t>
-  </si>
-  <si>
-    <t>09-02-2026 18:11:48</t>
+    <t>12-02-2026 16:04:34</t>
+  </si>
+  <si>
+    <t>13-02-2026 16:58:39</t>
+  </si>
+  <si>
+    <t>17-02-2026 17:48:58</t>
+  </si>
+  <si>
+    <t>13-02-2026 14:50:25</t>
+  </si>
+  <si>
+    <t>13-02-2026 17:03:29</t>
   </si>
   <si>
     <t>10-02-2026 17:23:26</t>
   </si>
   <si>
-    <t>10-02-2026 07:49:10</t>
+    <t>15-02-2026 12:05:48</t>
+  </si>
+  <si>
+    <t>17-02-2026 19:05:24</t>
   </si>
   <si>
     <t>13-02-2026 14:48:21</t>
   </si>
   <si>
-    <t>12-02-2026 16:04:34</t>
-  </si>
-  <si>
     <t>15-02-2026 12:36:33</t>
   </si>
   <si>
+    <t>16-02-2026 17:43:53</t>
+  </si>
+  <si>
+    <t>17-02-2026 09:59:28</t>
+  </si>
+  <si>
+    <t>17-02-2026 10:03:24</t>
+  </si>
+  <si>
     <t>10-02-2026 17:16:16</t>
   </si>
   <si>
-    <t>15-02-2026 12:05:48</t>
-  </si>
-  <si>
-    <t>13-02-2026 14:50:25</t>
-  </si>
-  <si>
-    <t>13-02-2026 17:03:29</t>
-  </si>
-  <si>
-    <t>13-02-2026 16:58:39</t>
-  </si>
-  <si>
     <t>15-02-2026 12:21:19</t>
   </si>
   <si>
+    <t>inscripcion promo 199</t>
+  </si>
+  <si>
     <t>Tarifas 2026 LE</t>
   </si>
   <si>
@@ -1267,6 +1432,9 @@
     <t>Sin contrato</t>
   </si>
   <si>
+    <t>No Forzoso</t>
+  </si>
+  <si>
     <t>PROMO FEBRERO 12 MESES</t>
   </si>
   <si>
@@ -1279,15 +1447,27 @@
     <t>3 MESES $1,899</t>
   </si>
   <si>
+    <t>PLAN FAMILIAR RECURRENTE $999</t>
+  </si>
+  <si>
     <t>499</t>
   </si>
   <si>
     <t>633</t>
   </si>
   <si>
+    <t>999</t>
+  </si>
+  <si>
     <t>13-02-2026 18:00:19</t>
   </si>
   <si>
+    <t>05-02-2026 19:25:52</t>
+  </si>
+  <si>
+    <t>16-02-2026 07:18:36</t>
+  </si>
+  <si>
     <t>02-02-2026 19:13:53</t>
   </si>
   <si>
@@ -1300,111 +1480,129 @@
     <t>02-02-2026 11:52:16</t>
   </si>
   <si>
-    <t>05-02-2026 19:25:52</t>
+    <t>02-02-2026 15:45:59</t>
   </si>
   <si>
     <t>02-02-2026 11:50:19</t>
   </si>
   <si>
+    <t>03-02-2026 07:27:24</t>
+  </si>
+  <si>
+    <t>03-02-2026 10:57:53</t>
+  </si>
+  <si>
     <t>01-02-2026 09:51:51</t>
   </si>
   <si>
-    <t>02-02-2026 15:45:59</t>
-  </si>
-  <si>
-    <t>03-02-2026 07:27:24</t>
-  </si>
-  <si>
-    <t>03-02-2026 10:57:53</t>
-  </si>
-  <si>
     <t>03-02-2026 11:02:47</t>
   </si>
   <si>
     <t>04-02-2026 12:24:18</t>
   </si>
   <si>
+    <t>05-02-2026 16:09:19</t>
+  </si>
+  <si>
     <t>04-02-2026 17:31:39</t>
   </si>
   <si>
+    <t>08-02-2026 10:02:56</t>
+  </si>
+  <si>
+    <t>08-02-2026 13:36:45</t>
+  </si>
+  <si>
+    <t>08-02-2026 13:32:56</t>
+  </si>
+  <si>
+    <t>08-02-2026 11:58:57</t>
+  </si>
+  <si>
+    <t>09-02-2026 14:52:27</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:14:46</t>
+  </si>
+  <si>
+    <t>09-02-2026 08:34:47</t>
+  </si>
+  <si>
+    <t>09-02-2026 15:06:28</t>
+  </si>
+  <si>
     <t>04-02-2026 17:26:19</t>
   </si>
   <si>
-    <t>05-02-2026 16:09:19</t>
-  </si>
-  <si>
-    <t>08-02-2026 10:02:56</t>
-  </si>
-  <si>
-    <t>08-02-2026 13:32:56</t>
+    <t>12-02-2026 18:07:17</t>
+  </si>
+  <si>
+    <t>06-02-2026 17:06:08</t>
+  </si>
+  <si>
+    <t>10-02-2026 07:55:17</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:19:45</t>
   </si>
   <si>
     <t>08-02-2026 10:07:34</t>
   </si>
   <si>
-    <t>08-02-2026 13:36:45</t>
-  </si>
-  <si>
-    <t>06-02-2026 17:06:08</t>
-  </si>
-  <si>
-    <t>09-02-2026 14:52:27</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:07:17</t>
-  </si>
-  <si>
-    <t>08-02-2026 11:58:57</t>
-  </si>
-  <si>
-    <t>09-02-2026 08:34:47</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:19:45</t>
-  </si>
-  <si>
     <t>09-02-2026 16:06:40</t>
   </si>
   <si>
-    <t>09-02-2026 15:06:28</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:14:46</t>
+    <t>12-02-2026 16:26:22</t>
+  </si>
+  <si>
+    <t>13-02-2026 17:12:37</t>
+  </si>
+  <si>
+    <t>17-02-2026 18:01:12</t>
+  </si>
+  <si>
+    <t>13-02-2026 14:59:34</t>
+  </si>
+  <si>
+    <t>13-02-2026 17:19:38</t>
   </si>
   <si>
     <t>10-02-2026 17:27:27</t>
   </si>
   <si>
-    <t>10-02-2026 07:55:17</t>
+    <t>15-02-2026 12:25:35</t>
+  </si>
+  <si>
+    <t>17-02-2026 19:14:49</t>
   </si>
   <si>
     <t>13-02-2026 15:06:00</t>
   </si>
   <si>
-    <t>12-02-2026 16:26:22</t>
+    <t>16-02-2026 18:16:35</t>
+  </si>
+  <si>
+    <t>17-02-2026 10:14:17</t>
+  </si>
+  <si>
+    <t>17-02-2026 10:10:20</t>
   </si>
   <si>
     <t>10-02-2026 17:21:18</t>
   </si>
   <si>
-    <t>15-02-2026 12:25:35</t>
-  </si>
-  <si>
-    <t>13-02-2026 14:59:34</t>
-  </si>
-  <si>
-    <t>13-02-2026 17:19:38</t>
-  </si>
-  <si>
-    <t>13-02-2026 17:12:37</t>
-  </si>
-  <si>
     <t>15-02-2026 12:21:20</t>
   </si>
   <si>
     <t>13-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>05-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>16-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>02-03-2026 23:59:59</t>
   </si>
   <si>
@@ -1417,9 +1615,6 @@
     <t>28-02-2026 23:59:59</t>
   </si>
   <si>
-    <t>05-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>03-03-2026 23:59:59</t>
   </si>
   <si>
@@ -1432,21 +1627,30 @@
     <t>08-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>12-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>06-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>12-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>10-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>17-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>15-03-2026 23:59:59</t>
   </si>
   <si>
     <t>13-02-2026 18:00:00</t>
   </si>
   <si>
+    <t>05-02-2026 19:22:43</t>
+  </si>
+  <si>
+    <t>16-02-2026 07:17:49</t>
+  </si>
+  <si>
     <t>02-02-2026 19:13:00</t>
   </si>
   <si>
@@ -1459,24 +1663,21 @@
     <t>30-01-2026 09:31:10</t>
   </si>
   <si>
-    <t>05-02-2026 19:22:43</t>
+    <t>02-02-2026 15:34:51</t>
   </si>
   <si>
     <t>30-01-2026 09:36:03</t>
   </si>
   <si>
+    <t>03-02-2026 07:26:21</t>
+  </si>
+  <si>
+    <t>03-02-2026 10:57:16</t>
+  </si>
+  <si>
     <t>01-02-2026 09:51:00</t>
   </si>
   <si>
-    <t>02-02-2026 15:34:51</t>
-  </si>
-  <si>
-    <t>03-02-2026 07:26:21</t>
-  </si>
-  <si>
-    <t>03-02-2026 10:57:16</t>
-  </si>
-  <si>
     <t>03-02-2026 11:02:16</t>
   </si>
   <si>
@@ -1486,75 +1687,90 @@
     <t>04-02-2026 17:30:29</t>
   </si>
   <si>
+    <t>08-02-2026 10:02:01</t>
+  </si>
+  <si>
+    <t>08-02-2026 13:36:11</t>
+  </si>
+  <si>
+    <t>08-02-2026 13:32:13</t>
+  </si>
+  <si>
+    <t>08-02-2026 11:57:36</t>
+  </si>
+  <si>
+    <t>09-02-2026 14:50:55</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:13:56</t>
+  </si>
+  <si>
+    <t>09-02-2026 08:34:00</t>
+  </si>
+  <si>
+    <t>09-02-2026 15:05:32</t>
+  </si>
+  <si>
     <t>04-02-2026 17:25:23</t>
   </si>
   <si>
-    <t>08-02-2026 10:02:01</t>
-  </si>
-  <si>
-    <t>08-02-2026 13:32:13</t>
+    <t>12-02-2026 18:06:58</t>
+  </si>
+  <si>
+    <t>06-02-2026 16:20:48</t>
+  </si>
+  <si>
+    <t>10-02-2026 07:53:33</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:19:19</t>
   </si>
   <si>
     <t>08-02-2026 10:07:05</t>
   </si>
   <si>
-    <t>08-02-2026 13:36:11</t>
-  </si>
-  <si>
-    <t>06-02-2026 16:20:48</t>
-  </si>
-  <si>
-    <t>09-02-2026 14:50:55</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:06:58</t>
-  </si>
-  <si>
-    <t>08-02-2026 11:57:36</t>
-  </si>
-  <si>
-    <t>09-02-2026 08:34:00</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:19:19</t>
-  </si>
-  <si>
     <t>09-02-2026 16:06:13</t>
   </si>
   <si>
-    <t>09-02-2026 15:05:32</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:13:56</t>
+    <t>12-02-2026 16:25:47</t>
+  </si>
+  <si>
+    <t>13-02-2026 17:10:18</t>
+  </si>
+  <si>
+    <t>17-02-2026 17:59:12</t>
+  </si>
+  <si>
+    <t>13-02-2026 14:59:07</t>
+  </si>
+  <si>
+    <t>13-02-2026 17:18:02</t>
   </si>
   <si>
     <t>10-02-2026 17:26:23</t>
   </si>
   <si>
-    <t>10-02-2026 07:53:33</t>
+    <t>15-02-2026 12:18:06</t>
+  </si>
+  <si>
+    <t>17-02-2026 19:14:20</t>
   </si>
   <si>
     <t>13-02-2026 15:05:03</t>
   </si>
   <si>
-    <t>12-02-2026 16:25:47</t>
+    <t>16-02-2026 18:15:46</t>
+  </si>
+  <si>
+    <t>17-02-2026 10:13:36</t>
+  </si>
+  <si>
+    <t>17-02-2026 10:08:56</t>
   </si>
   <si>
     <t>10-02-2026 17:20:26</t>
   </si>
   <si>
-    <t>15-02-2026 12:18:06</t>
-  </si>
-  <si>
-    <t>13-02-2026 14:59:07</t>
-  </si>
-  <si>
-    <t>13-02-2026 17:18:02</t>
-  </si>
-  <si>
-    <t>13-02-2026 17:10:18</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -1567,6 +1783,12 @@
     <t>26220522327410003797</t>
   </si>
   <si>
+    <t>26220522118170003054</t>
+  </si>
+  <si>
+    <t>26220522378990003894</t>
+  </si>
+  <si>
     <t>26220522021850002707</t>
   </si>
   <si>
@@ -1579,106 +1801,118 @@
     <t>26220522007790002644</t>
   </si>
   <si>
-    <t>26220522118170003054</t>
+    <t>26220522015050002682</t>
   </si>
   <si>
     <t>26220522007760002643</t>
   </si>
   <si>
+    <t>26220522032080002726</t>
+  </si>
+  <si>
+    <t>26220522036640002738</t>
+  </si>
+  <si>
     <t>26220521988250002583</t>
   </si>
   <si>
-    <t>26220522015050002682</t>
-  </si>
-  <si>
-    <t>26220522032080002726</t>
-  </si>
-  <si>
-    <t>26220522036640002738</t>
-  </si>
-  <si>
     <t>26220522036720002739</t>
   </si>
   <si>
     <t>26220522073370002861</t>
   </si>
   <si>
+    <t>26220522109710003012</t>
+  </si>
+  <si>
     <t>26220522082650002911</t>
   </si>
   <si>
+    <t>26220522169080003210</t>
+  </si>
+  <si>
+    <t>26220522172570003226</t>
+  </si>
+  <si>
+    <t>26220522172520003225</t>
+  </si>
+  <si>
+    <t>26220522171210003218</t>
+  </si>
+  <si>
+    <t>26220522193980003288</t>
+  </si>
+  <si>
+    <t>26220522301970003709</t>
+  </si>
+  <si>
+    <t>26220522185040003259</t>
+  </si>
+  <si>
+    <t>26220522194630003292</t>
+  </si>
+  <si>
     <t>26220522082390002907</t>
   </si>
   <si>
-    <t>26220522109710003012</t>
-  </si>
-  <si>
-    <t>26220522169080003210</t>
-  </si>
-  <si>
-    <t>26220522172520003225</t>
+    <t>26220522301550003706</t>
+  </si>
+  <si>
+    <t>26220522142170003123</t>
+  </si>
+  <si>
+    <t>26220522224790003405</t>
+  </si>
+  <si>
+    <t>26220522302230003710</t>
   </si>
   <si>
     <t>26220522169210003211</t>
   </si>
   <si>
-    <t>26220522172570003226</t>
-  </si>
-  <si>
-    <t>26220522142170003123</t>
-  </si>
-  <si>
-    <t>26220522193980003288</t>
-  </si>
-  <si>
-    <t>26220522301550003706</t>
-  </si>
-  <si>
-    <t>26220522171210003218</t>
-  </si>
-  <si>
-    <t>26220522185040003259</t>
-  </si>
-  <si>
-    <t>26220522302230003710</t>
-  </si>
-  <si>
     <t>26220522197030003304</t>
   </si>
   <si>
-    <t>26220522194630003292</t>
-  </si>
-  <si>
-    <t>26220522301970003709</t>
+    <t>26220522297530003689</t>
+  </si>
+  <si>
+    <t>26220522325890003776</t>
+  </si>
+  <si>
+    <t>26220522439570004122</t>
+  </si>
+  <si>
+    <t>26220522321910003759</t>
+  </si>
+  <si>
+    <t>26220522326190003779</t>
   </si>
   <si>
     <t>26220522239800003484</t>
   </si>
   <si>
-    <t>26220522224790003405</t>
+    <t>26220522365480003867</t>
+  </si>
+  <si>
+    <t>26220522443720004140</t>
   </si>
   <si>
     <t>26220522322030003760</t>
   </si>
   <si>
-    <t>26220522297530003689</t>
-  </si>
-  <si>
     <t>26220522365710003869</t>
   </si>
   <si>
+    <t>26220522403640003978</t>
+  </si>
+  <si>
+    <t>26220522423710004040</t>
+  </si>
+  <si>
+    <t>26220522423620004039</t>
+  </si>
+  <si>
     <t>26220522239450003479</t>
-  </si>
-  <si>
-    <t>26220522365480003867</t>
-  </si>
-  <si>
-    <t>26220522321910003759</t>
-  </si>
-  <si>
-    <t>26220522326190003779</t>
-  </si>
-  <si>
-    <t>26220522325890003776</t>
   </si>
   <si>
     <t>26220522365380003866</t>
@@ -2069,7 +2303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -2166,79 +2400,79 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="F2" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="G2" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H2" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="I2" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="J2" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="K2" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="L2" t="s">
-        <v>334</v>
+        <v>376</v>
       </c>
       <c r="M2" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
       <c r="O2" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P2" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q2" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R2" t="s">
-        <v>423</v>
+        <v>481</v>
       </c>
       <c r="S2" t="s">
-        <v>462</v>
+        <v>526</v>
       </c>
       <c r="T2" t="s">
-        <v>476</v>
+        <v>542</v>
       </c>
       <c r="U2" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V2" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="W2" t="s">
         <v>2</v>
       </c>
       <c r="X2" t="s">
-        <v>516</v>
+        <v>588</v>
       </c>
       <c r="AA2" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB2" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC2" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -2246,79 +2480,82 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="F3" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="G3" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H3" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="I3" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="J3" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="K3" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="L3" t="s">
-        <v>335</v>
+        <v>377</v>
       </c>
       <c r="M3" t="s">
-        <v>375</v>
+        <v>423</v>
       </c>
       <c r="O3" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P3" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q3" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R3" t="s">
-        <v>424</v>
+        <v>482</v>
       </c>
       <c r="S3" t="s">
-        <v>463</v>
+        <v>527</v>
       </c>
       <c r="T3" t="s">
-        <v>477</v>
+        <v>543</v>
       </c>
       <c r="U3" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V3" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W3" t="s">
         <v>2</v>
       </c>
       <c r="X3" t="s">
-        <v>517</v>
+        <v>589</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>634</v>
       </c>
       <c r="AA3" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB3" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC3" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -2326,82 +2563,82 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="F4" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="G4" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H4" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="I4" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="J4" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="K4" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="L4" t="s">
-        <v>336</v>
+        <v>378</v>
       </c>
       <c r="M4" t="s">
-        <v>376</v>
+        <v>424</v>
+      </c>
+      <c r="N4" t="s">
+        <v>468</v>
       </c>
       <c r="O4" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P4" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q4" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R4" t="s">
-        <v>425</v>
+        <v>483</v>
       </c>
       <c r="S4" t="s">
-        <v>464</v>
+        <v>528</v>
       </c>
       <c r="T4" t="s">
-        <v>478</v>
+        <v>544</v>
       </c>
       <c r="U4" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V4" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W4" t="s">
         <v>2</v>
       </c>
       <c r="X4" t="s">
-        <v>518</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>556</v>
+        <v>590</v>
       </c>
       <c r="AA4" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB4" t="s">
-        <v>560</v>
+        <v>637</v>
       </c>
       <c r="AC4" t="s">
-        <v>565</v>
+        <v>642</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -2409,85 +2646,79 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="F5" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="G5" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H5" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="I5" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="J5" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="K5" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="L5" t="s">
-        <v>337</v>
+        <v>379</v>
       </c>
       <c r="M5" t="s">
-        <v>377</v>
+        <v>425</v>
       </c>
       <c r="O5" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P5" t="s">
-        <v>418</v>
+        <v>473</v>
       </c>
       <c r="Q5" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R5" t="s">
-        <v>426</v>
+        <v>484</v>
       </c>
       <c r="S5" t="s">
-        <v>465</v>
+        <v>529</v>
       </c>
       <c r="T5" t="s">
-        <v>479</v>
+        <v>545</v>
       </c>
       <c r="U5" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V5" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W5" t="s">
         <v>2</v>
       </c>
       <c r="X5" t="s">
-        <v>519</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>556</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>557</v>
+        <v>591</v>
       </c>
       <c r="AA5" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB5" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC5" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -2495,79 +2726,82 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="F6" t="s">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="G6" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H6" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="I6" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="J6" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="K6" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="L6" t="s">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="M6" t="s">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="O6" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P6" t="s">
-        <v>419</v>
+        <v>473</v>
       </c>
       <c r="Q6" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R6" t="s">
-        <v>427</v>
+        <v>485</v>
       </c>
       <c r="S6" t="s">
-        <v>466</v>
+        <v>530</v>
       </c>
       <c r="T6" t="s">
-        <v>480</v>
+        <v>546</v>
       </c>
       <c r="U6" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V6" t="s">
-        <v>513</v>
+        <v>586</v>
       </c>
       <c r="W6" t="s">
         <v>2</v>
       </c>
       <c r="X6" t="s">
-        <v>520</v>
+        <v>592</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>634</v>
       </c>
       <c r="AA6" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB6" t="s">
-        <v>559</v>
+        <v>638</v>
       </c>
       <c r="AC6" t="s">
-        <v>564</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -2575,82 +2809,85 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="F7" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="G7" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H7" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="I7" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="J7" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="K7" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="L7" t="s">
-        <v>339</v>
+        <v>381</v>
       </c>
       <c r="M7" t="s">
-        <v>379</v>
+        <v>427</v>
       </c>
       <c r="O7" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P7" t="s">
-        <v>417</v>
+        <v>474</v>
       </c>
       <c r="Q7" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R7" t="s">
-        <v>428</v>
+        <v>486</v>
       </c>
       <c r="S7" t="s">
-        <v>467</v>
+        <v>531</v>
       </c>
       <c r="T7" t="s">
-        <v>481</v>
+        <v>547</v>
       </c>
       <c r="U7" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V7" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W7" t="s">
         <v>2</v>
       </c>
       <c r="X7" t="s">
-        <v>521</v>
+        <v>593</v>
       </c>
       <c r="Y7" t="s">
-        <v>556</v>
+        <v>634</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>635</v>
       </c>
       <c r="AA7" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB7" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC7" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -2658,79 +2895,79 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="F8" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="G8" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H8" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="I8" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="J8" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="K8" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="L8" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="M8" t="s">
-        <v>380</v>
+        <v>428</v>
       </c>
       <c r="O8" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P8" t="s">
-        <v>419</v>
+        <v>475</v>
       </c>
       <c r="Q8" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R8" t="s">
-        <v>429</v>
+        <v>487</v>
       </c>
       <c r="S8" t="s">
-        <v>466</v>
+        <v>532</v>
       </c>
       <c r="T8" t="s">
-        <v>482</v>
+        <v>548</v>
       </c>
       <c r="U8" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V8" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="W8" t="s">
         <v>2</v>
       </c>
       <c r="X8" t="s">
-        <v>522</v>
+        <v>594</v>
       </c>
       <c r="AA8" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB8" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC8" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -2738,85 +2975,79 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="F9" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="G9" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H9" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="I9" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="J9" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="K9" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="L9" t="s">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="M9" t="s">
-        <v>381</v>
+        <v>429</v>
       </c>
       <c r="O9" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P9" t="s">
-        <v>418</v>
+        <v>473</v>
       </c>
       <c r="Q9" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R9" t="s">
-        <v>430</v>
+        <v>488</v>
       </c>
       <c r="S9" t="s">
-        <v>465</v>
+        <v>529</v>
       </c>
       <c r="T9" t="s">
-        <v>483</v>
+        <v>549</v>
       </c>
       <c r="U9" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V9" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W9" t="s">
         <v>2</v>
       </c>
       <c r="X9" t="s">
-        <v>523</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>556</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>557</v>
+        <v>595</v>
       </c>
       <c r="AA9" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB9" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC9" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -2824,79 +3055,79 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="F10" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="G10" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H10" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="I10" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="J10" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="K10" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="L10" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="M10" t="s">
-        <v>382</v>
+        <v>430</v>
       </c>
       <c r="O10" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P10" t="s">
-        <v>417</v>
+        <v>475</v>
       </c>
       <c r="Q10" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R10" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="S10" t="s">
-        <v>463</v>
+        <v>532</v>
       </c>
       <c r="T10" t="s">
-        <v>484</v>
+        <v>550</v>
       </c>
       <c r="U10" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V10" t="s">
-        <v>514</v>
+        <v>585</v>
       </c>
       <c r="W10" t="s">
         <v>2</v>
       </c>
       <c r="X10" t="s">
-        <v>524</v>
+        <v>596</v>
       </c>
       <c r="AA10" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB10" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC10" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -2904,82 +3135,82 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="F11" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="G11" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H11" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="I11" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="J11" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="K11" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="L11" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="M11" t="s">
-        <v>383</v>
+        <v>431</v>
       </c>
       <c r="O11" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P11" t="s">
-        <v>418</v>
+        <v>474</v>
       </c>
       <c r="Q11" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R11" t="s">
-        <v>432</v>
+        <v>490</v>
       </c>
       <c r="S11" t="s">
-        <v>468</v>
+        <v>533</v>
       </c>
       <c r="T11" t="s">
-        <v>485</v>
+        <v>551</v>
       </c>
       <c r="U11" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V11" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W11" t="s">
         <v>2</v>
       </c>
       <c r="X11" t="s">
-        <v>525</v>
+        <v>597</v>
       </c>
       <c r="Y11" t="s">
-        <v>556</v>
+        <v>634</v>
       </c>
       <c r="AA11" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB11" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC11" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -2987,79 +3218,79 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="F12" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="G12" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H12" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="I12" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="J12" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="K12" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="L12" t="s">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="M12" t="s">
-        <v>384</v>
+        <v>432</v>
       </c>
       <c r="O12" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P12" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q12" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R12" t="s">
-        <v>433</v>
+        <v>491</v>
       </c>
       <c r="S12" t="s">
-        <v>468</v>
+        <v>533</v>
       </c>
       <c r="T12" t="s">
-        <v>486</v>
+        <v>552</v>
       </c>
       <c r="U12" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V12" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W12" t="s">
         <v>2</v>
       </c>
       <c r="X12" t="s">
-        <v>526</v>
+        <v>598</v>
       </c>
       <c r="AA12" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB12" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC12" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -3067,79 +3298,85 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F13" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="G13" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H13" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="I13" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="J13" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="K13" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="L13" t="s">
-        <v>345</v>
+        <v>387</v>
       </c>
       <c r="M13" t="s">
-        <v>385</v>
+        <v>433</v>
       </c>
       <c r="O13" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P13" t="s">
-        <v>417</v>
+        <v>474</v>
       </c>
       <c r="Q13" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R13" t="s">
-        <v>434</v>
+        <v>492</v>
       </c>
       <c r="S13" t="s">
-        <v>468</v>
+        <v>531</v>
       </c>
       <c r="T13" t="s">
-        <v>487</v>
+        <v>553</v>
       </c>
       <c r="U13" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V13" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W13" t="s">
         <v>2</v>
       </c>
       <c r="X13" t="s">
-        <v>527</v>
+        <v>599</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>634</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>635</v>
       </c>
       <c r="AA13" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB13" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC13" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -3147,79 +3384,79 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="F14" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="G14" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H14" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="I14" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="J14" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="K14" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="L14" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="M14" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="O14" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P14" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q14" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R14" t="s">
-        <v>435</v>
+        <v>493</v>
       </c>
       <c r="S14" t="s">
-        <v>469</v>
+        <v>533</v>
       </c>
       <c r="T14" t="s">
-        <v>488</v>
+        <v>554</v>
       </c>
       <c r="U14" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V14" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W14" t="s">
         <v>2</v>
       </c>
       <c r="X14" t="s">
-        <v>528</v>
+        <v>600</v>
       </c>
       <c r="AA14" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB14" t="s">
-        <v>560</v>
+        <v>637</v>
       </c>
       <c r="AC14" t="s">
-        <v>565</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -3227,79 +3464,79 @@
         <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="E15" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="F15" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="G15" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H15" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="I15" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="J15" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="K15" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="L15" t="s">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="M15" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="O15" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P15" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q15" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R15" t="s">
-        <v>436</v>
+        <v>494</v>
       </c>
       <c r="S15" t="s">
-        <v>469</v>
+        <v>534</v>
       </c>
       <c r="T15" t="s">
-        <v>489</v>
+        <v>555</v>
       </c>
       <c r="U15" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V15" t="s">
-        <v>513</v>
+        <v>586</v>
       </c>
       <c r="W15" t="s">
         <v>2</v>
       </c>
       <c r="X15" t="s">
-        <v>529</v>
+        <v>601</v>
       </c>
       <c r="AA15" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB15" t="s">
-        <v>561</v>
+        <v>638</v>
       </c>
       <c r="AC15" t="s">
-        <v>565</v>
+        <v>643</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -3307,79 +3544,73 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="F16" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="G16" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H16" t="s">
-        <v>231</v>
-      </c>
-      <c r="I16" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="J16" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="K16" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="L16" t="s">
-        <v>348</v>
+        <v>390</v>
       </c>
       <c r="M16" t="s">
-        <v>388</v>
+        <v>436</v>
+      </c>
+      <c r="N16" t="s">
+        <v>469</v>
       </c>
       <c r="O16" t="s">
-        <v>415</v>
+        <v>471</v>
       </c>
       <c r="P16" t="s">
-        <v>417</v>
+        <v>476</v>
       </c>
       <c r="Q16" t="s">
-        <v>421</v>
+        <v>479</v>
       </c>
       <c r="R16" t="s">
-        <v>437</v>
+        <v>495</v>
       </c>
       <c r="S16" t="s">
-        <v>469</v>
-      </c>
-      <c r="T16" t="s">
-        <v>490</v>
+        <v>535</v>
       </c>
       <c r="U16" t="s">
-        <v>513</v>
-      </c>
-      <c r="V16" t="s">
-        <v>513</v>
+        <v>586</v>
       </c>
       <c r="W16" t="s">
         <v>2</v>
       </c>
       <c r="X16" t="s">
-        <v>530</v>
+        <v>602</v>
       </c>
       <c r="AA16" t="s">
-        <v>421</v>
+        <v>636</v>
       </c>
       <c r="AB16" t="s">
-        <v>561</v>
+        <v>637</v>
       </c>
       <c r="AC16" t="s">
-        <v>565</v>
+        <v>642</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -3387,73 +3618,79 @@
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="F17" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="G17" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H17" t="s">
-        <v>232</v>
+        <v>257</v>
+      </c>
+      <c r="I17" t="s">
+        <v>301</v>
       </c>
       <c r="J17" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="K17" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="L17" t="s">
-        <v>349</v>
+        <v>391</v>
       </c>
       <c r="M17" t="s">
-        <v>389</v>
-      </c>
-      <c r="N17" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="O17" t="s">
-        <v>416</v>
+        <v>470</v>
       </c>
       <c r="P17" t="s">
-        <v>420</v>
+        <v>473</v>
       </c>
       <c r="Q17" t="s">
-        <v>422</v>
+        <v>478</v>
       </c>
       <c r="R17" t="s">
-        <v>438</v>
+        <v>496</v>
       </c>
       <c r="S17" t="s">
-        <v>470</v>
+        <v>534</v>
+      </c>
+      <c r="T17" t="s">
+        <v>556</v>
       </c>
       <c r="U17" t="s">
-        <v>514</v>
+        <v>585</v>
+      </c>
+      <c r="V17" t="s">
+        <v>585</v>
       </c>
       <c r="W17" t="s">
         <v>2</v>
       </c>
       <c r="X17" t="s">
-        <v>531</v>
+        <v>603</v>
       </c>
       <c r="AA17" t="s">
-        <v>558</v>
+        <v>478</v>
       </c>
       <c r="AB17" t="s">
-        <v>559</v>
+        <v>639</v>
       </c>
       <c r="AC17" t="s">
-        <v>564</v>
+        <v>643</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -3461,79 +3698,79 @@
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E18" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F18" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="G18" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H18" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="I18" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="J18" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="K18" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="L18" t="s">
-        <v>350</v>
+        <v>392</v>
       </c>
       <c r="M18" t="s">
-        <v>390</v>
+        <v>438</v>
       </c>
       <c r="O18" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P18" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q18" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R18" t="s">
-        <v>439</v>
+        <v>497</v>
       </c>
       <c r="S18" t="s">
-        <v>471</v>
+        <v>536</v>
       </c>
       <c r="T18" t="s">
-        <v>491</v>
+        <v>557</v>
       </c>
       <c r="U18" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V18" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W18" t="s">
         <v>2</v>
       </c>
       <c r="X18" t="s">
-        <v>532</v>
+        <v>604</v>
       </c>
       <c r="AA18" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB18" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC18" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -3541,79 +3778,79 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="E19" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="F19" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="G19" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H19" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="I19" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="J19" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="K19" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="L19" t="s">
-        <v>351</v>
+        <v>393</v>
       </c>
       <c r="M19" t="s">
-        <v>391</v>
+        <v>439</v>
       </c>
       <c r="O19" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P19" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q19" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R19" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="S19" t="s">
-        <v>471</v>
+        <v>536</v>
       </c>
       <c r="T19" t="s">
-        <v>492</v>
+        <v>558</v>
       </c>
       <c r="U19" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V19" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W19" t="s">
         <v>2</v>
       </c>
       <c r="X19" t="s">
-        <v>533</v>
+        <v>605</v>
       </c>
       <c r="AA19" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB19" t="s">
-        <v>560</v>
+        <v>638</v>
       </c>
       <c r="AC19" t="s">
-        <v>565</v>
+        <v>643</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -3621,79 +3858,79 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="E20" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="F20" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="G20" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H20" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="I20" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="J20" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="K20" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="L20" t="s">
-        <v>352</v>
+        <v>394</v>
       </c>
       <c r="M20" t="s">
-        <v>392</v>
+        <v>440</v>
       </c>
       <c r="O20" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P20" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q20" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R20" t="s">
-        <v>441</v>
+        <v>499</v>
       </c>
       <c r="S20" t="s">
-        <v>471</v>
+        <v>536</v>
       </c>
       <c r="T20" t="s">
-        <v>493</v>
+        <v>559</v>
       </c>
       <c r="U20" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V20" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W20" t="s">
         <v>2</v>
       </c>
       <c r="X20" t="s">
-        <v>534</v>
+        <v>606</v>
       </c>
       <c r="AA20" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB20" t="s">
-        <v>559</v>
+        <v>638</v>
       </c>
       <c r="AC20" t="s">
-        <v>564</v>
+        <v>643</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -3701,79 +3938,79 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E21" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="F21" t="s">
-        <v>150</v>
+        <v>207</v>
       </c>
       <c r="G21" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H21" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="I21" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="J21" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="K21" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="L21" t="s">
-        <v>353</v>
+        <v>395</v>
       </c>
       <c r="M21" t="s">
-        <v>393</v>
+        <v>441</v>
       </c>
       <c r="O21" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P21" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q21" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R21" t="s">
-        <v>442</v>
+        <v>500</v>
       </c>
       <c r="S21" t="s">
-        <v>471</v>
+        <v>536</v>
       </c>
       <c r="T21" t="s">
-        <v>494</v>
+        <v>560</v>
       </c>
       <c r="U21" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V21" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W21" t="s">
         <v>2</v>
       </c>
       <c r="X21" t="s">
-        <v>535</v>
+        <v>607</v>
       </c>
       <c r="AA21" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB21" t="s">
-        <v>560</v>
+        <v>640</v>
       </c>
       <c r="AC21" t="s">
-        <v>565</v>
+        <v>643</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -3781,79 +4018,79 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E22" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="F22" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="G22" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H22" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="I22" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="J22" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="K22" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="L22" t="s">
-        <v>354</v>
+        <v>396</v>
       </c>
       <c r="M22" t="s">
-        <v>394</v>
+        <v>442</v>
       </c>
       <c r="O22" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P22" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q22" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R22" t="s">
-        <v>443</v>
+        <v>501</v>
       </c>
       <c r="S22" t="s">
-        <v>472</v>
+        <v>530</v>
       </c>
       <c r="T22" t="s">
-        <v>495</v>
+        <v>561</v>
       </c>
       <c r="U22" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V22" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W22" t="s">
         <v>2</v>
       </c>
       <c r="X22" t="s">
-        <v>536</v>
+        <v>608</v>
       </c>
       <c r="AA22" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB22" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC22" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -3861,79 +4098,82 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E23" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="F23" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="G23" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H23" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="I23" t="s">
-        <v>274</v>
+        <v>307</v>
       </c>
       <c r="J23" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="K23" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="L23" t="s">
-        <v>355</v>
+        <v>397</v>
       </c>
       <c r="M23" t="s">
-        <v>395</v>
+        <v>443</v>
       </c>
       <c r="O23" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P23" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q23" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R23" t="s">
-        <v>444</v>
+        <v>502</v>
       </c>
       <c r="S23" t="s">
-        <v>464</v>
+        <v>537</v>
       </c>
       <c r="T23" t="s">
-        <v>496</v>
+        <v>562</v>
       </c>
       <c r="U23" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V23" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W23" t="s">
         <v>2</v>
       </c>
       <c r="X23" t="s">
-        <v>537</v>
+        <v>609</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>634</v>
       </c>
       <c r="AA23" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB23" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC23" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -3941,82 +4181,79 @@
         <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E24" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="F24" t="s">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="G24" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H24" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="I24" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="J24" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="K24" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="L24" t="s">
-        <v>356</v>
+        <v>398</v>
       </c>
       <c r="M24" t="s">
-        <v>396</v>
+        <v>444</v>
       </c>
       <c r="O24" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P24" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q24" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R24" t="s">
-        <v>445</v>
+        <v>503</v>
       </c>
       <c r="S24" t="s">
-        <v>473</v>
+        <v>530</v>
       </c>
       <c r="T24" t="s">
-        <v>497</v>
+        <v>563</v>
       </c>
       <c r="U24" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V24" t="s">
-        <v>513</v>
+        <v>586</v>
       </c>
       <c r="W24" t="s">
         <v>2</v>
       </c>
       <c r="X24" t="s">
-        <v>538</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>556</v>
+        <v>610</v>
       </c>
       <c r="AA24" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB24" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC24" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -4024,79 +4261,79 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="F25" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="G25" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H25" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="I25" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="J25" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="K25" t="s">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="L25" t="s">
-        <v>357</v>
+        <v>399</v>
       </c>
       <c r="M25" t="s">
-        <v>397</v>
+        <v>445</v>
       </c>
       <c r="O25" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P25" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q25" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R25" t="s">
-        <v>446</v>
+        <v>504</v>
       </c>
       <c r="S25" t="s">
-        <v>471</v>
+        <v>530</v>
       </c>
       <c r="T25" t="s">
-        <v>498</v>
+        <v>564</v>
       </c>
       <c r="U25" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V25" t="s">
-        <v>514</v>
+        <v>585</v>
       </c>
       <c r="W25" t="s">
         <v>2</v>
       </c>
       <c r="X25" t="s">
-        <v>539</v>
+        <v>611</v>
       </c>
       <c r="AA25" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB25" t="s">
-        <v>562</v>
+        <v>638</v>
       </c>
       <c r="AC25" t="s">
-        <v>565</v>
+        <v>643</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -4104,79 +4341,79 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F26" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G26" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H26" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="I26" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="J26" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="K26" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="L26" t="s">
-        <v>358</v>
+        <v>400</v>
       </c>
       <c r="M26" t="s">
-        <v>398</v>
+        <v>446</v>
       </c>
       <c r="O26" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P26" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q26" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R26" t="s">
-        <v>447</v>
+        <v>505</v>
       </c>
       <c r="S26" t="s">
-        <v>464</v>
+        <v>534</v>
       </c>
       <c r="T26" t="s">
-        <v>499</v>
+        <v>565</v>
       </c>
       <c r="U26" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V26" t="s">
-        <v>514</v>
+        <v>585</v>
       </c>
       <c r="W26" t="s">
         <v>2</v>
       </c>
       <c r="X26" t="s">
-        <v>540</v>
+        <v>612</v>
       </c>
       <c r="AA26" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB26" t="s">
-        <v>559</v>
+        <v>639</v>
       </c>
       <c r="AC26" t="s">
-        <v>564</v>
+        <v>643</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -4184,82 +4421,82 @@
         <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E27" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="F27" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="G27" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H27" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="I27" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="J27" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="K27" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="L27" t="s">
-        <v>359</v>
+        <v>401</v>
       </c>
       <c r="M27" t="s">
-        <v>399</v>
+        <v>447</v>
       </c>
       <c r="O27" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P27" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q27" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R27" t="s">
-        <v>448</v>
+        <v>506</v>
       </c>
       <c r="S27" t="s">
-        <v>473</v>
+        <v>537</v>
       </c>
       <c r="T27" t="s">
-        <v>500</v>
+        <v>566</v>
       </c>
       <c r="U27" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V27" t="s">
-        <v>514</v>
+        <v>585</v>
       </c>
       <c r="W27" t="s">
         <v>2</v>
       </c>
       <c r="X27" t="s">
-        <v>541</v>
+        <v>613</v>
       </c>
       <c r="Y27" t="s">
-        <v>556</v>
+        <v>634</v>
       </c>
       <c r="AA27" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB27" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC27" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -4267,79 +4504,79 @@
         <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E28" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F28" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="G28" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H28" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="I28" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="J28" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="K28" t="s">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="L28" t="s">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="M28" t="s">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="O28" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P28" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q28" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R28" t="s">
-        <v>449</v>
+        <v>507</v>
       </c>
       <c r="S28" t="s">
-        <v>464</v>
+        <v>538</v>
       </c>
       <c r="T28" t="s">
-        <v>501</v>
+        <v>567</v>
       </c>
       <c r="U28" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V28" t="s">
-        <v>513</v>
+        <v>586</v>
       </c>
       <c r="W28" t="s">
         <v>2</v>
       </c>
       <c r="X28" t="s">
-        <v>542</v>
+        <v>614</v>
       </c>
       <c r="AA28" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB28" t="s">
-        <v>561</v>
+        <v>637</v>
       </c>
       <c r="AC28" t="s">
-        <v>565</v>
+        <v>642</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -4347,79 +4584,79 @@
         <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="E29" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="F29" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="G29" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H29" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="I29" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="J29" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="K29" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="L29" t="s">
-        <v>361</v>
+        <v>403</v>
       </c>
       <c r="M29" t="s">
-        <v>401</v>
+        <v>449</v>
       </c>
       <c r="O29" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P29" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q29" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R29" t="s">
-        <v>450</v>
+        <v>508</v>
       </c>
       <c r="S29" t="s">
-        <v>464</v>
+        <v>539</v>
       </c>
       <c r="T29" t="s">
-        <v>502</v>
+        <v>568</v>
       </c>
       <c r="U29" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V29" t="s">
-        <v>513</v>
+        <v>586</v>
       </c>
       <c r="W29" t="s">
         <v>2</v>
       </c>
       <c r="X29" t="s">
-        <v>543</v>
+        <v>615</v>
       </c>
       <c r="AA29" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB29" t="s">
-        <v>560</v>
+        <v>641</v>
       </c>
       <c r="AC29" t="s">
-        <v>565</v>
+        <v>643</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -4427,82 +4664,82 @@
         <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E30" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="F30" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="G30" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H30" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="I30" t="s">
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="J30" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="K30" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="L30" t="s">
-        <v>362</v>
+        <v>404</v>
       </c>
       <c r="M30" t="s">
-        <v>402</v>
+        <v>450</v>
       </c>
       <c r="O30" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P30" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q30" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R30" t="s">
-        <v>451</v>
+        <v>509</v>
       </c>
       <c r="S30" t="s">
-        <v>473</v>
+        <v>537</v>
       </c>
       <c r="T30" t="s">
-        <v>503</v>
+        <v>569</v>
       </c>
       <c r="U30" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V30" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W30" t="s">
         <v>2</v>
       </c>
       <c r="X30" t="s">
-        <v>544</v>
+        <v>616</v>
       </c>
       <c r="Y30" t="s">
-        <v>556</v>
+        <v>634</v>
       </c>
       <c r="AA30" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB30" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC30" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -4510,79 +4747,79 @@
         <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E31" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="F31" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="G31" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H31" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="I31" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="J31" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="K31" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
       <c r="L31" t="s">
-        <v>363</v>
+        <v>405</v>
       </c>
       <c r="M31" t="s">
-        <v>403</v>
+        <v>451</v>
       </c>
       <c r="O31" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P31" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q31" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R31" t="s">
-        <v>452</v>
+        <v>510</v>
       </c>
       <c r="S31" t="s">
-        <v>474</v>
+        <v>536</v>
       </c>
       <c r="T31" t="s">
-        <v>504</v>
+        <v>570</v>
       </c>
       <c r="U31" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V31" t="s">
-        <v>513</v>
+        <v>586</v>
       </c>
       <c r="W31" t="s">
         <v>2</v>
       </c>
       <c r="X31" t="s">
-        <v>545</v>
+        <v>617</v>
       </c>
       <c r="AA31" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB31" t="s">
-        <v>560</v>
+        <v>637</v>
       </c>
       <c r="AC31" t="s">
-        <v>565</v>
+        <v>642</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -4590,79 +4827,79 @@
         <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E32" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="F32" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="G32" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H32" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="I32" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="J32" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="K32" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="L32" t="s">
-        <v>364</v>
+        <v>406</v>
       </c>
       <c r="M32" t="s">
-        <v>404</v>
+        <v>452</v>
       </c>
       <c r="O32" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P32" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q32" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R32" t="s">
-        <v>453</v>
+        <v>511</v>
       </c>
       <c r="S32" t="s">
-        <v>474</v>
+        <v>530</v>
       </c>
       <c r="T32" t="s">
-        <v>505</v>
+        <v>571</v>
       </c>
       <c r="U32" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V32" t="s">
-        <v>514</v>
+        <v>585</v>
       </c>
       <c r="W32" t="s">
         <v>2</v>
       </c>
       <c r="X32" t="s">
-        <v>546</v>
+        <v>618</v>
       </c>
       <c r="AA32" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB32" t="s">
-        <v>563</v>
+        <v>639</v>
       </c>
       <c r="AC32" t="s">
-        <v>565</v>
+        <v>643</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -4670,79 +4907,79 @@
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="E33" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="F33" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="G33" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H33" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="I33" t="s">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="J33" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="K33" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="L33" t="s">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="M33" t="s">
-        <v>405</v>
+        <v>453</v>
       </c>
       <c r="O33" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P33" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q33" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R33" t="s">
-        <v>454</v>
+        <v>512</v>
       </c>
       <c r="S33" t="s">
-        <v>462</v>
+        <v>537</v>
       </c>
       <c r="T33" t="s">
-        <v>506</v>
+        <v>572</v>
       </c>
       <c r="U33" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V33" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W33" t="s">
         <v>2</v>
       </c>
       <c r="X33" t="s">
-        <v>547</v>
+        <v>619</v>
       </c>
       <c r="AA33" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB33" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC33" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -4750,79 +4987,79 @@
         <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="E34" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="F34" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="G34" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H34" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="I34" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="J34" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="K34" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="L34" t="s">
-        <v>366</v>
+        <v>408</v>
       </c>
       <c r="M34" t="s">
-        <v>406</v>
+        <v>454</v>
       </c>
       <c r="O34" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P34" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q34" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R34" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="S34" t="s">
-        <v>473</v>
+        <v>526</v>
       </c>
       <c r="T34" t="s">
-        <v>507</v>
+        <v>573</v>
       </c>
       <c r="U34" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V34" t="s">
-        <v>514</v>
+        <v>585</v>
       </c>
       <c r="W34" t="s">
         <v>2</v>
       </c>
       <c r="X34" t="s">
-        <v>548</v>
+        <v>620</v>
       </c>
       <c r="AA34" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB34" t="s">
-        <v>559</v>
+        <v>639</v>
       </c>
       <c r="AC34" t="s">
-        <v>564</v>
+        <v>643</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -4830,79 +5067,82 @@
         <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E35" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="F35" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="G35" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H35" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="I35" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="J35" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="K35" t="s">
-        <v>327</v>
+        <v>363</v>
       </c>
       <c r="L35" t="s">
-        <v>367</v>
+        <v>409</v>
       </c>
       <c r="M35" t="s">
-        <v>407</v>
+        <v>455</v>
+      </c>
+      <c r="N35" t="s">
+        <v>469</v>
       </c>
       <c r="O35" t="s">
-        <v>415</v>
+        <v>472</v>
       </c>
       <c r="P35" t="s">
-        <v>417</v>
+        <v>477</v>
       </c>
       <c r="Q35" t="s">
-        <v>421</v>
+        <v>480</v>
       </c>
       <c r="R35" t="s">
-        <v>407</v>
+        <v>514</v>
       </c>
       <c r="S35" t="s">
-        <v>475</v>
+        <v>540</v>
       </c>
       <c r="T35" t="s">
-        <v>407</v>
+        <v>574</v>
       </c>
       <c r="U35" t="s">
-        <v>515</v>
+        <v>585</v>
       </c>
       <c r="V35" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W35" t="s">
         <v>2</v>
       </c>
       <c r="X35" t="s">
-        <v>549</v>
+        <v>621</v>
       </c>
       <c r="AA35" t="s">
-        <v>421</v>
+        <v>480</v>
       </c>
       <c r="AB35" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC35" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -4910,79 +5150,79 @@
         <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D36" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="E36" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="F36" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="G36" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H36" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="I36" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="J36" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="K36" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="L36" t="s">
-        <v>368</v>
+        <v>410</v>
       </c>
       <c r="M36" t="s">
-        <v>408</v>
+        <v>456</v>
       </c>
       <c r="O36" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P36" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q36" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R36" t="s">
-        <v>456</v>
+        <v>515</v>
       </c>
       <c r="S36" t="s">
-        <v>474</v>
+        <v>526</v>
       </c>
       <c r="T36" t="s">
-        <v>508</v>
+        <v>575</v>
       </c>
       <c r="U36" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V36" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W36" t="s">
         <v>2</v>
       </c>
       <c r="X36" t="s">
-        <v>550</v>
+        <v>622</v>
       </c>
       <c r="AA36" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB36" t="s">
-        <v>560</v>
+        <v>637</v>
       </c>
       <c r="AC36" t="s">
-        <v>565</v>
+        <v>642</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -4990,79 +5230,79 @@
         <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="E37" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="F37" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="G37" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H37" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="I37" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="J37" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="K37" t="s">
-        <v>329</v>
+        <v>365</v>
       </c>
       <c r="L37" t="s">
-        <v>369</v>
+        <v>411</v>
       </c>
       <c r="M37" t="s">
-        <v>409</v>
+        <v>457</v>
       </c>
       <c r="O37" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P37" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q37" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R37" t="s">
-        <v>457</v>
+        <v>516</v>
       </c>
       <c r="S37" t="s">
-        <v>475</v>
+        <v>526</v>
       </c>
       <c r="T37" t="s">
-        <v>509</v>
+        <v>576</v>
       </c>
       <c r="U37" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V37" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="W37" t="s">
         <v>2</v>
       </c>
       <c r="X37" t="s">
-        <v>551</v>
+        <v>623</v>
       </c>
       <c r="AA37" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB37" t="s">
-        <v>559</v>
+        <v>639</v>
       </c>
       <c r="AC37" t="s">
-        <v>564</v>
+        <v>643</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -5070,79 +5310,79 @@
         <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E38" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="F38" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="G38" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H38" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="I38" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="J38" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="K38" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="L38" t="s">
-        <v>370</v>
+        <v>412</v>
       </c>
       <c r="M38" t="s">
-        <v>410</v>
+        <v>458</v>
       </c>
       <c r="O38" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P38" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q38" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R38" t="s">
-        <v>458</v>
+        <v>517</v>
       </c>
       <c r="S38" t="s">
-        <v>462</v>
+        <v>539</v>
       </c>
       <c r="T38" t="s">
-        <v>510</v>
+        <v>577</v>
       </c>
       <c r="U38" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V38" t="s">
-        <v>514</v>
+        <v>585</v>
       </c>
       <c r="W38" t="s">
         <v>2</v>
       </c>
       <c r="X38" t="s">
-        <v>552</v>
+        <v>624</v>
       </c>
       <c r="AA38" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB38" t="s">
-        <v>559</v>
+        <v>638</v>
       </c>
       <c r="AC38" t="s">
-        <v>564</v>
+        <v>643</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -5150,79 +5390,79 @@
         <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="E39" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="F39" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="G39" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H39" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="I39" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="J39" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="K39" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="L39" t="s">
-        <v>371</v>
+        <v>413</v>
       </c>
       <c r="M39" t="s">
-        <v>411</v>
+        <v>459</v>
       </c>
       <c r="O39" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P39" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q39" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R39" t="s">
-        <v>459</v>
+        <v>518</v>
       </c>
       <c r="S39" t="s">
-        <v>462</v>
+        <v>541</v>
       </c>
       <c r="T39" t="s">
-        <v>511</v>
+        <v>578</v>
       </c>
       <c r="U39" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V39" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="W39" t="s">
         <v>2</v>
       </c>
       <c r="X39" t="s">
-        <v>553</v>
+        <v>625</v>
       </c>
       <c r="AA39" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB39" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC39" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -5230,79 +5470,82 @@
         <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C40" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D40" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="E40" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="F40" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="G40" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H40" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="I40" t="s">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="J40" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="K40" t="s">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="L40" t="s">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="M40" t="s">
-        <v>412</v>
+        <v>460</v>
+      </c>
+      <c r="N40" t="s">
+        <v>468</v>
       </c>
       <c r="O40" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P40" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q40" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R40" t="s">
-        <v>460</v>
+        <v>519</v>
       </c>
       <c r="S40" t="s">
-        <v>462</v>
+        <v>540</v>
       </c>
       <c r="T40" t="s">
-        <v>512</v>
+        <v>579</v>
       </c>
       <c r="U40" t="s">
-        <v>513</v>
+        <v>585</v>
       </c>
       <c r="V40" t="s">
-        <v>513</v>
+        <v>586</v>
       </c>
       <c r="W40" t="s">
         <v>2</v>
       </c>
       <c r="X40" t="s">
-        <v>554</v>
+        <v>626</v>
       </c>
       <c r="AA40" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="AB40" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="AC40" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -5310,79 +5553,568 @@
         <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C41" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D41" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="E41" t="s">
-        <v>154</v>
+        <v>204</v>
       </c>
       <c r="F41" t="s">
-        <v>152</v>
+        <v>237</v>
       </c>
       <c r="G41" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="H41" t="s">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="I41" t="s">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="J41" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="K41" t="s">
-        <v>333</v>
+        <v>369</v>
       </c>
       <c r="L41" t="s">
-        <v>373</v>
+        <v>415</v>
       </c>
       <c r="M41" t="s">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="O41" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="P41" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="Q41" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="R41" t="s">
-        <v>461</v>
+        <v>520</v>
       </c>
       <c r="S41" t="s">
-        <v>475</v>
+        <v>526</v>
       </c>
       <c r="T41" t="s">
-        <v>461</v>
+        <v>580</v>
       </c>
       <c r="U41" t="s">
-        <v>515</v>
+        <v>585</v>
       </c>
       <c r="V41" t="s">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="W41" t="s">
         <v>2</v>
       </c>
       <c r="X41" t="s">
-        <v>555</v>
+        <v>627</v>
       </c>
       <c r="AA41" t="s">
+        <v>478</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>637</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29">
+      <c r="A42" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" t="s">
+        <v>121</v>
+      </c>
+      <c r="D42" t="s">
+        <v>162</v>
+      </c>
+      <c r="E42" t="s">
+        <v>205</v>
+      </c>
+      <c r="F42" t="s">
+        <v>238</v>
+      </c>
+      <c r="G42" t="s">
+        <v>241</v>
+      </c>
+      <c r="H42" t="s">
+        <v>282</v>
+      </c>
+      <c r="I42" t="s">
+        <v>324</v>
+      </c>
+      <c r="J42" t="s">
+        <v>329</v>
+      </c>
+      <c r="K42" t="s">
+        <v>370</v>
+      </c>
+      <c r="L42" t="s">
+        <v>416</v>
+      </c>
+      <c r="M42" t="s">
+        <v>462</v>
+      </c>
+      <c r="O42" t="s">
+        <v>470</v>
+      </c>
+      <c r="P42" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>478</v>
+      </c>
+      <c r="R42" t="s">
+        <v>462</v>
+      </c>
+      <c r="S42" t="s">
+        <v>541</v>
+      </c>
+      <c r="T42" t="s">
+        <v>462</v>
+      </c>
+      <c r="U42" t="s">
+        <v>587</v>
+      </c>
+      <c r="V42" t="s">
+        <v>586</v>
+      </c>
+      <c r="W42" t="s">
+        <v>2</v>
+      </c>
+      <c r="X42" t="s">
+        <v>628</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>478</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>637</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29">
+      <c r="A43" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" t="s">
+        <v>121</v>
+      </c>
+      <c r="D43" t="s">
+        <v>163</v>
+      </c>
+      <c r="E43" t="s">
+        <v>206</v>
+      </c>
+      <c r="F43" t="s">
+        <v>239</v>
+      </c>
+      <c r="G43" t="s">
+        <v>241</v>
+      </c>
+      <c r="H43" t="s">
+        <v>283</v>
+      </c>
+      <c r="I43" t="s">
+        <v>325</v>
+      </c>
+      <c r="J43" t="s">
+        <v>328</v>
+      </c>
+      <c r="K43" t="s">
+        <v>371</v>
+      </c>
+      <c r="L43" t="s">
+        <v>417</v>
+      </c>
+      <c r="M43" t="s">
+        <v>463</v>
+      </c>
+      <c r="N43" t="s">
+        <v>468</v>
+      </c>
+      <c r="O43" t="s">
+        <v>470</v>
+      </c>
+      <c r="P43" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>478</v>
+      </c>
+      <c r="R43" t="s">
+        <v>521</v>
+      </c>
+      <c r="S43" t="s">
+        <v>528</v>
+      </c>
+      <c r="T43" t="s">
+        <v>581</v>
+      </c>
+      <c r="U43" t="s">
+        <v>585</v>
+      </c>
+      <c r="V43" t="s">
+        <v>585</v>
+      </c>
+      <c r="W43" t="s">
+        <v>2</v>
+      </c>
+      <c r="X43" t="s">
+        <v>629</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>478</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>639</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29">
+      <c r="A44" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" t="s">
+        <v>164</v>
+      </c>
+      <c r="E44" t="s">
+        <v>207</v>
+      </c>
+      <c r="F44" t="s">
+        <v>238</v>
+      </c>
+      <c r="G44" t="s">
+        <v>241</v>
+      </c>
+      <c r="H44" t="s">
+        <v>284</v>
+      </c>
+      <c r="I44" t="s">
+        <v>326</v>
+      </c>
+      <c r="J44" t="s">
+        <v>329</v>
+      </c>
+      <c r="K44" t="s">
+        <v>372</v>
+      </c>
+      <c r="L44" t="s">
+        <v>418</v>
+      </c>
+      <c r="M44" t="s">
+        <v>464</v>
+      </c>
+      <c r="N44" t="s">
+        <v>468</v>
+      </c>
+      <c r="O44" t="s">
+        <v>470</v>
+      </c>
+      <c r="P44" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>478</v>
+      </c>
+      <c r="R44" t="s">
+        <v>522</v>
+      </c>
+      <c r="S44" t="s">
+        <v>540</v>
+      </c>
+      <c r="T44" t="s">
+        <v>582</v>
+      </c>
+      <c r="U44" t="s">
+        <v>585</v>
+      </c>
+      <c r="V44" t="s">
+        <v>585</v>
+      </c>
+      <c r="W44" t="s">
+        <v>2</v>
+      </c>
+      <c r="X44" t="s">
+        <v>630</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>478</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>637</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29">
+      <c r="A45" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45" t="s">
+        <v>118</v>
+      </c>
+      <c r="C45" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" t="s">
+        <v>165</v>
+      </c>
+      <c r="E45" t="s">
+        <v>208</v>
+      </c>
+      <c r="F45" t="s">
+        <v>168</v>
+      </c>
+      <c r="G45" t="s">
+        <v>241</v>
+      </c>
+      <c r="H45" t="s">
+        <v>285</v>
+      </c>
+      <c r="I45" t="s">
+        <v>164</v>
+      </c>
+      <c r="J45" t="s">
+        <v>328</v>
+      </c>
+      <c r="K45" t="s">
+        <v>373</v>
+      </c>
+      <c r="L45" t="s">
+        <v>419</v>
+      </c>
+      <c r="M45" t="s">
+        <v>465</v>
+      </c>
+      <c r="N45" t="s">
+        <v>468</v>
+      </c>
+      <c r="O45" t="s">
+        <v>470</v>
+      </c>
+      <c r="P45" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>478</v>
+      </c>
+      <c r="R45" t="s">
+        <v>523</v>
+      </c>
+      <c r="S45" t="s">
+        <v>540</v>
+      </c>
+      <c r="T45" t="s">
+        <v>583</v>
+      </c>
+      <c r="U45" t="s">
+        <v>585</v>
+      </c>
+      <c r="V45" t="s">
+        <v>585</v>
+      </c>
+      <c r="W45" t="s">
+        <v>2</v>
+      </c>
+      <c r="X45" t="s">
+        <v>631</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>478</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>637</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29">
+      <c r="A46" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46" t="s">
+        <v>119</v>
+      </c>
+      <c r="C46" t="s">
+        <v>121</v>
+      </c>
+      <c r="D46" t="s">
+        <v>166</v>
+      </c>
+      <c r="E46" t="s">
+        <v>209</v>
+      </c>
+      <c r="F46" t="s">
+        <v>240</v>
+      </c>
+      <c r="G46" t="s">
+        <v>241</v>
+      </c>
+      <c r="H46" t="s">
+        <v>286</v>
+      </c>
+      <c r="I46" t="s">
+        <v>327</v>
+      </c>
+      <c r="J46" t="s">
+        <v>328</v>
+      </c>
+      <c r="K46" t="s">
+        <v>374</v>
+      </c>
+      <c r="L46" t="s">
+        <v>420</v>
+      </c>
+      <c r="M46" t="s">
+        <v>466</v>
+      </c>
+      <c r="O46" t="s">
+        <v>470</v>
+      </c>
+      <c r="P46" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>478</v>
+      </c>
+      <c r="R46" t="s">
+        <v>524</v>
+      </c>
+      <c r="S46" t="s">
+        <v>539</v>
+      </c>
+      <c r="T46" t="s">
+        <v>584</v>
+      </c>
+      <c r="U46" t="s">
+        <v>585</v>
+      </c>
+      <c r="V46" t="s">
+        <v>586</v>
+      </c>
+      <c r="W46" t="s">
+        <v>2</v>
+      </c>
+      <c r="X46" t="s">
+        <v>632</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>478</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>638</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29">
+      <c r="A47" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47" t="s">
+        <v>120</v>
+      </c>
+      <c r="C47" t="s">
+        <v>121</v>
+      </c>
+      <c r="D47" t="s">
+        <v>167</v>
+      </c>
+      <c r="E47" t="s">
+        <v>174</v>
+      </c>
+      <c r="F47" t="s">
+        <v>172</v>
+      </c>
+      <c r="G47" t="s">
+        <v>241</v>
+      </c>
+      <c r="H47" t="s">
+        <v>287</v>
+      </c>
+      <c r="I47" t="s">
+        <v>324</v>
+      </c>
+      <c r="J47" t="s">
+        <v>328</v>
+      </c>
+      <c r="K47" t="s">
+        <v>375</v>
+      </c>
+      <c r="L47" t="s">
         <v>421</v>
       </c>
-      <c r="AB41" t="s">
-        <v>559</v>
-      </c>
-      <c r="AC41" t="s">
-        <v>564</v>
+      <c r="M47" t="s">
+        <v>467</v>
+      </c>
+      <c r="O47" t="s">
+        <v>470</v>
+      </c>
+      <c r="P47" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>478</v>
+      </c>
+      <c r="R47" t="s">
+        <v>525</v>
+      </c>
+      <c r="S47" t="s">
+        <v>541</v>
+      </c>
+      <c r="T47" t="s">
+        <v>525</v>
+      </c>
+      <c r="U47" t="s">
+        <v>587</v>
+      </c>
+      <c r="V47" t="s">
+        <v>586</v>
+      </c>
+      <c r="W47" t="s">
+        <v>2</v>
+      </c>
+      <c r="X47" t="s">
+        <v>633</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>478</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>637</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>642</v>
       </c>
     </row>
   </sheetData>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>339258</t>
+          <t>233666</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>31171</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PAOLA</t>
+          <t xml:space="preserve">NATALY </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ARTEAGA</t>
+          <t>VILLALPANDO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">CADENA </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5512421794</t>
+          <t>5564992033</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AV. JOSE MARIA MARTINEZ MZA 24 LY 19</t>
+          <t>AV LOS PINOS MZ 37 LT 17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,20 +628,24 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>07-04-1992</t>
+          <t>30-11-1985</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>LOOPZY_9797@HOTMAIL.COM</t>
+          <t>NATYVILLALPANDO6@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>30-01-2026 09:21:25</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>09-05-2024 07:51:19</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -649,7 +653,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -659,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-02-2026 11:50:19</t>
+          <t>16-02-2026 07:18:36</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>30-01-2026 09:36:03</t>
+          <t>16-02-2026 07:17:49</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -679,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -689,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26220522007760002643</t>
+          <t>26220522378990003894</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -713,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>339174</t>
+          <t>236785</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>MARIA DEL ROSARIO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CRISOSTOMO</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CARDOSO</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,32 +752,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5550539848</t>
+          <t>5573035144</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CDA 21 DE MARZO 12</t>
+          <t>CDA BOSQUE DE EUCALIPTOS MZA 29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>03-06-1998</t>
+          <t>24-06-1985</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>DEIVID.AYD.CRI98@GMAIL.COM</t>
+          <t>PRINCESS_CHAIN@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>29-01-2026 19:21:28</t>
+          <t>28-05-2024 18:11:53</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -794,17 +798,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>05-02-2026 19:25:52</t>
+          <t>02-02-2026 19:13:53</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>05-02-2026 19:22:43</t>
+          <t>02-02-2026 19:13:00</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -824,14 +828,10 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26220522118170003054</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522021850002707</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
@@ -852,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>233666</t>
+          <t>339258</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NATALY </t>
+          <t>PAOLA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VILLALPANDO</t>
+          <t>ARTEAGA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CADENA </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5564992033</t>
+          <t>5512421794</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AV LOS PINOS MZ 37 LT 17</t>
+          <t>AV. JOSE MARIA MARTINEZ MZA 24 LY 19</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -902,24 +902,20 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>30-11-1985</t>
+          <t>07-04-1992</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>NATYVILLALPANDO6@GMAIL.COM</t>
+          <t>LOOPZY_9797@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>09-05-2024 07:51:19</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>30-01-2026 09:21:25</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -927,7 +923,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -937,17 +933,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>16-02-2026 07:18:36</t>
+          <t>02-02-2026 11:50:19</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>16-02-2026 07:17:49</t>
+          <t>30-01-2026 09:36:03</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -957,7 +953,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -967,7 +963,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26220522378990003894</t>
+          <t>26220522007760002643</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -991,12 +987,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>236785</t>
+          <t>338953</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +1002,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MARIA DEL ROSARIO</t>
+          <t xml:space="preserve">FABIOLA </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>PLATA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,12 +1022,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5573035144</t>
+          <t>5582314058</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CDA BOSQUE DE EUCALIPTOS MZA 29</t>
+          <t>CDA DE JAZMINES MZ 20 LT 10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1041,17 +1037,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>24-06-1985</t>
+          <t>11-04-1991</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PRINCESS_CHAIN@HOTMAIL.COM</t>
+          <t>FALIZEE004@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>28-05-2024 18:11:53</t>
+          <t>29-01-2026 08:24:12</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1062,7 +1058,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1072,17 +1068,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-02-2026 19:13:53</t>
+          <t>01-02-2026 09:51:51</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-02-2026 19:13:00</t>
+          <t>01-02-2026 09:51:00</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1102,11 +1098,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26220522021850002707</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26220521988250002583</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>499</t>
@@ -1126,12 +1130,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>340216</t>
+          <t>332845</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1141,17 +1145,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AXEL ZADKYEL</t>
+          <t>MIRSHA ASERET</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1161,32 +1165,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5591647693</t>
+          <t>5574210862</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SAN BUENAVENTURA</t>
+          <t>C IGNACIO ZARAGOZA MZ 25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>24-05-2006</t>
+          <t>11-02-2000</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>AXELVALDEZ099@GMAL.COM</t>
+          <t>MIRSHA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-02-2026 15:29:08</t>
+          <t>07-01-2026 14:07:05</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1207,17 +1211,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-02-2026 15:45:59</t>
+          <t>13-02-2026 18:00:19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-02-2026 15:34:51</t>
+          <t>13-02-2026 18:00:00</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1227,7 +1231,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1237,7 +1241,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26220522015050002682</t>
+          <t>26220522327410003797</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1261,12 +1265,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>340315</t>
+          <t>340516</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>18334</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1280,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MAYRA JAZMIN</t>
+          <t>CARLOS ENRIQUE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KURY</t>
+          <t xml:space="preserve">RUEDA </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AVILES</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,32 +1300,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5561248221</t>
+          <t>5619885190</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IXTAP</t>
+          <t>IXTA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>13-08-1980</t>
+          <t>05-08-1991</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MAYRACGT@GMAIL.COM</t>
+          <t>ENRIQUE-RUEDA@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-02-2026 17:44:11</t>
+          <t>03-02-2026 10:59:53</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1332,7 +1336,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1342,7 +1346,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-02-2026 07:27:24</t>
+          <t>03-02-2026 11:02:47</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1352,7 +1356,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03-02-2026 07:26:21</t>
+          <t>03-02-2026 11:02:16</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1372,14 +1376,10 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26220522032080002726</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522036720002739</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1400,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>340512</t>
+          <t>341617</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ROSA LIDIA</t>
+          <t xml:space="preserve">EDILBERTO </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ANZALDO</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,32 +1435,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5521196367</t>
+          <t>5540185856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IXTA</t>
+          <t>ACACIA 80</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>14-04-1993</t>
+          <t>13-08-1979</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ROSYN_N@HOTMAIL.COM</t>
+          <t>GONZALEZCRUZEDILBERTO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-02-2026 10:51:49</t>
+          <t>06-02-2026 16:14:24</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1481,17 +1481,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-02-2026 10:57:53</t>
+          <t>06-02-2026 17:06:08</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-02-2026 10:57:16</t>
+          <t>06-02-2026 16:20:48</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26220522036640002738</t>
+          <t>26220522142170003123</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1535,12 +1535,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>338953</t>
+          <t>341101</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FABIOLA </t>
+          <t>CHRISTIAN OWEN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PLATA</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1570,32 +1570,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5582314058</t>
+          <t>5643127118</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CDA DE JAZMINES MZ 20 LT 10</t>
+          <t>C CATEDRAL METROPOLITANA 204</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>11-04-1991</t>
+          <t>18-06-2011</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FALIZEE004@GMAIL.COM</t>
+          <t>CHRISTIAN09MENDEZ1234@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>29-01-2026 08:24:12</t>
+          <t>04-02-2026 17:18:13</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1616,17 +1616,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>01-02-2026 09:51:51</t>
+          <t>04-02-2026 17:31:39</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>01-02-2026 09:51:00</t>
+          <t>04-02-2026 17:30:29</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1646,19 +1646,11 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26220521988250002583</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522082650002911</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>499</t>
@@ -1666,24 +1658,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340960</t>
+          <t>339592</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1693,17 +1685,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LUIS ANGEL</t>
+          <t>MARIA GUADALUPE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>LANDIN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1713,32 +1705,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5669156876</t>
+          <t>5588006100</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C TONATICO 197</t>
+          <t>EL CAPULIN</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>19-02-1993</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BUICKGOLIFE856@GMAIL.COM</t>
+          <t>LANDINGUADALUPE95@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>04-02-2026 12:16:09</t>
+          <t>31-01-2026 09:45:22</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1759,17 +1751,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-02-2026 12:24:18</t>
+          <t>09-02-2026 14:59:33</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>04-02-2026 12:23:46</t>
+          <t>09-02-2026 14:59:02</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1789,10 +1781,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26220522073370002861</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
+          <t>26220522194280003290</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1813,12 +1809,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>332845</t>
+          <t>341099</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1828,17 +1824,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MIRSHA ASERET</t>
+          <t>AXEL KALID</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1848,32 +1844,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5574210862</t>
+          <t>5635122950</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C IGNACIO ZARAGOZA MZ 25</t>
+          <t>C CATEDRAL METROPOLITANA 204</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>11-02-2000</t>
+          <t>23-07-2004</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MIRSHA@GMAIL.COM</t>
+          <t>GUERREROAXEL190@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>07-01-2026 14:07:05</t>
+          <t>04-02-2026 17:15:27</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1894,17 +1890,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>13-02-2026 18:00:19</t>
+          <t>04-02-2026 17:26:19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>13-02-2026 18:00:00</t>
+          <t>04-02-2026 17:25:23</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1924,7 +1920,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26220522327410003797</t>
+          <t>26220522082390002907</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1936,24 +1932,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>339592</t>
+          <t>339174</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1963,17 +1959,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MARIA GUADALUPE</t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>CRISOSTOMO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LANDIN</t>
+          <t>CARDOSO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1983,32 +1979,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5588006100</t>
+          <t>5550539848</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EL CAPULIN</t>
+          <t>CDA 21 DE MARZO 12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>03-06-1998</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>LANDINGUADALUPE95@GMAIL.COM</t>
+          <t>DEIVID.AYD.CRI98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>31-01-2026 09:45:22</t>
+          <t>29-01-2026 19:21:28</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2029,17 +2025,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>09-02-2026 14:59:33</t>
+          <t>05-02-2026 19:25:52</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>09-02-2026 14:59:02</t>
+          <t>05-02-2026 19:22:43</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2059,7 +2055,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26220522194280003290</t>
+          <t>26220522118170003054</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2075,24 +2071,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>341357</t>
+          <t>341894</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>19712</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2102,17 +2098,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DAMIAN</t>
+          <t xml:space="preserve">JONATHAN </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTERO </t>
+          <t xml:space="preserve">URBAN </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2122,10 +2118,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5634592607</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>5574445964</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LOTOS</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2133,56 +2133,60 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>25-11-2010</t>
+          <t>06-12-1990</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>DENI.QUINTERO2010@GMAIL.COM</t>
+          <t>SOLDADO.DE.DIOS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>05-02-2026 16:04:32</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>08-02-2026 10:05:09</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>05-02-2026 16:09:19</t>
+          <t>08-02-2026 10:07:34</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>05-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>08-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>08-02-2026 10:07:05</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2190,14 +2194,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26220522109710003012</t>
+          <t>26220522169210003211</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2214,12 +2218,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>341889</t>
+          <t>342227</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2229,17 +2233,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LUCIA</t>
+          <t>YORDI JESUS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>PADRON</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2249,32 +2253,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5574445968</t>
+          <t>5613711355</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>LOTOS</t>
+          <t>CDA HACIENDA DE JALPA MZ 19 LT 115C</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>06-03-1990</t>
+          <t>23-10-2002</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>LUCYCOSA06039@GMAIL.COM</t>
+          <t>TREYOI.1023.ROCHA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>08-02-2026 09:58:42</t>
+          <t>09-02-2026 15:55:59</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2295,17 +2299,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>08-02-2026 10:02:56</t>
+          <t>09-02-2026 16:06:40</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>08-02-2026 10:02:01</t>
+          <t>09-02-2026 16:06:13</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2315,7 +2319,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2325,7 +2329,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26220522169080003210</t>
+          <t>26220522197030003304</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2337,24 +2341,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>340516</t>
+          <t>341951</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18334</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2364,17 +2368,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CARLOS ENRIQUE</t>
+          <t xml:space="preserve">ADRIANA </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUEDA </t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2384,32 +2388,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5619885190</t>
+          <t>5641136687</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IXTA</t>
+          <t>RANCHO</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>05-08-1991</t>
+          <t>05-03-1965</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ENRIQUE-RUEDA@OUTLOOK.COM</t>
+          <t>ADRIANA.CERVANT.AL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-02-2026 10:59:53</t>
+          <t>08-02-2026 13:24:14</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2430,17 +2434,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-02-2026 11:02:47</t>
+          <t>08-02-2026 13:32:56</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>03-02-2026 11:02:16</t>
+          <t>08-02-2026 13:32:13</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2460,7 +2464,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26220522036720002739</t>
+          <t>26220522172520003225</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2472,24 +2476,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>341952</t>
+          <t>340216</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2499,17 +2503,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RAMON</t>
+          <t>AXEL ZADKYEL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2519,12 +2523,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5520734799</t>
+          <t>5591647693</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>RANCHOO</t>
+          <t>SAN BUENAVENTURA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2534,17 +2538,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>31-08-1964</t>
+          <t>24-05-2006</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MONN.64KAISER@GMAIL.COM</t>
+          <t>AXELVALDEZ099@GMAL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>08-02-2026 13:27:30</t>
+          <t>02-02-2026 15:29:08</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2565,17 +2569,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>08-02-2026 13:36:45</t>
+          <t>02-02-2026 15:45:59</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>08-02-2026 13:36:11</t>
+          <t>02-02-2026 15:34:51</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2595,7 +2599,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26220522172570003226</t>
+          <t>26220522015050002682</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2607,24 +2611,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>341617</t>
+          <t>340315</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2634,17 +2638,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDILBERTO </t>
+          <t>MAYRA JAZMIN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>KURY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>AVILES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2654,32 +2658,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5540185856</t>
+          <t>5561248221</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ACACIA 80</t>
+          <t>IXTAP</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13-08-1979</t>
+          <t>13-08-1980</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>GONZALEZCRUZEDILBERTO@GMAIL.COM</t>
+          <t>MAYRACGT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>06-02-2026 16:14:24</t>
+          <t>02-02-2026 17:44:11</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2690,7 +2694,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2700,17 +2704,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>06-02-2026 17:06:08</t>
+          <t>03-02-2026 07:27:24</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>06-02-2026 16:20:48</t>
+          <t>03-02-2026 07:26:21</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2730,10 +2734,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26220522142170003123</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+          <t>26220522032080002726</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2754,12 +2762,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341101</t>
+          <t>342097</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2769,17 +2777,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CHRISTIAN OWEN</t>
+          <t xml:space="preserve">ALICIA </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t xml:space="preserve">SAUCEDO </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2789,35 +2797,39 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5643127118</t>
+          <t>5522530023</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C CATEDRAL METROPOLITANA 204</t>
+          <t>CDA MAGDALENA SN IXTAPALUCA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18-06-2011</t>
+          <t>23-03-1966</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CHRISTIAN09MENDEZ1234@GMAIL.COM</t>
+          <t>SAUCEDOGALICIAALICIA32@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>04-02-2026 17:18:13</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>09-02-2026 10:35:09</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2835,17 +2847,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>04-02-2026 17:31:39</t>
+          <t>18-02-2026 15:06:39</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>04-02-2026 17:30:29</t>
+          <t>18-02-2026 15:05:44</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2865,11 +2877,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26220522082650002911</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26220522463670004215</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>499</t>
@@ -2877,7 +2897,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2889,12 +2909,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>341099</t>
+          <t>338952</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2904,17 +2924,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AXEL KALID</t>
+          <t xml:space="preserve">ANABEL </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>PLATA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2924,32 +2944,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5635122950</t>
+          <t>5543867324</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C CATEDRAL METROPOLITANA 204</t>
+          <t>CDA DE JAZMINEZ MZ 20 LT 10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>23-07-2004</t>
+          <t>22-10-1998</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>GUERREROAXEL190@GMAIL.COM</t>
+          <t>MAPA_220@HOTMAIL.ES</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>04-02-2026 17:15:27</t>
+          <t>29-01-2026 08:22:19</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2960,7 +2980,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2970,17 +2990,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>04-02-2026 17:26:19</t>
+          <t>01-02-2026 10:00:34</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>04-02-2026 17:25:23</t>
+          <t>01-02-2026 09:59:59</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2990,7 +3010,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3000,11 +3020,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26220522082390002907</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>26220521988460002587</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>499</t>
@@ -3012,7 +3040,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3024,12 +3052,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342227</t>
+          <t>339256</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3039,17 +3067,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>YORDI JESUS</t>
+          <t>CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PADRON</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3059,12 +3087,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5613711355</t>
+          <t>5528464677</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CDA HACIENDA DE JALPA MZ 19 LT 115C</t>
+          <t xml:space="preserve">AV. JOSE MARIA MARTINEZ MZA 24 LT 19 </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3074,17 +3102,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>23-10-2002</t>
+          <t>12-01-1990</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TREYOI.1023.ROCHA@GMAIL.COM</t>
+          <t>ELDA.SOLRAC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 15:55:59</t>
+          <t>30-01-2026 09:16:32</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3095,7 +3123,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3105,17 +3133,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>09-02-2026 16:06:40</t>
+          <t>02-02-2026 11:52:16</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>09-02-2026 16:06:13</t>
+          <t>30-01-2026 09:31:10</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3135,7 +3163,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26220522197030003304</t>
+          <t>26220522007790002644</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3147,24 +3175,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342375</t>
+          <t>342750</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3174,17 +3202,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA AMELIA </t>
+          <t>MANUEL RAFAEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SIERNA</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3194,32 +3222,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5532857495</t>
+          <t>5574265455</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AV DEL POPO MZA 56</t>
+          <t>C CEBADA MZ 6 LT 3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>10-08-1975</t>
+          <t>23-11-1999</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>DIANAALINE10@HOTMAIL.COM</t>
+          <t>MANUEL_LVNA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-02-2026 18:11:48</t>
+          <t>10-02-2026 17:23:26</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3240,17 +3268,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>12-02-2026 18:14:46</t>
+          <t>10-02-2026 17:27:27</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>12-02-2026 18:13:56</t>
+          <t>10-02-2026 17:26:23</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3260,7 +3288,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3270,14 +3298,10 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26220522301970003709</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522239800003484</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
@@ -3286,24 +3310,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>341894</t>
+          <t>342375</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3313,17 +3337,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">JONATHAN </t>
+          <t xml:space="preserve">DIANA AMELIA </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">URBAN </t>
+          <t>SIERNA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3333,32 +3357,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5574445964</t>
+          <t>5532857495</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LOTOS</t>
+          <t>AV DEL POPO MZA 56</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>06-12-1990</t>
+          <t>10-08-1975</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SOLDADO.DE.DIOS@HOTMAIL.COM</t>
+          <t>DIANAALINE10@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>08-02-2026 10:05:09</t>
+          <t>09-02-2026 18:11:48</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3379,17 +3403,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>08-02-2026 10:07:34</t>
+          <t>12-02-2026 18:14:46</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>08-02-2026 10:07:05</t>
+          <t>12-02-2026 18:13:56</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3409,10 +3433,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26220522169210003211</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
+          <t>26220522301970003709</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
@@ -3433,12 +3461,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342097</t>
+          <t>342184</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3448,17 +3476,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALICIA </t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUCEDO </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>VICENTE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3468,39 +3496,35 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5522530023</t>
+          <t>5537110647</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CDA MAGDALENA SN IXTAPALUCA</t>
+          <t>COL SANTA CRUZ TLAPACOYA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>23-03-1966</t>
+          <t>25-07-2017</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>SAUCEDOGALICIAALICIA32@GMAIL.COM</t>
+          <t>KARINAFLORESVICENTE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-02-2026 10:35:09</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 14:42:03</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3518,17 +3542,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>18-02-2026 15:06:39</t>
+          <t>09-02-2026 14:52:27</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>18-02-2026 15:05:44</t>
+          <t>09-02-2026 14:50:55</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3538,7 +3562,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3548,19 +3572,11 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26220522463670004215</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522193980003288</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
           <t>499</t>
@@ -3568,24 +3584,24 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>341951</t>
+          <t>340512</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3595,17 +3611,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIANA </t>
+          <t>ROSA LIDIA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>ANZALDO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3615,12 +3631,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5641136687</t>
+          <t>5521196367</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>RANCHO</t>
+          <t>IXTA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3630,17 +3646,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>05-03-1965</t>
+          <t>14-04-1993</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ADRIANA.CERVANT.AL@GMAIL.COM</t>
+          <t>ROSYN_N@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>08-02-2026 13:24:14</t>
+          <t>03-02-2026 10:51:49</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3661,17 +3677,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>08-02-2026 13:32:56</t>
+          <t>03-02-2026 10:57:53</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>08-02-2026 13:32:13</t>
+          <t>03-02-2026 10:57:16</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3691,7 +3707,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26220522172520003225</t>
+          <t>26220522036640002738</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3703,24 +3719,24 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342745</t>
+          <t>342290</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20562</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3730,17 +3746,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ITZEL STEPHANY</t>
+          <t>ADRIANA ITZEL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VERDE</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SERVIN</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3750,12 +3766,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5584585348</t>
+          <t>5510440090</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CDA BARRANCA DE MEZQUITE MZ 56</t>
+          <t>C VILLAHERMOSA MZA 47</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3765,20 +3781,24 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>21-12-1995</t>
+          <t>14-08-1994</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ITZEL_VERDE95@ICLOUD.COM</t>
+          <t>ADRIANANAVA149@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10-02-2026 17:16:16</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>09-02-2026 16:53:59</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3796,17 +3816,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10-02-2026 17:21:18</t>
+          <t>18-02-2026 18:14:20</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10-02-2026 17:20:26</t>
+          <t>18-02-2026 18:13:49</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3816,7 +3836,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3826,10 +3846,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26220522239450003479</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
+          <t>26220522471810004257</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3838,24 +3862,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>342290</t>
+          <t>342380</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3865,17 +3889,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ADRIANA ITZEL</t>
+          <t>DIANA ALINE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3885,12 +3909,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5510973508</t>
+          <t>5625435058</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C VILLAHERMOSA MZA 47</t>
+          <t xml:space="preserve">C CASTILLO DE CHAPULTEPEC </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3900,24 +3924,20 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>14-08-1994</t>
+          <t>22-12-1996</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ADRIANANAVA149@GMAIL.COM</t>
+          <t>DIGTZ15@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>09-02-2026 16:53:59</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 18:16:13</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3935,17 +3955,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:20</t>
+          <t>12-02-2026 18:19:45</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>18-02-2026 18:13:49</t>
+          <t>12-02-2026 18:19:19</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3955,7 +3975,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3965,7 +3985,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26220522471810004257</t>
+          <t>26220522302230003710</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3993,12 +4013,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342184</t>
+          <t>342745</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20562</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4008,17 +4028,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>ITZEL STEPHANY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>VERDE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>VICENTE</t>
+          <t>SERVIN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4028,32 +4048,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5537110647</t>
+          <t>5584585348</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COL SANTA CRUZ TLAPACOYA</t>
+          <t>CDA BARRANCA DE MEZQUITE MZ 56</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>25-07-2017</t>
+          <t>21-12-1995</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>KARINAFLORESVICENTE@GMAIL.COM</t>
+          <t>ITZEL_VERDE95@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>09-02-2026 14:42:03</t>
+          <t>10-02-2026 17:16:16</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4074,17 +4094,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09-02-2026 14:52:27</t>
+          <t>10-02-2026 17:21:18</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>09-02-2026 14:50:55</t>
+          <t>10-02-2026 17:20:26</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4104,7 +4124,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26220522193980003288</t>
+          <t>26220522239450003479</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -4116,24 +4136,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>338952</t>
+          <t>340960</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>18778</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4143,17 +4163,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANABEL </t>
+          <t>LUIS ANGEL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PLATA</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4163,32 +4183,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5543867324</t>
+          <t>5669156876</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CDA DE JAZMINEZ MZ 20 LT 10</t>
+          <t>C TONATICO 197</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>22-10-1998</t>
+          <t>19-02-1993</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>MAPA_220@HOTMAIL.ES</t>
+          <t>BUICKGOLIFE856@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>29-01-2026 08:22:19</t>
+          <t>04-02-2026 12:16:09</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4199,7 +4219,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4209,17 +4229,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>01-02-2026 10:00:34</t>
+          <t>04-02-2026 12:24:18</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>01-02-2026 09:59:59</t>
+          <t>04-02-2026 12:23:46</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4239,19 +4259,11 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26220521988460002587</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522073370002861</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>499</t>
@@ -4259,24 +4271,24 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>339256</t>
+          <t>343503</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4286,17 +4298,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO</t>
+          <t>DIANA VIANEY</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">CARREON </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>YAÑEZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4306,32 +4318,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5528464677</t>
+          <t>5614816775</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV. JOSE MARIA MARTINEZ MZA 24 LT 19 </t>
+          <t>C TEPOYAN 5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>12-01-1990</t>
+          <t>16-10-1986</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ELDA.SOLRAC@GMAIL.COM</t>
+          <t>DIANACARREON995@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>30-01-2026 09:16:32</t>
+          <t>13-02-2026 14:48:21</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4342,7 +4354,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -4352,17 +4364,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-02-2026 11:52:16</t>
+          <t>13-02-2026 15:06:00</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>30-01-2026 09:31:10</t>
+          <t>13-02-2026 15:05:03</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4372,7 +4384,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4382,7 +4394,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26220522007790002644</t>
+          <t>26220522322030003760</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4406,12 +4418,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342750</t>
+          <t>341357</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4421,17 +4433,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MANUEL RAFAEL</t>
+          <t>DAMIAN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t xml:space="preserve">QUINTERO </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4441,14 +4453,10 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5574265455</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>C CEBADA MZ 6 LT 3</t>
-        </is>
-      </c>
+          <t>5634592607</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4456,60 +4464,56 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>23-11-1999</t>
+          <t>25-11-2010</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MANUEL_LVNA@HOTMAIL.COM</t>
+          <t>DENI.QUINTERO2010@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10-02-2026 17:23:26</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>05-02-2026 16:04:32</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>10-02-2026 17:27:27</t>
+          <t>05-02-2026 16:09:19</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>10-02-2026 17:26:23</t>
-        </is>
-      </c>
+          <t>05-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4517,36 +4521,36 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26220522239800003484</t>
+          <t>26220522109710003012</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342287</t>
+          <t>343838</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4556,17 +4560,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IRVING DONNOVAN</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO </t>
+          <t xml:space="preserve">MORAN </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4576,12 +4580,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5564343538</t>
+          <t>2206073345</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C PERA SAN MARCOS</t>
+          <t>CALLE MAGNOLIA 242</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4591,17 +4595,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>06-09-1992</t>
+          <t>26-02-1995</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>DONNOVANBR@OUTLOOK.COM</t>
+          <t>TRILLISO_BET@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-02-2026 16:52:02</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4622,27 +4626,27 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>12-02-2026 18:07:17</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>12-02-2026 18:06:58</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4652,14 +4656,10 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26220522301550003706</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522365710003869</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4680,12 +4680,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342380</t>
+          <t>344433</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4695,17 +4695,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DIANA ALINE</t>
+          <t>IRIS MONTSERRAT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>CHAVARIN</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4715,12 +4715,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5625435058</t>
+          <t>5564692994</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">C CASTILLO DE CHAPULTEPEC </t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4730,20 +4730,24 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>22-12-1996</t>
+          <t>29-08-1994</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>DIGTZ15@GMAIL.COM</t>
+          <t>MONTSERRAT_94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>09-02-2026 18:16:13</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>17-02-2026 10:03:24</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4761,17 +4765,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>12-02-2026 18:19:45</t>
+          <t>17-02-2026 10:10:20</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>12-02-2026 18:19:19</t>
+          <t>17-02-2026 10:08:56</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4781,7 +4785,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4791,14 +4795,10 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26220522302230003710</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522423620004039</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4819,12 +4819,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>344626</t>
+          <t>341889</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4834,17 +4834,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IXCHEL YARELI</t>
+          <t>LUCIA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIN </t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5579912763</t>
+          <t>5574445968</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>C DZILAM MZ 814 LT 4</t>
+          <t>LOTOS</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4869,52 +4869,48 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>31-01-1989</t>
+          <t>06-03-1990</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>IXCHELMARIN@OUTLOOK.COM</t>
+          <t>LUCYCOSA06039@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>17-02-2026 17:48:58</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>08-02-2026 09:58:42</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PLAN FAMILIAR RECURRENTE $999</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>17-02-2026 18:01:12</t>
+          <t>08-02-2026 10:02:56</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>17-02-2026 17:59:12</t>
+          <t>08-02-2026 10:02:01</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4934,36 +4930,36 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26220522439570004122</t>
+          <t>26220522169080003210</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>343831</t>
+          <t>341952</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4973,17 +4969,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JESSICA</t>
+          <t>RAMON</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4993,32 +4989,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2217041181</t>
+          <t>5520734799</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CALLE MAGNOLIA 242</t>
+          <t>RANCHOO</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>14-12-1998</t>
+          <t>31-08-1964</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>JESSICAHERNANDEZVAZQUEZ@OUTLOOK.COM</t>
+          <t>MONN.64KAISER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:19</t>
+          <t>08-02-2026 13:27:30</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -5039,22 +5035,22 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:20</t>
+          <t>08-02-2026 13:36:45</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:20</t>
+          <t>08-02-2026 13:36:11</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -5069,7 +5065,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26220522365380003866</t>
+          <t>26220522172570003226</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5081,24 +5077,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>343503</t>
+          <t>343831</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5108,17 +5104,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DIANA VIANEY</t>
+          <t>JESSICA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARREON </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>YAÑEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5128,12 +5124,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5614816775</t>
+          <t>2217041181</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C TEPOYAN 5</t>
+          <t>CALLE MAGNOLIA 242</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5143,17 +5139,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>16-10-1986</t>
+          <t>14-12-1998</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>DIANACARREON995@GMAIL.COM</t>
+          <t>JESSICAHERNANDEZVAZQUEZ@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>13-02-2026 14:48:21</t>
+          <t>15-02-2026 12:21:19</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5174,22 +5170,22 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>13-02-2026 15:06:00</t>
+          <t>15-02-2026 12:21:20</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>13-02-2026 15:05:03</t>
+          <t>15-02-2026 12:21:20</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -5204,7 +5200,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26220522322030003760</t>
+          <t>26220522365380003866</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5228,12 +5224,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>344676</t>
+          <t>342287</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22493</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5243,17 +5239,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JESSICA BERENICE</t>
+          <t>IRVING DONNOVAN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">BRAVO </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5263,39 +5259,35 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2219009457</t>
+          <t>5564343538</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C CIPRECES MZ 3</t>
+          <t>C PERA SAN MARCOS</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>02-04-1995</t>
+          <t>06-09-1992</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>JEBER18@YAHOO.COM.MX</t>
+          <t>DONNOVANBR@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>17-02-2026 19:05:24</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 16:52:02</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5313,17 +5305,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>17-02-2026 19:14:49</t>
+          <t>12-02-2026 18:07:17</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>17-02-2026 19:14:20</t>
+          <t>12-02-2026 18:06:58</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5333,7 +5325,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5343,10 +5335,14 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26220522443720004140</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
+          <t>26220522301550003706</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
@@ -5367,12 +5363,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>343301</t>
+          <t>344676</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5382,17 +5378,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>JESSICA BERENICE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ESPEJEL</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5402,35 +5398,39 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5516346350</t>
+          <t>2219009457</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
+          <t>C CIPRECES MZ 3</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>06-07-1995</t>
+          <t>02-04-1995</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>DIEGOLUPUS@GMAIL.COM</t>
+          <t>JEBER18@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>12-02-2026 16:04:34</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>17-02-2026 19:05:24</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>12-02-2026 16:26:22</t>
+          <t>17-02-2026 19:14:49</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>12-02-2026 16:25:47</t>
+          <t>17-02-2026 19:14:20</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26220522297530003689</t>
+          <t>26220522443720004140</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5502,12 +5502,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>343838</t>
+          <t>344233</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>22050</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5517,17 +5517,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORAN </t>
+          <t xml:space="preserve">JEREZ </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5537,35 +5537,39 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2206073345</t>
+          <t>5611753742</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CALLE MAGNOLIA 242</t>
+          <t xml:space="preserve">FRACC LOS HEROES </t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>26-02-1995</t>
+          <t>07-08-1998</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>TRILLISO_BET@HOTMAIL.COM</t>
+          <t>CASTROMARIAFERNANDA57@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>16-02-2026 17:43:53</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5583,27 +5587,27 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>16-02-2026 18:16:35</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>16-02-2026 18:15:46</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5613,7 +5617,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26220522365710003869</t>
+          <t>26220522403640003978</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5625,24 +5629,24 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344233</t>
+          <t>345379</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22050</t>
+          <t>87544</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5652,17 +5656,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>EMMANUEL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEREZ </t>
+          <t>DE JESUS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5672,32 +5676,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5611753742</t>
+          <t>5581003622</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRACC LOS HEROES </t>
+          <t>C AGUSTIN DE ITURBIDE 228</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>07-08-1998</t>
+          <t>17-12-1995</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CASTROMARIAFERNANDA57@GMAIL.COM</t>
+          <t>EMMANUELDJF17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>16-02-2026 17:43:53</t>
+          <t>20-02-2026 18:06:05</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5722,17 +5726,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>16-02-2026 18:16:35</t>
+          <t>20-02-2026 18:17:25</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>16-02-2026 18:15:46</t>
+          <t>20-02-2026 18:16:44</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5752,7 +5756,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26220522403640003978</t>
+          <t>26220522533780004518</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5764,7 +5768,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5776,12 +5780,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>344900</t>
+          <t>343824</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>21641</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5791,17 +5795,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ADRIAN BERENICE</t>
+          <t>MARISOL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5811,10 +5815,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5540961768</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>5531971979</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>COL CENTRO CDMX</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5822,17 +5830,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>05-03-1999</t>
+          <t>02-03-1973</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>BEREADRY99@HOTMAIL.COM</t>
+          <t>MAPGUE2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>18-02-2026 17:32:28</t>
+          <t>15-02-2026 12:05:48</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5843,7 +5851,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -5853,17 +5861,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>18-02-2026 17:43:39</t>
+          <t>15-02-2026 12:25:35</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>18-02-2026 17:43:01</t>
+          <t>15-02-2026 12:18:06</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5873,7 +5881,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5883,7 +5891,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26220522470070004245</t>
+          <t>26220522365480003867</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5895,24 +5903,24 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>344432</t>
+          <t>341922</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5922,19 +5930,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>YANNEVY ARIADNE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>PACHECO</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>GONZALEZ</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>52</t>
@@ -5942,39 +5950,35 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5515226715</t>
+          <t>5580261394</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ALFREDIO</t>
+          <t>HEROES</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>23-08-1991</t>
+          <t>25-11-1994</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>LIC.ALFREDO.91@GMAIL.COM</t>
+          <t>YENNEVY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>17-02-2026 09:59:28</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>08-02-2026 11:53:18</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5992,17 +5996,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>17-02-2026 10:14:17</t>
+          <t>08-02-2026 11:58:57</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>17-02-2026 10:13:36</t>
+          <t>08-02-2026 11:57:36</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6012,7 +6016,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6022,7 +6026,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26220522423710004040</t>
+          <t>26220522171210003218</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -6034,24 +6038,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344433</t>
+          <t>344432</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6061,17 +6065,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IRIS MONTSERRAT</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CHAVARIN</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6081,32 +6085,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5564692994</t>
+          <t>5515226715</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>ALFREDIO</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>29-08-1994</t>
+          <t>23-08-1991</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>MONTSERRAT_94@HOTMAIL.COM</t>
+          <t>LIC.ALFREDO.91@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>17-02-2026 10:03:24</t>
+          <t>17-02-2026 09:59:28</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6131,7 +6135,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>17-02-2026 10:10:20</t>
+          <t>17-02-2026 10:14:17</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -6141,7 +6145,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>17-02-2026 10:08:56</t>
+          <t>17-02-2026 10:13:36</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6161,7 +6165,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26220522423620004039</t>
+          <t>26220522423710004040</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6185,12 +6189,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>343505</t>
+          <t>344895</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>22712</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6200,17 +6204,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ALVARO O BRIAN</t>
+          <t>ALMA ROSA BASILISA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>VALADEZ</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BLANCA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6220,35 +6224,39 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5591919598</t>
+          <t>5611775850</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AV NUEVO MEXICO 301</t>
+          <t>C JOSE MARIA MORELOS</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>12-09-1993</t>
+          <t>02-04-1963</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>POSEIDONBALA93@OUTLOOK.COM</t>
+          <t>ALMAROSACASTRO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>13-02-2026 14:50:25</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>18-02-2026 17:26:28</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6266,17 +6274,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>13-02-2026 14:59:34</t>
+          <t>18-02-2026 17:48:07</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>13-02-2026 14:59:07</t>
+          <t>18-02-2026 17:46:56</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6296,7 +6304,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26220522321910003759</t>
+          <t>26220522470370004248</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6320,12 +6328,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>343544</t>
+          <t>345233</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>87398</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6335,7 +6343,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LAURA AMAYRANI</t>
+          <t xml:space="preserve">LEONEL YUARI </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6345,7 +6353,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">MANRIQUEZ </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6355,35 +6363,39 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5546447212</t>
+          <t>5521514699</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
+          <t xml:space="preserve">ZOL AGRICOLA ORIENTAL </t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>13-03-2007</t>
+          <t>27-06-2004</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>LAUPRD25@GMAIL.COM</t>
+          <t>STARCICI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>13-02-2026 17:03:29</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>20-02-2026 09:01:39</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6401,17 +6413,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:38</t>
+          <t>20-02-2026 09:08:59</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>13-02-2026 17:18:02</t>
+          <t>20-02-2026 09:08:21</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6431,7 +6443,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26220522326190003779</t>
+          <t>26220522522290004459</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
@@ -6443,24 +6455,24 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>344895</t>
+          <t>344934</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22712</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6470,17 +6482,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ALMA ROSA BASILISA</t>
+          <t xml:space="preserve">YENNIFER </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6490,12 +6502,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5611775850</t>
+          <t>5512992481</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>C JOSE MARIA MORELOS</t>
+          <t>TULTITLAM MEX</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6505,17 +6517,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>02-04-1963</t>
+          <t>17-09-1993</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ALMAROSACASTRO@HOTMAIL.COM</t>
+          <t>YLOPEZFLORES17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>18-02-2026 17:26:28</t>
+          <t>18-02-2026 18:57:05</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6540,7 +6552,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>18-02-2026 17:48:07</t>
+          <t>18-02-2026 19:01:48</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -6550,7 +6562,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>18-02-2026 17:46:56</t>
+          <t>18-02-2026 19:00:57</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6560,7 +6572,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6570,7 +6582,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26220522470370004248</t>
+          <t>26220522473980004280</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6594,12 +6606,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>344934</t>
+          <t>345129</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22751</t>
+          <t>87294</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6609,17 +6621,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">YENNIFER </t>
+          <t>KIMBERLY ABIGAIL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6629,12 +6641,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5512992481</t>
+          <t>5619291534</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TULTITLAM MEX</t>
+          <t>U HAB 4 VIENTOS</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6644,17 +6656,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>17-09-1993</t>
+          <t>20-08-2007</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>YLOPEZFLORES17@GMAIL.COM</t>
+          <t>KKKIMBERLYY2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>18-02-2026 18:57:05</t>
+          <t>19-02-2026 16:52:09</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6679,17 +6691,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>18-02-2026 19:01:48</t>
+          <t>19-02-2026 17:04:47</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>18-02-2026 19:00:57</t>
+          <t>19-02-2026 17:03:32</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6699,7 +6711,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6709,7 +6721,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26220522473980004280</t>
+          <t>26220522500320004391</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
@@ -6733,12 +6745,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>343824</t>
+          <t>345130</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>87295</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6748,17 +6760,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MARISOL</t>
+          <t>MARISELA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6768,12 +6780,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5531971979</t>
+          <t>5538014107</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COL CENTRO CDMX</t>
+          <t>U HAB 4 VIENTOS</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6783,20 +6795,24 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>02-03-1973</t>
+          <t>02-12-1975</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>MAPGUE2@GMAIL.COM</t>
+          <t>KIMBERLY89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>15-02-2026 12:05:48</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>19-02-2026 16:54:23</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6814,17 +6830,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>15-02-2026 12:25:35</t>
+          <t>19-02-2026 17:08:32</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>15-02-2026 12:18:06</t>
+          <t>19-02-2026 17:08:01</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6834,7 +6850,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6844,7 +6860,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26220522365480003867</t>
+          <t>26220522500550004392</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6868,12 +6884,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>341922</t>
+          <t>342048</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6883,17 +6899,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>YANNEVY ARIADNE</t>
+          <t>DULCE IVONNE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>ZARCO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6903,12 +6919,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5580261394</t>
+          <t>5519303247</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>HEROES</t>
+          <t xml:space="preserve">C. LA CIGARRA COL. ESPERANZA </t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6918,17 +6934,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>25-11-1994</t>
+          <t>01-08-1991</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>YENNEVY@GMAIL.COM</t>
+          <t>DULCEIVONNETORRESZARCO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>08-02-2026 11:53:18</t>
+          <t>09-02-2026 08:22:24</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6949,17 +6965,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>08-02-2026 11:58:57</t>
+          <t>09-02-2026 08:34:47</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>08-02-2026 11:57:36</t>
+          <t>09-02-2026 08:34:00</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6979,7 +6995,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26220522171210003218</t>
+          <t>26220522185040003259</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -6991,24 +7007,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>David Guillermo  Fuentes Carrillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>342048</t>
+          <t>344900</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>22717</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7018,17 +7034,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DULCE IVONNE</t>
+          <t>ADRIAN BERENICE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ZARCO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7038,14 +7054,10 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>5519303247</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C. LA CIGARRA COL. ESPERANZA </t>
-        </is>
-      </c>
+          <t>5540961768</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7053,17 +7065,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>01-08-1991</t>
+          <t>05-03-1999</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>DULCEIVONNETORRESZARCO@GMAIL.COM</t>
+          <t>BEREADRY99@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>09-02-2026 08:22:24</t>
+          <t>18-02-2026 17:32:28</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -7074,7 +7086,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -7084,17 +7096,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>09-02-2026 08:34:47</t>
+          <t>18-02-2026 17:43:39</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>09-02-2026 08:34:00</t>
+          <t>18-02-2026 17:43:01</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7114,7 +7126,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26220522185040003259</t>
+          <t>26220522470070004245</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -7126,24 +7138,24 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>342192</t>
+          <t>345055</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20010</t>
+          <t>87220</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7153,17 +7165,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JESUS ZAID</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>BORREGO</t>
+          <t>TALAVERA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>PANIAGUA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7173,12 +7185,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4055882651</t>
+          <t>5540308509</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">C MELCHOR OCAMPO S/N COL. LA ESPERANZA </t>
+          <t>C SUR 171</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7188,48 +7200,52 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>23-12-1999</t>
+          <t>20-02-1963</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>SAIDD.BST@GMAIL.COM</t>
+          <t>ANLGELTALAVERAP63@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>09-02-2026 14:52:50</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>19-02-2026 13:00:23</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>09-02-2026 15:06:28</t>
+          <t>19-02-2026 13:17:48</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>09-02-2026 15:05:32</t>
+          <t>19-02-2026 13:16:38</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7239,7 +7255,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -7249,36 +7265,36 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26220522194630003292</t>
+          <t>26220522493820004335</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>344940</t>
+          <t>345063</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>87228</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7288,17 +7304,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRANDON </t>
+          <t>MARIA DE LA LUZ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MONTESINOS</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7308,67 +7324,67 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5613578379</t>
+          <t>5561186386</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>C CIPRECES MZA 3</t>
+          <t>C SUR 171</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>08-03-1994</t>
+          <t>15-04-1963</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>BRANDON.FAMDA@GMAIL.COM</t>
+          <t>LG.JACK63@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>18-02-2026 19:14:37</t>
+          <t>19-02-2026 13:21:09</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>18-02-2026 19:17:54</t>
+          <t>19-02-2026 13:30:22</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>18-02-2026 19:17:35</t>
+          <t>19-02-2026 13:29:04</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7388,14 +7404,14 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26220522474720004282</t>
+          <t>26220522494100004341</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7412,12 +7428,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344931</t>
+          <t>342192</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7427,17 +7443,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ANDRES JESUS</t>
+          <t>JESUS ZAID</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>BORREGO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7447,12 +7463,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5537846550</t>
+          <t>4055882651</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>MZ H EDIF 2B</t>
+          <t xml:space="preserve">C MELCHOR OCAMPO S/N COL. LA ESPERANZA </t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7462,24 +7478,20 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>10-11-1992</t>
+          <t>23-12-1999</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>RAZIEL_FO@HOTMAIL.COM</t>
+          <t>SAIDD.BST@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>18-02-2026 18:46:57</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 14:52:50</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7497,17 +7509,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>18-02-2026 18:54:43</t>
+          <t>09-02-2026 15:06:28</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>18-02-2026 18:52:58</t>
+          <t>09-02-2026 15:05:32</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7527,7 +7539,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26220522473750004279</t>
+          <t>26220522194630003292</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7539,24 +7551,24 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>342536</t>
+          <t>344931</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7566,17 +7578,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>HANNIA ATZIRY</t>
+          <t>ANDRES JESUS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7586,35 +7598,39 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5541561912</t>
+          <t>5537346724</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>TEJALPA</t>
+          <t>MZ H EDIF 2B</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>22-01-1997</t>
+          <t>10-11-1992</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>HANNIA_22_SANDOVAL@HOTMAIL.COM</t>
+          <t>RAZIEL_FO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>10-02-2026 07:49:10</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>18-02-2026 18:46:57</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7632,17 +7648,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10-02-2026 07:55:17</t>
+          <t>18-02-2026 18:54:43</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>10-02-2026 07:53:33</t>
+          <t>18-02-2026 18:52:58</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7652,7 +7668,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7662,7 +7678,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26220522224790003405</t>
+          <t>26220522473750004279</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
@@ -7674,24 +7690,24 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>343539</t>
+          <t>342536</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7701,17 +7717,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ROCIO</t>
+          <t>HANNIA ATZIRY</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>JAIMEZ</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7721,12 +7737,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5534063877</t>
+          <t>5541561912</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>C CUAUTZINGO MZA 34</t>
+          <t>TEJALPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7736,17 +7752,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>12-01-1998</t>
+          <t>22-01-1997</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
+          <t>HANNIA_22_SANDOVAL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>13-02-2026 16:58:39</t>
+          <t>10-02-2026 07:49:10</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7767,17 +7783,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>13-02-2026 17:12:37</t>
+          <t>10-02-2026 07:55:17</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>13-02-2026 17:10:18</t>
+          <t>10-02-2026 07:53:33</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7787,7 +7803,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7797,7 +7813,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26220522325890003776</t>
+          <t>26220522224790003405</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
@@ -7809,12 +7825,1112 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
+          <t>Brenda Anahi  Escamilla Mendez</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>343301</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>21118</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DIEGO</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>TOVAR</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ESPEJEL</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>5516346350</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>06-07-1995</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>DIEGOLUPUS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>12-02-2026 16:04:34</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>12-02-2026 16:26:22</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>12-02-2026 16:25:47</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26220522297530003689</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>343505</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>21322</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ALVARO O BRIAN</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>VALADEZ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>BLANCA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>5591919598</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>AV NUEVO MEXICO 301</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>12-09-1993</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>POSEIDONBALA93@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>13-02-2026 14:50:25</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>13-02-2026 14:59:34</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>13-02-2026 14:59:07</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26220522321910003759</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>343544</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>21361</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LAURA AMAYRANI</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>5546447212</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>13-03-2007</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>LAUPRD25@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:03:29</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:19:38</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:18:02</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26220522326190003779</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
           <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
+      <c r="AC57" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>344217</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>22034</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ELIZALDE</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>7473547605</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV. NIÑOS HEROES COL. SANTA CRUZ </t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>09-07-1998</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>ALEXGARCIAE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:34:05</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:50:26</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:49:51</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26220522497590004364</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>343539</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>21356</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ROCIO</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>JAIMEZ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>5534063877</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>C CUAUTZINGO MZA 34</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>12-01-1998</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:58:39</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:12:37</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:10:18</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26220522325890003776</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Luis Antonio  Chaparro Alonso</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>344626</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>22443</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>IXCHEL YARELI</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIN </t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>MUÑOZ</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>5579912763</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>C DZILAM MZ 814 LT 4</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>31-01-1989</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>IXCHELMARIN@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>17-02-2026 17:48:58</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>PLAN FAMILIAR RECURRENTE $999</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>17-02-2026 18:01:12</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>17-02-2026 17:59:12</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26220522439570004122</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Luis Antonio  Chaparro Alonso</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>345338</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>87503</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUADALUPE </t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CARRANZA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>5615722096</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRACC HACIENDA DE LAS PALMAS III </t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>03-09-1981</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>GUADALUPECARRANZA2830@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>20-02-2026 16:38:08</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>20-02-2026 16:51:02</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>20-02-2026 16:49:11</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26220522530660004497</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Luis Antonio  Chaparro Alonso</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>344940</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>22757</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRANDON </t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DELGADO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>MONTESINOS</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>5613578379</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>C CIPRECES MZA 3</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>08-03-1994</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>BRANDON.FAMDA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:14:37</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:17:54</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:17:35</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26220522474720004282</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1400,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>341617</t>
+          <t>341099</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDILBERTO </t>
+          <t>AXEL KALID</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5540185856</t>
+          <t>5635122950</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ACACIA 80</t>
+          <t>C CATEDRAL METROPOLITANA 204</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>13-08-1979</t>
+          <t>23-07-2004</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>GONZALEZCRUZEDILBERTO@GMAIL.COM</t>
+          <t>GUERREROAXEL190@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>06-02-2026 16:14:24</t>
+          <t>04-02-2026 17:15:27</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1481,17 +1481,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>06-02-2026 17:06:08</t>
+          <t>04-02-2026 17:26:19</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>06-02-2026 16:20:48</t>
+          <t>04-02-2026 17:25:23</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26220522142170003123</t>
+          <t>26220522082390002907</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1523,24 +1523,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>341101</t>
+          <t>341617</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CHRISTIAN OWEN</t>
+          <t xml:space="preserve">EDILBERTO </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5643127118</t>
+          <t>5540185856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C CATEDRAL METROPOLITANA 204</t>
+          <t>ACACIA 80</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1585,17 +1585,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>18-06-2011</t>
+          <t>13-08-1979</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CHRISTIAN09MENDEZ1234@GMAIL.COM</t>
+          <t>GONZALEZCRUZEDILBERTO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>04-02-2026 17:18:13</t>
+          <t>06-02-2026 16:14:24</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1616,17 +1616,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>04-02-2026 17:31:39</t>
+          <t>06-02-2026 17:06:08</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>04-02-2026 17:30:29</t>
+          <t>06-02-2026 16:20:48</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26220522082650002911</t>
+          <t>26220522142170003123</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1658,24 +1658,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>339592</t>
+          <t>339174</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1685,17 +1685,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MARIA GUADALUPE</t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>CRISOSTOMO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LANDIN</t>
+          <t>CARDOSO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1705,32 +1705,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5588006100</t>
+          <t>5550539848</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>EL CAPULIN</t>
+          <t>CDA 21 DE MARZO 12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>03-06-1998</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>LANDINGUADALUPE95@GMAIL.COM</t>
+          <t>DEIVID.AYD.CRI98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>31-01-2026 09:45:22</t>
+          <t>29-01-2026 19:21:28</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1751,17 +1751,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>09-02-2026 14:59:33</t>
+          <t>05-02-2026 19:25:52</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>09-02-2026 14:59:02</t>
+          <t>05-02-2026 19:22:43</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26220522194280003290</t>
+          <t>26220522118170003054</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1797,24 +1797,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>341099</t>
+          <t>341101</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AXEL KALID</t>
+          <t>CHRISTIAN OWEN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5635122950</t>
+          <t>5643127118</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1859,17 +1859,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>23-07-2004</t>
+          <t>18-06-2011</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>GUERREROAXEL190@GMAIL.COM</t>
+          <t>CHRISTIAN09MENDEZ1234@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>04-02-2026 17:15:27</t>
+          <t>04-02-2026 17:18:13</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>04-02-2026 17:26:19</t>
+          <t>04-02-2026 17:31:39</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>04-02-2026 17:25:23</t>
+          <t>04-02-2026 17:30:29</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26220522082390002907</t>
+          <t>26220522082650002911</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1944,12 +1944,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>339174</t>
+          <t>342375</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1959,17 +1959,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t xml:space="preserve">DIANA AMELIA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CRISOSTOMO</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CARDOSO</t>
+          <t>SIERNA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1979,32 +1979,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5550539848</t>
+          <t>5532857495</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CDA 21 DE MARZO 12</t>
+          <t>AV DEL POPO MZA 56</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>03-06-1998</t>
+          <t>10-08-1975</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>DEIVID.AYD.CRI98@GMAIL.COM</t>
+          <t>DIANAALINE10@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>29-01-2026 19:21:28</t>
+          <t>09-02-2026 18:11:48</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2025,17 +2025,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>05-02-2026 19:25:52</t>
+          <t>12-02-2026 18:14:46</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>05-02-2026 19:22:43</t>
+          <t>12-02-2026 18:13:56</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26220522118170003054</t>
+          <t>26220522301970003709</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2218,12 +2218,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>342227</t>
+          <t>340216</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>YORDI JESUS</t>
+          <t>AXEL ZADKYEL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PADRON</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5613711355</t>
+          <t>5591647693</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CDA HACIENDA DE JALPA MZ 19 LT 115C</t>
+          <t>SAN BUENAVENTURA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23-10-2002</t>
+          <t>24-05-2006</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>TREYOI.1023.ROCHA@GMAIL.COM</t>
+          <t>AXELVALDEZ099@GMAL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>09-02-2026 15:55:59</t>
+          <t>02-02-2026 15:29:08</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>09-02-2026 16:06:40</t>
+          <t>02-02-2026 15:45:59</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>09-02-2026 16:06:13</t>
+          <t>02-02-2026 15:34:51</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26220522197030003304</t>
+          <t>26220522015050002682</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2341,24 +2341,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341951</t>
+          <t>342097</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIANA </t>
+          <t xml:space="preserve">ALICIA </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t xml:space="preserve">SAUCEDO </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5641136687</t>
+          <t>5522530023</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>RANCHO</t>
+          <t>CDA MAGDALENA SN IXTAPALUCA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2403,20 +2403,24 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>05-03-1965</t>
+          <t>23-03-1966</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ADRIANA.CERVANT.AL@GMAIL.COM</t>
+          <t>SAUCEDOGALICIAALICIA32@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>08-02-2026 13:24:14</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>09-02-2026 10:35:09</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2434,17 +2438,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>08-02-2026 13:32:56</t>
+          <t>18-02-2026 15:06:39</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>08-02-2026 13:32:13</t>
+          <t>18-02-2026 15:05:44</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2454,7 +2458,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2464,11 +2468,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26220522172520003225</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>26220522463670004215</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>499</t>
@@ -2476,7 +2488,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2488,12 +2500,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>340216</t>
+          <t>342227</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2503,17 +2515,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AXEL ZADKYEL</t>
+          <t>YORDI JESUS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>PADRON</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2523,12 +2535,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5591647693</t>
+          <t>5613711355</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SAN BUENAVENTURA</t>
+          <t>CDA HACIENDA DE JALPA MZ 19 LT 115C</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2538,17 +2550,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>24-05-2006</t>
+          <t>23-10-2002</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>AXELVALDEZ099@GMAL.COM</t>
+          <t>TREYOI.1023.ROCHA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-02-2026 15:29:08</t>
+          <t>09-02-2026 15:55:59</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2569,17 +2581,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-02-2026 15:45:59</t>
+          <t>09-02-2026 16:06:40</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-02-2026 15:34:51</t>
+          <t>09-02-2026 16:06:13</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2589,7 +2601,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2599,7 +2611,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26220522015050002682</t>
+          <t>26220522197030003304</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2611,24 +2623,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340315</t>
+          <t>339592</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2638,17 +2650,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MAYRA JAZMIN</t>
+          <t>MARIA GUADALUPE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KURY</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AVILES</t>
+          <t>LANDIN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2658,12 +2670,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5561248221</t>
+          <t>5588006100</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IXTAP</t>
+          <t>EL CAPULIN</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2673,17 +2685,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13-08-1980</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MAYRACGT@GMAIL.COM</t>
+          <t>LANDINGUADALUPE95@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-02-2026 17:44:11</t>
+          <t>31-01-2026 09:45:22</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2694,7 +2706,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2704,17 +2716,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-02-2026 07:27:24</t>
+          <t>09-02-2026 14:59:33</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>03-02-2026 07:26:21</t>
+          <t>09-02-2026 14:59:02</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2734,7 +2746,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26220522032080002726</t>
+          <t>26220522194280003290</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2750,24 +2762,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>342097</t>
+          <t>340315</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2777,17 +2789,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALICIA </t>
+          <t>MAYRA JAZMIN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUCEDO </t>
+          <t>KURY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>AVILES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2797,12 +2809,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5522530023</t>
+          <t>5561248221</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CDA MAGDALENA SN IXTAPALUCA</t>
+          <t>IXTAP</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2812,24 +2824,20 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>23-03-1966</t>
+          <t>13-08-1980</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>SAUCEDOGALICIAALICIA32@GMAIL.COM</t>
+          <t>MAYRACGT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>09-02-2026 10:35:09</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>02-02-2026 17:44:11</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2837,7 +2845,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2847,17 +2855,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>18-02-2026 15:06:39</t>
+          <t>03-02-2026 07:27:24</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>18-02-2026 15:05:44</t>
+          <t>03-02-2026 07:26:21</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2867,7 +2875,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2877,7 +2885,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26220522463670004215</t>
+          <t>26220522032080002726</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2885,11 +2893,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
           <t>499</t>
@@ -2897,24 +2901,24 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>338952</t>
+          <t>340512</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2924,17 +2928,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANABEL </t>
+          <t>ROSA LIDIA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PLATA</t>
+          <t>ANZALDO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2944,12 +2948,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5543867324</t>
+          <t>5521196367</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CDA DE JAZMINEZ MZ 20 LT 10</t>
+          <t>IXTA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2959,17 +2963,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22-10-1998</t>
+          <t>14-04-1993</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MAPA_220@HOTMAIL.ES</t>
+          <t>ROSYN_N@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>29-01-2026 08:22:19</t>
+          <t>03-02-2026 10:51:49</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2980,7 +2984,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2990,17 +2994,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>01-02-2026 10:00:34</t>
+          <t>03-02-2026 10:57:53</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>01-02-2026 09:59:59</t>
+          <t>03-02-2026 10:57:16</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3020,19 +3024,11 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26220521988460002587</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522036640002738</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>499</t>
@@ -3040,24 +3036,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>339256</t>
+          <t>341951</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3067,17 +3063,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO</t>
+          <t xml:space="preserve">ADRIANA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3087,32 +3083,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5528464677</t>
+          <t>5641136687</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV. JOSE MARIA MARTINEZ MZA 24 LT 19 </t>
+          <t>RANCHO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>12-01-1990</t>
+          <t>05-03-1965</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ELDA.SOLRAC@GMAIL.COM</t>
+          <t>ADRIANA.CERVANT.AL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>30-01-2026 09:16:32</t>
+          <t>08-02-2026 13:24:14</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3123,7 +3119,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3133,17 +3129,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-02-2026 11:52:16</t>
+          <t>08-02-2026 13:32:56</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>30-01-2026 09:31:10</t>
+          <t>08-02-2026 13:32:13</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3153,7 +3149,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3163,7 +3159,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26220522007790002644</t>
+          <t>26220522172520003225</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3175,24 +3171,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342750</t>
+          <t>338952</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3202,17 +3198,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MANUEL RAFAEL</t>
+          <t xml:space="preserve">ANABEL </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>PLATA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3222,32 +3218,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5574265455</t>
+          <t>5543867324</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C CEBADA MZ 6 LT 3</t>
+          <t>CDA DE JAZMINEZ MZ 20 LT 10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>23-11-1999</t>
+          <t>22-10-1998</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MANUEL_LVNA@HOTMAIL.COM</t>
+          <t>MAPA_220@HOTMAIL.ES</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>10-02-2026 17:23:26</t>
+          <t>29-01-2026 08:22:19</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3258,7 +3254,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3268,17 +3264,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>10-02-2026 17:27:27</t>
+          <t>01-02-2026 10:00:34</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>10-02-2026 17:26:23</t>
+          <t>01-02-2026 09:59:59</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3288,7 +3284,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3298,11 +3294,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26220522239800003484</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>26220521988460002587</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>499</t>
@@ -3322,12 +3326,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342375</t>
+          <t>339256</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3337,17 +3341,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA AMELIA </t>
+          <t>CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SIERNA</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3357,32 +3361,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5532857495</t>
+          <t>5528464677</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AV DEL POPO MZA 56</t>
+          <t xml:space="preserve">AV. JOSE MARIA MARTINEZ MZA 24 LT 19 </t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>10-08-1975</t>
+          <t>12-01-1990</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>DIANAALINE10@HOTMAIL.COM</t>
+          <t>ELDA.SOLRAC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>09-02-2026 18:11:48</t>
+          <t>30-01-2026 09:16:32</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3393,7 +3397,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3403,17 +3407,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>12-02-2026 18:14:46</t>
+          <t>02-02-2026 11:52:16</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>12-02-2026 18:13:56</t>
+          <t>30-01-2026 09:31:10</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3423,7 +3427,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3433,14 +3437,10 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26220522301970003709</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522007790002644</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
@@ -3461,12 +3461,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342184</t>
+          <t>342290</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>ADRIANA ITZEL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VICENTE</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3496,35 +3496,39 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5537110647</t>
+          <t>5510440090</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COL SANTA CRUZ TLAPACOYA</t>
+          <t>C VILLAHERMOSA MZA 47</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>25-07-2017</t>
+          <t>14-08-1994</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>KARINAFLORESVICENTE@GMAIL.COM</t>
+          <t>ADRIANANAVA149@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-02-2026 14:42:03</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>09-02-2026 16:53:59</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3542,17 +3546,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-02-2026 14:52:27</t>
+          <t>18-02-2026 18:14:20</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>09-02-2026 14:50:55</t>
+          <t>18-02-2026 18:13:49</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3562,7 +3566,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3572,10 +3576,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26220522193980003288</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
+          <t>26220522471810004257</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3596,12 +3604,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>340512</t>
+          <t>342184</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3611,17 +3619,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ROSA LIDIA</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ANZALDO</t>
+          <t>VICENTE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3631,32 +3639,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5521196367</t>
+          <t>5537110647</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IXTA</t>
+          <t>COL SANTA CRUZ TLAPACOYA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>14-04-1993</t>
+          <t>25-07-2017</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ROSYN_N@HOTMAIL.COM</t>
+          <t>KARINAFLORESVICENTE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>03-02-2026 10:51:49</t>
+          <t>09-02-2026 14:42:03</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3677,17 +3685,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>03-02-2026 10:57:53</t>
+          <t>09-02-2026 14:52:27</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>03-02-2026 10:57:16</t>
+          <t>09-02-2026 14:50:55</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3707,7 +3715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26220522036640002738</t>
+          <t>26220522193980003288</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3731,12 +3739,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342290</t>
+          <t>342750</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3746,17 +3754,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ADRIANA ITZEL</t>
+          <t>MANUEL RAFAEL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3766,39 +3774,35 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5510440090</t>
+          <t>5574265455</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>C VILLAHERMOSA MZA 47</t>
+          <t>C CEBADA MZ 6 LT 3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>14-08-1994</t>
+          <t>23-11-1999</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ADRIANANAVA149@GMAIL.COM</t>
+          <t>MANUEL_LVNA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>09-02-2026 16:53:59</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 17:23:26</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3816,17 +3820,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:20</t>
+          <t>10-02-2026 17:27:27</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>18-02-2026 18:13:49</t>
+          <t>10-02-2026 17:26:23</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3846,14 +3850,10 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26220522471810004257</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522239800003484</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3862,24 +3862,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>342380</t>
+          <t>342745</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>20562</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3889,17 +3889,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DIANA ALINE</t>
+          <t>ITZEL STEPHANY</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>VERDE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>SERVIN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5625435058</t>
+          <t>5584585348</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">C CASTILLO DE CHAPULTEPEC </t>
+          <t>CDA BARRANCA DE MEZQUITE MZ 56</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3924,17 +3924,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>22-12-1996</t>
+          <t>21-12-1995</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>DIGTZ15@GMAIL.COM</t>
+          <t>ITZEL_VERDE95@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>09-02-2026 18:16:13</t>
+          <t>10-02-2026 17:16:16</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3955,17 +3955,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>12-02-2026 18:19:45</t>
+          <t>10-02-2026 17:21:18</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>12-02-2026 18:19:19</t>
+          <t>10-02-2026 17:20:26</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3985,14 +3985,10 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26220522302230003710</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522239450003479</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
@@ -4001,24 +3997,24 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342745</t>
+          <t>342380</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20562</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4028,17 +4024,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ITZEL STEPHANY</t>
+          <t>DIANA ALINE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VERDE</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SERVIN</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4048,12 +4044,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5584585348</t>
+          <t>5625435058</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CDA BARRANCA DE MEZQUITE MZ 56</t>
+          <t xml:space="preserve">C CASTILLO DE CHAPULTEPEC </t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4063,17 +4059,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>21-12-1995</t>
+          <t>22-12-1996</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ITZEL_VERDE95@ICLOUD.COM</t>
+          <t>DIGTZ15@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10-02-2026 17:16:16</t>
+          <t>09-02-2026 18:16:13</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4094,17 +4090,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>10-02-2026 17:21:18</t>
+          <t>12-02-2026 18:19:45</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>10-02-2026 17:20:26</t>
+          <t>12-02-2026 18:19:19</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4124,10 +4120,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26220522239450003479</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
+          <t>26220522302230003710</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -4283,12 +4283,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>343503</t>
+          <t>341357</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4298,17 +4298,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DIANA VIANEY</t>
+          <t>DAMIAN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARREON </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>YAÑEZ</t>
+          <t xml:space="preserve">QUINTERO </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4318,75 +4318,67 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5614816775</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>C TEPOYAN 5</t>
-        </is>
-      </c>
+          <t>5634592607</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>16-10-1986</t>
+          <t>25-11-2010</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>DIANACARREON995@GMAIL.COM</t>
+          <t>DENI.QUINTERO2010@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>13-02-2026 14:48:21</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>05-02-2026 16:04:32</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>13-02-2026 15:06:00</t>
+          <t>05-02-2026 16:09:19</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>13-02-2026 15:05:03</t>
-        </is>
-      </c>
+          <t>05-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4394,14 +4386,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26220522322030003760</t>
+          <t>26220522109710003012</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4418,12 +4410,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>341357</t>
+          <t>344676</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4433,17 +4425,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DAMIAN</t>
+          <t>JESSICA BERENICE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTERO </t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4453,67 +4445,79 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5634592607</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>2219009457</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>C CIPRECES MZ 3</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>25-11-2010</t>
+          <t>02-04-1995</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>DENI.QUINTERO2010@GMAIL.COM</t>
+          <t>JEBER18@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>05-02-2026 16:04:32</t>
+          <t>17-02-2026 19:05:24</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>05-02-2026 16:09:19</t>
+          <t>17-02-2026 19:14:49</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>05-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>17-02-2026 19:14:20</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4521,14 +4525,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26220522109710003012</t>
+          <t>26220522443720004140</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4545,12 +4549,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>343838</t>
+          <t>343503</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4560,17 +4564,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>DIANA VIANEY</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORAN </t>
+          <t xml:space="preserve">CARREON </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>YAÑEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4580,32 +4584,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2206073345</t>
+          <t>5614816775</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CALLE MAGNOLIA 242</t>
+          <t>C TEPOYAN 5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>26-02-1995</t>
+          <t>16-10-1986</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>TRILLISO_BET@HOTMAIL.COM</t>
+          <t>DIANACARREON995@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>13-02-2026 14:48:21</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4626,22 +4630,22 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>13-02-2026 15:06:00</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>13-02-2026 15:05:03</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -4656,7 +4660,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26220522365710003869</t>
+          <t>26220522322030003760</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4680,12 +4684,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>344433</t>
+          <t>343838</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4695,17 +4699,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IRIS MONTSERRAT</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CHAVARIN</t>
+          <t xml:space="preserve">MORAN </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4715,39 +4719,35 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5564692994</t>
+          <t>2206073345</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>CALLE MAGNOLIA 242</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>29-08-1994</t>
+          <t>26-02-1995</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>MONTSERRAT_94@HOTMAIL.COM</t>
+          <t>TRILLISO_BET@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>17-02-2026 10:03:24</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>15-02-2026 12:36:33</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4765,27 +4765,27 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>17-02-2026 10:10:20</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>17-02-2026 10:08:56</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26220522423620004039</t>
+          <t>26220522365710003869</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -5089,12 +5089,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>343831</t>
+          <t>345379</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>87544</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5104,17 +5104,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JESSICA</t>
+          <t>EMMANUEL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>DE JESUS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5124,35 +5124,39 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2217041181</t>
+          <t>5581003622</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CALLE MAGNOLIA 242</t>
+          <t>C AGUSTIN DE ITURBIDE 228</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>14-12-1998</t>
+          <t>17-12-1995</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>JESSICAHERNANDEZVAZQUEZ@OUTLOOK.COM</t>
+          <t>EMMANUELDJF17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:19</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>20-02-2026 18:06:05</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5170,27 +5174,27 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:20</t>
+          <t>20-02-2026 18:17:25</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:20</t>
+          <t>20-02-2026 18:16:44</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5200,7 +5204,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26220522365380003866</t>
+          <t>26220522533780004518</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5212,24 +5216,24 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342287</t>
+          <t>343831</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5239,17 +5243,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IRVING DONNOVAN</t>
+          <t>JESSICA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5259,32 +5263,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5564343538</t>
+          <t>2217041181</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C PERA SAN MARCOS</t>
+          <t>CALLE MAGNOLIA 242</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>06-09-1992</t>
+          <t>14-12-1998</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>DONNOVANBR@OUTLOOK.COM</t>
+          <t>JESSICAHERNANDEZVAZQUEZ@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>09-02-2026 16:52:02</t>
+          <t>15-02-2026 12:21:19</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5305,27 +5309,27 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>12-02-2026 18:07:17</t>
+          <t>15-02-2026 12:21:20</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>12-02-2026 18:06:58</t>
+          <t>15-02-2026 12:21:20</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5335,14 +5339,10 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26220522301550003706</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522365380003866</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
@@ -5363,12 +5363,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>344676</t>
+          <t>346013</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22493</t>
+          <t>88178</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JESSICA BERENICE</t>
+          <t>MICHELLE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2219009457</t>
+          <t>5619228106</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C CIPRECES MZ 3</t>
+          <t>C ORIENTE 32 MZ 25</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5413,52 +5413,52 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>02-04-1995</t>
+          <t>30-07-2003</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>JEBER18@YAHOO.COM.MX</t>
+          <t>MICHELLE.GOMZ2303@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>17-02-2026 19:05:24</t>
+          <t>23-02-2026 19:02:28</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>17-02-2026 19:14:49</t>
+          <t>23-02-2026 19:08:04</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>17-02-2026 19:14:20</t>
+          <t>23-02-2026 19:07:28</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5478,14 +5478,14 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26220522443720004140</t>
+          <t>26220522598490004729</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5502,12 +5502,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>344233</t>
+          <t>344433</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22050</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5517,17 +5517,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>IRIS MONTSERRAT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEREZ </t>
+          <t>CHAVARIN</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5537,12 +5537,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5611753742</t>
+          <t>5564692994</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRACC LOS HEROES </t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5552,17 +5552,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>07-08-1998</t>
+          <t>29-08-1994</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CASTROMARIAFERNANDA57@GMAIL.COM</t>
+          <t>MONTSERRAT_94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>16-02-2026 17:43:53</t>
+          <t>17-02-2026 10:03:24</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5587,17 +5587,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>16-02-2026 18:16:35</t>
+          <t>17-02-2026 10:10:20</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>16-02-2026 18:15:46</t>
+          <t>17-02-2026 10:08:56</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26220522403640003978</t>
+          <t>26220522423620004039</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5629,24 +5629,24 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>345379</t>
+          <t>344233</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>87544</t>
+          <t>22050</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EMMANUEL</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DE JESUS</t>
+          <t xml:space="preserve">JEREZ </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5676,32 +5676,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5581003622</t>
+          <t>5611753742</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>C AGUSTIN DE ITURBIDE 228</t>
+          <t xml:space="preserve">FRACC LOS HEROES </t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>17-12-1995</t>
+          <t>07-08-1998</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>EMMANUELDJF17@GMAIL.COM</t>
+          <t>CASTROMARIAFERNANDA57@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>20-02-2026 18:06:05</t>
+          <t>16-02-2026 17:43:53</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5726,17 +5726,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>20-02-2026 18:17:25</t>
+          <t>16-02-2026 18:16:35</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>20-02-2026 18:16:44</t>
+          <t>16-02-2026 18:15:46</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26220522533780004518</t>
+          <t>26220522403640003978</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5780,12 +5780,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>343824</t>
+          <t>344432</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5795,17 +5795,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MARISOL</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5815,35 +5815,39 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5531971979</t>
+          <t>5515226715</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COL CENTRO CDMX</t>
+          <t>ALFREDIO</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>02-03-1973</t>
+          <t>23-08-1991</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>MAPGUE2@GMAIL.COM</t>
+          <t>LIC.ALFREDO.91@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>15-02-2026 12:05:48</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>17-02-2026 09:59:28</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5861,17 +5865,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>15-02-2026 12:25:35</t>
+          <t>17-02-2026 10:14:17</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>15-02-2026 12:18:06</t>
+          <t>17-02-2026 10:13:36</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5891,7 +5895,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26220522365480003867</t>
+          <t>26220522423710004040</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5915,12 +5919,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>341922</t>
+          <t>343824</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>21641</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5930,17 +5934,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>YANNEVY ARIADNE</t>
+          <t>MARISOL</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5950,12 +5954,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5580261394</t>
+          <t>5531971979</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>HEROES</t>
+          <t>COL CENTRO CDMX</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5965,17 +5969,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>25-11-1994</t>
+          <t>02-03-1973</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>YENNEVY@GMAIL.COM</t>
+          <t>MAPGUE2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>08-02-2026 11:53:18</t>
+          <t>15-02-2026 12:05:48</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5996,17 +6000,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>08-02-2026 11:58:57</t>
+          <t>15-02-2026 12:25:35</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>08-02-2026 11:57:36</t>
+          <t>15-02-2026 12:18:06</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6016,7 +6020,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6026,7 +6030,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26220522171210003218</t>
+          <t>26220522365480003867</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -6038,24 +6042,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>David Guillermo  Fuentes Carrillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344432</t>
+          <t>344895</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>22712</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6065,17 +6069,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>ALMA ROSA BASILISA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6085,32 +6089,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5515226715</t>
+          <t>5611775850</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ALFREDIO</t>
+          <t>C JOSE MARIA MORELOS</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>23-08-1991</t>
+          <t>02-04-1963</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>LIC.ALFREDO.91@GMAIL.COM</t>
+          <t>ALMAROSACASTRO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>17-02-2026 09:59:28</t>
+          <t>18-02-2026 17:26:28</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6135,17 +6139,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>17-02-2026 10:14:17</t>
+          <t>18-02-2026 17:48:07</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>17-02-2026 10:13:36</t>
+          <t>18-02-2026 17:46:56</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6155,7 +6159,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -6165,7 +6169,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26220522423710004040</t>
+          <t>26220522470370004248</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6189,12 +6193,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>344895</t>
+          <t>344934</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22712</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6204,17 +6208,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ALMA ROSA BASILISA</t>
+          <t xml:space="preserve">YENNIFER </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6224,12 +6228,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5611775850</t>
+          <t>5512992481</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>C JOSE MARIA MORELOS</t>
+          <t>TULTITLAM MEX</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6239,17 +6243,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>02-04-1963</t>
+          <t>17-09-1993</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ALMAROSACASTRO@HOTMAIL.COM</t>
+          <t>YLOPEZFLORES17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>18-02-2026 17:26:28</t>
+          <t>18-02-2026 18:57:05</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6274,7 +6278,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>18-02-2026 17:48:07</t>
+          <t>18-02-2026 19:01:48</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -6284,7 +6288,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>18-02-2026 17:46:56</t>
+          <t>18-02-2026 19:00:57</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6294,7 +6298,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6304,7 +6308,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26220522470370004248</t>
+          <t>26220522473980004280</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6328,12 +6332,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>345233</t>
+          <t>341922</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>87398</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6343,17 +6347,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONEL YUARI </t>
+          <t>YANNEVY ARIADNE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANRIQUEZ </t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6363,39 +6367,35 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5521514699</t>
+          <t>5580261394</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZOL AGRICOLA ORIENTAL </t>
+          <t>HEROES</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>27-06-2004</t>
+          <t>25-11-1994</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>STARCICI@GMAIL.COM</t>
+          <t>YENNEVY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>20-02-2026 09:01:39</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>08-02-2026 11:53:18</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6413,17 +6413,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>20-02-2026 09:08:59</t>
+          <t>08-02-2026 11:58:57</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>20-02-2026 09:08:21</t>
+          <t>08-02-2026 11:57:36</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26220522522290004459</t>
+          <t>26220522171210003218</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
@@ -6455,24 +6455,24 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>344934</t>
+          <t>342048</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22751</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6482,17 +6482,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">YENNIFER </t>
+          <t>DULCE IVONNE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>ZARCO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5512992481</t>
+          <t>5519303247</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TULTITLAM MEX</t>
+          <t xml:space="preserve">C. LA CIGARRA COL. ESPERANZA </t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6517,24 +6517,20 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>17-09-1993</t>
+          <t>01-08-1991</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>YLOPEZFLORES17@GMAIL.COM</t>
+          <t>DULCEIVONNETORRESZARCO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>18-02-2026 18:57:05</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 08:22:24</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6552,17 +6548,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>18-02-2026 19:01:48</t>
+          <t>09-02-2026 08:34:47</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>18-02-2026 19:00:57</t>
+          <t>09-02-2026 08:34:00</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6572,7 +6568,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6582,7 +6578,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26220522473980004280</t>
+          <t>26220522185040003259</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6606,12 +6602,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>345129</t>
+          <t>345233</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>87294</t>
+          <t>87398</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6621,17 +6617,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KIMBERLY ABIGAIL</t>
+          <t xml:space="preserve">LEONEL YUARI </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t xml:space="preserve">MANRIQUEZ </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6641,32 +6637,32 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5619291534</t>
+          <t>5521514699</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>U HAB 4 VIENTOS</t>
+          <t xml:space="preserve">ZOL AGRICOLA ORIENTAL </t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>20-08-2007</t>
+          <t>27-06-2004</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>KKKIMBERLYY2@GMAIL.COM</t>
+          <t>STARCICI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>19-02-2026 16:52:09</t>
+          <t>20-02-2026 09:01:39</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6691,17 +6687,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>19-02-2026 17:04:47</t>
+          <t>20-02-2026 09:08:59</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>19-02-2026 17:03:32</t>
+          <t>20-02-2026 09:08:21</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6711,7 +6707,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6721,7 +6717,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26220522500320004391</t>
+          <t>26220522522290004459</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
@@ -6745,12 +6741,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>345130</t>
+          <t>342287</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>87295</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6760,17 +6756,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MARISELA</t>
+          <t>IRVING DONNOVAN</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t xml:space="preserve">BRAVO </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6780,39 +6776,35 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5538014107</t>
+          <t>5564343538</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>U HAB 4 VIENTOS</t>
+          <t>C PERA SAN MARCOS</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>02-12-1975</t>
+          <t>06-09-1992</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>KIMBERLY89@GMAIL.COM</t>
+          <t>DONNOVANBR@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>19-02-2026 16:54:23</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 16:52:02</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6830,17 +6822,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>19-02-2026 17:08:32</t>
+          <t>12-02-2026 18:07:17</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>19-02-2026 17:08:01</t>
+          <t>12-02-2026 18:06:58</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6850,7 +6842,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6860,10 +6852,14 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26220522500550004392</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr"/>
+          <t>26220522301550003706</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
@@ -6884,12 +6880,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>342048</t>
+          <t>345129</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>87294</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6899,17 +6895,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DULCE IVONNE</t>
+          <t>KIMBERLY ABIGAIL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ZARCO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6919,12 +6915,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5519303247</t>
+          <t>5619291534</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. LA CIGARRA COL. ESPERANZA </t>
+          <t>U HAB 4 VIENTOS</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6934,20 +6930,24 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>01-08-1991</t>
+          <t>20-08-2007</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>DULCEIVONNETORRESZARCO@GMAIL.COM</t>
+          <t>KKKIMBERLYY2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>09-02-2026 08:22:24</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>19-02-2026 16:52:09</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6965,17 +6965,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>09-02-2026 08:34:47</t>
+          <t>19-02-2026 17:04:47</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>09-02-2026 08:34:00</t>
+          <t>19-02-2026 17:03:32</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26220522185040003259</t>
+          <t>26220522500320004391</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -7019,12 +7019,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>344900</t>
+          <t>345130</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>87295</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7034,17 +7034,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ADRIAN BERENICE</t>
+          <t>MARISELA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7054,10 +7054,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>5540961768</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>5538014107</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>U HAB 4 VIENTOS</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7065,20 +7069,24 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>05-03-1999</t>
+          <t>02-12-1975</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>BEREADRY99@HOTMAIL.COM</t>
+          <t>KIMBERLY89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>18-02-2026 17:32:28</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>19-02-2026 16:54:23</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7086,7 +7094,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -7096,17 +7104,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>18-02-2026 17:43:39</t>
+          <t>19-02-2026 17:08:32</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>18-02-2026 17:43:01</t>
+          <t>19-02-2026 17:08:01</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7126,7 +7134,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26220522470070004245</t>
+          <t>26220522500550004392</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -7138,24 +7146,24 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>345055</t>
+          <t>344900</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>87220</t>
+          <t>22717</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7165,17 +7173,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>ADRIAN BERENICE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TALAVERA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PANIAGUA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7185,67 +7193,59 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5540308509</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>C SUR 171</t>
-        </is>
-      </c>
+          <t>5540961768</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>20-02-1963</t>
+          <t>05-03-1999</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ANLGELTALAVERAP63@GMAIL.COM</t>
+          <t>BEREADRY99@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>19-02-2026 13:00:23</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>18-02-2026 17:32:28</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>19-02-2026 13:17:48</t>
+          <t>18-02-2026 17:43:39</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>19-02-2026 13:16:38</t>
+          <t>18-02-2026 17:43:01</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7265,36 +7265,36 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26220522493820004335</t>
+          <t>26220522470070004245</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>345063</t>
+          <t>345055</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>87228</t>
+          <t>87220</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MARIA DE LA LUZ</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>TALAVERA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>PANIAGUA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5561186386</t>
+          <t>5540308509</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -7334,22 +7334,22 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>15-04-1963</t>
+          <t>20-02-1963</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>LG.JACK63@GMAIL.COM</t>
+          <t>ANLGELTALAVERAP63@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>19-02-2026 13:21:09</t>
+          <t>19-02-2026 13:00:23</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>19-02-2026 13:30:22</t>
+          <t>19-02-2026 13:17:48</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>19-02-2026 13:29:04</t>
+          <t>19-02-2026 13:16:38</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26220522494100004341</t>
+          <t>26220522493820004335</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
@@ -7428,12 +7428,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>342192</t>
+          <t>345063</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20010</t>
+          <t>87228</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JESUS ZAID</t>
+          <t>MARIA DE LA LUZ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>BORREGO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7463,63 +7463,67 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4055882651</t>
+          <t>5561186386</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">C MELCHOR OCAMPO S/N COL. LA ESPERANZA </t>
+          <t>C SUR 171</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>23-12-1999</t>
+          <t>15-04-1963</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>SAIDD.BST@GMAIL.COM</t>
+          <t>LG.JACK63@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>09-02-2026 14:52:50</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>19-02-2026 13:21:09</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>09-02-2026 15:06:28</t>
+          <t>19-02-2026 13:30:22</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>09-02-2026 15:05:32</t>
+          <t>19-02-2026 13:29:04</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7529,7 +7533,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -7539,36 +7543,36 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26220522194630003292</t>
+          <t>26220522494100004341</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>344931</t>
+          <t>342192</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7578,17 +7582,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ANDRES JESUS</t>
+          <t>JESUS ZAID</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>BORREGO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7598,12 +7602,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5537346724</t>
+          <t>4055882651</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MZ H EDIF 2B</t>
+          <t xml:space="preserve">C MELCHOR OCAMPO S/N COL. LA ESPERANZA </t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7613,24 +7617,20 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>10-11-1992</t>
+          <t>23-12-1999</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>RAZIEL_FO@HOTMAIL.COM</t>
+          <t>SAIDD.BST@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>18-02-2026 18:46:57</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 14:52:50</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7648,17 +7648,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>18-02-2026 18:54:43</t>
+          <t>09-02-2026 15:06:28</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>18-02-2026 18:52:58</t>
+          <t>09-02-2026 15:05:32</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26220522473750004279</t>
+          <t>26220522194630003292</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
@@ -7690,12 +7690,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -7837,12 +7837,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>343301</t>
+          <t>344931</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7852,17 +7852,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>ANDRES JESUS</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ESPEJEL</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>5516346350</t>
+          <t>5537346724</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
+          <t>MZ H EDIF 2B</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7887,20 +7887,24 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>06-07-1995</t>
+          <t>10-11-1992</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>DIEGOLUPUS@GMAIL.COM</t>
+          <t>RAZIEL_FO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>12-02-2026 16:04:34</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>18-02-2026 18:46:57</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7918,17 +7922,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>12-02-2026 16:26:22</t>
+          <t>18-02-2026 18:54:43</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>12-02-2026 16:25:47</t>
+          <t>18-02-2026 18:52:58</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7938,7 +7942,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7948,7 +7952,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26220522297530003689</t>
+          <t>26220522473750004279</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
@@ -7972,12 +7976,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>343505</t>
+          <t>345074</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>87239</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7987,17 +7991,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ALVARO O BRIAN</t>
+          <t>SANDRA ESTRELLA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>VALADEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BLANCA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8007,75 +8011,67 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>5591919598</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>AV NUEVO MEXICO 301</t>
-        </is>
-      </c>
+          <t>5545570437</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>12-09-1993</t>
+          <t>19-06-1974</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>POSEIDONBALA93@OUTLOOK.COM</t>
+          <t>GARCIA_SANDRA98@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>13-02-2026 14:50:25</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>19-02-2026 14:14:15</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>13-02-2026 14:59:34</t>
+          <t>23-02-2026 14:12:47</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>13-02-2026 14:59:07</t>
-        </is>
-      </c>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8083,14 +8079,22 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26220522321910003759</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
+          <t>26220522581980004643</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>DIANA MADRID ORTIZ</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -8107,12 +8111,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>343544</t>
+          <t>345977</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>88142</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8122,17 +8126,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LAURA AMAYRANI</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>PAYAN</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8142,75 +8146,63 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5546447212</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
-        </is>
-      </c>
+          <t>5586887467</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>13-03-2007</t>
+          <t>01-11-1978</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>LAUPRD25@GMAIL.COM</t>
+          <t>JUANCARLOSLARAPAYAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>13-02-2026 17:03:29</t>
+          <t>23-02-2026 18:23:19</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:38</t>
+          <t>23-02-2026 18:25:30</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>13-02-2026 17:18:02</t>
-        </is>
-      </c>
+          <t>23-03-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8218,24 +8210,24 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26220522326190003779</t>
+          <t>26220522595510004713</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -8385,12 +8377,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>343539</t>
+          <t>343301</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8400,17 +8392,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ROCIO</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JAIMEZ</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>ESPEJEL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8420,32 +8412,32 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5534063877</t>
+          <t>5516346350</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>C CUAUTZINGO MZA 34</t>
+          <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>12-01-1998</t>
+          <t>06-07-1995</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
+          <t>DIEGOLUPUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>13-02-2026 16:58:39</t>
+          <t>12-02-2026 16:04:34</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -8466,17 +8458,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>13-02-2026 17:12:37</t>
+          <t>12-02-2026 16:26:22</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>13-02-2026 17:10:18</t>
+          <t>12-02-2026 16:25:47</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8486,7 +8478,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -8496,7 +8488,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26220522325890003776</t>
+          <t>26220522297530003689</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
@@ -8508,24 +8500,24 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>344626</t>
+          <t>343505</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8535,17 +8527,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>IXCHEL YARELI</t>
+          <t>ALVARO O BRIAN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIN </t>
+          <t>VALADEZ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>BLANCA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8555,67 +8547,63 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5579912763</t>
+          <t>5591919598</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>C DZILAM MZ 814 LT 4</t>
+          <t>AV NUEVO MEXICO 301</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>31-01-1989</t>
+          <t>12-09-1993</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>IXCHELMARIN@OUTLOOK.COM</t>
+          <t>POSEIDONBALA93@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>17-02-2026 17:48:58</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 14:50:25</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>PLAN FAMILIAR RECURRENTE $999</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>17-02-2026 18:01:12</t>
+          <t>13-02-2026 14:59:34</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>17-02-2026 17:59:12</t>
+          <t>13-02-2026 14:59:07</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8635,36 +8623,36 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26220522439570004122</t>
+          <t>26220522321910003759</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>345338</t>
+          <t>343544</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>87503</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8674,17 +8662,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUADALUPE </t>
+          <t>LAURA AMAYRANI</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CARRANZA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8694,12 +8682,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5615722096</t>
+          <t>5546447212</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRACC HACIENDA DE LAS PALMAS III </t>
+          <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8709,24 +8697,20 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>03-09-1981</t>
+          <t>13-03-2007</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>GUADALUPECARRANZA2830@GMAIL.COM</t>
+          <t>LAUPRD25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>20-02-2026 16:38:08</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>13-02-2026 17:03:29</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8744,17 +8728,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>20-02-2026 16:51:02</t>
+          <t>13-02-2026 17:19:38</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>20-02-2026 16:49:11</t>
+          <t>13-02-2026 17:18:02</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8764,7 +8748,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -8774,7 +8758,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26220522530660004497</t>
+          <t>26220522326190003779</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
@@ -8798,12 +8782,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>344940</t>
+          <t>344626</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8813,17 +8797,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRANDON </t>
+          <t>IXCHEL YARELI</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t xml:space="preserve">MARIN </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MONTESINOS</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8833,67 +8817,67 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5613578379</t>
+          <t>5579912763</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>C CIPRECES MZA 3</t>
+          <t>C DZILAM MZ 814 LT 4</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>08-03-1994</t>
+          <t>31-01-1989</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>BRANDON.FAMDA@GMAIL.COM</t>
+          <t>IXCHELMARIN@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>18-02-2026 19:14:37</t>
+          <t>17-02-2026 17:48:58</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIAR RECURRENTE $999</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>18-02-2026 19:17:54</t>
+          <t>17-02-2026 18:01:12</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>18-02-2026 19:17:35</t>
+          <t>17-02-2026 17:59:12</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8913,22 +8897,574 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26220522474720004282</t>
+          <t>26220522439570004122</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
+          <t>Luis Antonio  Chaparro Alonso</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>343539</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>21356</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ROCIO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>JAIMEZ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>5534063877</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>C CUAUTZINGO MZA 34</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>12-01-1998</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:58:39</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:12:37</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:10:18</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26220522325890003776</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Luis Antonio  Chaparro Alonso</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>345338</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>87503</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUADALUPE </t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CARRANZA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>5615722096</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRACC HACIENDA DE LAS PALMAS III </t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>03-09-1981</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>GUADALUPECARRANZA2830@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>20-02-2026 16:38:08</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>20-02-2026 16:51:02</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>20-02-2026 16:49:11</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26220522530660004497</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Luis Antonio  Chaparro Alonso</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>344940</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>22757</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRANDON </t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DELGADO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>MONTESINOS</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>5613578379</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>C CIPRECES MZA 3</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>08-03-1994</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>BRANDON.FAMDA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:14:37</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:17:54</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:17:35</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26220522474720004282</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>346020</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>88185</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>JOSE RODOLFO</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>5574468176</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>COL FRATERNIDAD ANTORCHISTA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>06-10-1998</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>ALCANTARAEZEQUIEL380@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:10:57</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:13:59</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:13:31</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26220522598880004730</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,7 +772,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PRINCESS_CHAIN@HOTMAIL.COM</t>
+          <t>PRINCESS_CHARIN@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -840,24 +840,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>339258</t>
+          <t>338953</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PAOLA</t>
+          <t xml:space="preserve">FABIOLA </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ARTEAGA</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>PLATA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5512421794</t>
+          <t>5582314058</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AV. JOSE MARIA MARTINEZ MZA 24 LY 19</t>
+          <t>CDA DE JAZMINES MZ 20 LT 10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>07-04-1992</t>
+          <t>11-04-1991</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>LOOPZY_9797@HOTMAIL.COM</t>
+          <t>FALIZEE0204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>30-01-2026 09:21:25</t>
+          <t>29-01-2026 08:24:12</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -923,7 +923,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-02-2026 11:50:19</t>
+          <t>01-02-2026 09:51:51</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>30-01-2026 09:36:03</t>
+          <t>01-02-2026 09:51:00</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -963,11 +963,19 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26220522007760002643</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26220521988250002583</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>499</t>
@@ -975,24 +983,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>338953</t>
+          <t>332845</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1002,17 +1010,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FABIOLA </t>
+          <t>MIRSHA ASERET</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PLATA</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1022,12 +1030,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5582314058</t>
+          <t>5574210862</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CDA DE JAZMINES MZ 20 LT 10</t>
+          <t>C IGNACIO ZARAGOZA MZ 25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1037,17 +1045,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>11-04-1991</t>
+          <t>11-02-2000</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>FALIZEE004@GMAIL.COM</t>
+          <t>MIRSHA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>29-01-2026 08:24:12</t>
+          <t>07-01-2026 14:07:05</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1058,7 +1066,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1068,17 +1076,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>01-02-2026 09:51:51</t>
+          <t>13-02-2026 18:00:19</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>01-02-2026 09:51:00</t>
+          <t>13-02-2026 18:00:00</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1088,7 +1096,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1098,19 +1106,11 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26220521988250002583</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522327410003797</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>499</t>
@@ -1130,12 +1130,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>332845</t>
+          <t>339258</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MIRSHA ASERET</t>
+          <t>PAOLA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>ARTEAGA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5574210862</t>
+          <t>5512421794</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C IGNACIO ZARAGOZA MZ 25</t>
+          <t>AV. JOSE MARIA MARTINEZ MZA 24 LY 19</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>11-02-2000</t>
+          <t>07-04-1992</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MIRSHA@GMAIL.COM</t>
+          <t>LOOPZY_9797@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>07-01-2026 14:07:05</t>
+          <t>30-01-2026 09:21:25</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>13-02-2026 18:00:19</t>
+          <t>02-02-2026 11:50:19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>13-02-2026 18:00:00</t>
+          <t>30-01-2026 09:36:03</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26220522327410003797</t>
+          <t>26220522007760002643</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1400,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>341099</t>
+          <t>341101</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AXEL KALID</t>
+          <t>CHRISTIAN OWEN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5635122950</t>
+          <t>5643127118</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>23-07-2004</t>
+          <t>18-06-2011</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>GUERREROAXEL190@GMAIL.COM</t>
+          <t>CHRISTIAN09MENDEZ1234@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>04-02-2026 17:15:27</t>
+          <t>04-02-2026 17:18:13</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>04-02-2026 17:26:19</t>
+          <t>04-02-2026 17:31:39</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>04-02-2026 17:25:23</t>
+          <t>04-02-2026 17:30:29</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26220522082390002907</t>
+          <t>26220522082650002911</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>GONZALEZCRUZEDILBERTO@GMAIL.COM</t>
+          <t>GONZALEZCRUZEDILBERTO660@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1809,12 +1809,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>341101</t>
+          <t>342375</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1824,17 +1824,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CHRISTIAN OWEN</t>
+          <t xml:space="preserve">DIANA AMELIA </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>SIERNA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1844,32 +1844,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5643127118</t>
+          <t>5532857495</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C CATEDRAL METROPOLITANA 204</t>
+          <t>AV DEL POPO MZA 56</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>18-06-2011</t>
+          <t>10-08-1975</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CHRISTIAN09MENDEZ1234@GMAIL.COM</t>
+          <t>DIANAALINE10@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>04-02-2026 17:18:13</t>
+          <t>09-02-2026 18:11:48</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1890,17 +1890,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>04-02-2026 17:31:39</t>
+          <t>12-02-2026 18:14:46</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>04-02-2026 17:30:29</t>
+          <t>12-02-2026 18:13:56</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1920,10 +1920,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26220522082650002911</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
+          <t>26220522301970003709</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1932,24 +1936,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>342375</t>
+          <t>341951</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1959,17 +1963,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA AMELIA </t>
+          <t xml:space="preserve">ADRIANA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SIERNA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1979,12 +1983,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5532857495</t>
+          <t>5641136687</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AV DEL POPO MZA 56</t>
+          <t>RANCHO</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1994,17 +1998,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>10-08-1975</t>
+          <t>05-03-1965</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>DIANAALINE10@HOTMAIL.COM</t>
+          <t>ADRIANA.CERVANT.AL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>09-02-2026 18:11:48</t>
+          <t>08-02-2026 13:24:14</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2025,17 +2029,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>12-02-2026 18:14:46</t>
+          <t>08-02-2026 13:32:56</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>12-02-2026 18:13:56</t>
+          <t>08-02-2026 13:32:13</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2055,14 +2059,10 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26220522301970003709</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522172520003225</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2071,24 +2071,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>341894</t>
+          <t>342227</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2098,17 +2098,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">JONATHAN </t>
+          <t>YORDI JESUS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">URBAN </t>
+          <t>PADRON</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5574445964</t>
+          <t>5613711355</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LOTOS</t>
+          <t>CDA HACIENDA DE JALPA MZ 19 LT 115C</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>06-12-1990</t>
+          <t>23-10-2002</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>SOLDADO.DE.DIOS@HOTMAIL.COM</t>
+          <t>TREYOI.1023.ROCHA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>08-02-2026 10:05:09</t>
+          <t>09-02-2026 15:55:59</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2164,17 +2164,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>08-02-2026 10:07:34</t>
+          <t>09-02-2026 16:06:40</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>08-02-2026 10:07:05</t>
+          <t>09-02-2026 16:06:13</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26220522169210003211</t>
+          <t>26220522197030003304</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2206,24 +2206,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340216</t>
+          <t>339592</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AXEL ZADKYEL</t>
+          <t>MARIA GUADALUPE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>LANDIN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2253,32 +2253,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5591647693</t>
+          <t>5588006100</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SAN BUENAVENTURA</t>
+          <t>EL CAPULIN</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>24-05-2006</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>AXELVALDEZ099@GMAL.COM</t>
+          <t>LANDINGUADALUPE95@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-02-2026 15:29:08</t>
+          <t>31-01-2026 09:45:22</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-02-2026 15:45:59</t>
+          <t>09-02-2026 14:59:33</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-02-2026 15:34:51</t>
+          <t>09-02-2026 14:59:02</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2329,10 +2329,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26220522015050002682</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+          <t>26220522194280003290</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2341,24 +2345,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>342097</t>
+          <t>342184</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2368,17 +2372,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALICIA </t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUCEDO </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>VICENTE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2388,39 +2392,35 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5522530023</t>
+          <t>5537110647</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CDA MAGDALENA SN IXTAPALUCA</t>
+          <t>COL SANTA CRUZ TLAPACOYA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>23-03-1966</t>
+          <t>25-07-2017</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>SAUCEDOGALICIAALICIA32@GMAIL.COM</t>
+          <t>KARINAFLORESVICENTE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>09-02-2026 10:35:09</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 14:42:03</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2438,17 +2438,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>18-02-2026 15:06:39</t>
+          <t>09-02-2026 14:52:27</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>18-02-2026 15:05:44</t>
+          <t>09-02-2026 14:50:55</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2468,19 +2468,11 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26220522463670004215</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522193980003288</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>499</t>
@@ -2488,24 +2480,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>342227</t>
+          <t>340216</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2515,17 +2507,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>YORDI JESUS</t>
+          <t>AXEL ZADKYEL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PADRON</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2535,12 +2527,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5613711355</t>
+          <t>5591647693</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CDA HACIENDA DE JALPA MZ 19 LT 115C</t>
+          <t>SAN BUENAVENTURA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2550,17 +2542,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>23-10-2002</t>
+          <t>24-05-2006</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>TREYOI.1023.ROCHA@GMAIL.COM</t>
+          <t>AXELVALDEZ099@GMAL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>09-02-2026 15:55:59</t>
+          <t>02-02-2026 15:29:08</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2581,17 +2573,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>09-02-2026 16:06:40</t>
+          <t>02-02-2026 15:45:59</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>09-02-2026 16:06:13</t>
+          <t>02-02-2026 15:34:51</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2601,7 +2593,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2611,7 +2603,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26220522197030003304</t>
+          <t>26220522015050002682</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2623,24 +2615,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>339592</t>
+          <t>340315</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2650,17 +2642,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MARIA GUADALUPE</t>
+          <t>MAYRA JAZMIN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>KURY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LANDIN</t>
+          <t>AVILES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2670,12 +2662,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5588006100</t>
+          <t>5561248221</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>EL CAPULIN</t>
+          <t>IXTAP</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2685,17 +2677,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>13-08-1980</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>LANDINGUADALUPE95@GMAIL.COM</t>
+          <t>MAYRACGT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>31-01-2026 09:45:22</t>
+          <t>02-02-2026 17:44:11</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2706,7 +2698,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2716,17 +2708,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>09-02-2026 14:59:33</t>
+          <t>03-02-2026 07:27:24</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>09-02-2026 14:59:02</t>
+          <t>03-02-2026 07:26:21</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2746,7 +2738,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26220522194280003290</t>
+          <t>26220522032080002726</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2762,24 +2754,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340315</t>
+          <t>340512</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2789,17 +2781,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MAYRA JAZMIN</t>
+          <t>ROSA LIDIA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KURY</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AVILES</t>
+          <t>ANZALDO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2809,12 +2801,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5561248221</t>
+          <t>5521196367</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IXTAP</t>
+          <t>IXTA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2824,17 +2816,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>13-08-1980</t>
+          <t>14-04-1993</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MAYRACGT@GMAIL.COM</t>
+          <t>ROSYN_N@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-02-2026 17:44:11</t>
+          <t>03-02-2026 10:51:49</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2845,7 +2837,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2855,7 +2847,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-02-2026 07:27:24</t>
+          <t>03-02-2026 10:57:53</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2865,7 +2857,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>03-02-2026 07:26:21</t>
+          <t>03-02-2026 10:57:16</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2885,14 +2877,10 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26220522032080002726</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522036640002738</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2913,12 +2901,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>340512</t>
+          <t>338952</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2928,17 +2916,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ROSA LIDIA</t>
+          <t xml:space="preserve">ANABEL </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ANZALDO</t>
+          <t>PLATA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2948,12 +2936,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5521196367</t>
+          <t>5543867324</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IXTA</t>
+          <t>CDA DE JAZMINEZ MZ 20 LT 10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2963,17 +2951,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>14-04-1993</t>
+          <t>22-10-1998</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ROSYN_N@HOTMAIL.COM</t>
+          <t>MAPA_220@HOTMAIL.ES</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-02-2026 10:51:49</t>
+          <t>29-01-2026 08:22:19</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2984,7 +2972,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2994,17 +2982,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-02-2026 10:57:53</t>
+          <t>01-02-2026 10:00:34</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>03-02-2026 10:57:16</t>
+          <t>01-02-2026 09:59:59</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3024,11 +3012,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26220522036640002738</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>26220521988460002587</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>499</t>
@@ -3036,24 +3032,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341951</t>
+          <t>342380</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3063,17 +3059,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIANA </t>
+          <t>DIANA ALINE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3083,12 +3079,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5641136687</t>
+          <t>5625435058</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>RANCHO</t>
+          <t xml:space="preserve">C CASTILLO DE CHAPULTEPEC </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3098,17 +3094,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>05-03-1965</t>
+          <t>22-12-1996</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ADRIANA.CERVANT.AL@GMAIL.COM</t>
+          <t>DIGTZ15@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>08-02-2026 13:24:14</t>
+          <t>09-02-2026 18:16:13</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3129,17 +3125,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>08-02-2026 13:32:56</t>
+          <t>12-02-2026 18:19:45</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>08-02-2026 13:32:13</t>
+          <t>12-02-2026 18:19:19</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3159,10 +3155,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26220522172520003225</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
+          <t>26220522302230003710</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
@@ -3171,24 +3171,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>338952</t>
+          <t>342750</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3198,17 +3198,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANABEL </t>
+          <t>MANUEL RAFAEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PLATA</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3218,32 +3218,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5543867324</t>
+          <t>5574265455</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CDA DE JAZMINEZ MZ 20 LT 10</t>
+          <t>C CEBADA MZ 6 LT 3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>22-10-1998</t>
+          <t>23-11-1999</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MAPA_220@HOTMAIL.ES</t>
+          <t>MANUEL_LVNA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>29-01-2026 08:22:19</t>
+          <t>10-02-2026 17:23:26</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3264,17 +3264,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>01-02-2026 10:00:34</t>
+          <t>10-02-2026 17:27:27</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>01-02-2026 09:59:59</t>
+          <t>10-02-2026 17:26:23</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3294,19 +3294,11 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26220521988460002587</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522239800003484</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
           <t>499</t>
@@ -3461,12 +3453,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342290</t>
+          <t>340960</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>18778</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3476,17 +3468,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ADRIANA ITZEL</t>
+          <t>LUIS ANGEL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3496,39 +3488,35 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5510440090</t>
+          <t>5669156876</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C VILLAHERMOSA MZA 47</t>
+          <t>C TONATICO 197</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>14-08-1994</t>
+          <t>19-02-1993</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ADRIANANAVA149@GMAIL.COM</t>
+          <t>BUICKGOLIFE856@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-02-2026 16:53:59</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>04-02-2026 12:16:09</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3546,17 +3534,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:20</t>
+          <t>04-02-2026 12:24:18</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>18-02-2026 18:13:49</t>
+          <t>04-02-2026 12:23:46</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3566,7 +3554,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3576,14 +3564,10 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26220522471810004257</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522073370002861</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3592,24 +3576,24 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342184</t>
+          <t>341357</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3619,17 +3603,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>DAMIAN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VICENTE</t>
+          <t xml:space="preserve">QUINTERO </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3639,14 +3623,10 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5537110647</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>COL SANTA CRUZ TLAPACOYA</t>
-        </is>
-      </c>
+          <t>5634592607</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3654,60 +3634,56 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>25-07-2017</t>
+          <t>25-11-2010</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>KARINAFLORESVICENTE@GMAIL.COM</t>
+          <t>DENI.QUINTERO2010@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>09-02-2026 14:42:03</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>05-02-2026 16:04:32</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>09-02-2026 14:52:27</t>
+          <t>05-02-2026 16:09:19</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>09-02-2026 14:50:55</t>
-        </is>
-      </c>
+          <t>05-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3715,14 +3691,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26220522193980003288</t>
+          <t>26220522109710003012</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3739,12 +3715,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342750</t>
+          <t>344676</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3754,17 +3730,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MANUEL RAFAEL</t>
+          <t>JESSICA BERENICE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3774,35 +3750,39 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5574265455</t>
+          <t>2219009457</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>C CEBADA MZ 6 LT 3</t>
+          <t>C CIPRECES MZ 3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>23-11-1999</t>
+          <t>02-04-1995</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>MANUEL_LVNA@HOTMAIL.COM</t>
+          <t>JEBER18@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10-02-2026 17:23:26</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>17-02-2026 19:05:24</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3820,17 +3800,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10-02-2026 17:27:27</t>
+          <t>17-02-2026 19:14:49</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10-02-2026 17:26:23</t>
+          <t>17-02-2026 19:14:20</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3840,7 +3820,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3850,7 +3830,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26220522239800003484</t>
+          <t>26220522443720004140</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3862,7 +3842,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4009,12 +3989,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342380</t>
+          <t>341889</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4024,17 +4004,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DIANA ALINE</t>
+          <t>LUCIA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4044,12 +4024,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5625435058</t>
+          <t>5574445968</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">C CASTILLO DE CHAPULTEPEC </t>
+          <t>LOTOS</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4059,17 +4039,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>22-12-1996</t>
+          <t>06-03-1990</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>DIGTZ15@GMAIL.COM</t>
+          <t>LUCYCOSA06039@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>09-02-2026 18:16:13</t>
+          <t>08-02-2026 09:58:42</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4090,17 +4070,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>12-02-2026 18:19:45</t>
+          <t>08-02-2026 10:02:56</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>12-02-2026 18:19:19</t>
+          <t>08-02-2026 10:02:01</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4120,14 +4100,10 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26220522302230003710</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522169080003210</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
@@ -4148,12 +4124,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>340960</t>
+          <t>341099</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4163,17 +4139,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LUIS ANGEL</t>
+          <t>AXEL KALID</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4183,12 +4159,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5669156876</t>
+          <t>5635122950</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C TONATICO 197</t>
+          <t>C CATEDRAL METROPOLITANA 204</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4198,17 +4174,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19-02-1993</t>
+          <t>23-07-2004</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>BUICKGOLIFE856@GMAIL.COM</t>
+          <t>GUERREROAXEL190@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>04-02-2026 12:16:09</t>
+          <t>04-02-2026 17:15:27</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4229,7 +4205,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>04-02-2026 12:24:18</t>
+          <t>04-02-2026 17:26:19</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4239,7 +4215,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>04-02-2026 12:23:46</t>
+          <t>04-02-2026 17:25:23</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4249,7 +4225,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4259,7 +4235,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26220522073370002861</t>
+          <t>26220522082390002907</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4271,7 +4247,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4283,12 +4259,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>341357</t>
+          <t>341952</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4298,17 +4274,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DAMIAN</t>
+          <t>RAMON</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTERO </t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4318,10 +4294,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5634592607</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>5520734799</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>RANCHOO</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4329,56 +4309,60 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>25-11-2010</t>
+          <t>31-08-1964</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>DENI.QUINTERO2010@GMAIL.COM</t>
+          <t>MONN.64KAISER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>05-02-2026 16:04:32</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>08-02-2026 13:27:30</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>05-02-2026 16:09:19</t>
+          <t>08-02-2026 13:36:45</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>05-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>08-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>08-02-2026 13:36:11</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4386,36 +4370,36 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26220522109710003012</t>
+          <t>26220522172570003226</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>344676</t>
+          <t>345379</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>22493</t>
+          <t>87544</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4425,17 +4409,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>JESSICA BERENICE</t>
+          <t>EMMANUEL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>DE JESUS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4445,32 +4429,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2219009457</t>
+          <t>5581003622</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C CIPRECES MZ 3</t>
+          <t>C AGUSTIN DE ITURBIDE 228</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>02-04-1995</t>
+          <t>17-12-1995</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>JEBER18@YAHOO.COM.MX</t>
+          <t>EMMANUELDJF17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>17-02-2026 19:05:24</t>
+          <t>20-02-2026 18:06:05</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4495,17 +4479,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>17-02-2026 19:14:49</t>
+          <t>20-02-2026 18:17:25</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>17-02-2026 19:14:20</t>
+          <t>20-02-2026 18:16:44</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4515,7 +4499,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4525,7 +4509,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26220522443720004140</t>
+          <t>26220522533780004518</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4537,24 +4521,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>343503</t>
+          <t>341894</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>19712</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4564,17 +4548,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DIANA VIANEY</t>
+          <t xml:space="preserve">JONATHAN </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARREON </t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>YAÑEZ</t>
+          <t xml:space="preserve">URBAN </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4584,32 +4568,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5614816775</t>
+          <t>5574445964</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C TEPOYAN 5</t>
+          <t>LOTOS</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>16-10-1986</t>
+          <t>06-12-1990</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>DIANACARREON995@GMAIL.COM</t>
+          <t>SOLDADO.DE.DIOS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>13-02-2026 14:48:21</t>
+          <t>08-02-2026 10:05:09</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4630,17 +4614,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>13-02-2026 15:06:00</t>
+          <t>08-02-2026 10:07:34</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>13-02-2026 15:05:03</t>
+          <t>08-02-2026 10:07:05</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4660,7 +4644,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26220522322030003760</t>
+          <t>26220522169210003211</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4684,12 +4668,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>343838</t>
+          <t>342097</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4699,17 +4683,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t xml:space="preserve">ALICIA </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORAN </t>
+          <t xml:space="preserve">SAUCEDO </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4719,35 +4703,39 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2206073345</t>
+          <t>5522530023</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CALLE MAGNOLIA 242</t>
+          <t>CDA MAGDALENA SN IXTAPALUCA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>26-02-1995</t>
+          <t>23-03-1966</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>TRILLISO_BET@HOTMAIL.COM</t>
+          <t>SAUCEDOGALICIAALICIA32@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>09-02-2026 10:35:09</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4765,27 +4753,27 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>18-02-2026 15:06:39</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>18-02-2026 15:05:44</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4795,11 +4783,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26220522365710003869</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+          <t>26220522463670004215</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>499</t>
@@ -4807,24 +4803,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>341889</t>
+          <t>343824</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>21641</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4834,17 +4830,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LUCIA</t>
+          <t>MARISOL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4854,12 +4850,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5574445968</t>
+          <t>5531971979</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LOTOS</t>
+          <t>COL CENTRO CDMX</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4869,17 +4865,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>06-03-1990</t>
+          <t>02-03-1973</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>LUCYCOSA06039@GMAIL.COM</t>
+          <t>MAPGUE2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>08-02-2026 09:58:42</t>
+          <t>15-02-2026 12:05:48</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4900,17 +4896,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>08-02-2026 10:02:56</t>
+          <t>15-02-2026 12:25:35</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>08-02-2026 10:02:01</t>
+          <t>15-02-2026 12:18:06</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4920,7 +4916,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4930,7 +4926,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26220522169080003210</t>
+          <t>26220522365480003867</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4954,12 +4950,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>341952</t>
+          <t>344433</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4969,12 +4965,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RAMON</t>
+          <t>IRIS MONTSERRAT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>CHAVARIN</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4989,35 +4985,39 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5520734799</t>
+          <t>5564692994</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>RANCHOO</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>31-08-1964</t>
+          <t>29-08-1994</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>MONN.64KAISER@GMAIL.COM</t>
+          <t>MONTSERRAT_94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>08-02-2026 13:27:30</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>17-02-2026 10:03:24</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5035,17 +5035,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>08-02-2026 13:36:45</t>
+          <t>17-02-2026 10:10:20</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>08-02-2026 13:36:11</t>
+          <t>17-02-2026 10:08:56</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26220522172570003226</t>
+          <t>26220522423620004039</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5077,24 +5077,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>345379</t>
+          <t>346013</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>87544</t>
+          <t>88178</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5104,17 +5104,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EMMANUEL</t>
+          <t>MICHELLE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DE JESUS</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5124,67 +5124,67 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5581003622</t>
+          <t>5619228106</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C AGUSTIN DE ITURBIDE 228</t>
+          <t>C ORIENTE 32 MZ 25</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>17-12-1995</t>
+          <t>30-07-2003</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>EMMANUELDJF17@GMAIL.COM</t>
+          <t>MICHELLE.GOMZ2303@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>20-02-2026 18:06:05</t>
+          <t>23-02-2026 19:02:28</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>20-02-2026 18:17:25</t>
+          <t>23-02-2026 19:08:04</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>20-02-2026 18:16:44</t>
+          <t>23-02-2026 19:07:28</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5204,19 +5204,19 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26220522533780004518</t>
+          <t>26220522598490004729</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5228,12 +5228,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>343831</t>
+          <t>342290</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5243,17 +5243,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JESSICA</t>
+          <t>ADRIANA ITZEL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2217041181</t>
+          <t>5510440090</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CALLE MAGNOLIA 242</t>
+          <t>C VILLAHERMOSA MZA 47</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5278,20 +5278,24 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>14-12-1998</t>
+          <t>14-08-1994</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>JESSICAHERNANDEZVAZQUEZ@OUTLOOK.COM</t>
+          <t>ADRIANANAVA149@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:19</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>09-02-2026 16:53:59</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5309,27 +5313,27 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:20</t>
+          <t>18-02-2026 18:14:20</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:20</t>
+          <t>18-02-2026 18:13:49</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5339,10 +5343,14 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26220522365380003866</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
+          <t>26220522471810004257</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
@@ -5363,12 +5371,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>346013</t>
+          <t>344895</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>88178</t>
+          <t>22712</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5378,12 +5386,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MICHELLE</t>
+          <t>ALMA ROSA BASILISA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5398,12 +5406,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5619228106</t>
+          <t>5611775850</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C ORIENTE 32 MZ 25</t>
+          <t>C JOSE MARIA MORELOS</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5413,52 +5421,52 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>30-07-2003</t>
+          <t>02-04-1963</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>MICHELLE.GOMZ2303@GMAIL.COM</t>
+          <t>ALMAROSACASTRO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>23-02-2026 19:02:28</t>
+          <t>18-02-2026 17:26:28</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>23-02-2026 19:08:04</t>
+          <t>18-02-2026 17:48:07</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>23-02-2026 19:07:28</t>
+          <t>18-02-2026 17:46:56</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5468,7 +5476,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5478,14 +5486,14 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26220522598490004729</t>
+          <t>26220522470370004248</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5502,12 +5510,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>344433</t>
+          <t>343831</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5517,17 +5525,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IRIS MONTSERRAT</t>
+          <t>JESSICA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CHAVARIN</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5537,12 +5545,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5564692994</t>
+          <t>2217041181</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>CALLE MAGNOLIA 242</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5552,24 +5560,20 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>29-08-1994</t>
+          <t>14-12-1998</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>MONTSERRAT_94@HOTMAIL.COM</t>
+          <t>JESSICAHERNANDEZVAZQUEZ@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>17-02-2026 10:03:24</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>15-02-2026 12:21:19</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5587,27 +5591,27 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>17-02-2026 10:10:20</t>
+          <t>15-02-2026 12:21:20</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>17-02-2026 10:08:56</t>
+          <t>15-02-2026 12:21:20</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5617,7 +5621,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26220522423620004039</t>
+          <t>26220522365380003866</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5641,12 +5645,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344233</t>
+          <t>345233</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22050</t>
+          <t>87398</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5656,17 +5660,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t xml:space="preserve">LEONEL YUARI </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEREZ </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">MANRIQUEZ </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5676,32 +5680,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5611753742</t>
+          <t>5521514699</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRACC LOS HEROES </t>
+          <t xml:space="preserve">ZOL AGRICOLA ORIENTAL </t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>07-08-1998</t>
+          <t>27-06-2004</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CASTROMARIAFERNANDA57@GMAIL.COM</t>
+          <t>STARCICI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>16-02-2026 17:43:53</t>
+          <t>20-02-2026 09:01:39</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5726,17 +5730,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>16-02-2026 18:16:35</t>
+          <t>20-02-2026 09:08:59</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>16-02-2026 18:15:46</t>
+          <t>20-02-2026 09:08:21</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5756,7 +5760,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26220522403640003978</t>
+          <t>26220522522290004459</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5768,24 +5772,24 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>344432</t>
+          <t>342287</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5795,17 +5799,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>IRVING DONNOVAN</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t xml:space="preserve">BRAVO </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5815,12 +5819,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5515226715</t>
+          <t>5564343538</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ALFREDIO</t>
+          <t>C PERA SAN MARCOS</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5830,24 +5834,20 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>23-08-1991</t>
+          <t>06-09-1992</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>LIC.ALFREDO.91@GMAIL.COM</t>
+          <t>DONNOVANBR@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>17-02-2026 09:59:28</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 16:52:02</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5865,17 +5865,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>17-02-2026 10:14:17</t>
+          <t>12-02-2026 18:07:17</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>17-02-2026 10:13:36</t>
+          <t>12-02-2026 18:06:58</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5895,10 +5895,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26220522423710004040</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
+          <t>26220522301550003706</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
@@ -5919,12 +5923,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>343824</t>
+          <t>341922</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5934,17 +5938,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MARISOL</t>
+          <t>YANNEVY ARIADNE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5954,12 +5958,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5531971979</t>
+          <t>5580261394</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COL CENTRO CDMX</t>
+          <t>HEROES</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5969,17 +5973,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>02-03-1973</t>
+          <t>25-11-1994</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>MAPGUE2@GMAIL.COM</t>
+          <t>YENNEVY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>15-02-2026 12:05:48</t>
+          <t>08-02-2026 11:53:18</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -6000,17 +6004,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>15-02-2026 12:25:35</t>
+          <t>08-02-2026 11:58:57</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>15-02-2026 12:18:06</t>
+          <t>08-02-2026 11:57:36</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6020,7 +6024,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6030,7 +6034,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26220522365480003867</t>
+          <t>26220522171210003218</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -6042,24 +6046,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344895</t>
+          <t>342048</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22712</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6069,17 +6073,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ALMA ROSA BASILISA</t>
+          <t>DULCE IVONNE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>ZARCO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6089,12 +6093,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5611775850</t>
+          <t>5519303247</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>C JOSE MARIA MORELOS</t>
+          <t xml:space="preserve">C. LA CIGARRA COL. ESPERANZA </t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6104,24 +6108,20 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>02-04-1963</t>
+          <t>01-08-1991</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ALMAROSACASTRO@HOTMAIL.COM</t>
+          <t>DULCEIVONNETORRESZARCO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>18-02-2026 17:26:28</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 08:22:24</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6139,17 +6139,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>18-02-2026 17:48:07</t>
+          <t>09-02-2026 08:34:47</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>18-02-2026 17:46:56</t>
+          <t>09-02-2026 08:34:00</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26220522470370004248</t>
+          <t>26220522185040003259</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6193,12 +6193,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>344934</t>
+          <t>344931</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22751</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6208,17 +6208,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">YENNIFER </t>
+          <t>ANDRES JESUS</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6228,32 +6228,32 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5512992481</t>
+          <t>5537346724</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TULTITLAM MEX</t>
+          <t>MZ H EDIF 2B</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>17-09-1993</t>
+          <t>10-11-1992</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>YLOPEZFLORES17@GMAIL.COM</t>
+          <t>RAZIEL_FO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>18-02-2026 18:57:05</t>
+          <t>18-02-2026 18:46:57</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>18-02-2026 19:01:48</t>
+          <t>18-02-2026 18:54:43</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>18-02-2026 19:00:57</t>
+          <t>18-02-2026 18:52:58</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26220522473980004280</t>
+          <t>26220522473750004279</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6332,12 +6332,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>341922</t>
+          <t>345074</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>87239</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6347,17 +6347,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>YANNEVY ARIADNE</t>
+          <t>SANDRA ESTRELLA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6367,14 +6367,10 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5580261394</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>HEROES</t>
-        </is>
-      </c>
+          <t>5545570437</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6382,60 +6378,56 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>25-11-1994</t>
+          <t>19-06-1974</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>YENNEVY@GMAIL.COM</t>
+          <t>GARCIA_SANDRA98@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>08-02-2026 11:53:18</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>19-02-2026 14:14:15</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>08-02-2026 11:58:57</t>
+          <t>23-02-2026 14:12:47</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>08-02-2026 11:57:36</t>
-        </is>
-      </c>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6443,36 +6435,44 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26220522171210003218</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
+          <t>26220522581980004643</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>DIANA MADRID ORTIZ</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>David Guillermo  Fuentes Carrillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342048</t>
+          <t>342192</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6482,17 +6482,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DULCE IVONNE</t>
+          <t>JESUS ZAID</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>BORREGO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ZARCO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6502,32 +6502,32 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5519303247</t>
+          <t>4055882651</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. LA CIGARRA COL. ESPERANZA </t>
+          <t xml:space="preserve">C MELCHOR OCAMPO S/N COL. LA ESPERANZA </t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>01-08-1991</t>
+          <t>23-12-1999</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>DULCEIVONNETORRESZARCO@GMAIL.COM</t>
+          <t>SAIDD.BST@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>09-02-2026 08:22:24</t>
+          <t>09-02-2026 14:52:50</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>09-02-2026 08:34:47</t>
+          <t>09-02-2026 15:06:28</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>09-02-2026 08:34:00</t>
+          <t>09-02-2026 15:05:32</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26220522185040003259</t>
+          <t>26220522194630003292</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6590,24 +6590,24 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>345233</t>
+          <t>342536</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>87398</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6617,17 +6617,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONEL YUARI </t>
+          <t>HANNIA ATZIRY</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANRIQUEZ </t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6637,39 +6637,35 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5521514699</t>
+          <t>5541561912</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZOL AGRICOLA ORIENTAL </t>
+          <t>TEJALPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>27-06-2004</t>
+          <t>22-01-1997</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>STARCICI@GMAIL.COM</t>
+          <t>HANNIA_22_SANDOVAL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>20-02-2026 09:01:39</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 07:49:10</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6687,17 +6683,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>20-02-2026 09:08:59</t>
+          <t>10-02-2026 07:55:17</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>20-02-2026 09:08:21</t>
+          <t>10-02-2026 07:53:33</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6707,7 +6703,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6717,7 +6713,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26220522522290004459</t>
+          <t>26220522224790003405</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
@@ -6729,24 +6725,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>342287</t>
+          <t>345401</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>87566</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6756,17 +6752,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>IRVING DONNOVAN</t>
+          <t>MELANY SAMANTHA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t>ESPINOSA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6776,63 +6772,67 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5564343538</t>
+          <t>5636743221</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>C PERA SAN MARCOS</t>
+          <t>AV DE CANAL MZ 27</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>06-09-1992</t>
+          <t>03-09-2007</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>DONNOVANBR@OUTLOOK.COM</t>
+          <t>MELANILOPES36@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>09-02-2026 16:52:02</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>20-02-2026 18:57:58</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>12-02-2026 18:07:17</t>
+          <t>24-02-2026 18:38:06</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>12-02-2026 18:06:58</t>
+          <t>24-02-2026 18:37:40</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26220522301550003706</t>
+          <t>26220522632110004851</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -6863,7 +6863,7 @@
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6880,12 +6880,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>345129</t>
+          <t>343503</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>87294</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6895,17 +6895,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KIMBERLY ABIGAIL</t>
+          <t>DIANA VIANEY</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">CARREON </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>YAÑEZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5619291534</t>
+          <t>5614816775</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>U HAB 4 VIENTOS</t>
+          <t>C TEPOYAN 5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6930,24 +6930,20 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>20-08-2007</t>
+          <t>16-10-1986</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>KKKIMBERLYY2@GMAIL.COM</t>
+          <t>DIANACARREON995@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>19-02-2026 16:52:09</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>13-02-2026 14:48:21</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6965,17 +6961,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>19-02-2026 17:04:47</t>
+          <t>13-02-2026 15:06:00</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>19-02-2026 17:03:32</t>
+          <t>13-02-2026 15:05:03</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6995,7 +6991,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26220522500320004391</t>
+          <t>26220522322030003760</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -7019,12 +7015,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>345130</t>
+          <t>345977</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>87295</t>
+          <t>88142</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7034,17 +7030,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MARISELA</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>PAYAN</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7054,79 +7050,63 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>5538014107</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>U HAB 4 VIENTOS</t>
-        </is>
-      </c>
+          <t>5586887467</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>02-12-1975</t>
+          <t>01-11-1978</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>KIMBERLY89@GMAIL.COM</t>
+          <t>JUANCARLOSLARAPAYAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>19-02-2026 16:54:23</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>23-02-2026 18:23:19</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>19-02-2026 17:08:32</t>
+          <t>23-02-2026 18:25:30</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>19-02-2026 17:08:01</t>
-        </is>
-      </c>
+          <t>23-03-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7134,24 +7114,24 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26220522500550004392</t>
+          <t>26220522595510004713</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7547,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>342192</t>
+          <t>343838</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20010</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7582,17 +7562,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>JESUS ZAID</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BORREGO</t>
+          <t xml:space="preserve">MORAN </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7602,12 +7582,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4055882651</t>
+          <t>2206073345</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">C MELCHOR OCAMPO S/N COL. LA ESPERANZA </t>
+          <t>CALLE MAGNOLIA 242</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7617,17 +7597,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>23-12-1999</t>
+          <t>26-02-1995</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>SAIDD.BST@GMAIL.COM</t>
+          <t>TRILLISO_BET@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>09-02-2026 14:52:50</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -7648,27 +7628,27 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>09-02-2026 15:06:28</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>09-02-2026 15:05:32</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7678,7 +7658,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26220522194630003292</t>
+          <t>26220522365710003869</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
@@ -7690,24 +7670,24 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>342536</t>
+          <t>346085</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>88250</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7717,17 +7697,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>HANNIA ATZIRY</t>
+          <t xml:space="preserve">ARACELI </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t xml:space="preserve">SALMORAN </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>VILLAGOMEZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7737,12 +7717,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5541561912</t>
+          <t>5539066958</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>TEJALPA</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7752,23 +7732,23 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>22-01-1997</t>
+          <t>16-11-1982</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>HANNIA_22_SANDOVAL@HOTMAIL.COM</t>
+          <t>ARACELI.TSGS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>10-02-2026 07:49:10</t>
+          <t>24-02-2026 08:14:04</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7778,34 +7758,26 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>698</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10-02-2026 07:55:17</t>
+          <t>24-02-2026 08:00:00</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>10-02-2026 07:53:33</t>
-        </is>
-      </c>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7813,36 +7785,36 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26220522224790003405</t>
+          <t>26220522612860004768</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>698</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>344931</t>
+          <t>344217</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7852,17 +7824,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ANDRES JESUS</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>ELIZALDE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7872,12 +7844,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>5537346724</t>
+          <t>7473547605</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>MZ H EDIF 2B</t>
+          <t xml:space="preserve">AV. NIÑOS HEROES COL. SANTA CRUZ </t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7887,17 +7859,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>10-11-1992</t>
+          <t>09-07-1998</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>RAZIEL_FO@HOTMAIL.COM</t>
+          <t>ALEXGARCIAE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>18-02-2026 18:46:57</t>
+          <t>16-02-2026 17:34:05</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7922,17 +7894,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>18-02-2026 18:54:43</t>
+          <t>19-02-2026 15:50:26</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>18-02-2026 18:52:58</t>
+          <t>19-02-2026 15:49:51</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7942,7 +7914,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7952,10 +7924,14 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26220522473750004279</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
+          <t>26220522497590004364</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
@@ -7976,12 +7952,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>345074</t>
+          <t>343301</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>87239</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7991,17 +7967,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SANDRA ESTRELLA</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>ESPEJEL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8011,67 +7987,75 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>5545570437</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>5516346350</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>19-06-1974</t>
+          <t>06-07-1995</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>GARCIA_SANDRA98@YAHOO.COM.MX</t>
+          <t>DIEGOLUPUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>19-02-2026 14:14:15</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 16:04:34</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>23-02-2026 14:12:47</t>
+          <t>12-02-2026 16:26:22</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>12-02-2026 16:25:47</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8079,22 +8063,14 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26220522581980004643</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>DIANA MADRID ORTIZ</t>
-        </is>
-      </c>
+          <t>26220522297530003689</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -8111,12 +8087,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>345977</t>
+          <t>343505</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>88142</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8126,17 +8102,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>ALVARO O BRIAN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>VALADEZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PAYAN</t>
+          <t>BLANCA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8146,10 +8122,14 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5586887467</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>5591919598</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>AV NUEVO MEXICO 301</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8157,52 +8137,60 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>01-11-1978</t>
+          <t>12-09-1993</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>JUANCARLOSLARAPAYAN@GMAIL.COM</t>
+          <t>POSEIDONBALA93@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>23-02-2026 18:23:19</t>
+          <t>13-02-2026 14:50:25</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>23-02-2026 18:25:30</t>
+          <t>13-02-2026 14:59:34</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>23-03-2027 23:59:59</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>13-02-2026 14:59:07</t>
+        </is>
+      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8210,14 +8198,14 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26220522595510004713</t>
+          <t>26220522321910003759</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -8234,12 +8222,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>344217</t>
+          <t>343544</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22034</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8249,17 +8237,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>LAURA AMAYRANI</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ELIZALDE</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8269,39 +8257,35 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>7473547605</t>
+          <t>5546447212</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV. NIÑOS HEROES COL. SANTA CRUZ </t>
+          <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>09-07-1998</t>
+          <t>13-03-2007</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>ALEXGARCIAE@GMAIL.COM</t>
+          <t>LAUPRD25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>16-02-2026 17:34:05</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>13-02-2026 17:03:29</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8319,17 +8303,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>19-02-2026 15:50:26</t>
+          <t>13-02-2026 17:19:38</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>19-02-2026 15:49:51</t>
+          <t>13-02-2026 17:18:02</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8339,7 +8323,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -8349,14 +8333,10 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26220522497590004364</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522326190003779</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
@@ -8365,24 +8345,24 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>343301</t>
+          <t>344233</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>22050</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8392,17 +8372,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t xml:space="preserve">JEREZ </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ESPEJEL</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8412,35 +8392,39 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5516346350</t>
+          <t>5611753742</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
+          <t xml:space="preserve">FRACC LOS HEROES </t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>06-07-1995</t>
+          <t>07-08-1998</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>DIEGOLUPUS@GMAIL.COM</t>
+          <t>CASTROMARIAFERNANDA57@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>12-02-2026 16:04:34</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>16-02-2026 17:43:53</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8458,17 +8442,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>12-02-2026 16:26:22</t>
+          <t>16-02-2026 18:16:35</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>12-02-2026 16:25:47</t>
+          <t>16-02-2026 18:15:46</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8478,7 +8462,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -8488,7 +8472,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26220522297530003689</t>
+          <t>26220522403640003978</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
@@ -8500,24 +8484,24 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>343505</t>
+          <t>343539</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8527,17 +8511,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ALVARO O BRIAN</t>
+          <t>ROCIO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>VALADEZ</t>
+          <t>JAIMEZ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>BLANCA</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8547,32 +8531,32 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5591919598</t>
+          <t>5534063877</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>AV NUEVO MEXICO 301</t>
+          <t>C CUAUTZINGO MZA 34</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>12-09-1993</t>
+          <t>12-01-1998</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>POSEIDONBALA93@OUTLOOK.COM</t>
+          <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>13-02-2026 14:50:25</t>
+          <t>13-02-2026 16:58:39</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -8593,7 +8577,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>13-02-2026 14:59:34</t>
+          <t>13-02-2026 17:12:37</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -8603,7 +8587,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>13-02-2026 14:59:07</t>
+          <t>13-02-2026 17:10:18</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8613,7 +8597,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -8623,7 +8607,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26220522321910003759</t>
+          <t>26220522325890003776</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
@@ -8635,24 +8619,24 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>343544</t>
+          <t>344432</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8662,17 +8646,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LAURA AMAYRANI</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8682,35 +8666,39 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5546447212</t>
+          <t>5515226715</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
+          <t>ALFREDIO</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>13-03-2007</t>
+          <t>23-08-1991</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>LAUPRD25@GMAIL.COM</t>
+          <t>LIC.ALFREDO.91@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>13-02-2026 17:03:29</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>17-02-2026 09:59:28</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8728,17 +8716,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:38</t>
+          <t>17-02-2026 10:14:17</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>13-02-2026 17:18:02</t>
+          <t>17-02-2026 10:13:36</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8758,7 +8746,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26220522326190003779</t>
+          <t>26220522423710004040</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
@@ -8770,12 +8758,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8909,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>343539</t>
+          <t>344934</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8936,17 +8924,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ROCIO</t>
+          <t xml:space="preserve">YENNIFER </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>JAIMEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8956,12 +8944,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>5534063877</t>
+          <t>5512992481</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>C CUAUTZINGO MZA 34</t>
+          <t>TULTITLAM MEX</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8971,20 +8959,24 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>12-01-1998</t>
+          <t>17-09-1993</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
+          <t>YLOPEZFLORES17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>13-02-2026 16:58:39</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>18-02-2026 18:57:05</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9002,17 +8994,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>13-02-2026 17:12:37</t>
+          <t>18-02-2026 19:01:48</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>13-02-2026 17:10:18</t>
+          <t>18-02-2026 19:00:57</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -9032,7 +9024,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26220522325890003776</t>
+          <t>26220522473980004280</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
@@ -9044,24 +9036,24 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>345338</t>
+          <t>345129</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>87503</t>
+          <t>87294</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9071,17 +9063,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUADALUPE </t>
+          <t>KIMBERLY ABIGAIL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CARRANZA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9091,12 +9083,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>5615722096</t>
+          <t>5619291534</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRACC HACIENDA DE LAS PALMAS III </t>
+          <t>U HAB 4 VIENTOS</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9106,17 +9098,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>03-09-1981</t>
+          <t>20-08-2007</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>GUADALUPECARRANZA2830@GMAIL.COM</t>
+          <t>KKKIMBERLYY2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>20-02-2026 16:38:08</t>
+          <t>19-02-2026 16:52:09</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9141,17 +9133,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>20-02-2026 16:51:02</t>
+          <t>19-02-2026 17:04:47</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>20-02-2026 16:49:11</t>
+          <t>19-02-2026 17:03:32</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -9171,7 +9163,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26220522530660004497</t>
+          <t>26220522500320004391</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
@@ -9183,24 +9175,24 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>344940</t>
+          <t>345130</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>87295</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9210,17 +9202,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRANDON </t>
+          <t>MARISELA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MONTESINOS</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9230,32 +9222,32 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>5613578379</t>
+          <t>5538014107</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>C CIPRECES MZA 3</t>
+          <t>U HAB 4 VIENTOS</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>08-03-1994</t>
+          <t>02-12-1975</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>BRANDON.FAMDA@GMAIL.COM</t>
+          <t>KIMBERLY89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>18-02-2026 19:14:37</t>
+          <t>19-02-2026 16:54:23</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -9280,17 +9272,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>18-02-2026 19:17:54</t>
+          <t>19-02-2026 17:08:32</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>18-02-2026 19:17:35</t>
+          <t>19-02-2026 17:08:01</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9310,7 +9302,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26220522474720004282</t>
+          <t>26220522500550004392</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
@@ -9334,12 +9326,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>346020</t>
+          <t>345338</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>88185</t>
+          <t>87503</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9349,17 +9341,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>JOSE RODOLFO</t>
+          <t xml:space="preserve">GUADALUPE </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>CARRANZA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9369,67 +9361,67 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5574468176</t>
+          <t>5615722096</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COL FRATERNIDAD ANTORCHISTA</t>
+          <t xml:space="preserve">FRACC HACIENDA DE LAS PALMAS III </t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>06-10-1998</t>
+          <t>03-09-1981</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>ALCANTARAEZEQUIEL380@GMAIL.COM</t>
+          <t>GUADALUPECARRANZA2830@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>23-02-2026 19:10:57</t>
+          <t>20-02-2026 16:38:08</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>23-02-2026 19:13:59</t>
+          <t>20-02-2026 16:51:02</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>23-02-2026 19:13:31</t>
+          <t>20-02-2026 16:49:11</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -9439,7 +9431,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -9449,24 +9441,302 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26220522598880004730</t>
+          <t>26220522530660004497</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Luis Antonio  Chaparro Alonso</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>344940</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>22757</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRANDON </t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>DELGADO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>MONTESINOS</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>5613578379</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>C CIPRECES MZA 3</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>08-03-1994</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>BRANDON.FAMDA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:14:37</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:17:54</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:17:35</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26220522474720004282</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>346020</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>88185</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>JOSE RODOLFO</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>5574468176</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>COL FRATERNIDAD ANTORCHISTA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>06-10-1998</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>ALCANTARAEZEQUIEL380@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:10:57</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>sin rutina</t>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:13:59</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:13:31</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>26220522598880004730</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Luis Antonio  Chaparro Alonso</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>233666</t>
+          <t>186014</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>83521</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NATALY </t>
+          <t xml:space="preserve">DANIEL </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>VILLALPANDO</t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CADENA </t>
+          <t xml:space="preserve">PACHECO </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,79 +613,67 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5564992033</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>AV LOS PINOS MZ 37 LT 17</t>
-        </is>
-      </c>
+          <t>5644326491</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30-11-1985</t>
+          <t>05-02-1994</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>NATYVILLALPANDO6@GMAIL.COM</t>
+          <t>DANIELPERPACH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>09-05-2024 07:51:19</t>
+          <t>22-07-2023 07:23:44</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>16-02-2026 07:18:36</t>
+          <t>26-02-2026 06:36:12</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>16-02-2026 07:17:49</t>
-        </is>
-      </c>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,14 +681,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26220522378990003894</t>
+          <t>26220522676110005013</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -717,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>236785</t>
+          <t>233666</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>31171</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MARIA DEL ROSARIO</t>
+          <t xml:space="preserve">NATALY </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>VILLALPANDO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t xml:space="preserve">CADENA </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,12 +740,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5573035144</t>
+          <t>5564992033</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CDA BOSQUE DE EUCALIPTOS MZA 29</t>
+          <t>AV LOS PINOS MZ 37 LT 17</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -767,20 +755,24 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>24-06-1985</t>
+          <t>30-11-1985</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PRINCESS_CHARIN@HOTMAIL.COM</t>
+          <t>NATYVILLALPANDO6@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>28-05-2024 18:11:53</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>09-05-2024 07:51:19</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -798,17 +790,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-02-2026 19:13:53</t>
+          <t>16-02-2026 07:18:36</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>02-02-2026 19:13:00</t>
+          <t>16-02-2026 07:17:49</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -828,7 +820,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26220522021850002707</t>
+          <t>26220522378990003894</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -840,24 +832,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>David Guillermo  Fuentes Carrillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>338953</t>
+          <t>236785</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FABIOLA </t>
+          <t>MARIA DEL ROSARIO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PLATA</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,12 +879,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5582314058</t>
+          <t>5573035144</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CDA DE JAZMINES MZ 20 LT 10</t>
+          <t>CDA BOSQUE DE EUCALIPTOS MZA 29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -902,17 +894,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>11-04-1991</t>
+          <t>24-06-1985</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>FALIZEE0204@GMAIL.COM</t>
+          <t>PRINCESS_CHARIN@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>29-01-2026 08:24:12</t>
+          <t>28-05-2024 18:11:53</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -923,7 +915,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -933,17 +925,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>01-02-2026 09:51:51</t>
+          <t>02-02-2026 19:13:53</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>01-02-2026 09:51:00</t>
+          <t>02-02-2026 19:13:00</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -963,19 +955,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26220521988250002583</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522021850002707</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>499</t>
@@ -983,7 +967,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1265,12 +1249,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>340516</t>
+          <t>338953</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18334</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1280,17 +1264,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CARLOS ENRIQUE</t>
+          <t xml:space="preserve">FABIOLA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUEDA </t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PLATA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1300,32 +1284,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5619885190</t>
+          <t>5582314058</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IXTA</t>
+          <t>CDA DE JAZMINES MZ 20 LT 10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>05-08-1991</t>
+          <t>11-04-1991</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ENRIQUE-RUEDA@OUTLOOK.COM</t>
+          <t>FALIZEE0204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>03-02-2026 10:59:53</t>
+          <t>29-01-2026 08:24:12</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1336,7 +1320,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1346,17 +1330,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-02-2026 11:02:47</t>
+          <t>01-02-2026 09:51:51</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03-02-2026 11:02:16</t>
+          <t>01-02-2026 09:51:00</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1376,11 +1360,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26220522036720002739</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26220521988250002583</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>499</t>
@@ -1388,24 +1380,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>341101</t>
+          <t>340516</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>18334</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1407,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CHRISTIAN OWEN</t>
+          <t>CARLOS ENRIQUE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t xml:space="preserve">RUEDA </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,12 +1427,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5643127118</t>
+          <t>5619885190</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C CATEDRAL METROPOLITANA 204</t>
+          <t>IXTA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1450,17 +1442,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>18-06-2011</t>
+          <t>05-08-1991</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CHRISTIAN09MENDEZ1234@GMAIL.COM</t>
+          <t>ENRIQUE-RUEDA@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>04-02-2026 17:18:13</t>
+          <t>03-02-2026 10:59:53</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1481,17 +1473,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>04-02-2026 17:31:39</t>
+          <t>03-02-2026 11:02:47</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>04-02-2026 17:30:29</t>
+          <t>03-02-2026 11:02:16</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1501,7 +1493,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1511,7 +1503,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26220522082650002911</t>
+          <t>26220522036720002739</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1523,24 +1515,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>341617</t>
+          <t>339174</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1550,17 +1542,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDILBERTO </t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>CRISOSTOMO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>CARDOSO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1570,12 +1562,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5540185856</t>
+          <t>5550539848</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ACACIA 80</t>
+          <t>CDA 21 DE MARZO 12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1585,17 +1577,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13-08-1979</t>
+          <t>03-06-1998</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>GONZALEZCRUZEDILBERTO660@GMAIL.COM</t>
+          <t>DEIVID.AYD.CRI98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>06-02-2026 16:14:24</t>
+          <t>29-01-2026 19:21:28</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1616,17 +1608,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>06-02-2026 17:06:08</t>
+          <t>05-02-2026 19:25:52</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>06-02-2026 16:20:48</t>
+          <t>05-02-2026 19:22:43</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1646,10 +1638,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26220522142170003123</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26220522118170003054</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1658,24 +1654,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>339174</t>
+          <t>339592</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1685,17 +1681,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>MARIA GUADALUPE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CRISOSTOMO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CARDOSO</t>
+          <t>LANDIN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1705,32 +1701,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5550539848</t>
+          <t>5588006100</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CDA 21 DE MARZO 12</t>
+          <t>EL CAPULIN</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>03-06-1998</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>DEIVID.AYD.CRI98@GMAIL.COM</t>
+          <t>LANDINGUADALUPE95@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>29-01-2026 19:21:28</t>
+          <t>31-01-2026 09:45:22</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1751,17 +1747,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>05-02-2026 19:25:52</t>
+          <t>09-02-2026 14:59:33</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>05-02-2026 19:22:43</t>
+          <t>09-02-2026 14:59:02</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1781,7 +1777,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26220522118170003054</t>
+          <t>26220522194280003290</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1797,24 +1793,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>342375</t>
+          <t>341101</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1824,17 +1820,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA AMELIA </t>
+          <t>CHRISTIAN OWEN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SIERNA</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1844,32 +1840,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5532857495</t>
+          <t>5643127118</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AV DEL POPO MZA 56</t>
+          <t>C CATEDRAL METROPOLITANA 204</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>10-08-1975</t>
+          <t>18-06-2011</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>DIANAALINE10@HOTMAIL.COM</t>
+          <t>CHRISTIAN09MENDEZ1234@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>09-02-2026 18:11:48</t>
+          <t>04-02-2026 17:18:13</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1890,17 +1886,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>12-02-2026 18:14:46</t>
+          <t>04-02-2026 17:31:39</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>12-02-2026 18:13:56</t>
+          <t>04-02-2026 17:30:29</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1910,7 +1906,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1920,14 +1916,10 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26220522301970003709</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522082650002911</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1936,24 +1928,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>341951</t>
+          <t>341617</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1963,17 +1955,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIANA </t>
+          <t xml:space="preserve">EDILBERTO </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1983,32 +1975,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5641136687</t>
+          <t>5540185856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>RANCHO</t>
+          <t>ACACIA 80</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>05-03-1965</t>
+          <t>13-08-1979</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ADRIANA.CERVANT.AL@GMAIL.COM</t>
+          <t>GONZALEZCRUZEDILBERTO660@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>08-02-2026 13:24:14</t>
+          <t>06-02-2026 16:14:24</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2029,17 +2021,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>08-02-2026 13:32:56</t>
+          <t>06-02-2026 17:06:08</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>08-02-2026 13:32:13</t>
+          <t>06-02-2026 16:20:48</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2059,7 +2051,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26220522172520003225</t>
+          <t>26220522142170003123</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2071,7 +2063,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2083,12 +2075,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>342227</t>
+          <t>338952</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2098,17 +2090,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>YORDI JESUS</t>
+          <t xml:space="preserve">ANABEL </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PADRON</t>
+          <t>PLATA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2118,32 +2110,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5613711355</t>
+          <t>5543867324</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CDA HACIENDA DE JALPA MZ 19 LT 115C</t>
+          <t>CDA DE JAZMINEZ MZ 20 LT 10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>23-10-2002</t>
+          <t>22-10-1998</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>TREYOI.1023.ROCHA@GMAIL.COM</t>
+          <t>MAPA_220@HOTMAIL.ES</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>09-02-2026 15:55:59</t>
+          <t>29-01-2026 08:22:19</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2154,7 +2146,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2164,17 +2156,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>09-02-2026 16:06:40</t>
+          <t>01-02-2026 10:00:34</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>09-02-2026 16:06:13</t>
+          <t>01-02-2026 09:59:59</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2184,7 +2176,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2194,11 +2186,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26220522197030003304</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26220521988460002587</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>499</t>
@@ -2218,12 +2218,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>339592</t>
+          <t>339256</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MARIA GUADALUPE</t>
+          <t>CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LANDIN</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2253,32 +2253,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5588006100</t>
+          <t>5528464677</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EL CAPULIN</t>
+          <t xml:space="preserve">AV. JOSE MARIA MARTINEZ MZA 24 LT 19 </t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>12-01-1990</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>LANDINGUADALUPE95@GMAIL.COM</t>
+          <t>ELDA.SOLRAC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>31-01-2026 09:45:22</t>
+          <t>30-01-2026 09:16:32</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2299,17 +2299,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>09-02-2026 14:59:33</t>
+          <t>02-02-2026 11:52:16</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>09-02-2026 14:59:02</t>
+          <t>30-01-2026 09:31:10</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2329,14 +2329,10 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26220522194280003290</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522007790002644</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2345,24 +2341,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>342184</t>
+          <t>340216</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2372,17 +2368,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>AXEL ZADKYEL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VICENTE</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2392,12 +2388,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5537110647</t>
+          <t>5591647693</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COL SANTA CRUZ TLAPACOYA</t>
+          <t>SAN BUENAVENTURA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2407,17 +2403,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>25-07-2017</t>
+          <t>24-05-2006</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>KARINAFLORESVICENTE@GMAIL.COM</t>
+          <t>AXELVALDEZ099@GMAL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>09-02-2026 14:42:03</t>
+          <t>02-02-2026 15:29:08</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2438,17 +2434,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>09-02-2026 14:52:27</t>
+          <t>02-02-2026 15:45:59</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>09-02-2026 14:50:55</t>
+          <t>02-02-2026 15:34:51</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2468,7 +2464,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26220522193980003288</t>
+          <t>26220522015050002682</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2492,12 +2488,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>340216</t>
+          <t>340315</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2507,17 +2503,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AXEL ZADKYEL</t>
+          <t>MAYRA JAZMIN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>KURY</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>AVILES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2527,32 +2523,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5591647693</t>
+          <t>5561248221</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SAN BUENAVENTURA</t>
+          <t>IXTAP</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>24-05-2006</t>
+          <t>13-08-1980</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>AXELVALDEZ099@GMAL.COM</t>
+          <t>MAYRACGT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-02-2026 15:29:08</t>
+          <t>02-02-2026 17:44:11</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2563,7 +2559,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2573,17 +2569,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-02-2026 15:45:59</t>
+          <t>03-02-2026 07:27:24</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-02-2026 15:34:51</t>
+          <t>03-02-2026 07:26:21</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2603,10 +2599,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26220522015050002682</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
+          <t>26220522032080002726</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2627,12 +2627,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340315</t>
+          <t>342227</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2642,17 +2642,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MAYRA JAZMIN</t>
+          <t>YORDI JESUS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KURY</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AVILES</t>
+          <t>PADRON</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2662,32 +2662,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5561248221</t>
+          <t>5613711355</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IXTAP</t>
+          <t>CDA HACIENDA DE JALPA MZ 19 LT 115C</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13-08-1980</t>
+          <t>23-10-2002</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MAYRACGT@GMAIL.COM</t>
+          <t>TREYOI.1023.ROCHA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-02-2026 17:44:11</t>
+          <t>09-02-2026 15:55:59</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2708,17 +2708,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-02-2026 07:27:24</t>
+          <t>09-02-2026 16:06:40</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>03-02-2026 07:26:21</t>
+          <t>09-02-2026 16:06:13</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2738,14 +2738,10 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26220522032080002726</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522197030003304</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2754,12 +2750,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2897,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>338952</t>
+          <t>341951</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2916,17 +2912,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANABEL </t>
+          <t xml:space="preserve">ADRIANA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PLATA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2936,12 +2932,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5543867324</t>
+          <t>5641136687</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CDA DE JAZMINEZ MZ 20 LT 10</t>
+          <t>RANCHO</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2951,17 +2947,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22-10-1998</t>
+          <t>05-03-1965</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MAPA_220@HOTMAIL.ES</t>
+          <t>ADRIANA.CERVANT.AL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>29-01-2026 08:22:19</t>
+          <t>08-02-2026 13:24:14</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2972,7 +2968,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2982,17 +2978,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>01-02-2026 10:00:34</t>
+          <t>08-02-2026 13:32:56</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>01-02-2026 09:59:59</t>
+          <t>08-02-2026 13:32:13</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3012,19 +3008,11 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26220521988460002587</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522172520003225</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>499</t>
@@ -3032,7 +3020,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3044,12 +3032,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342380</t>
+          <t>340960</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>18778</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3059,17 +3047,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DIANA ALINE</t>
+          <t>LUIS ANGEL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3079,32 +3067,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5625435058</t>
+          <t>5669156876</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">C CASTILLO DE CHAPULTEPEC </t>
+          <t>C TONATICO 197</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>22-12-1996</t>
+          <t>19-02-1993</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>DIGTZ15@GMAIL.COM</t>
+          <t>BUICKGOLIFE856@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 18:16:13</t>
+          <t>04-02-2026 12:16:09</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3125,17 +3113,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>12-02-2026 18:19:45</t>
+          <t>04-02-2026 12:24:18</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>12-02-2026 18:19:19</t>
+          <t>04-02-2026 12:23:46</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3155,14 +3143,10 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26220522302230003710</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522073370002861</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
@@ -3171,24 +3155,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342750</t>
+          <t>342184</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3198,17 +3182,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MANUEL RAFAEL</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>VICENTE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3218,12 +3202,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5574265455</t>
+          <t>5537110647</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C CEBADA MZ 6 LT 3</t>
+          <t>COL SANTA CRUZ TLAPACOYA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3233,17 +3217,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>23-11-1999</t>
+          <t>25-07-2017</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MANUEL_LVNA@HOTMAIL.COM</t>
+          <t>KARINAFLORESVICENTE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>10-02-2026 17:23:26</t>
+          <t>09-02-2026 14:42:03</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3264,17 +3248,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>10-02-2026 17:27:27</t>
+          <t>09-02-2026 14:52:27</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>10-02-2026 17:26:23</t>
+          <t>09-02-2026 14:50:55</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3284,7 +3268,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3294,7 +3278,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26220522239800003484</t>
+          <t>26220522193980003288</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3306,24 +3290,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>339256</t>
+          <t>342750</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3333,17 +3317,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO</t>
+          <t>MANUEL RAFAEL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3353,12 +3337,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5528464677</t>
+          <t>5574265455</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV. JOSE MARIA MARTINEZ MZA 24 LT 19 </t>
+          <t>C CEBADA MZ 6 LT 3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3368,17 +3352,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>12-01-1990</t>
+          <t>23-11-1999</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ELDA.SOLRAC@GMAIL.COM</t>
+          <t>MANUEL_LVNA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>30-01-2026 09:16:32</t>
+          <t>10-02-2026 17:23:26</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3389,7 +3373,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3399,17 +3383,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-02-2026 11:52:16</t>
+          <t>10-02-2026 17:27:27</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>30-01-2026 09:31:10</t>
+          <t>10-02-2026 17:26:23</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3429,7 +3413,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26220522007790002644</t>
+          <t>26220522239800003484</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3441,24 +3425,24 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>340960</t>
+          <t>341357</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3468,17 +3452,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LUIS ANGEL</t>
+          <t>DAMIAN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t xml:space="preserve">QUINTERO </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3488,14 +3472,10 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5669156876</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>C TONATICO 197</t>
-        </is>
-      </c>
+          <t>5634592607</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3503,60 +3483,56 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19-02-1993</t>
+          <t>25-11-2010</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BUICKGOLIFE856@GMAIL.COM</t>
+          <t>DENI.QUINTERO2010@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>04-02-2026 12:16:09</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>05-02-2026 16:04:32</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>04-02-2026 12:24:18</t>
+          <t>05-02-2026 16:09:19</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>04-02-2026 12:23:46</t>
-        </is>
-      </c>
+          <t>05-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3564,36 +3540,36 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26220522073370002861</t>
+          <t>26220522109710003012</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>341357</t>
+          <t>342380</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3603,17 +3579,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DAMIAN</t>
+          <t>DIANA ALINE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTERO </t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3623,67 +3599,75 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5634592607</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>5625435058</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C CASTILLO DE CHAPULTEPEC </t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>25-11-2010</t>
+          <t>22-12-1996</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>DENI.QUINTERO2010@GMAIL.COM</t>
+          <t>DIGTZ15@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>05-02-2026 16:04:32</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 18:16:13</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>05-02-2026 16:09:19</t>
+          <t>12-02-2026 18:19:45</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>05-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>12-02-2026 18:19:19</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3691,14 +3675,18 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26220522109710003012</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
+          <t>26220522302230003710</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3715,12 +3703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>344676</t>
+          <t>342745</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22493</t>
+          <t>20562</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3730,17 +3718,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>JESSICA BERENICE</t>
+          <t>ITZEL STEPHANY</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>VERDE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SERVIN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3750,12 +3738,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2219009457</t>
+          <t>5584585348</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>C CIPRECES MZ 3</t>
+          <t>CDA BARRANCA DE MEZQUITE MZ 56</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3765,24 +3753,20 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>02-04-1995</t>
+          <t>21-12-1995</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>JEBER18@YAHOO.COM.MX</t>
+          <t>ITZEL_VERDE95@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>17-02-2026 19:05:24</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 17:16:16</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3800,17 +3784,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>17-02-2026 19:14:49</t>
+          <t>10-02-2026 17:21:18</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>17-02-2026 19:14:20</t>
+          <t>10-02-2026 17:20:26</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3830,7 +3814,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26220522443720004140</t>
+          <t>26220522239450003479</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3842,7 +3826,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3854,12 +3838,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>342745</t>
+          <t>341099</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20562</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3869,17 +3853,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ITZEL STEPHANY</t>
+          <t>AXEL KALID</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VERDE</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SERVIN</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3889,32 +3873,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5584585348</t>
+          <t>5635122950</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CDA BARRANCA DE MEZQUITE MZ 56</t>
+          <t>C CATEDRAL METROPOLITANA 204</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21-12-1995</t>
+          <t>23-07-2004</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ITZEL_VERDE95@ICLOUD.COM</t>
+          <t>GUERREROAXEL190@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10-02-2026 17:16:16</t>
+          <t>04-02-2026 17:15:27</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3935,17 +3919,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>10-02-2026 17:21:18</t>
+          <t>04-02-2026 17:26:19</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>10-02-2026 17:20:26</t>
+          <t>04-02-2026 17:25:23</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3955,7 +3939,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3965,7 +3949,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26220522239450003479</t>
+          <t>26220522082390002907</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3977,7 +3961,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3989,12 +3973,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>341889</t>
+          <t>341894</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>19712</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4004,17 +3988,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LUCIA</t>
+          <t xml:space="preserve">JONATHAN </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t xml:space="preserve">URBAN </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4024,7 +4008,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5574445968</t>
+          <t>5574445964</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4034,22 +4018,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>06-03-1990</t>
+          <t>06-12-1990</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>LUCYCOSA06039@GMAIL.COM</t>
+          <t>SOLDADO.DE.DIOS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>08-02-2026 09:58:42</t>
+          <t>08-02-2026 10:05:09</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4070,7 +4054,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>08-02-2026 10:02:56</t>
+          <t>08-02-2026 10:07:34</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4080,7 +4064,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>08-02-2026 10:02:01</t>
+          <t>08-02-2026 10:07:05</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4100,7 +4084,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26220522169080003210</t>
+          <t>26220522169210003211</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -4124,12 +4108,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>341099</t>
+          <t>342097</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4139,17 +4123,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AXEL KALID</t>
+          <t xml:space="preserve">ALICIA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t xml:space="preserve">SAUCEDO </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4159,35 +4143,39 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5635122950</t>
+          <t>5522530023</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C CATEDRAL METROPOLITANA 204</t>
+          <t>CDA MAGDALENA SN IXTAPALUCA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>23-07-2004</t>
+          <t>23-03-1966</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>GUERREROAXEL190@GMAIL.COM</t>
+          <t>SAUCEDOGALICIAALICIA32@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>04-02-2026 17:15:27</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>09-02-2026 10:35:09</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4205,17 +4193,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>04-02-2026 17:26:19</t>
+          <t>18-02-2026 15:06:39</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>04-02-2026 17:25:23</t>
+          <t>18-02-2026 15:05:44</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4235,11 +4223,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26220522082390002907</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
+          <t>26220522463670004215</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>499</t>
@@ -4247,7 +4243,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4259,12 +4255,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>341952</t>
+          <t>341889</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4274,17 +4270,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>RAMON</t>
+          <t>LUCIA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4294,32 +4290,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5520734799</t>
+          <t>5574445968</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>RANCHOO</t>
+          <t>LOTOS</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>31-08-1964</t>
+          <t>06-03-1990</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>MONN.64KAISER@GMAIL.COM</t>
+          <t>LUCYCOSA06039@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>08-02-2026 13:27:30</t>
+          <t>08-02-2026 09:58:42</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4340,7 +4336,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>08-02-2026 13:36:45</t>
+          <t>08-02-2026 10:02:56</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4350,7 +4346,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>08-02-2026 13:36:11</t>
+          <t>08-02-2026 10:02:01</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4370,7 +4366,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26220522172570003226</t>
+          <t>26220522169080003210</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4382,24 +4378,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>345379</t>
+          <t>341952</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>87544</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4409,17 +4405,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EMMANUEL</t>
+          <t>RAMON</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DE JESUS</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4429,12 +4425,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5581003622</t>
+          <t>5520734799</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C AGUSTIN DE ITURBIDE 228</t>
+          <t>RANCHOO</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4444,24 +4440,20 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>17-12-1995</t>
+          <t>31-08-1964</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>EMMANUELDJF17@GMAIL.COM</t>
+          <t>MONN.64KAISER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>20-02-2026 18:06:05</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>08-02-2026 13:27:30</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4479,17 +4471,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>20-02-2026 18:17:25</t>
+          <t>08-02-2026 13:36:45</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>20-02-2026 18:16:44</t>
+          <t>08-02-2026 13:36:11</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4499,7 +4491,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4509,7 +4501,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26220522533780004518</t>
+          <t>26220522172570003226</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4521,7 +4513,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4533,12 +4525,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>341894</t>
+          <t>342290</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4548,17 +4540,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">JONATHAN </t>
+          <t>ADRIANA ITZEL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">URBAN </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4568,35 +4560,39 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5574445964</t>
+          <t>5510440090</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LOTOS</t>
+          <t>C VILLAHERMOSA MZA 47</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>06-12-1990</t>
+          <t>14-08-1994</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>SOLDADO.DE.DIOS@HOTMAIL.COM</t>
+          <t>ADRIANANAVA149@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>08-02-2026 10:05:09</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>09-02-2026 16:53:59</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4614,17 +4610,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>08-02-2026 10:07:34</t>
+          <t>18-02-2026 18:14:20</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>08-02-2026 10:07:05</t>
+          <t>18-02-2026 18:13:49</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4634,7 +4630,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4644,10 +4640,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26220522169210003211</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr"/>
+          <t>26220522471810004257</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4668,12 +4668,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342097</t>
+          <t>342287</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4683,17 +4683,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALICIA </t>
+          <t>IRVING DONNOVAN</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUCEDO </t>
+          <t xml:space="preserve">BRAVO </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4703,39 +4703,35 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5522530023</t>
+          <t>5564343538</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CDA MAGDALENA SN IXTAPALUCA</t>
+          <t>C PERA SAN MARCOS</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>23-03-1966</t>
+          <t>06-09-1992</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>SAUCEDOGALICIAALICIA32@GMAIL.COM</t>
+          <t>DONNOVANBR@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>09-02-2026 10:35:09</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 16:52:02</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4753,17 +4749,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>18-02-2026 15:06:39</t>
+          <t>12-02-2026 18:07:17</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>18-02-2026 15:05:44</t>
+          <t>12-02-2026 18:06:58</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4783,7 +4779,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26220522463670004215</t>
+          <t>26220522301550003706</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4791,11 +4787,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
           <t>499</t>
@@ -4803,24 +4795,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343824</t>
+          <t>341922</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4830,17 +4822,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MARISOL</t>
+          <t>YANNEVY ARIADNE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4850,12 +4842,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5531971979</t>
+          <t>5580261394</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COL CENTRO CDMX</t>
+          <t>HEROES</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4865,17 +4857,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>02-03-1973</t>
+          <t>25-11-1994</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>MAPGUE2@GMAIL.COM</t>
+          <t>YENNEVY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>15-02-2026 12:05:48</t>
+          <t>08-02-2026 11:53:18</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4896,17 +4888,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>15-02-2026 12:25:35</t>
+          <t>08-02-2026 11:58:57</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>15-02-2026 12:18:06</t>
+          <t>08-02-2026 11:57:36</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4916,7 +4908,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4926,7 +4918,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26220522365480003867</t>
+          <t>26220522171210003218</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4938,24 +4930,24 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>344433</t>
+          <t>342048</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4965,17 +4957,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IRIS MONTSERRAT</t>
+          <t>DULCE IVONNE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CHAVARIN</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>ZARCO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4985,12 +4977,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5564692994</t>
+          <t>5519303247</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t xml:space="preserve">C. LA CIGARRA COL. ESPERANZA </t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5000,24 +4992,20 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>29-08-1994</t>
+          <t>01-08-1991</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>MONTSERRAT_94@HOTMAIL.COM</t>
+          <t>DULCEIVONNETORRESZARCO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>17-02-2026 10:03:24</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 08:22:24</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5035,17 +5023,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>17-02-2026 10:10:20</t>
+          <t>09-02-2026 08:34:47</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>17-02-2026 10:08:56</t>
+          <t>09-02-2026 08:34:00</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5055,7 +5043,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5065,7 +5053,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26220522423620004039</t>
+          <t>26220522185040003259</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5089,12 +5077,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>346013</t>
+          <t>342192</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>88178</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5104,17 +5092,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MICHELLE</t>
+          <t>JESUS ZAID</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>BORREGO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5124,67 +5112,63 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5619228106</t>
+          <t>4055882651</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C ORIENTE 32 MZ 25</t>
+          <t xml:space="preserve">C MELCHOR OCAMPO S/N COL. LA ESPERANZA </t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>30-07-2003</t>
+          <t>23-12-1999</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>MICHELLE.GOMZ2303@GMAIL.COM</t>
+          <t>SAIDD.BST@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>23-02-2026 19:02:28</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 14:52:50</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>23-02-2026 19:08:04</t>
+          <t>09-02-2026 15:06:28</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>23-02-2026 19:07:28</t>
+          <t>09-02-2026 15:05:32</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5204,19 +5188,19 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26220522598490004729</t>
+          <t>26220522194630003292</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5228,12 +5212,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342290</t>
+          <t>343831</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5243,17 +5227,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ADRIANA ITZEL</t>
+          <t>JESSICA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5263,12 +5247,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5510440090</t>
+          <t>2217041181</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C VILLAHERMOSA MZA 47</t>
+          <t>CALLE MAGNOLIA 242</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5278,24 +5262,20 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>14-08-1994</t>
+          <t>14-12-1998</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ADRIANANAVA149@GMAIL.COM</t>
+          <t>JESSICAHERNANDEZVAZQUEZ@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>09-02-2026 16:53:59</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>15-02-2026 12:21:19</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5313,27 +5293,27 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:20</t>
+          <t>15-02-2026 12:21:20</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>18-02-2026 18:13:49</t>
+          <t>15-02-2026 12:21:20</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5343,14 +5323,10 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26220522471810004257</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522365380003866</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
@@ -5371,12 +5347,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>344895</t>
+          <t>344433</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22712</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5386,17 +5362,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ALMA ROSA BASILISA</t>
+          <t>IRIS MONTSERRAT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>CHAVARIN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5406,12 +5382,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5611775850</t>
+          <t>5564692994</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C JOSE MARIA MORELOS</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5421,17 +5397,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>02-04-1963</t>
+          <t>29-08-1994</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>ALMAROSACASTRO@HOTMAIL.COM</t>
+          <t>MONTSERRAT_94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>18-02-2026 17:26:28</t>
+          <t>17-02-2026 10:03:24</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5456,17 +5432,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>18-02-2026 17:48:07</t>
+          <t>17-02-2026 10:10:20</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>18-02-2026 17:46:56</t>
+          <t>17-02-2026 10:08:56</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5476,7 +5452,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5486,7 +5462,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26220522470370004248</t>
+          <t>26220522423620004039</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5510,12 +5486,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>343831</t>
+          <t>342536</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5525,17 +5501,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>JESSICA</t>
+          <t>HANNIA ATZIRY</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5545,12 +5521,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2217041181</t>
+          <t>5541561912</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CALLE MAGNOLIA 242</t>
+          <t>TEJALPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5560,17 +5536,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>14-12-1998</t>
+          <t>22-01-1997</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>JESSICAHERNANDEZVAZQUEZ@OUTLOOK.COM</t>
+          <t>HANNIA_22_SANDOVAL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:19</t>
+          <t>10-02-2026 07:49:10</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5591,22 +5567,22 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:20</t>
+          <t>10-02-2026 07:55:17</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:20</t>
+          <t>10-02-2026 07:53:33</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -5621,7 +5597,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26220522365380003866</t>
+          <t>26220522224790003405</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5633,24 +5609,24 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>345233</t>
+          <t>343824</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>87398</t>
+          <t>21641</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5660,17 +5636,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONEL YUARI </t>
+          <t>MARISOL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANRIQUEZ </t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5680,39 +5656,35 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5521514699</t>
+          <t>5531971979</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZOL AGRICOLA ORIENTAL </t>
+          <t>COL CENTRO CDMX</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>27-06-2004</t>
+          <t>02-03-1973</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>STARCICI@GMAIL.COM</t>
+          <t>MAPGUE2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>20-02-2026 09:01:39</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>15-02-2026 12:05:48</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5730,17 +5702,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>20-02-2026 09:08:59</t>
+          <t>15-02-2026 12:25:35</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>20-02-2026 09:08:21</t>
+          <t>15-02-2026 12:18:06</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5760,7 +5732,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26220522522290004459</t>
+          <t>26220522365480003867</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5784,12 +5756,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>342287</t>
+          <t>344895</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>22712</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5799,17 +5771,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>IRVING DONNOVAN</t>
+          <t>ALMA ROSA BASILISA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO </t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5819,35 +5791,39 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5564343538</t>
+          <t>5611775850</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>C PERA SAN MARCOS</t>
+          <t>C JOSE MARIA MORELOS</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>06-09-1992</t>
+          <t>02-04-1963</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>DONNOVANBR@OUTLOOK.COM</t>
+          <t>ALMAROSACASTRO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>09-02-2026 16:52:02</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>18-02-2026 17:26:28</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5865,17 +5841,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>12-02-2026 18:07:17</t>
+          <t>18-02-2026 17:48:07</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>12-02-2026 18:06:58</t>
+          <t>18-02-2026 17:46:56</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5885,7 +5861,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5895,14 +5871,10 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26220522301550003706</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522470370004248</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
@@ -5923,12 +5895,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>341922</t>
+          <t>343503</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5938,17 +5910,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>YANNEVY ARIADNE</t>
+          <t>DIANA VIANEY</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">CARREON </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>YAÑEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5958,12 +5930,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5580261394</t>
+          <t>5614816775</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>HEROES</t>
+          <t>C TEPOYAN 5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5973,17 +5945,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>25-11-1994</t>
+          <t>16-10-1986</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>YENNEVY@GMAIL.COM</t>
+          <t>DIANACARREON995@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>08-02-2026 11:53:18</t>
+          <t>13-02-2026 14:48:21</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -6004,17 +5976,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>08-02-2026 11:58:57</t>
+          <t>13-02-2026 15:06:00</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>08-02-2026 11:57:36</t>
+          <t>13-02-2026 15:05:03</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6034,7 +6006,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26220522171210003218</t>
+          <t>26220522322030003760</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -6046,24 +6018,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>David Guillermo  Fuentes Carrillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>342048</t>
+          <t>345233</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>87398</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6073,17 +6045,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DULCE IVONNE</t>
+          <t xml:space="preserve">LEONEL YUARI </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ZARCO</t>
+          <t xml:space="preserve">MANRIQUEZ </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6093,35 +6065,39 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5519303247</t>
+          <t>5521514699</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. LA CIGARRA COL. ESPERANZA </t>
+          <t xml:space="preserve">ZOL AGRICOLA ORIENTAL </t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>01-08-1991</t>
+          <t>27-06-2004</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>DULCEIVONNETORRESZARCO@GMAIL.COM</t>
+          <t>STARCICI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>09-02-2026 08:22:24</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>20-02-2026 09:01:39</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6139,17 +6115,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>09-02-2026 08:34:47</t>
+          <t>20-02-2026 09:08:59</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>09-02-2026 08:34:00</t>
+          <t>20-02-2026 09:08:21</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6159,7 +6135,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -6169,7 +6145,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26220522185040003259</t>
+          <t>26220522522290004459</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6193,12 +6169,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>344931</t>
+          <t>342375</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6208,17 +6184,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ANDRES JESUS</t>
+          <t xml:space="preserve">DIANA AMELIA </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>SIERNA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6228,39 +6204,35 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5537346724</t>
+          <t>5532857495</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>MZ H EDIF 2B</t>
+          <t>AV DEL POPO MZA 56</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>10-11-1992</t>
+          <t>10-08-1975</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>RAZIEL_FO@HOTMAIL.COM</t>
+          <t>DIANAALINE10@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>18-02-2026 18:46:57</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 18:11:48</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6278,17 +6250,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>18-02-2026 18:54:43</t>
+          <t>12-02-2026 18:14:46</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>18-02-2026 18:52:58</t>
+          <t>12-02-2026 18:13:56</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6298,7 +6270,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6308,10 +6280,14 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26220522473750004279</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr"/>
+          <t>26220522301970003709</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
@@ -6332,12 +6308,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>345074</t>
+          <t>343301</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>87239</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6347,17 +6323,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SANDRA ESTRELLA</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>ESPEJEL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6367,67 +6343,75 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5545570437</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>5516346350</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>19-06-1974</t>
+          <t>06-07-1995</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>GARCIA_SANDRA98@YAHOO.COM.MX</t>
+          <t>DIEGOLUPPUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>19-02-2026 14:14:15</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 16:04:34</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>23-02-2026 14:12:47</t>
+          <t>12-02-2026 16:26:22</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>12-02-2026 16:25:47</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6435,44 +6419,36 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26220522581980004643</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>DIANA MADRID ORTIZ</t>
-        </is>
-      </c>
+          <t>26220522297530003689</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342192</t>
+          <t>343505</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20010</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6482,17 +6458,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>JESUS ZAID</t>
+          <t>ALVARO O BRIAN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>BORREGO</t>
+          <t>VALADEZ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>BLANCA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6502,12 +6478,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>4055882651</t>
+          <t>5591919598</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">C MELCHOR OCAMPO S/N COL. LA ESPERANZA </t>
+          <t>AV NUEVO MEXICO 301</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6517,17 +6493,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>23-12-1999</t>
+          <t>12-09-1993</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>SAIDD.BST@GMAIL.COM</t>
+          <t>POSEIDONBALA93@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>09-02-2026 14:52:50</t>
+          <t>13-02-2026 14:50:25</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6548,17 +6524,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>09-02-2026 15:06:28</t>
+          <t>13-02-2026 14:59:34</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>09-02-2026 15:05:32</t>
+          <t>13-02-2026 14:59:07</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6568,7 +6544,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6578,7 +6554,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26220522194630003292</t>
+          <t>26220522321910003759</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6590,24 +6566,24 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>342536</t>
+          <t>343544</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6617,17 +6593,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>HANNIA ATZIRY</t>
+          <t>LAURA AMAYRANI</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6637,12 +6613,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5541561912</t>
+          <t>5546447212</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TEJALPA</t>
+          <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6652,17 +6628,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>22-01-1997</t>
+          <t>13-03-2007</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>HANNIA_22_SANDOVAL@HOTMAIL.COM</t>
+          <t>LAUPRD25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>10-02-2026 07:49:10</t>
+          <t>13-02-2026 17:03:29</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6683,17 +6659,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>10-02-2026 07:55:17</t>
+          <t>13-02-2026 17:19:38</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>10-02-2026 07:53:33</t>
+          <t>13-02-2026 17:18:02</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6703,7 +6679,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6713,7 +6689,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26220522224790003405</t>
+          <t>26220522326190003779</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
@@ -6725,7 +6701,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6737,12 +6713,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>345401</t>
+          <t>343838</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>87566</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6752,17 +6728,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MELANY SAMANTHA</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">MORAN </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ESPINOSA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6772,77 +6748,73 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5636743221</t>
+          <t>2206073345</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>AV DE CANAL MZ 27</t>
+          <t>CALLE MAGNOLIA 242</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>03-09-2007</t>
+          <t>26-02-1995</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>MELANILOPES36@GMAIL.COM</t>
+          <t>TRILLISO_BET@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>20-02-2026 18:57:58</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-02-2026 12:36:33</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>24-02-2026 18:38:06</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>24-02-2026 18:37:40</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6852,18 +6824,14 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26220522632110004851</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522365710003869</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6880,12 +6848,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>343503</t>
+          <t>343539</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6895,17 +6863,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DIANA VIANEY</t>
+          <t>ROCIO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARREON </t>
+          <t>JAIMEZ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>YAÑEZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6915,12 +6883,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5614816775</t>
+          <t>5534063877</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>C TEPOYAN 5</t>
+          <t>C CUAUTZINGO MZA 34</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6930,17 +6898,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>16-10-1986</t>
+          <t>12-01-1998</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>DIANACARREON995@GMAIL.COM</t>
+          <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>13-02-2026 14:48:21</t>
+          <t>13-02-2026 16:58:39</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6961,7 +6929,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>13-02-2026 15:06:00</t>
+          <t>13-02-2026 17:12:37</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -6971,7 +6939,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>13-02-2026 15:05:03</t>
+          <t>13-02-2026 17:10:18</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6981,7 +6949,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6991,7 +6959,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26220522322030003760</t>
+          <t>26220522325890003776</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -7003,24 +6971,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>345977</t>
+          <t>344217</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>88142</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7030,17 +6998,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PAYAN</t>
+          <t>ELIZALDE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7050,10 +7018,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>5586887467</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>7473547605</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV. NIÑOS HEROES COL. SANTA CRUZ </t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7061,52 +7033,64 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>01-11-1978</t>
+          <t>09-07-1998</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>JUANCARLOSLARAPAYAN@GMAIL.COM</t>
+          <t>ALEXGARCIAE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>23-02-2026 18:23:19</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>16-02-2026 17:34:05</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>23-02-2026 18:25:30</t>
+          <t>19-02-2026 15:50:26</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>23-03-2027 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:49:51</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7114,36 +7098,40 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26220522595510004713</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr"/>
+          <t>26220522497590004364</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344900</t>
+          <t>344931</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7153,17 +7141,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ADRIAN BERENICE</t>
+          <t>ANDRES JESUS</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7173,31 +7161,39 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5540961768</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>5537346724</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>MZ H EDIF 2B</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>05-03-1999</t>
+          <t>10-11-1992</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BEREADRY99@HOTMAIL.COM</t>
+          <t>RAZIEL_FO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>18-02-2026 17:32:28</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>18-02-2026 18:46:57</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7205,7 +7201,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -7215,7 +7211,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>18-02-2026 17:43:39</t>
+          <t>18-02-2026 18:54:43</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -7225,7 +7221,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>18-02-2026 17:43:01</t>
+          <t>18-02-2026 18:52:58</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7235,7 +7231,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -7245,7 +7241,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26220522470070004245</t>
+          <t>26220522473750004279</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7257,24 +7253,24 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>345055</t>
+          <t>345074</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>87220</t>
+          <t>87239</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7284,17 +7280,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>SANDRA ESTRELLA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TALAVERA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>PANIAGUA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7304,32 +7300,28 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5540308509</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>C SUR 171</t>
-        </is>
-      </c>
+          <t>5545570437</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>20-02-1963</t>
+          <t>19-06-1974</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>ANLGELTALAVERAP63@GMAIL.COM</t>
+          <t>GARCIA_SANDRA98@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>19-02-2026 13:00:23</t>
+          <t>19-02-2026 14:14:15</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7339,44 +7331,36 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>19-02-2026 13:17:48</t>
+          <t>23-02-2026 14:12:47</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>19-02-2026 13:16:38</t>
-        </is>
-      </c>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7384,14 +7368,22 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26220522493820004335</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
+          <t>26220522581980004643</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>DIANA MADRID ORTIZ</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7408,12 +7400,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>345063</t>
+          <t>344233</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>87228</t>
+          <t>22050</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7423,17 +7415,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MARIA DE LA LUZ</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t xml:space="preserve">JEREZ </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7443,12 +7435,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5561186386</t>
+          <t>5611753742</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>C SUR 171</t>
+          <t xml:space="preserve">FRACC LOS HEROES </t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7458,52 +7450,52 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>15-04-1963</t>
+          <t>07-08-1998</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>LG.JACK63@GMAIL.COM</t>
+          <t>CASTROMARIAFERNANDA57@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>19-02-2026 13:21:09</t>
+          <t>16-02-2026 17:43:53</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>19-02-2026 13:30:22</t>
+          <t>16-02-2026 18:16:35</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>19-02-2026 13:29:04</t>
+          <t>16-02-2026 18:15:46</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7513,7 +7505,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -7523,36 +7515,36 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26220522494100004341</t>
+          <t>26220522403640003978</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>343838</t>
+          <t>345401</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>87566</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7562,17 +7554,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>MELANY SAMANTHA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORAN </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ESPINOSA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7582,73 +7574,77 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2206073345</t>
+          <t>5636743221</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CALLE MAGNOLIA 242</t>
+          <t>AV DE CANAL MZ 27</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>26-02-1995</t>
+          <t>03-09-2007</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>TRILLISO_BET@HOTMAIL.COM</t>
+          <t>MELANILOPES36@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>20-02-2026 18:57:58</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>24-02-2026 18:38:06</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>24-02-2026 18:37:40</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7658,14 +7654,18 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26220522365710003869</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr"/>
+          <t>26220522632110004851</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -7682,12 +7682,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>346085</t>
+          <t>344626</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>88250</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7697,17 +7697,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARACELI </t>
+          <t>IXCHEL YARELI</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALMORAN </t>
+          <t xml:space="preserve">MARIN </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>VILLAGOMEZ</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5539066958</t>
+          <t>5579912763</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>C DZILAM MZ 814 LT 4</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7732,52 +7732,64 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>16-11-1982</t>
+          <t>31-01-1989</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>ARACELI.TSGS@GMAIL.COM</t>
+          <t>IXCHELMARIN@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>24-02-2026 08:14:04</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>17-02-2026 17:48:58</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIAR RECURRENTE $999</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>24-02-2026 08:00:00</t>
+          <t>17-02-2026 18:01:12</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>17-02-2026 17:59:12</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7785,36 +7797,36 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26220522612860004768</t>
+          <t>26220522439570004122</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>344217</t>
+          <t>345977</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22034</t>
+          <t>88142</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7824,17 +7836,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ELIZALDE</t>
+          <t>PAYAN</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7844,14 +7856,10 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>7473547605</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AV. NIÑOS HEROES COL. SANTA CRUZ </t>
-        </is>
-      </c>
+          <t>5586887467</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7859,64 +7867,52 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>09-07-1998</t>
+          <t>01-11-1978</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>ALEXGARCIAE@GMAIL.COM</t>
+          <t>JUANCARLOSLARAPAYAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>16-02-2026 17:34:05</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>23-02-2026 18:23:19</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>19-02-2026 15:50:26</t>
+          <t>23-02-2026 18:25:30</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>19-02-2026 15:49:51</t>
-        </is>
-      </c>
+          <t>23-03-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7924,40 +7920,36 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26220522497590004364</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522595510004713</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>343301</t>
+          <t>344432</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7967,17 +7959,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ESPEJEL</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7987,12 +7979,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>5516346350</t>
+          <t>5515226715</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
+          <t>ALFREDIO</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -8002,20 +7994,24 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>06-07-1995</t>
+          <t>23-08-1991</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>DIEGOLUPUS@GMAIL.COM</t>
+          <t>LIC.ALFREDO.91@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>12-02-2026 16:04:34</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>17-02-2026 09:59:28</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8033,17 +8029,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>12-02-2026 16:26:22</t>
+          <t>17-02-2026 10:14:17</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>12-02-2026 16:25:47</t>
+          <t>17-02-2026 10:13:36</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -8053,7 +8049,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -8063,7 +8059,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26220522297530003689</t>
+          <t>26220522423710004040</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
@@ -8087,12 +8083,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>343505</t>
+          <t>345338</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>87503</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8102,17 +8098,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ALVARO O BRIAN</t>
+          <t xml:space="preserve">GUADALUPE </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>VALADEZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BLANCA</t>
+          <t>CARRANZA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8122,35 +8118,39 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5591919598</t>
+          <t>5615722096</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AV NUEVO MEXICO 301</t>
+          <t xml:space="preserve">FRACC HACIENDA DE LAS PALMAS III </t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>12-09-1993</t>
+          <t>03-09-1981</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>POSEIDONBALA93@OUTLOOK.COM</t>
+          <t>GUADALUPECARRANZA2830@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>13-02-2026 14:50:25</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>20-02-2026 16:38:08</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8168,17 +8168,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>13-02-2026 14:59:34</t>
+          <t>20-02-2026 16:51:02</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13-02-2026 14:59:07</t>
+          <t>20-02-2026 16:49:11</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26220522321910003759</t>
+          <t>26220522530660004497</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
@@ -8210,24 +8210,24 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>343544</t>
+          <t>344940</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LAURA AMAYRANI</t>
+          <t xml:space="preserve">BRANDON </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MONTESINOS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8257,35 +8257,39 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>5546447212</t>
+          <t>5613578379</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
+          <t>C CIPRECES MZA 3</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>13-03-2007</t>
+          <t>08-03-1994</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>LAUPRD25@GMAIL.COM</t>
+          <t>BRANDON.FAMDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>13-02-2026 17:03:29</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>18-02-2026 19:14:37</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8303,17 +8307,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:38</t>
+          <t>18-02-2026 19:17:54</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>13-02-2026 17:18:02</t>
+          <t>18-02-2026 19:17:35</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8323,7 +8327,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -8333,7 +8337,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26220522326190003779</t>
+          <t>26220522474720004282</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
@@ -8345,24 +8349,24 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>344233</t>
+          <t>346085</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22050</t>
+          <t>88250</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8372,17 +8376,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t xml:space="preserve">ARACELI </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEREZ </t>
+          <t xml:space="preserve">SALMORAN </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>VILLAGOMEZ</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8392,12 +8396,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5611753742</t>
+          <t>5539066958</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRACC LOS HEROES </t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8407,27 +8411,23 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>07-08-1998</t>
+          <t>16-11-1982</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CASTROMARIAFERNANDA57@GMAIL.COM</t>
+          <t>ARACELI.TSGS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>16-02-2026 17:43:53</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>24-02-2026 08:14:04</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8437,34 +8437,26 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>698</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>16-02-2026 18:16:35</t>
+          <t>24-02-2026 08:00:00</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>16-02-2026 18:15:46</t>
-        </is>
-      </c>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8472,36 +8464,36 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26220522403640003978</t>
+          <t>26220522612860004768</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>698</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>343539</t>
+          <t>344934</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8511,17 +8503,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ROCIO</t>
+          <t xml:space="preserve">YENNIFER </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>JAIMEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8531,12 +8523,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5534063877</t>
+          <t>5512992481</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>C CUAUTZINGO MZA 34</t>
+          <t>TULTITLAM MEX</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8546,20 +8538,24 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>12-01-1998</t>
+          <t>17-09-1993</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
+          <t>YLOPEZFLORES17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>13-02-2026 16:58:39</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>18-02-2026 18:57:05</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8577,17 +8573,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>13-02-2026 17:12:37</t>
+          <t>18-02-2026 19:01:48</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>13-02-2026 17:10:18</t>
+          <t>18-02-2026 19:00:57</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8607,7 +8603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26220522325890003776</t>
+          <t>26220522473980004280</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
@@ -8619,24 +8615,24 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>344432</t>
+          <t>345129</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>87294</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8646,17 +8642,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>KIMBERLY ABIGAIL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8666,32 +8662,32 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5515226715</t>
+          <t>5619291534</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ALFREDIO</t>
+          <t>U HAB 4 VIENTOS</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>23-08-1991</t>
+          <t>20-08-2007</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>LIC.ALFREDO.91@GMAIL.COM</t>
+          <t>KKKIMBERLYY2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>17-02-2026 09:59:28</t>
+          <t>19-02-2026 16:52:09</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8716,17 +8712,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>17-02-2026 10:14:17</t>
+          <t>19-02-2026 17:04:47</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>17-02-2026 10:13:36</t>
+          <t>19-02-2026 17:03:32</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8736,7 +8732,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -8746,7 +8742,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26220522423710004040</t>
+          <t>26220522500320004391</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
@@ -8770,12 +8766,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>344626</t>
+          <t>345130</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>87295</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8785,17 +8781,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>IXCHEL YARELI</t>
+          <t>MARISELA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIN </t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8805,12 +8801,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5579912763</t>
+          <t>5538014107</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>C DZILAM MZ 814 LT 4</t>
+          <t>U HAB 4 VIENTOS</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8820,52 +8816,52 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>31-01-1989</t>
+          <t>02-12-1975</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>IXCHELMARIN@OUTLOOK.COM</t>
+          <t>KIMBERLY89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>17-02-2026 17:48:58</t>
+          <t>19-02-2026 16:54:23</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>PLAN FAMILIAR RECURRENTE $999</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>17-02-2026 18:01:12</t>
+          <t>19-02-2026 17:08:32</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>17-02-2026 17:59:12</t>
+          <t>19-02-2026 17:08:01</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8885,36 +8881,36 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26220522439570004122</t>
+          <t>26220522500550004392</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>344934</t>
+          <t>344900</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22751</t>
+          <t>22717</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8924,17 +8920,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">YENNIFER </t>
+          <t>ADRIAN BERENICE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8944,14 +8940,10 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>5512992481</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>TULTITLAM MEX</t>
-        </is>
-      </c>
+          <t>5540961768</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8959,24 +8951,20 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>17-09-1993</t>
+          <t>05-03-1999</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>YLOPEZFLORES17@GMAIL.COM</t>
+          <t>BEREADRY99@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>18-02-2026 18:57:05</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>18-02-2026 17:32:28</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8984,7 +8972,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -8994,7 +8982,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>18-02-2026 19:01:48</t>
+          <t>18-02-2026 17:43:39</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -9004,7 +8992,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>18-02-2026 19:00:57</t>
+          <t>18-02-2026 17:43:01</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -9014,7 +9002,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -9024,7 +9012,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26220522473980004280</t>
+          <t>26220522470070004245</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
@@ -9036,24 +9024,24 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>345129</t>
+          <t>345055</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>87294</t>
+          <t>87220</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9063,17 +9051,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KIMBERLY ABIGAIL</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>TALAVERA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>PANIAGUA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9083,57 +9071,57 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>5619291534</t>
+          <t>5540308509</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>U HAB 4 VIENTOS</t>
+          <t>C SUR 171</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>20-08-2007</t>
+          <t>20-02-1963</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>KKKIMBERLYY2@GMAIL.COM</t>
+          <t>ANGELTALAVERAP63@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>19-02-2026 16:52:09</t>
+          <t>19-02-2026 13:00:23</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>19-02-2026 17:04:47</t>
+          <t>19-02-2026 13:17:48</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -9143,7 +9131,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>19-02-2026 17:03:32</t>
+          <t>19-02-2026 13:16:38</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -9163,14 +9151,14 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26220522500320004391</t>
+          <t>26220522493820004335</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -9187,12 +9175,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>345130</t>
+          <t>345063</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>87295</t>
+          <t>87228</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9202,17 +9190,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MARISELA</t>
+          <t>MARIA DE LA LUZ</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9222,12 +9210,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>5538014107</t>
+          <t>5561186386</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>U HAB 4 VIENTOS</t>
+          <t>C SUR 171</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -9237,42 +9225,42 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>02-12-1975</t>
+          <t>15-04-1963</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>KIMBERLY89@GMAIL.COM</t>
+          <t>LG.JACK63@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>19-02-2026 16:54:23</t>
+          <t>19-02-2026 13:21:09</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>19-02-2026 17:08:32</t>
+          <t>19-02-2026 13:30:22</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -9282,7 +9270,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>19-02-2026 17:08:01</t>
+          <t>19-02-2026 13:29:04</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9302,14 +9290,14 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26220522500550004392</t>
+          <t>26220522494100004341</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
@@ -9326,12 +9314,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>345338</t>
+          <t>346020</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>87503</t>
+          <t>88185</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9341,17 +9329,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUADALUPE </t>
+          <t>JOSE RODOLFO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CARRANZA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9361,67 +9349,67 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5615722096</t>
+          <t>5574468176</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRACC HACIENDA DE LAS PALMAS III </t>
+          <t>COL FRATERNIDAD ANTORCHISTA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>03-09-1981</t>
+          <t>06-10-1998</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>GUADALUPECARRANZA2830@GMAIL.COM</t>
+          <t>ALCANTARAEZEQUIEL380@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>20-02-2026 16:38:08</t>
+          <t>23-02-2026 19:10:57</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>20-02-2026 16:51:02</t>
+          <t>23-02-2026 19:13:59</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>20-02-2026 16:49:11</t>
+          <t>23-02-2026 19:13:31</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -9431,7 +9419,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -9441,14 +9429,14 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26220522530660004497</t>
+          <t>26220522598880004730</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
@@ -9465,12 +9453,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>344940</t>
+          <t>346618</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>88783</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9480,17 +9468,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRANDON </t>
+          <t xml:space="preserve">PATRICIA </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t xml:space="preserve">LUNA </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MONTESINOS</t>
+          <t>BENITEZ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9500,79 +9488,67 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>5613578379</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>C CIPRECES MZA 3</t>
-        </is>
-      </c>
+          <t>5526558363</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>08-03-1994</t>
+          <t>24-06-1991</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>BRANDON.FAMDA@GMAIL.COM</t>
+          <t>MANRIQUE_MARTIN@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>18-02-2026 19:14:37</t>
+          <t>26-02-2026 04:34:59</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>18-02-2026 19:17:54</t>
+          <t>26-02-2026 04:36:22</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>18-02-2026 19:17:35</t>
-        </is>
-      </c>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9580,14 +9556,14 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26220522474720004282</t>
+          <t>26220522669450004996</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
@@ -9604,12 +9580,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>346020</t>
+          <t>344676</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>88185</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9619,17 +9595,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>JOSE RODOLFO</t>
+          <t>JESSICA BERENICE</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9639,67 +9615,67 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>5574468176</t>
+          <t>2219009457</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COL FRATERNIDAD ANTORCHISTA</t>
+          <t>C CIPRECES MZ 3</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>06-10-1998</t>
+          <t>02-04-1995</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>ALCANTARAEZEQUIEL380@GMAIL.COM</t>
+          <t>JEBER18@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>23-02-2026 19:10:57</t>
+          <t>17-02-2026 19:05:24</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>23-02-2026 19:13:59</t>
+          <t>17-02-2026 19:14:49</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>23-02-2026 19:13:31</t>
+          <t>17-02-2026 19:14:20</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -9709,7 +9685,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -9719,22 +9695,427 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26220522598880004730</t>
+          <t>26220522443720004140</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Luis Antonio  Chaparro Alonso</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>346617</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>88782</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRISTIAN </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORALES </t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>MANRIQUEZ</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>5513431982</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>22-07-1992</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>CRISTIAN_@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>26-02-2026 04:30:59</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>26-02-2026 04:33:00</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>26220522669400004995</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>345379</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>87544</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EMMANUEL</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>DE JESUS</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>5581003622</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>C AGUSTIN DE ITURBIDE 228</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>17-12-1995</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>EMMANUELDJF17@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:06:05</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:17:25</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>20-02-2026 18:16:44</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>26220522533780004518</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Brenda Anahi  Escamilla Mendez</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>346013</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>88178</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>MICHELLE</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>5619228106</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>C ORIENTE 32 MZ 25</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>30-07-2003</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>MICHELLE.GOMZ2303@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:02:28</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:08:04</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:07:28</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>26220522598490004729</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
         <is>
           <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
+      <c r="AC71" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,12 +844,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>236785</t>
+          <t>338953</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MARIA DEL ROSARIO</t>
+          <t xml:space="preserve">FABIOLA </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>PLATA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5573035144</t>
+          <t>5582314058</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CDA BOSQUE DE EUCALIPTOS MZA 29</t>
+          <t>CDA DE JAZMINES MZ 20 LT 10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -894,17 +894,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>24-06-1985</t>
+          <t>11-04-1991</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PRINCESS_CHARIN@HOTMAIL.COM</t>
+          <t>FALIZEE0204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>28-05-2024 18:11:53</t>
+          <t>29-01-2026 08:24:12</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -925,17 +925,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-02-2026 19:13:53</t>
+          <t>01-02-2026 09:51:51</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-02-2026 19:13:00</t>
+          <t>01-02-2026 09:51:00</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -955,11 +955,19 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26220522021850002707</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26220521988250002583</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>499</t>
@@ -967,7 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>David Guillermo  Fuentes Carrillo</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -979,12 +987,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>332845</t>
+          <t>339258</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +1002,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MIRSHA ASERET</t>
+          <t>PAOLA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>ARTEAGA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,12 +1022,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5574210862</t>
+          <t>5512421794</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C IGNACIO ZARAGOZA MZ 25</t>
+          <t>AV. JOSE MARIA MARTINEZ MZA 24 LY 19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1029,17 +1037,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>11-02-2000</t>
+          <t>07-04-1992</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>MIRSHA@GMAIL.COM</t>
+          <t>LOOPZY_9797@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>07-01-2026 14:07:05</t>
+          <t>30-01-2026 09:21:25</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1050,27 +1058,27 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13-02-2026 18:00:19</t>
+          <t>02-02-2026 11:50:19</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13-02-2026 18:00:00</t>
+          <t>30-01-2026 09:36:03</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1090,14 +1098,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26220522327410003797</t>
+          <t>26220522007760002643</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1114,12 +1122,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>339258</t>
+          <t>263370</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>60874</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1129,17 +1137,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PAOLA</t>
+          <t xml:space="preserve">JORGE </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ARTEAGA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>PEÑA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1149,35 +1157,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5512421794</t>
+          <t>5521403814</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AV. JOSE MARIA MARTINEZ MZA 24 LY 19</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>07-04-1992</t>
+          <t>23-04-1980</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>LOOPZY_9797@HOTMAIL.COM</t>
+          <t>JOARTE33@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>30-01-2026 09:21:25</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>23-10-2024 11:45:14</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1195,17 +1207,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-02-2026 11:50:19</t>
+          <t>27-02-2026 09:45:51</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>30-01-2026 09:36:03</t>
+          <t>27-02-2026 09:45:21</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1215,7 +1227,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1225,7 +1237,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26220522007760002643</t>
+          <t>26220522707890005139</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1249,12 +1261,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>338953</t>
+          <t>297854</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>95352</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FABIOLA </t>
+          <t>SHEYLA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t xml:space="preserve">GIL </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PLATA</t>
+          <t>MONDRAGON</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,12 +1296,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5582314058</t>
+          <t>5513701882</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CDA DE JAZMINES MZ 20 LT 10</t>
+          <t>C HELIOTROPOS MZ 37</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1299,20 +1311,24 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>11-04-1991</t>
+          <t>30-08-1991</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>FALIZEE0204@GMAIL.COM</t>
+          <t>SHEY.PAO33@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>29-01-2026 08:24:12</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>11-06-2025 11:03:41</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1320,7 +1336,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1330,17 +1346,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>01-02-2026 09:51:51</t>
+          <t>27-02-2026 12:31:09</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>01-02-2026 09:51:00</t>
+          <t>27-02-2026 12:25:11</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1360,19 +1376,11 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26220521988250002583</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522710370005151</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
           <t>499</t>
@@ -1380,24 +1388,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>340516</t>
+          <t>339258</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18334</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1407,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CARLOS ENRIQUE</t>
+          <t>PAOLA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUEDA </t>
+          <t>ARTEAGA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1427,32 +1435,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5619885190</t>
+          <t>5512421794</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IXTA</t>
+          <t>AV. JOSE MARIA MARTINEZ MZA 24 LY 19</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>05-08-1991</t>
+          <t>07-04-1992</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ENRIQUE-RUEDA@OUTLOOK.COM</t>
+          <t>LOOPZY_9797@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-02-2026 10:59:53</t>
+          <t>30-01-2026 09:21:25</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1463,7 +1471,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1473,17 +1481,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-02-2026 11:02:47</t>
+          <t>02-02-2026 11:50:19</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-02-2026 11:02:16</t>
+          <t>30-01-2026 09:36:03</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1493,7 +1501,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1503,7 +1511,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26220522036720002739</t>
+          <t>26220522007760002643</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1527,12 +1535,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>339174</t>
+          <t>341617</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1550,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t xml:space="preserve">EDILBERTO </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CRISOSTOMO</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CARDOSO</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,12 +1570,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5550539848</t>
+          <t>5540185856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CDA 21 DE MARZO 12</t>
+          <t>ACACIA 80</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1577,17 +1585,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>03-06-1998</t>
+          <t>13-08-1979</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>DEIVID.AYD.CRI98@GMAIL.COM</t>
+          <t>GONZALEZCRUZEDILBERTO660@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>29-01-2026 19:21:28</t>
+          <t>06-02-2026 16:14:24</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1608,17 +1616,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>05-02-2026 19:25:52</t>
+          <t>06-02-2026 17:06:08</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>05-02-2026 19:22:43</t>
+          <t>06-02-2026 16:20:48</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1638,14 +1646,10 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26220522118170003054</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522142170003123</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1654,24 +1658,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>339592</t>
+          <t>332845</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1681,17 +1685,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MARIA GUADALUPE</t>
+          <t>MIRSHA ASERET</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LANDIN</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1701,12 +1705,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5588006100</t>
+          <t>5574210862</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>EL CAPULIN</t>
+          <t>C IGNACIO ZARAGOZA MZ 25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1716,17 +1720,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>01-01-2000</t>
+          <t>11-02-2000</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>LANDINGUADALUPE95@GMAIL.COM</t>
+          <t>MIRSHA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>31-01-2026 09:45:22</t>
+          <t>07-01-2026 14:07:05</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1747,17 +1751,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>09-02-2026 14:59:33</t>
+          <t>13-02-2026 18:00:19</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>09-02-2026 14:59:02</t>
+          <t>13-02-2026 18:00:00</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1767,7 +1771,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1777,14 +1781,10 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26220522194280003290</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522327410003797</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1793,24 +1793,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>341101</t>
+          <t>236785</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,17 +1820,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CHRISTIAN OWEN</t>
+          <t>MARIA DEL ROSARIO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1840,32 +1840,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5643127118</t>
+          <t>5573035144</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C CATEDRAL METROPOLITANA 204</t>
+          <t>CDA BOSQUE DE EUCALIPTOS MZA 29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>18-06-2011</t>
+          <t>24-06-1985</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CHRISTIAN09MENDEZ1234@GMAIL.COM</t>
+          <t>PRINCESS_CHARIN@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>04-02-2026 17:18:13</t>
+          <t>28-05-2024 18:11:53</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1886,17 +1886,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>04-02-2026 17:31:39</t>
+          <t>02-02-2026 19:13:53</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>04-02-2026 17:30:29</t>
+          <t>02-02-2026 19:13:00</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26220522082650002911</t>
+          <t>26220522021850002707</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1940,12 +1940,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>341617</t>
+          <t>342227</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDILBERTO </t>
+          <t>YORDI JESUS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>PADRON</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5540185856</t>
+          <t>5613711355</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ACACIA 80</t>
+          <t>CDA HACIENDA DE JALPA MZ 19 LT 115C</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1990,17 +1990,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>13-08-1979</t>
+          <t>23-10-2002</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>GONZALEZCRUZEDILBERTO660@GMAIL.COM</t>
+          <t>TREYOI.1023.ROCHA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>06-02-2026 16:14:24</t>
+          <t>09-02-2026 15:55:59</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2021,17 +2021,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>06-02-2026 17:06:08</t>
+          <t>09-02-2026 16:06:40</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>06-02-2026 16:20:48</t>
+          <t>09-02-2026 16:06:13</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26220522142170003123</t>
+          <t>26220522197030003304</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>338952</t>
+          <t>339174</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2090,17 +2090,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANABEL </t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>CRISOSTOMO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PLATA</t>
+          <t>CARDOSO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2110,32 +2110,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5543867324</t>
+          <t>5550539848</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CDA DE JAZMINEZ MZ 20 LT 10</t>
+          <t>CDA 21 DE MARZO 12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22-10-1998</t>
+          <t>03-06-1998</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>MAPA_220@HOTMAIL.ES</t>
+          <t>DEIVID.AYD.CRI98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>29-01-2026 08:22:19</t>
+          <t>29-01-2026 19:21:28</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2156,17 +2156,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>01-02-2026 10:00:34</t>
+          <t>05-02-2026 19:25:52</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>01-02-2026 09:59:59</t>
+          <t>05-02-2026 19:22:43</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26220521988460002587</t>
+          <t>26220522118170003054</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2194,11 +2194,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
           <t>499</t>
@@ -2206,24 +2202,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>339256</t>
+          <t>339592</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2233,17 +2229,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO</t>
+          <t>MARIA GUADALUPE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>LANDIN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2253,32 +2249,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5528464677</t>
+          <t>5588006100</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV. JOSE MARIA MARTINEZ MZA 24 LT 19 </t>
+          <t>EL CAPULIN</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12-01-1990</t>
+          <t>01-01-2000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ELDA.SOLRAC@GMAIL.COM</t>
+          <t>LANDINGUADALUPE95@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>30-01-2026 09:16:32</t>
+          <t>31-01-2026 09:45:22</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2289,7 +2285,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2299,17 +2295,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-02-2026 11:52:16</t>
+          <t>09-02-2026 14:59:33</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>30-01-2026 09:31:10</t>
+          <t>09-02-2026 14:59:02</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2319,7 +2315,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2329,10 +2325,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26220522007790002644</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+          <t>26220522194280003290</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2341,24 +2341,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>340216</t>
+          <t>342375</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AXEL ZADKYEL</t>
+          <t xml:space="preserve">DIANA AMELIA </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>SIERNA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2388,32 +2388,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5591647693</t>
+          <t>5532857495</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SAN BUENAVENTURA</t>
+          <t>AV DEL POPO MZA 56</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>24-05-2006</t>
+          <t>10-08-1975</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>AXELVALDEZ099@GMAL.COM</t>
+          <t>DIANAALINE10@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-02-2026 15:29:08</t>
+          <t>09-02-2026 18:11:48</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2434,17 +2434,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-02-2026 15:45:59</t>
+          <t>12-02-2026 18:14:46</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>02-02-2026 15:34:51</t>
+          <t>12-02-2026 18:13:56</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2464,10 +2464,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26220522015050002682</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+          <t>26220522301970003709</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2488,12 +2492,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>340315</t>
+          <t>342750</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2503,17 +2507,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MAYRA JAZMIN</t>
+          <t>MANUEL RAFAEL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KURY</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AVILES</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2523,32 +2527,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5561248221</t>
+          <t>5574265455</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IXTAP</t>
+          <t>C CEBADA MZ 6 LT 3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>13-08-1980</t>
+          <t>23-11-1999</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MAYRACGT@GMAIL.COM</t>
+          <t>MANUEL_LVNA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-02-2026 17:44:11</t>
+          <t>10-02-2026 17:23:26</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2559,7 +2563,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2569,17 +2573,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-02-2026 07:27:24</t>
+          <t>10-02-2026 17:27:27</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>03-02-2026 07:26:21</t>
+          <t>10-02-2026 17:26:23</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2589,7 +2593,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2599,14 +2603,10 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26220522032080002726</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522239800003484</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2615,24 +2615,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>342227</t>
+          <t>338952</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2642,17 +2642,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>YORDI JESUS</t>
+          <t xml:space="preserve">ANABEL </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PADRON</t>
+          <t>PLATA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2662,32 +2662,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5613711355</t>
+          <t>5543867324</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CDA HACIENDA DE JALPA MZ 19 LT 115C</t>
+          <t>CDA DE JAZMINEZ MZ 20 LT 10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>23-10-2002</t>
+          <t>22-10-1998</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>TREYOI.1023.ROCHA@GMAIL.COM</t>
+          <t>MAPA_220@HOTMAIL.ES</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>09-02-2026 15:55:59</t>
+          <t>29-01-2026 08:22:19</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2708,17 +2708,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>09-02-2026 16:06:40</t>
+          <t>01-02-2026 10:00:34</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>09-02-2026 16:06:13</t>
+          <t>01-02-2026 09:59:59</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2738,11 +2738,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26220522197030003304</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26220521988460002587</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>499</t>
@@ -2762,12 +2770,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340512</t>
+          <t>339256</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2777,17 +2785,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ROSA LIDIA</t>
+          <t>CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ANZALDO</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2797,32 +2805,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5521196367</t>
+          <t>5528464677</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IXTA</t>
+          <t xml:space="preserve">AV. JOSE MARIA MARTINEZ MZA 24 LT 19 </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>14-04-1993</t>
+          <t>12-01-1990</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ROSYN_N@HOTMAIL.COM</t>
+          <t>ELDA.SOLRAC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-02-2026 10:51:49</t>
+          <t>30-01-2026 09:16:32</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2833,27 +2841,27 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-02-2026 10:57:53</t>
+          <t>02-02-2026 11:52:16</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>03-02-2026 10:57:16</t>
+          <t>30-01-2026 09:31:10</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2863,7 +2871,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2873,14 +2881,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26220522036640002738</t>
+          <t>26220522007790002644</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2897,12 +2905,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>341951</t>
+          <t>339256</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2912,17 +2920,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIANA </t>
+          <t>CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2932,32 +2940,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5641136687</t>
+          <t>5528464677</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>RANCHO</t>
+          <t xml:space="preserve">AV. JOSE MARIA MARTINEZ MZA 24 LT 19 </t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>05-03-1965</t>
+          <t>12-01-1990</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ADRIANA.CERVANT.AL@GMAIL.COM</t>
+          <t>ELDA.SOLRAC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>08-02-2026 13:24:14</t>
+          <t>30-01-2026 09:16:32</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2968,7 +2976,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2978,17 +2986,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>08-02-2026 13:32:56</t>
+          <t>02-02-2026 11:52:16</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>08-02-2026 13:32:13</t>
+          <t>30-01-2026 09:31:10</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2998,7 +3006,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3008,7 +3016,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26220522172520003225</t>
+          <t>26220522007790002644</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3020,24 +3028,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>340960</t>
+          <t>340216</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3047,17 +3055,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LUIS ANGEL</t>
+          <t>AXEL ZADKYEL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AYALA</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3067,12 +3075,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5669156876</t>
+          <t>5591647693</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C TONATICO 197</t>
+          <t>SAN BUENAVENTURA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3082,17 +3090,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19-02-1993</t>
+          <t>24-05-2006</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BUICKGOLIFE856@GMAIL.COM</t>
+          <t>AXELVALDEZ099@GMAL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>04-02-2026 12:16:09</t>
+          <t>02-02-2026 15:29:08</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3113,17 +3121,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>04-02-2026 12:24:18</t>
+          <t>02-02-2026 15:45:59</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>04-02-2026 12:23:46</t>
+          <t>02-02-2026 15:34:51</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3143,7 +3151,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26220522073370002861</t>
+          <t>26220522015050002682</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3155,24 +3163,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342184</t>
+          <t>340315</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3182,17 +3190,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>MAYRA JAZMIN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>KURY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VICENTE</t>
+          <t>AVILES</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3202,32 +3210,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5537110647</t>
+          <t>5561248221</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COL SANTA CRUZ TLAPACOYA</t>
+          <t>IXTAP</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>25-07-2017</t>
+          <t>13-08-1980</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>KARINAFLORESVICENTE@GMAIL.COM</t>
+          <t>MAYRACGT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-02-2026 14:42:03</t>
+          <t>02-02-2026 17:44:11</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3238,7 +3246,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3248,17 +3256,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-02-2026 14:52:27</t>
+          <t>03-02-2026 07:27:24</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>09-02-2026 14:50:55</t>
+          <t>03-02-2026 07:26:21</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3278,10 +3286,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26220522193980003288</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
+          <t>26220522032080002726</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
@@ -3302,12 +3314,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342750</t>
+          <t>340516</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>18334</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3317,17 +3329,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MANUEL RAFAEL</t>
+          <t>CARLOS ENRIQUE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t xml:space="preserve">RUEDA </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3337,12 +3349,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5574265455</t>
+          <t>5619885190</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C CEBADA MZ 6 LT 3</t>
+          <t>IXTA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3352,17 +3364,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>23-11-1999</t>
+          <t>05-08-1991</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MANUEL_LVNA@HOTMAIL.COM</t>
+          <t>ENRIQUE-RUEDA@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>10-02-2026 17:23:26</t>
+          <t>03-02-2026 10:59:53</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3383,17 +3395,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>10-02-2026 17:27:27</t>
+          <t>03-02-2026 11:02:47</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>10-02-2026 17:26:23</t>
+          <t>03-02-2026 11:02:16</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3403,7 +3415,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3413,7 +3425,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26220522239800003484</t>
+          <t>26220522036720002739</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3425,24 +3437,24 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>341357</t>
+          <t>340512</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3452,17 +3464,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DAMIAN</t>
+          <t>ROSA LIDIA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTERO </t>
+          <t>ANZALDO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3472,67 +3484,75 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5634592607</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>5521196367</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>IXTA</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>25-11-2010</t>
+          <t>14-04-1993</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>DENI.QUINTERO2010@GMAIL.COM</t>
+          <t>ROSYN_N@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>05-02-2026 16:04:32</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 10:51:49</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>05-02-2026 16:09:19</t>
+          <t>03-02-2026 10:57:53</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>05-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>03-02-2026 10:57:16</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3540,14 +3560,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26220522109710003012</t>
+          <t>26220522036640002738</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3564,12 +3584,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342380</t>
+          <t>340960</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>18778</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3579,17 +3599,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DIANA ALINE</t>
+          <t>LUIS ANGEL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>AYALA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3599,32 +3619,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5625435058</t>
+          <t>5669156876</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">C CASTILLO DE CHAPULTEPEC </t>
+          <t>C TONATICO 197</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>22-12-1996</t>
+          <t>19-02-1993</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>DIGTZ15@GMAIL.COM</t>
+          <t>BUICKGOLIFE856@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>09-02-2026 18:16:13</t>
+          <t>04-02-2026 12:16:09</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3645,17 +3665,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>12-02-2026 18:19:45</t>
+          <t>04-02-2026 12:24:18</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>12-02-2026 18:19:19</t>
+          <t>04-02-2026 12:23:46</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3675,14 +3695,10 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26220522302230003710</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522073370002861</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3691,24 +3707,24 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342745</t>
+          <t>341101</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20562</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3718,17 +3734,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ITZEL STEPHANY</t>
+          <t>CHRISTIAN OWEN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VERDE</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SERVIN</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3738,32 +3754,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5584585348</t>
+          <t>5643127118</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CDA BARRANCA DE MEZQUITE MZ 56</t>
+          <t>C CATEDRAL METROPOLITANA 204</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>21-12-1995</t>
+          <t>18-06-2011</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ITZEL_VERDE95@ICLOUD.COM</t>
+          <t>CHRISTIAN09MENDEZ1234@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10-02-2026 17:16:16</t>
+          <t>04-02-2026 17:18:13</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3784,17 +3800,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10-02-2026 17:21:18</t>
+          <t>04-02-2026 17:31:39</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10-02-2026 17:20:26</t>
+          <t>04-02-2026 17:30:29</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3804,7 +3820,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3814,7 +3830,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26220522239450003479</t>
+          <t>26220522082650002911</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3826,7 +3842,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3838,12 +3854,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>341099</t>
+          <t>341357</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3853,17 +3869,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AXEL KALID</t>
+          <t>DAMIAN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t xml:space="preserve">QUINTERO </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3873,14 +3889,10 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5635122950</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>C CATEDRAL METROPOLITANA 204</t>
-        </is>
-      </c>
+          <t>5634592607</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3888,60 +3900,56 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>23-07-2004</t>
+          <t>25-11-2010</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>GUERREROAXEL190@GMAIL.COM</t>
+          <t>DENI.QUINTERO2010@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>04-02-2026 17:15:27</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>05-02-2026 16:04:32</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>04-02-2026 17:26:19</t>
+          <t>05-02-2026 16:09:19</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>04-02-2026 17:25:23</t>
-        </is>
-      </c>
+          <t>05-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3949,36 +3957,36 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26220522082390002907</t>
+          <t>26220522109710003012</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>341894</t>
+          <t>344676</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3988,17 +3996,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">JONATHAN </t>
+          <t>JESSICA BERENICE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">URBAN </t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4008,35 +4016,39 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5574445964</t>
+          <t>2219009457</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LOTOS</t>
+          <t>C CIPRECES MZ 3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>06-12-1990</t>
+          <t>02-04-1995</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>SOLDADO.DE.DIOS@HOTMAIL.COM</t>
+          <t>JEBER18@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>08-02-2026 10:05:09</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>17-02-2026 19:05:24</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4054,17 +4066,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>08-02-2026 10:07:34</t>
+          <t>17-02-2026 19:14:49</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>08-02-2026 10:07:05</t>
+          <t>17-02-2026 19:14:20</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4084,7 +4096,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26220522169210003211</t>
+          <t>26220522443720004140</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -4096,24 +4108,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342097</t>
+          <t>341951</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4123,17 +4135,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALICIA </t>
+          <t xml:space="preserve">ADRIANA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUCEDO </t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4143,12 +4155,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5522530023</t>
+          <t>5641136687</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CDA MAGDALENA SN IXTAPALUCA</t>
+          <t>RANCHO</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4158,24 +4170,20 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>23-03-1966</t>
+          <t>05-03-1965</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>SAUCEDOGALICIAALICIA32@GMAIL.COM</t>
+          <t>ADRIANA.CERVANT.AL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-02-2026 10:35:09</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>08-02-2026 13:24:14</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4193,17 +4201,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>18-02-2026 15:06:39</t>
+          <t>08-02-2026 13:32:56</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>18-02-2026 15:05:44</t>
+          <t>08-02-2026 13:32:13</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4213,7 +4221,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4223,19 +4231,11 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26220522463670004215</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522172520003225</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>499</t>
@@ -4255,12 +4255,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>341889</t>
+          <t>342184</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LUCIA</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>VICENTE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4290,32 +4290,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5574445968</t>
+          <t>5537110647</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LOTOS</t>
+          <t>COL SANTA CRUZ TLAPACOYA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>06-03-1990</t>
+          <t>25-07-2017</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>LUCYCOSA06039@GMAIL.COM</t>
+          <t>KARINAFLORESVICENTE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>08-02-2026 09:58:42</t>
+          <t>09-02-2026 14:42:03</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4336,17 +4336,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>08-02-2026 10:02:56</t>
+          <t>09-02-2026 14:52:27</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>08-02-2026 10:02:01</t>
+          <t>09-02-2026 14:50:55</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26220522169080003210</t>
+          <t>26220522193980003288</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4390,12 +4390,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>341952</t>
+          <t>341099</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4405,17 +4405,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RAMON</t>
+          <t>AXEL KALID</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5520734799</t>
+          <t>5635122950</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>RANCHOO</t>
+          <t>C CATEDRAL METROPOLITANA 204</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4440,17 +4440,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>31-08-1964</t>
+          <t>23-07-2004</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MONN.64KAISER@GMAIL.COM</t>
+          <t>GUERREROAXEL190@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>08-02-2026 13:27:30</t>
+          <t>04-02-2026 17:15:27</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4471,17 +4471,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>08-02-2026 13:36:45</t>
+          <t>04-02-2026 17:26:19</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>08-02-2026 13:36:11</t>
+          <t>04-02-2026 17:25:23</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26220522172570003226</t>
+          <t>26220522082390002907</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4525,12 +4525,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342290</t>
+          <t>342745</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>20562</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4540,17 +4540,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ADRIANA ITZEL</t>
+          <t>ITZEL STEPHANY</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>VERDE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>SERVIN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5510440090</t>
+          <t>5584585348</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C VILLAHERMOSA MZA 47</t>
+          <t>CDA BARRANCA DE MEZQUITE MZ 56</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4575,24 +4575,20 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>14-08-1994</t>
+          <t>21-12-1995</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ADRIANANAVA149@GMAIL.COM</t>
+          <t>ITZEL_VERDE95@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-02-2026 16:53:59</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 17:16:16</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4610,17 +4606,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:20</t>
+          <t>10-02-2026 17:21:18</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>18-02-2026 18:13:49</t>
+          <t>10-02-2026 17:20:26</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4630,7 +4626,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4640,14 +4636,10 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26220522471810004257</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522239450003479</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4656,24 +4648,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342287</t>
+          <t>344433</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4683,17 +4675,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IRVING DONNOVAN</t>
+          <t>IRIS MONTSERRAT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO </t>
+          <t>CHAVARIN</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4703,35 +4695,39 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5564343538</t>
+          <t>5564692994</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C PERA SAN MARCOS</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>06-09-1992</t>
+          <t>29-08-1994</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>DONNOVANBR@OUTLOOK.COM</t>
+          <t>MONTSERRAT_94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>09-02-2026 16:52:02</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>17-02-2026 10:03:24</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4749,17 +4745,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>12-02-2026 18:07:17</t>
+          <t>17-02-2026 10:10:20</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>12-02-2026 18:06:58</t>
+          <t>17-02-2026 10:08:56</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4779,14 +4775,10 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26220522301550003706</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522423620004039</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4807,12 +4799,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>341922</t>
+          <t>341894</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>19712</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4822,17 +4814,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>YANNEVY ARIADNE</t>
+          <t xml:space="preserve">JONATHAN </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t xml:space="preserve">URBAN </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4842,32 +4834,32 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5580261394</t>
+          <t>5574445964</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>HEROES</t>
+          <t>LOTOS</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>25-11-1994</t>
+          <t>06-12-1990</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>YENNEVY@GMAIL.COM</t>
+          <t>SOLDADO.DE.DIOS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>08-02-2026 11:53:18</t>
+          <t>08-02-2026 10:05:09</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4888,7 +4880,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>08-02-2026 11:58:57</t>
+          <t>08-02-2026 10:07:34</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4898,7 +4890,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>08-02-2026 11:57:36</t>
+          <t>08-02-2026 10:07:05</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4918,7 +4910,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26220522171210003218</t>
+          <t>26220522169210003211</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4930,24 +4922,24 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>David Guillermo  Fuentes Carrillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342048</t>
+          <t>342097</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4957,17 +4949,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DULCE IVONNE</t>
+          <t xml:space="preserve">ALICIA </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t xml:space="preserve">SAUCEDO </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ZARCO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4977,12 +4969,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5519303247</t>
+          <t>5522530023</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">C. LA CIGARRA COL. ESPERANZA </t>
+          <t>CDA MAGDALENA SN IXTAPALUCA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4992,20 +4984,24 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>01-08-1991</t>
+          <t>23-03-1966</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>DULCEIVONNETORRESZARCO@GMAIL.COM</t>
+          <t>SAUCEDOGALICIAALICIA32@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>09-02-2026 08:22:24</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>09-02-2026 10:35:09</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5023,17 +5019,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>09-02-2026 08:34:47</t>
+          <t>18-02-2026 15:06:39</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>09-02-2026 08:34:00</t>
+          <t>18-02-2026 15:05:44</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5043,7 +5039,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5053,11 +5049,19 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26220522185040003259</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>26220522463670004215</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>499</t>
@@ -5065,24 +5069,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342192</t>
+          <t>345379</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20010</t>
+          <t>87544</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5092,17 +5096,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JESUS ZAID</t>
+          <t>EMMANUEL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BORREGO</t>
+          <t>DE JESUS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5112,12 +5116,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4055882651</t>
+          <t>5581003622</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">C MELCHOR OCAMPO S/N COL. LA ESPERANZA </t>
+          <t>C AGUSTIN DE ITURBIDE 228</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5127,20 +5131,24 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>23-12-1999</t>
+          <t>17-12-1995</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>SAIDD.BST@GMAIL.COM</t>
+          <t>EMMANUELDJF17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-02-2026 14:52:50</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>20-02-2026 18:06:05</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5158,17 +5166,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 15:06:28</t>
+          <t>20-02-2026 18:17:25</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>09-02-2026 15:05:32</t>
+          <t>20-02-2026 18:16:44</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5188,7 +5196,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26220522194630003292</t>
+          <t>26220522533780004518</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5200,7 +5208,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5212,12 +5220,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>343831</t>
+          <t>341889</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5227,17 +5235,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JESSICA</t>
+          <t>LUCIA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5247,12 +5255,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2217041181</t>
+          <t>5574445968</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CALLE MAGNOLIA 242</t>
+          <t>LOTOS</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5262,17 +5270,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>14-12-1998</t>
+          <t>06-03-1990</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>JESSICAHERNANDEZVAZQUEZ@OUTLOOK.COM</t>
+          <t>LUCYCOSA06039@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:19</t>
+          <t>08-02-2026 09:58:42</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5293,22 +5301,22 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:20</t>
+          <t>08-02-2026 10:02:56</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:20</t>
+          <t>08-02-2026 10:02:01</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -5323,7 +5331,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26220522365380003866</t>
+          <t>26220522169080003210</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5347,12 +5355,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>344433</t>
+          <t>341952</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5362,12 +5370,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IRIS MONTSERRAT</t>
+          <t>RAMON</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CHAVARIN</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5382,39 +5390,35 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5564692994</t>
+          <t>5520734799</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>RANCHOO</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>29-08-1994</t>
+          <t>31-08-1964</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>MONTSERRAT_94@HOTMAIL.COM</t>
+          <t>MONN.64KAISER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>17-02-2026 10:03:24</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>08-02-2026 13:27:30</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5432,17 +5436,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>17-02-2026 10:10:20</t>
+          <t>08-02-2026 13:36:45</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>17-02-2026 10:08:56</t>
+          <t>08-02-2026 13:36:11</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5452,7 +5456,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5462,7 +5466,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26220522423620004039</t>
+          <t>26220522172570003226</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5474,24 +5478,24 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342536</t>
+          <t>346013</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>88178</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5501,17 +5505,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HANNIA ATZIRY</t>
+          <t>MICHELLE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5521,12 +5525,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5541561912</t>
+          <t>5619228106</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TEJALPA</t>
+          <t>C ORIENTE 32 MZ 25</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5536,48 +5540,52 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>22-01-1997</t>
+          <t>30-07-2003</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>HANNIA_22_SANDOVAL@HOTMAIL.COM</t>
+          <t>MICHELLE.GOMZ2303@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>10-02-2026 07:49:10</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>23-02-2026 19:02:28</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>10-02-2026 07:55:17</t>
+          <t>23-02-2026 19:08:04</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>10-02-2026 07:53:33</t>
+          <t>23-02-2026 19:07:28</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5587,7 +5595,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5597,19 +5605,19 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26220522224790003405</t>
+          <t>26220522598490004729</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5621,12 +5629,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>343824</t>
+          <t>342287</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5636,17 +5644,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MARISOL</t>
+          <t>IRVING DONNOVAN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t xml:space="preserve">BRAVO </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5656,32 +5664,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5531971979</t>
+          <t>5564343538</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COL CENTRO CDMX</t>
+          <t>C PERA SAN MARCOS</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>02-03-1973</t>
+          <t>06-09-1992</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>MAPGUE2@GMAIL.COM</t>
+          <t>DONNOVANBR@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>15-02-2026 12:05:48</t>
+          <t>09-02-2026 16:52:02</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5702,17 +5710,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>15-02-2026 12:25:35</t>
+          <t>12-02-2026 18:07:17</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>15-02-2026 12:18:06</t>
+          <t>12-02-2026 18:06:58</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5732,10 +5740,14 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26220522365480003867</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
+          <t>26220522301550003706</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
@@ -5756,12 +5768,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>344895</t>
+          <t>342380</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22712</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5771,17 +5783,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ALMA ROSA BASILISA</t>
+          <t>DIANA ALINE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5791,12 +5803,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5611775850</t>
+          <t>5625435058</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>C JOSE MARIA MORELOS</t>
+          <t xml:space="preserve">C CASTILLO DE CHAPULTEPEC </t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5806,24 +5818,20 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>02-04-1963</t>
+          <t>22-12-1996</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ALMAROSACASTRO@HOTMAIL.COM</t>
+          <t>DIGTZ15@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>18-02-2026 17:26:28</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 18:16:13</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5841,17 +5849,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>18-02-2026 17:48:07</t>
+          <t>12-02-2026 18:19:45</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>18-02-2026 17:46:56</t>
+          <t>12-02-2026 18:19:19</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5871,10 +5879,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26220522470370004248</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
+          <t>26220522302230003710</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
@@ -5895,12 +5907,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>343503</t>
+          <t>342290</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5910,17 +5922,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DIANA VIANEY</t>
+          <t>ADRIANA ITZEL</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARREON </t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>YAÑEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5930,12 +5942,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5614816775</t>
+          <t>5510440090</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>C TEPOYAN 5</t>
+          <t>C VILLAHERMOSA MZA 47</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5945,20 +5957,24 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>16-10-1986</t>
+          <t>14-08-1994</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>DIANACARREON995@GMAIL.COM</t>
+          <t>ADRIANANAVA149@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>13-02-2026 14:48:21</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>09-02-2026 16:53:59</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5976,17 +5992,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>13-02-2026 15:06:00</t>
+          <t>18-02-2026 18:14:20</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>13-02-2026 15:05:03</t>
+          <t>18-02-2026 18:13:49</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5996,7 +6012,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6006,10 +6022,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26220522322030003760</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
+          <t>26220522471810004257</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
@@ -6030,12 +6050,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>345233</t>
+          <t>341922</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>87398</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6045,17 +6065,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONEL YUARI </t>
+          <t>YANNEVY ARIADNE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANRIQUEZ </t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6065,39 +6085,35 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5521514699</t>
+          <t>5580261394</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZOL AGRICOLA ORIENTAL </t>
+          <t>HEROES</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>27-06-2004</t>
+          <t>25-11-1994</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>STARCICI@GMAIL.COM</t>
+          <t>YENNEVY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>20-02-2026 09:01:39</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>08-02-2026 11:53:18</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6115,17 +6131,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>20-02-2026 09:08:59</t>
+          <t>08-02-2026 11:58:57</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>20-02-2026 09:08:21</t>
+          <t>08-02-2026 11:57:36</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6135,7 +6151,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -6145,7 +6161,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26220522522290004459</t>
+          <t>26220522171210003218</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6157,24 +6173,24 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>342375</t>
+          <t>344895</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>22712</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6184,17 +6200,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA AMELIA </t>
+          <t>ALMA ROSA BASILISA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SIERNA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6204,12 +6220,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5532857495</t>
+          <t>5611775850</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AV DEL POPO MZA 56</t>
+          <t>C JOSE MARIA MORELOS</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6219,20 +6235,24 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>10-08-1975</t>
+          <t>02-04-1963</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>DIANAALINE10@HOTMAIL.COM</t>
+          <t>ALMAROSACASTRO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>09-02-2026 18:11:48</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>18-02-2026 17:26:28</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6250,17 +6270,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>12-02-2026 18:14:46</t>
+          <t>18-02-2026 17:48:07</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>12-02-2026 18:13:56</t>
+          <t>18-02-2026 17:46:56</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6280,14 +6300,10 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26220522301970003709</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522470370004248</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
@@ -6308,12 +6324,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>343301</t>
+          <t>345233</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>87398</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6323,17 +6339,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t xml:space="preserve">LEONEL YUARI </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ESPEJEL</t>
+          <t xml:space="preserve">MANRIQUEZ </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6343,12 +6359,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5516346350</t>
+          <t>5521514699</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
+          <t xml:space="preserve">ZOL AGRICOLA ORIENTAL </t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6358,20 +6374,24 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>06-07-1995</t>
+          <t>27-06-2004</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>DIEGOLUPPUS@GMAIL.COM</t>
+          <t>STARCICI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>12-02-2026 16:04:34</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>20-02-2026 09:01:39</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6389,17 +6409,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>12-02-2026 16:26:22</t>
+          <t>20-02-2026 09:08:59</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>12-02-2026 16:25:47</t>
+          <t>20-02-2026 09:08:21</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6409,7 +6429,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -6419,7 +6439,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26220522297530003689</t>
+          <t>26220522522290004459</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
@@ -6431,24 +6451,24 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>343505</t>
+          <t>342048</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6458,17 +6478,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ALVARO O BRIAN</t>
+          <t>DULCE IVONNE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>VALADEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>BLANCA</t>
+          <t>ZARCO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6478,32 +6498,32 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5591919598</t>
+          <t>5519303247</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AV NUEVO MEXICO 301</t>
+          <t xml:space="preserve">C. LA CIGARRA COL. ESPERANZA </t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>12-09-1993</t>
+          <t>01-08-1991</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>POSEIDONBALA93@OUTLOOK.COM</t>
+          <t>DULCEIVONNETORRESZARCO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>13-02-2026 14:50:25</t>
+          <t>09-02-2026 08:22:24</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6524,17 +6544,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>13-02-2026 14:59:34</t>
+          <t>09-02-2026 08:34:47</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>13-02-2026 14:59:07</t>
+          <t>09-02-2026 08:34:00</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6554,7 +6574,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26220522321910003759</t>
+          <t>26220522185040003259</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6578,12 +6598,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>343544</t>
+          <t>342192</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6593,17 +6613,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LAURA AMAYRANI</t>
+          <t>JESUS ZAID</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>BORREGO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6613,32 +6633,32 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5546447212</t>
+          <t>4055882651</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
+          <t xml:space="preserve">C MELCHOR OCAMPO S/N COL. LA ESPERANZA </t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>13-03-2007</t>
+          <t>23-12-1999</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>LAUPRD25@GMAIL.COM</t>
+          <t>SAIDD.BST@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>13-02-2026 17:03:29</t>
+          <t>09-02-2026 14:52:50</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6659,17 +6679,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:38</t>
+          <t>09-02-2026 15:06:28</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>13-02-2026 17:18:02</t>
+          <t>09-02-2026 15:05:32</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6689,7 +6709,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26220522326190003779</t>
+          <t>26220522194630003292</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
@@ -6701,7 +6721,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6713,12 +6733,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>343838</t>
+          <t>343831</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6728,17 +6748,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>JESSICA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORAN </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6748,7 +6768,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2206073345</t>
+          <t>2217041181</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6758,22 +6778,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>26-02-1995</t>
+          <t>14-12-1998</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>TRILLISO_BET@HOTMAIL.COM</t>
+          <t>JESSICAHERNANDEZVAZQUEZ@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>15-02-2026 12:21:19</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6794,7 +6814,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>15-02-2026 12:21:20</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6804,7 +6824,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>15-02-2026 12:21:20</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6824,7 +6844,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26220522365710003869</t>
+          <t>26220522365380003866</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6848,12 +6868,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>343539</t>
+          <t>342536</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6863,17 +6883,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ROCIO</t>
+          <t>HANNIA ATZIRY</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JAIMEZ</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6883,12 +6903,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5534063877</t>
+          <t>5541561912</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>C CUAUTZINGO MZA 34</t>
+          <t>TEJALPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6898,17 +6918,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>12-01-1998</t>
+          <t>22-01-1997</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
+          <t>HANNIA_22_SANDOVAL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>13-02-2026 16:58:39</t>
+          <t>10-02-2026 07:49:10</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6929,17 +6949,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>13-02-2026 17:12:37</t>
+          <t>10-02-2026 07:55:17</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>13-02-2026 17:10:18</t>
+          <t>10-02-2026 07:53:33</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6949,7 +6969,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6959,7 +6979,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26220522325890003776</t>
+          <t>26220522224790003405</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -6971,7 +6991,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6983,12 +7003,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>344217</t>
+          <t>343503</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22034</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6998,17 +7018,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>DIANA VIANEY</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">CARREON </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ELIZALDE</t>
+          <t>YAÑEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7018,39 +7038,35 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>7473547605</t>
+          <t>5614816775</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV. NIÑOS HEROES COL. SANTA CRUZ </t>
+          <t>C TEPOYAN 5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>09-07-1998</t>
+          <t>16-10-1986</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ALEXGARCIAE@GMAIL.COM</t>
+          <t>DIANACARREON995@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>16-02-2026 17:34:05</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>13-02-2026 14:48:21</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7068,17 +7084,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>19-02-2026 15:50:26</t>
+          <t>13-02-2026 15:06:00</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>19-02-2026 15:49:51</t>
+          <t>13-02-2026 15:05:03</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7098,14 +7114,10 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26220522497590004364</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522322030003760</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
@@ -7126,12 +7138,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344931</t>
+          <t>343301</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7141,17 +7153,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ANDRES JESUS</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>ESPEJEL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7161,12 +7173,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5537346724</t>
+          <t>5516346350</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>MZ H EDIF 2B</t>
+          <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7176,24 +7188,20 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>10-11-1992</t>
+          <t>06-07-1995</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>RAZIEL_FO@HOTMAIL.COM</t>
+          <t>DIEGOLUPPUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>18-02-2026 18:46:57</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 16:04:34</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7211,17 +7219,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>18-02-2026 18:54:43</t>
+          <t>12-02-2026 16:26:22</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>18-02-2026 18:52:58</t>
+          <t>12-02-2026 16:25:47</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7231,7 +7239,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -7241,7 +7249,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26220522473750004279</t>
+          <t>26220522297530003689</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7253,24 +7261,24 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>345074</t>
+          <t>343505</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>87239</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7280,17 +7288,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SANDRA ESTRELLA</t>
+          <t>ALVARO O BRIAN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>VALADEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>BLANCA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7300,67 +7308,75 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5545570437</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>5591919598</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>AV NUEVO MEXICO 301</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>19-06-1974</t>
+          <t>12-09-1993</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>GARCIA_SANDRA98@YAHOO.COM.MX</t>
+          <t>POSEIDONBALA93@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>19-02-2026 14:14:15</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 14:50:25</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>23-02-2026 14:12:47</t>
+          <t>13-02-2026 14:59:34</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>13-02-2026 14:59:07</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7368,22 +7384,14 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26220522581980004643</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>DIANA MADRID ORTIZ</t>
-        </is>
-      </c>
+          <t>26220522321910003759</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7400,12 +7408,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344233</t>
+          <t>343544</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22050</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7415,17 +7423,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>LAURA AMAYRANI</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEREZ </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7435,12 +7443,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5611753742</t>
+          <t>5546447212</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRACC LOS HEROES </t>
+          <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7450,24 +7458,20 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>07-08-1998</t>
+          <t>13-03-2007</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CASTROMARIAFERNANDA57@GMAIL.COM</t>
+          <t>LAUPRD25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-02-2026 17:43:53</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>13-02-2026 17:03:29</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7485,17 +7489,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>16-02-2026 18:16:35</t>
+          <t>13-02-2026 17:19:38</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>16-02-2026 18:15:46</t>
+          <t>13-02-2026 17:18:02</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7515,7 +7519,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26220522403640003978</t>
+          <t>26220522326190003779</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7539,12 +7543,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>345401</t>
+          <t>343838</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>87566</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7554,17 +7558,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>MELANY SAMANTHA</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">MORAN </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ESPINOSA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7574,77 +7578,73 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5636743221</t>
+          <t>2206073345</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>AV DE CANAL MZ 27</t>
+          <t>CALLE MAGNOLIA 242</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>03-09-2007</t>
+          <t>26-02-1995</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>MELANILOPES36@GMAIL.COM</t>
+          <t>TRILLISO_BET@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>20-02-2026 18:57:58</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-02-2026 12:36:33</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>24-02-2026 18:38:06</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>24-02-2026 18:37:40</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7654,18 +7654,14 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26220522632110004851</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522365710003869</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -7682,12 +7678,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>344626</t>
+          <t>343824</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21641</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7697,17 +7693,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>IXCHEL YARELI</t>
+          <t>MARISOL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIN </t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7717,12 +7713,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5579912763</t>
+          <t>5531971979</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>C DZILAM MZ 814 LT 4</t>
+          <t>COL CENTRO CDMX</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7732,52 +7728,48 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>31-01-1989</t>
+          <t>02-03-1973</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>IXCHELMARIN@OUTLOOK.COM</t>
+          <t>MAPGUE2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>17-02-2026 17:48:58</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-02-2026 12:05:48</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>PLAN FAMILIAR RECURRENTE $999</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>17-02-2026 18:01:12</t>
+          <t>15-02-2026 12:25:35</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>17-02-2026 17:59:12</t>
+          <t>15-02-2026 12:18:06</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7787,7 +7779,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7797,36 +7789,36 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26220522439570004122</t>
+          <t>26220522365480003867</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>345977</t>
+          <t>344217</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>88142</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7836,17 +7828,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PAYAN</t>
+          <t>ELIZALDE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7856,10 +7848,14 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>5586887467</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>7473547605</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV. NIÑOS HEROES COL. SANTA CRUZ </t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7867,52 +7863,64 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>01-11-1978</t>
+          <t>09-07-1998</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>JUANCARLOSLARAPAYAN@GMAIL.COM</t>
+          <t>ALEXGARCIAE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>23-02-2026 18:23:19</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>16-02-2026 17:34:05</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>23-02-2026 18:25:30</t>
+          <t>19-02-2026 15:50:26</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>23-03-2027 23:59:59</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>19-02-2026 15:49:51</t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7920,36 +7928,40 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26220522595510004713</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
+          <t>26220522497590004364</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>344432</t>
+          <t>344233</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>22050</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7959,17 +7971,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t xml:space="preserve">JEREZ </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7979,32 +7991,32 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>5515226715</t>
+          <t>5611753742</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ALFREDIO</t>
+          <t xml:space="preserve">FRACC LOS HEROES </t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>23-08-1991</t>
+          <t>07-08-1998</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>LIC.ALFREDO.91@GMAIL.COM</t>
+          <t>CASTROMARIAFERNANDA57@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>17-02-2026 09:59:28</t>
+          <t>16-02-2026 17:43:53</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8029,17 +8041,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>17-02-2026 10:14:17</t>
+          <t>16-02-2026 18:16:35</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>17-02-2026 10:13:36</t>
+          <t>16-02-2026 18:15:46</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -8059,7 +8071,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26220522423710004040</t>
+          <t>26220522403640003978</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
@@ -8071,24 +8083,24 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>345338</t>
+          <t>343539</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>87503</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8098,17 +8110,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUADALUPE </t>
+          <t>ROCIO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>JAIMEZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CARRANZA</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8118,12 +8130,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5615722096</t>
+          <t>5534063877</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRACC HACIENDA DE LAS PALMAS III </t>
+          <t>C CUAUTZINGO MZA 34</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8133,24 +8145,20 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>03-09-1981</t>
+          <t>12-01-1998</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>GUADALUPECARRANZA2830@GMAIL.COM</t>
+          <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>20-02-2026 16:38:08</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:58:39</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8168,17 +8176,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>20-02-2026 16:51:02</t>
+          <t>13-02-2026 17:12:37</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>20-02-2026 16:49:11</t>
+          <t>13-02-2026 17:10:18</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8188,7 +8196,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -8198,7 +8206,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26220522530660004497</t>
+          <t>26220522325890003776</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
@@ -8222,12 +8230,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>344940</t>
+          <t>344900</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>22717</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8237,17 +8245,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRANDON </t>
+          <t>ADRIAN BERENICE</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MONTESINOS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8257,39 +8265,31 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>5613578379</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>C CIPRECES MZA 3</t>
-        </is>
-      </c>
+          <t>5540961768</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>08-03-1994</t>
+          <t>05-03-1999</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BRANDON.FAMDA@GMAIL.COM</t>
+          <t>BEREADRY99@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>18-02-2026 19:14:37</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>18-02-2026 17:32:28</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>18-02-2026 19:17:54</t>
+          <t>18-02-2026 17:43:39</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>18-02-2026 19:17:35</t>
+          <t>18-02-2026 17:43:01</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26220522474720004282</t>
+          <t>26220522470070004245</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
@@ -8349,24 +8349,24 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>346085</t>
+          <t>345055</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>88250</t>
+          <t>87220</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8376,17 +8376,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARACELI </t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALMORAN </t>
+          <t>TALAVERA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>VILLAGOMEZ</t>
+          <t>PANIAGUA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8396,67 +8396,79 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5539066958</t>
+          <t>5540308509</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>C SUR 171</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>16-11-1982</t>
+          <t>20-02-1963</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>ARACELI.TSGS@GMAIL.COM</t>
+          <t>ANGELTALAVERAP63@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>24-02-2026 08:14:04</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>19-02-2026 13:00:23</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>24-02-2026 08:00:00</t>
+          <t>19-02-2026 13:17:48</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>19-02-2026 13:16:38</t>
+        </is>
+      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8464,14 +8476,14 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26220522612860004768</t>
+          <t>26220522493820004335</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -8488,12 +8500,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>344934</t>
+          <t>345063</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22751</t>
+          <t>87228</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8503,17 +8515,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">YENNIFER </t>
+          <t>MARIA DE LA LUZ</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8523,12 +8535,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5512992481</t>
+          <t>5561186386</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TULTITLAM MEX</t>
+          <t>C SUR 171</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8538,52 +8550,52 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>17-09-1993</t>
+          <t>15-04-1963</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>YLOPEZFLORES17@GMAIL.COM</t>
+          <t>LG.JACK63@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>18-02-2026 18:57:05</t>
+          <t>19-02-2026 13:21:09</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>18-02-2026 19:01:48</t>
+          <t>19-02-2026 13:30:22</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>18-02-2026 19:00:57</t>
+          <t>19-02-2026 13:29:04</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8593,7 +8605,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -8603,14 +8615,14 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26220522473980004280</t>
+          <t>26220522494100004341</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -8627,12 +8639,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>345129</t>
+          <t>344432</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>87294</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8642,17 +8654,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KIMBERLY ABIGAIL</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8662,32 +8674,32 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5619291534</t>
+          <t>5515226715</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>U HAB 4 VIENTOS</t>
+          <t>ALFREDIO</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>20-08-2007</t>
+          <t>23-08-1991</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>KKKIMBERLYY2@GMAIL.COM</t>
+          <t>LIC.ALFREDO.91@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>19-02-2026 16:52:09</t>
+          <t>17-02-2026 09:59:28</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8712,17 +8724,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>19-02-2026 17:04:47</t>
+          <t>17-02-2026 10:14:17</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>19-02-2026 17:03:32</t>
+          <t>17-02-2026 10:13:36</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8732,7 +8744,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -8742,7 +8754,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26220522500320004391</t>
+          <t>26220522423710004040</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
@@ -8766,12 +8778,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>345130</t>
+          <t>344626</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>87295</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8781,17 +8793,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MARISELA</t>
+          <t>IXCHEL YARELI</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t xml:space="preserve">MARIN </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8801,12 +8813,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5538014107</t>
+          <t>5579912763</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>U HAB 4 VIENTOS</t>
+          <t>C DZILAM MZ 814 LT 4</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8816,52 +8828,52 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>02-12-1975</t>
+          <t>31-01-1989</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>KIMBERLY89@GMAIL.COM</t>
+          <t>IXCHELMARIN@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>19-02-2026 16:54:23</t>
+          <t>17-02-2026 17:48:58</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIAR RECURRENTE $999</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>19-02-2026 17:08:32</t>
+          <t>17-02-2026 18:01:12</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>19-02-2026 17:08:01</t>
+          <t>17-02-2026 17:59:12</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8881,36 +8893,36 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26220522500550004392</t>
+          <t>26220522439570004122</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>344900</t>
+          <t>344934</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8920,17 +8932,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ADRIAN BERENICE</t>
+          <t xml:space="preserve">YENNIFER </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8940,10 +8952,14 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>5540961768</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>5512992481</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>TULTITLAM MEX</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8951,20 +8967,24 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>05-03-1999</t>
+          <t>17-09-1993</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>BEREADRY99@HOTMAIL.COM</t>
+          <t>YLOPEZFLORES17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>18-02-2026 17:32:28</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>18-02-2026 18:57:05</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8972,7 +8992,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -8982,7 +9002,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>18-02-2026 17:43:39</t>
+          <t>18-02-2026 19:01:48</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8992,7 +9012,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>18-02-2026 17:43:01</t>
+          <t>18-02-2026 19:00:57</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -9002,7 +9022,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -9012,7 +9032,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26220522470070004245</t>
+          <t>26220522473980004280</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
@@ -9024,24 +9044,24 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>345055</t>
+          <t>344931</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>87220</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9051,17 +9071,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>ANDRES JESUS</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>TALAVERA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PANIAGUA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9071,12 +9091,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>5540308509</t>
+          <t>5537346724</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>C SUR 171</t>
+          <t>MZ H EDIF 2B</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9086,52 +9106,52 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>20-02-1963</t>
+          <t>10-11-1992</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>ANGELTALAVERAP63@GMAIL.COM</t>
+          <t>RAZIEL_FO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>19-02-2026 13:00:23</t>
+          <t>18-02-2026 18:46:57</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>19-02-2026 13:17:48</t>
+          <t>18-02-2026 18:54:43</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>19-02-2026 13:16:38</t>
+          <t>18-02-2026 18:52:58</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -9141,7 +9161,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -9151,14 +9171,14 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26220522493820004335</t>
+          <t>26220522473750004279</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -9175,12 +9195,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>345063</t>
+          <t>345338</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>87228</t>
+          <t>87503</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9190,17 +9210,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MARIA DE LA LUZ</t>
+          <t xml:space="preserve">GUADALUPE </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>CARRANZA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9210,12 +9230,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>5561186386</t>
+          <t>5615722096</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>C SUR 171</t>
+          <t xml:space="preserve">FRACC HACIENDA DE LAS PALMAS III </t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -9225,52 +9245,52 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>15-04-1963</t>
+          <t>03-09-1981</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>LG.JACK63@GMAIL.COM</t>
+          <t>GUADALUPECARRANZA2830@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>19-02-2026 13:21:09</t>
+          <t>20-02-2026 16:38:08</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>19-02-2026 13:30:22</t>
+          <t>20-02-2026 16:51:02</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>19-02-2026 13:29:04</t>
+          <t>20-02-2026 16:49:11</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9290,36 +9310,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26220522494100004341</t>
+          <t>26220522530660004497</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>346020</t>
+          <t>344940</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>88185</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9329,17 +9349,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>JOSE RODOLFO</t>
+          <t xml:space="preserve">BRANDON </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MONTESINOS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9349,12 +9369,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5574468176</t>
+          <t>5613578379</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COL FRATERNIDAD ANTORCHISTA</t>
+          <t>C CIPRECES MZA 3</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -9364,52 +9384,52 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>06-10-1998</t>
+          <t>08-03-1994</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>ALCANTARAEZEQUIEL380@GMAIL.COM</t>
+          <t>BRANDON.FAMDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>23-02-2026 19:10:57</t>
+          <t>18-02-2026 19:14:37</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>23-02-2026 19:13:59</t>
+          <t>18-02-2026 19:17:54</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>23-02-2026 19:13:31</t>
+          <t>18-02-2026 19:17:35</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -9419,7 +9439,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -9429,36 +9449,36 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26220522598880004730</t>
+          <t>26220522474720004282</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>346618</t>
+          <t>345129</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>88783</t>
+          <t>87294</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9468,17 +9488,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">PATRICIA </t>
+          <t>KIMBERLY ABIGAIL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUNA </t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BENITEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9488,10 +9508,14 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>5526558363</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>5619291534</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>U HAB 4 VIENTOS</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9499,56 +9523,64 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>24-06-1991</t>
+          <t>20-08-2007</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>MANRIQUE_MARTIN@HOTMAIL.COM</t>
+          <t>KKKIMBERLYY2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>26-02-2026 04:34:59</t>
+          <t>19-02-2026 16:52:09</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>26-02-2026 04:36:22</t>
+          <t>19-02-2026 17:04:47</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:03:32</t>
+        </is>
+      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W67" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9556,36 +9588,36 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26220522669450004996</t>
+          <t>26220522500320004391</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>344676</t>
+          <t>345130</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22493</t>
+          <t>87295</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9595,17 +9627,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>JESSICA BERENICE</t>
+          <t>MARISELA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9615,12 +9647,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2219009457</t>
+          <t>5538014107</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>C CIPRECES MZ 3</t>
+          <t>U HAB 4 VIENTOS</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9630,17 +9662,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>02-04-1995</t>
+          <t>02-12-1975</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>JEBER18@YAHOO.COM.MX</t>
+          <t>KIMBERLY89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>17-02-2026 19:05:24</t>
+          <t>19-02-2026 16:54:23</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -9665,17 +9697,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>17-02-2026 19:14:49</t>
+          <t>19-02-2026 17:08:32</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>17-02-2026 19:14:20</t>
+          <t>19-02-2026 17:08:01</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -9695,7 +9727,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26220522443720004140</t>
+          <t>26220522500550004392</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
@@ -9707,24 +9739,24 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>346617</t>
+          <t>345074</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>88782</t>
+          <t>87239</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9734,17 +9766,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRISTIAN </t>
+          <t>SANDRA ESTRELLA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MANRIQUEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9754,28 +9786,28 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>5513431982</t>
+          <t>5545570437</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>22-07-1992</t>
+          <t>19-06-1974</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CRISTIAN_@HOTMAIL.COM</t>
+          <t>GARCIA_SANDRA98@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>26-02-2026 04:30:59</t>
+          <t>19-02-2026 14:14:15</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -9790,28 +9822,28 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>26-02-2026 04:33:00</t>
+          <t>23-02-2026 14:12:47</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V69" t="inlineStr"/>
@@ -9822,14 +9854,22 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26220522669400004995</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
+          <t>26220522581980004643</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>DIANA MADRID ORTIZ</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -9846,12 +9886,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>345379</t>
+          <t>345401</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>87544</t>
+          <t>87566</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9861,17 +9901,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EMMANUEL</t>
+          <t>MELANY SAMANTHA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>DE JESUS</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>ESPINOSA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9881,67 +9921,67 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>5581003622</t>
+          <t>5636743221</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>C AGUSTIN DE ITURBIDE 228</t>
+          <t>AV DE CANAL MZ 27</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>17-12-1995</t>
+          <t>03-09-2007</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>EMMANUELDJF17@GMAIL.COM</t>
+          <t>MELANILOPES36@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>20-02-2026 18:06:05</t>
+          <t>20-02-2026 18:57:58</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>20-02-2026 18:17:25</t>
+          <t>24-02-2026 18:38:06</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>20-02-2026 18:16:44</t>
+          <t>24-02-2026 18:37:40</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -9961,36 +10001,40 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26220522533780004518</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr"/>
+          <t>26220522632110004851</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>346013</t>
+          <t>346617</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>88178</t>
+          <t>88782</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10000,17 +10044,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MICHELLE</t>
+          <t xml:space="preserve">CRISTIAN </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>MANRIQUEZ</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -10020,32 +10064,28 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>5619228106</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>C ORIENTE 32 MZ 25</t>
-        </is>
-      </c>
+          <t>5513431982</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>30-07-2003</t>
+          <t>22-07-1992</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>MICHELLE.GOMZ2303@GMAIL.COM</t>
+          <t>CRISTIAN_@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>23-02-2026 19:02:28</t>
+          <t>26-02-2026 04:30:59</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -10055,44 +10095,36 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>23-02-2026 19:08:04</t>
+          <t>26-02-2026 04:33:00</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>23-02-2026 19:07:28</t>
-        </is>
-      </c>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10100,22 +10132,681 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26220522598490004729</t>
+          <t>26220522669400004995</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>346215</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>88380</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NANCY IVONN</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>CASTILLO</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>5514373677</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>IXTAPALIUUCA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>23-11-1977</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>GONZALEZCASTILLONANCYIVONN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>24-02-2026 16:32:59</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>27-02-2026 07:54:16</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>27-02-2026 07:53:55</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>26220522705980005132</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Luis Antonio  Chaparro Alonso</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>345977</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>88142</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>LARA</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>PAYAN</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>5586887467</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>01-11-1978</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>JUANCARLOSLARAPAYAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:23:19</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>461.46</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:25:30</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>23-03-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>26220522595510004713</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>5999</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>Luis Antonio  Chaparro Alonso</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>346085</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>88250</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARACELI </t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALMORAN </t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>VILLAGOMEZ</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>5539066958</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>ALFREDO</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>16-11-1982</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>ARACELI.TSGS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>24-02-2026 08:14:04</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>24-02-2026 08:00:00</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>26220522612860004768</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>346618</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>88783</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PATRICIA </t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUNA </t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>BENITEZ</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5526558363</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>24-06-1991</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>MANRIQUE_MARTIN@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>26-02-2026 04:34:59</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>26-02-2026 04:36:22</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>26220522669450004996</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>346020</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>88185</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>JOSE RODOLFO</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>5574468176</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>COL FRATERNIDAD ANTORCHISTA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>06-10-1998</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>ALCANTARAEZEQUIEL380@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:10:57</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:13:59</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:13:31</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>26220522598880004730</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
         <is>
           <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
+      <c r="AC76" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
@@ -1940,12 +1940,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>342227</t>
+          <t>339174</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>YORDI JESUS</t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t>CRISOSTOMO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PADRON</t>
+          <t>CARDOSO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5613711355</t>
+          <t>5550539848</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CDA HACIENDA DE JALPA MZ 19 LT 115C</t>
+          <t>CDA 21 DE MARZO 12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1990,17 +1990,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>23-10-2002</t>
+          <t>03-06-1998</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>TREYOI.1023.ROCHA@GMAIL.COM</t>
+          <t>DEIVID.AYD.CRI98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>09-02-2026 15:55:59</t>
+          <t>29-01-2026 19:21:28</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2021,17 +2021,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>09-02-2026 16:06:40</t>
+          <t>05-02-2026 19:25:52</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>09-02-2026 16:06:13</t>
+          <t>05-02-2026 19:22:43</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2051,10 +2051,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26220522197030003304</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26220522118170003054</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2063,24 +2067,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>339174</t>
+          <t>342227</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2090,17 +2094,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>YORDI JESUS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CRISOSTOMO</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CARDOSO</t>
+          <t>PADRON</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2110,12 +2114,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5550539848</t>
+          <t>5613711355</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CDA 21 DE MARZO 12</t>
+          <t>CDA HACIENDA DE JALPA MZ 19 LT 115C</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2125,17 +2129,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>03-06-1998</t>
+          <t>23-10-2002</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>DEIVID.AYD.CRI98@GMAIL.COM</t>
+          <t>TREYOI.1023.ROCHA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>29-01-2026 19:21:28</t>
+          <t>09-02-2026 15:55:59</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2156,17 +2160,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>05-02-2026 19:25:52</t>
+          <t>09-02-2026 16:06:40</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>05-02-2026 19:22:43</t>
+          <t>09-02-2026 16:06:13</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2176,7 +2180,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2186,14 +2190,10 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26220522118170003054</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522197030003304</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -2492,12 +2492,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>342750</t>
+          <t>340216</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2507,17 +2507,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MANUEL RAFAEL</t>
+          <t>AXEL ZADKYEL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5574265455</t>
+          <t>5591647693</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C CEBADA MZ 6 LT 3</t>
+          <t>SAN BUENAVENTURA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2542,17 +2542,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>23-11-1999</t>
+          <t>24-05-2006</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MANUEL_LVNA@HOTMAIL.COM</t>
+          <t>AXELVALDEZ099@GMAL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10-02-2026 17:23:26</t>
+          <t>02-02-2026 15:29:08</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2573,17 +2573,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>10-02-2026 17:27:27</t>
+          <t>02-02-2026 15:45:59</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>10-02-2026 17:26:23</t>
+          <t>02-02-2026 15:34:51</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26220522239800003484</t>
+          <t>26220522015050002682</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2615,24 +2615,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>338952</t>
+          <t>340315</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2642,17 +2642,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANABEL </t>
+          <t>MAYRA JAZMIN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>KURY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PLATA</t>
+          <t>AVILES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2662,12 +2662,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5543867324</t>
+          <t>5561248221</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CDA DE JAZMINEZ MZ 20 LT 10</t>
+          <t>IXTAP</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2677,17 +2677,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22-10-1998</t>
+          <t>13-08-1980</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MAPA_220@HOTMAIL.ES</t>
+          <t>MAYRACGT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>29-01-2026 08:22:19</t>
+          <t>02-02-2026 17:44:11</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2708,17 +2708,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>01-02-2026 10:00:34</t>
+          <t>03-02-2026 07:27:24</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>01-02-2026 09:59:59</t>
+          <t>03-02-2026 07:26:21</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26220521988460002587</t>
+          <t>26220522032080002726</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2746,11 +2746,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
           <t>499</t>
@@ -2758,24 +2754,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>339256</t>
+          <t>338952</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2785,17 +2781,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO</t>
+          <t xml:space="preserve">ANABEL </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>PLATA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2805,32 +2801,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5528464677</t>
+          <t>5543867324</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV. JOSE MARIA MARTINEZ MZA 24 LT 19 </t>
+          <t>CDA DE JAZMINEZ MZ 20 LT 10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>12-01-1990</t>
+          <t>22-10-1998</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ELDA.SOLRAC@GMAIL.COM</t>
+          <t>MAPA_220@HOTMAIL.ES</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>30-01-2026 09:16:32</t>
+          <t>29-01-2026 08:22:19</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2841,27 +2837,27 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-02-2026 11:52:16</t>
+          <t>01-02-2026 10:00:34</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>30-01-2026 09:31:10</t>
+          <t>01-02-2026 09:59:59</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2871,7 +2867,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2881,24 +2877,32 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26220522007790002644</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26220521988460002587</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -3040,12 +3044,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>340216</t>
+          <t>339256</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3055,17 +3059,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AXEL ZADKYEL</t>
+          <t>CARLOS EDUARDO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3075,12 +3079,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5591647693</t>
+          <t>5528464677</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SAN BUENAVENTURA</t>
+          <t xml:space="preserve">AV. JOSE MARIA MARTINEZ MZA 24 LT 19 </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3090,17 +3094,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>24-05-2006</t>
+          <t>12-01-1990</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>AXELVALDEZ099@GMAL.COM</t>
+          <t>ELDA.SOLRAC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-02-2026 15:29:08</t>
+          <t>30-01-2026 09:16:32</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3111,27 +3115,27 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-02-2026 15:45:59</t>
+          <t>02-02-2026 11:52:16</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-02-2026 15:34:51</t>
+          <t>30-01-2026 09:31:10</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3141,7 +3145,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3151,14 +3155,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26220522015050002682</t>
+          <t>26220522007790002644</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3175,12 +3179,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340315</t>
+          <t>342750</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3190,17 +3194,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MAYRA JAZMIN</t>
+          <t>MANUEL RAFAEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KURY</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AVILES</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3210,32 +3214,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5561248221</t>
+          <t>5574265455</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IXTAP</t>
+          <t>C CEBADA MZ 6 LT 3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>13-08-1980</t>
+          <t>23-11-1999</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MAYRACGT@GMAIL.COM</t>
+          <t>MANUEL_LVNA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-02-2026 17:44:11</t>
+          <t>10-02-2026 17:23:26</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3246,7 +3250,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3256,17 +3260,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>03-02-2026 07:27:24</t>
+          <t>10-02-2026 17:27:27</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>03-02-2026 07:26:21</t>
+          <t>10-02-2026 17:26:23</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3276,7 +3280,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3286,14 +3290,10 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26220522032080002726</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522239800003484</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
@@ -3302,24 +3302,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>340516</t>
+          <t>340512</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18334</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3329,17 +3329,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CARLOS ENRIQUE</t>
+          <t>ROSA LIDIA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUEDA </t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>ANZALDO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5619885190</t>
+          <t>5521196367</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3359,22 +3359,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>05-08-1991</t>
+          <t>14-04-1993</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ENRIQUE-RUEDA@OUTLOOK.COM</t>
+          <t>ROSYN_N@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>03-02-2026 10:59:53</t>
+          <t>03-02-2026 10:51:49</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03-02-2026 11:02:47</t>
+          <t>03-02-2026 10:57:53</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>03-02-2026 11:02:16</t>
+          <t>03-02-2026 10:57:16</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26220522036720002739</t>
+          <t>26220522036640002738</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3449,12 +3449,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>340512</t>
+          <t>340516</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>18334</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3464,17 +3464,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ROSA LIDIA</t>
+          <t>CARLOS ENRIQUE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t xml:space="preserve">RUEDA </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ANZALDO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5521196367</t>
+          <t>5619885190</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3494,22 +3494,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>14-04-1993</t>
+          <t>05-08-1991</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ROSYN_N@HOTMAIL.COM</t>
+          <t>ENRIQUE-RUEDA@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>03-02-2026 10:51:49</t>
+          <t>03-02-2026 10:59:53</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>03-02-2026 10:57:53</t>
+          <t>03-02-2026 11:02:47</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>03-02-2026 10:57:16</t>
+          <t>03-02-2026 11:02:16</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26220522036640002738</t>
+          <t>26220522036720002739</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3719,12 +3719,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>341101</t>
+          <t>341357</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3734,17 +3734,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CHRISTIAN OWEN</t>
+          <t>DAMIAN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t xml:space="preserve">QUINTERO </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3754,14 +3754,10 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5643127118</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>C CATEDRAL METROPOLITANA 204</t>
-        </is>
-      </c>
+          <t>5634592607</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3769,60 +3765,56 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18-06-2011</t>
+          <t>25-11-2010</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CHRISTIAN09MENDEZ1234@GMAIL.COM</t>
+          <t>DENI.QUINTERO2010@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>04-02-2026 17:18:13</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>05-02-2026 16:04:32</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>04-02-2026 17:31:39</t>
+          <t>05-02-2026 16:09:19</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>04-02-2026 17:30:29</t>
-        </is>
-      </c>
+          <t>05-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3830,36 +3822,36 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26220522082650002911</t>
+          <t>26220522109710003012</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>341357</t>
+          <t>341101</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3869,17 +3861,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DAMIAN</t>
+          <t>CHRISTIAN OWEN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTERO </t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3889,10 +3881,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5634592607</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>5643127118</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>C CATEDRAL METROPOLITANA 204</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3900,56 +3896,60 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>25-11-2010</t>
+          <t>18-06-2011</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>DENI.QUINTERO2010@GMAIL.COM</t>
+          <t>CHRISTIAN09MENDEZ1234@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>05-02-2026 16:04:32</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 17:18:13</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>05-02-2026 16:09:19</t>
+          <t>04-02-2026 17:31:39</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>05-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>04-02-2026 17:30:29</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3957,24 +3957,24 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26220522109710003012</t>
+          <t>26220522082650002911</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342184</t>
+          <t>341099</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>AXEL KALID</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>VICENTE</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5537110647</t>
+          <t>5635122950</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COL SANTA CRUZ TLAPACOYA</t>
+          <t>C CATEDRAL METROPOLITANA 204</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4305,17 +4305,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>25-07-2017</t>
+          <t>23-07-2004</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>KARINAFLORESVICENTE@GMAIL.COM</t>
+          <t>GUERREROAXEL190@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-02-2026 14:42:03</t>
+          <t>04-02-2026 17:15:27</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4336,17 +4336,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>09-02-2026 14:52:27</t>
+          <t>04-02-2026 17:26:19</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>09-02-2026 14:50:55</t>
+          <t>04-02-2026 17:25:23</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26220522193980003288</t>
+          <t>26220522082390002907</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4378,24 +4378,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>341099</t>
+          <t>342184</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4405,17 +4405,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AXEL KALID</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>VICENTE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5635122950</t>
+          <t>5537110647</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C CATEDRAL METROPOLITANA 204</t>
+          <t>COL SANTA CRUZ TLAPACOYA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4440,17 +4440,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>23-07-2004</t>
+          <t>25-07-2017</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>GUERREROAXEL190@GMAIL.COM</t>
+          <t>KARINAFLORESVICENTE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>04-02-2026 17:15:27</t>
+          <t>09-02-2026 14:42:03</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4471,17 +4471,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>04-02-2026 17:26:19</t>
+          <t>09-02-2026 14:52:27</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>04-02-2026 17:25:23</t>
+          <t>09-02-2026 14:50:55</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26220522082390002907</t>
+          <t>26220522193980003288</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4513,24 +4513,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342745</t>
+          <t>341889</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20562</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4540,17 +4540,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ITZEL STEPHANY</t>
+          <t>LUCIA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VERDE</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SERVIN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5584585348</t>
+          <t>5574445968</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CDA BARRANCA DE MEZQUITE MZ 56</t>
+          <t>LOTOS</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4575,17 +4575,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>21-12-1995</t>
+          <t>06-03-1990</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ITZEL_VERDE95@ICLOUD.COM</t>
+          <t>LUCYCOSA06039@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10-02-2026 17:16:16</t>
+          <t>08-02-2026 09:58:42</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4606,17 +4606,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10-02-2026 17:21:18</t>
+          <t>08-02-2026 10:02:56</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>10-02-2026 17:20:26</t>
+          <t>08-02-2026 10:02:01</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26220522239450003479</t>
+          <t>26220522169080003210</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4648,24 +4648,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>344433</t>
+          <t>341952</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IRIS MONTSERRAT</t>
+          <t>RAMON</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CHAVARIN</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4695,39 +4695,35 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5564692994</t>
+          <t>5520734799</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>RANCHOO</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>29-08-1994</t>
+          <t>31-08-1964</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>MONTSERRAT_94@HOTMAIL.COM</t>
+          <t>MONN.64KAISER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>17-02-2026 10:03:24</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>08-02-2026 13:27:30</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4745,17 +4741,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>17-02-2026 10:10:20</t>
+          <t>08-02-2026 13:36:45</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>17-02-2026 10:08:56</t>
+          <t>08-02-2026 13:36:11</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4765,7 +4761,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4775,7 +4771,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26220522423620004039</t>
+          <t>26220522172570003226</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4787,24 +4783,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>341894</t>
+          <t>344433</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4814,17 +4810,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">JONATHAN </t>
+          <t>IRIS MONTSERRAT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>CHAVARIN</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">URBAN </t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4834,35 +4830,39 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5574445964</t>
+          <t>5564692994</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LOTOS</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>06-12-1990</t>
+          <t>29-08-1994</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>SOLDADO.DE.DIOS@HOTMAIL.COM</t>
+          <t>MONTSERRAT_94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>08-02-2026 10:05:09</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>17-02-2026 10:03:24</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4880,17 +4880,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>08-02-2026 10:07:34</t>
+          <t>17-02-2026 10:10:20</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>08-02-2026 10:07:05</t>
+          <t>17-02-2026 10:08:56</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26220522169210003211</t>
+          <t>26220522423620004039</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4934,12 +4934,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342097</t>
+          <t>345379</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>87544</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4949,17 +4949,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALICIA </t>
+          <t>EMMANUEL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUCEDO </t>
+          <t>DE JESUS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5522530023</t>
+          <t>5581003622</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CDA MAGDALENA SN IXTAPALUCA</t>
+          <t>C AGUSTIN DE ITURBIDE 228</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>23-03-1966</t>
+          <t>17-12-1995</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>SAUCEDOGALICIAALICIA32@GMAIL.COM</t>
+          <t>EMMANUELDJF17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>09-02-2026 10:35:09</t>
+          <t>20-02-2026 18:06:05</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>18-02-2026 15:06:39</t>
+          <t>20-02-2026 18:17:25</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>18-02-2026 15:05:44</t>
+          <t>20-02-2026 18:16:44</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5049,19 +5049,11 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26220522463670004215</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522533780004518</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
           <t>499</t>
@@ -5069,7 +5061,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5081,12 +5073,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>345379</t>
+          <t>342745</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>87544</t>
+          <t>20562</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5096,17 +5088,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EMMANUEL</t>
+          <t>ITZEL STEPHANY</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DE JESUS</t>
+          <t>VERDE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>SERVIN</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5116,39 +5108,35 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5581003622</t>
+          <t>5584585348</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C AGUSTIN DE ITURBIDE 228</t>
+          <t>CDA BARRANCA DE MEZQUITE MZ 56</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>17-12-1995</t>
+          <t>21-12-1995</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>EMMANUELDJF17@GMAIL.COM</t>
+          <t>ITZEL_VERDE95@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>20-02-2026 18:06:05</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 17:16:16</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5166,17 +5154,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>20-02-2026 18:17:25</t>
+          <t>10-02-2026 17:21:18</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>20-02-2026 18:16:44</t>
+          <t>10-02-2026 17:20:26</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5186,7 +5174,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5196,7 +5184,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26220522533780004518</t>
+          <t>26220522239450003479</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5208,7 +5196,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5220,12 +5208,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>341889</t>
+          <t>341894</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>19712</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5235,17 +5223,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LUCIA</t>
+          <t xml:space="preserve">JONATHAN </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t xml:space="preserve">URBAN </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5255,7 +5243,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5574445968</t>
+          <t>5574445964</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -5265,22 +5253,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>06-03-1990</t>
+          <t>06-12-1990</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>LUCYCOSA06039@GMAIL.COM</t>
+          <t>SOLDADO.DE.DIOS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>08-02-2026 09:58:42</t>
+          <t>08-02-2026 10:05:09</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5301,7 +5289,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>08-02-2026 10:02:56</t>
+          <t>08-02-2026 10:07:34</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -5311,7 +5299,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>08-02-2026 10:02:01</t>
+          <t>08-02-2026 10:07:05</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5331,7 +5319,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26220522169080003210</t>
+          <t>26220522169210003211</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5355,12 +5343,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>341952</t>
+          <t>342097</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5370,17 +5358,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>RAMON</t>
+          <t xml:space="preserve">ALICIA </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t xml:space="preserve">SAUCEDO </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5390,35 +5378,39 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5520734799</t>
+          <t>5522530023</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>RANCHOO</t>
+          <t>CDA MAGDALENA SN IXTAPALUCA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>31-08-1964</t>
+          <t>23-03-1966</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>MONN.64KAISER@GMAIL.COM</t>
+          <t>SAUCEDOGALICIAALICIA32@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>08-02-2026 13:27:30</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>09-02-2026 10:35:09</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5436,17 +5428,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>08-02-2026 13:36:45</t>
+          <t>18-02-2026 15:06:39</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>08-02-2026 13:36:11</t>
+          <t>18-02-2026 15:05:44</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5456,7 +5448,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5466,11 +5458,19 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26220522172570003226</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+          <t>26220522463670004215</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>499</t>
@@ -5629,12 +5629,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>342287</t>
+          <t>342290</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5644,17 +5644,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IRVING DONNOVAN</t>
+          <t>ADRIANA ITZEL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAVO </t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ROCHA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5664,35 +5664,39 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5564343538</t>
+          <t>5510440090</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>C PERA SAN MARCOS</t>
+          <t>C VILLAHERMOSA MZA 47</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>06-09-1992</t>
+          <t>14-08-1994</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>DONNOVANBR@OUTLOOK.COM</t>
+          <t>ADRIANANAVA149@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>09-02-2026 16:52:02</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>09-02-2026 16:53:59</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5710,17 +5714,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>12-02-2026 18:07:17</t>
+          <t>18-02-2026 18:14:20</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>12-02-2026 18:06:58</t>
+          <t>18-02-2026 18:13:49</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5740,7 +5744,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26220522301550003706</t>
+          <t>26220522471810004257</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5768,12 +5772,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>342380</t>
+          <t>342287</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5783,17 +5787,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DIANA ALINE</t>
+          <t>IRVING DONNOVAN</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t xml:space="preserve">BRAVO </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>ROCHA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5803,32 +5807,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5625435058</t>
+          <t>5564343538</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">C CASTILLO DE CHAPULTEPEC </t>
+          <t>C PERA SAN MARCOS</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>22-12-1996</t>
+          <t>06-09-1992</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>DIGTZ15@GMAIL.COM</t>
+          <t>DONNOVANBR@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>09-02-2026 18:16:13</t>
+          <t>09-02-2026 16:52:02</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5849,7 +5853,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>12-02-2026 18:19:45</t>
+          <t>12-02-2026 18:07:17</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5859,7 +5863,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>12-02-2026 18:19:19</t>
+          <t>12-02-2026 18:06:58</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5869,7 +5873,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5879,7 +5883,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26220522302230003710</t>
+          <t>26220522301550003706</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5907,12 +5911,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>342290</t>
+          <t>342380</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5922,17 +5926,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ADRIANA ITZEL</t>
+          <t>DIANA ALINE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5942,12 +5946,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5510440090</t>
+          <t>5625435058</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>C VILLAHERMOSA MZA 47</t>
+          <t xml:space="preserve">C CASTILLO DE CHAPULTEPEC </t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5957,24 +5961,20 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>14-08-1994</t>
+          <t>22-12-1996</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ADRIANANAVA149@GMAIL.COM</t>
+          <t>DIGTZ15@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>09-02-2026 16:53:59</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 18:16:13</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5992,17 +5992,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:20</t>
+          <t>12-02-2026 18:19:45</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>18-02-2026 18:13:49</t>
+          <t>12-02-2026 18:19:19</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26220522471810004257</t>
+          <t>26220522302230003710</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -6050,12 +6050,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>341922</t>
+          <t>344895</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>22712</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6065,17 +6065,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>YANNEVY ARIADNE</t>
+          <t>ALMA ROSA BASILISA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6085,12 +6085,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5580261394</t>
+          <t>5611775850</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>HEROES</t>
+          <t>C JOSE MARIA MORELOS</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6100,20 +6100,24 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>25-11-1994</t>
+          <t>02-04-1963</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>YENNEVY@GMAIL.COM</t>
+          <t>ALMAROSACASTRO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>08-02-2026 11:53:18</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>18-02-2026 17:26:28</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6131,17 +6135,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>08-02-2026 11:58:57</t>
+          <t>18-02-2026 17:48:07</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>08-02-2026 11:57:36</t>
+          <t>18-02-2026 17:46:56</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6161,7 +6165,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26220522171210003218</t>
+          <t>26220522470370004248</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6173,24 +6177,24 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>David Guillermo  Fuentes Carrillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>344895</t>
+          <t>345233</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22712</t>
+          <t>87398</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6200,17 +6204,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ALMA ROSA BASILISA</t>
+          <t xml:space="preserve">LEONEL YUARI </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t xml:space="preserve">MANRIQUEZ </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6220,32 +6224,32 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5611775850</t>
+          <t>5521514699</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>C JOSE MARIA MORELOS</t>
+          <t xml:space="preserve">ZOL AGRICOLA ORIENTAL </t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>02-04-1963</t>
+          <t>27-06-2004</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ALMAROSACASTRO@HOTMAIL.COM</t>
+          <t>STARCICI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>18-02-2026 17:26:28</t>
+          <t>20-02-2026 09:01:39</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6270,17 +6274,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>18-02-2026 17:48:07</t>
+          <t>20-02-2026 09:08:59</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>18-02-2026 17:46:56</t>
+          <t>20-02-2026 09:08:21</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6290,7 +6294,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6300,7 +6304,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26220522470370004248</t>
+          <t>26220522522290004459</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6324,12 +6328,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>345233</t>
+          <t>341922</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>87398</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6339,17 +6343,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONEL YUARI </t>
+          <t>YANNEVY ARIADNE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANRIQUEZ </t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6359,39 +6363,35 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5521514699</t>
+          <t>5580261394</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZOL AGRICOLA ORIENTAL </t>
+          <t>HEROES</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>27-06-2004</t>
+          <t>25-11-1994</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>STARCICI@GMAIL.COM</t>
+          <t>YENNEVY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>20-02-2026 09:01:39</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>08-02-2026 11:53:18</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6409,17 +6409,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>20-02-2026 09:08:59</t>
+          <t>08-02-2026 11:58:57</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>20-02-2026 09:08:21</t>
+          <t>08-02-2026 11:57:36</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26220522522290004459</t>
+          <t>26220522171210003218</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
@@ -6451,12 +6451,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -6733,12 +6733,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>343831</t>
+          <t>342536</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6748,17 +6748,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>JESSICA</t>
+          <t>HANNIA ATZIRY</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6768,12 +6768,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2217041181</t>
+          <t>5541561912</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CALLE MAGNOLIA 242</t>
+          <t>TEJALPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6783,17 +6783,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>14-12-1998</t>
+          <t>22-01-1997</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>JESSICAHERNANDEZVAZQUEZ@OUTLOOK.COM</t>
+          <t>HANNIA_22_SANDOVAL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:19</t>
+          <t>10-02-2026 07:49:10</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6814,22 +6814,22 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:20</t>
+          <t>10-02-2026 07:55:17</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>15-02-2026 12:21:20</t>
+          <t>10-02-2026 07:53:33</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26220522365380003866</t>
+          <t>26220522224790003405</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6856,24 +6856,24 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>342536</t>
+          <t>343831</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6883,17 +6883,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>HANNIA ATZIRY</t>
+          <t>JESSICA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5541561912</t>
+          <t>2217041181</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TEJALPA</t>
+          <t>CALLE MAGNOLIA 242</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6918,17 +6918,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>22-01-1997</t>
+          <t>14-12-1998</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>HANNIA_22_SANDOVAL@HOTMAIL.COM</t>
+          <t>JESSICAHERNANDEZVAZQUEZ@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>10-02-2026 07:49:10</t>
+          <t>15-02-2026 12:21:19</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6949,22 +6949,22 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>10-02-2026 07:55:17</t>
+          <t>15-02-2026 12:21:20</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>10-02-2026 07:53:33</t>
+          <t>15-02-2026 12:21:20</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26220522224790003405</t>
+          <t>26220522365380003866</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -6991,12 +6991,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -7138,12 +7138,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>343301</t>
+          <t>344217</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7153,17 +7153,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ESPEJEL</t>
+          <t>ELIZALDE</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5516346350</t>
+          <t>7473547605</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
+          <t xml:space="preserve">AV. NIÑOS HEROES COL. SANTA CRUZ </t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7188,20 +7188,24 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>06-07-1995</t>
+          <t>09-07-1998</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>DIEGOLUPPUS@GMAIL.COM</t>
+          <t>ALEXGARCIAE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>12-02-2026 16:04:34</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>16-02-2026 17:34:05</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7219,17 +7223,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>12-02-2026 16:26:22</t>
+          <t>19-02-2026 15:50:26</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>12-02-2026 16:25:47</t>
+          <t>19-02-2026 15:49:51</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7249,10 +7253,14 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26220522297530003689</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr"/>
+          <t>26220522497590004364</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
@@ -7261,24 +7269,24 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>343505</t>
+          <t>343301</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7288,17 +7296,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ALVARO O BRIAN</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>VALADEZ</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BLANCA</t>
+          <t>ESPEJEL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7308,12 +7316,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5591919598</t>
+          <t>5516346350</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AV NUEVO MEXICO 301</t>
+          <t xml:space="preserve">C JARA MZA 12 LT 99 </t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7323,17 +7331,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>12-09-1993</t>
+          <t>06-07-1995</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>POSEIDONBALA93@OUTLOOK.COM</t>
+          <t>DIEGOLUPPUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>13-02-2026 14:50:25</t>
+          <t>12-02-2026 16:04:34</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7354,17 +7362,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>13-02-2026 14:59:34</t>
+          <t>12-02-2026 16:26:22</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>13-02-2026 14:59:07</t>
+          <t>12-02-2026 16:25:47</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7384,7 +7392,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26220522321910003759</t>
+          <t>26220522297530003689</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
@@ -7396,24 +7404,24 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>343544</t>
+          <t>343505</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7423,17 +7431,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LAURA AMAYRANI</t>
+          <t>ALVARO O BRIAN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>VALADEZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>BLANCA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7443,32 +7451,32 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5546447212</t>
+          <t>5591919598</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
+          <t>AV NUEVO MEXICO 301</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>13-03-2007</t>
+          <t>12-09-1993</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>LAUPRD25@GMAIL.COM</t>
+          <t>POSEIDONBALA93@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>13-02-2026 17:03:29</t>
+          <t>13-02-2026 14:50:25</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7489,7 +7497,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>13-02-2026 17:19:38</t>
+          <t>13-02-2026 14:59:34</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -7499,7 +7507,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>13-02-2026 17:18:02</t>
+          <t>13-02-2026 14:59:07</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7509,7 +7517,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -7519,7 +7527,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26220522326190003779</t>
+          <t>26220522321910003759</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7531,24 +7539,24 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>343838</t>
+          <t>343544</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7558,17 +7566,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>LAURA AMAYRANI</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORAN </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7578,32 +7586,32 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2206073345</t>
+          <t>5546447212</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CALLE MAGNOLIA 242</t>
+          <t xml:space="preserve">SAN GREGORIO CUAUTZINGO </t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>26-02-1995</t>
+          <t>13-03-2007</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>TRILLISO_BET@HOTMAIL.COM</t>
+          <t>LAUPRD25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>13-02-2026 17:03:29</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -7624,27 +7632,27 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>13-02-2026 17:19:38</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>15-02-2026 12:36:33</t>
+          <t>13-02-2026 17:18:02</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7654,7 +7662,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26220522365710003869</t>
+          <t>26220522326190003779</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
@@ -7666,12 +7674,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -7813,12 +7821,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>344217</t>
+          <t>343838</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22034</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7828,17 +7836,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">MORAN </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ELIZALDE</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7848,12 +7856,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>7473547605</t>
+          <t>2206073345</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV. NIÑOS HEROES COL. SANTA CRUZ </t>
+          <t>CALLE MAGNOLIA 242</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7863,24 +7871,20 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>09-07-1998</t>
+          <t>26-02-1995</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>ALEXGARCIAE@GMAIL.COM</t>
+          <t>TRILLISO_BET@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>16-02-2026 17:34:05</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>15-02-2026 12:36:33</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7898,22 +7902,22 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>19-02-2026 15:50:26</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>19-02-2026 15:49:51</t>
+          <t>15-02-2026 12:36:33</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -7928,14 +7932,10 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26220522497590004364</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522365710003869</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
@@ -8095,12 +8095,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>343539</t>
+          <t>344626</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8110,17 +8110,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ROCIO</t>
+          <t>IXCHEL YARELI</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>JAIMEZ</t>
+          <t xml:space="preserve">MARIN </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5534063877</t>
+          <t>5579912763</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>C CUAUTZINGO MZA 34</t>
+          <t>C DZILAM MZ 814 LT 4</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8145,48 +8145,52 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>12-01-1998</t>
+          <t>31-01-1989</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
+          <t>IXCHELMARIN@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>13-02-2026 16:58:39</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>17-02-2026 17:48:58</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIAR RECURRENTE $999</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>13-02-2026 17:12:37</t>
+          <t>17-02-2026 18:01:12</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13-02-2026 17:10:18</t>
+          <t>17-02-2026 17:59:12</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8196,7 +8200,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -8206,19 +8210,19 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26220522325890003776</t>
+          <t>26220522439570004122</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -8230,12 +8234,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>344900</t>
+          <t>343539</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8245,17 +8249,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ADRIAN BERENICE</t>
+          <t>ROCIO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>JAIMEZ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8265,10 +8269,14 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>5540961768</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>5534063877</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>C CUAUTZINGO MZA 34</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8276,17 +8284,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>05-03-1999</t>
+          <t>12-01-1998</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BEREADRY99@HOTMAIL.COM</t>
+          <t>ROCIOJAIMEZ1201@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>18-02-2026 17:32:28</t>
+          <t>13-02-2026 16:58:39</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -8297,7 +8305,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -8307,17 +8315,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>18-02-2026 17:43:39</t>
+          <t>13-02-2026 17:12:37</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>18-02-2026 17:43:01</t>
+          <t>13-02-2026 17:10:18</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8327,7 +8335,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -8337,7 +8345,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26220522470070004245</t>
+          <t>26220522325890003776</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
@@ -8361,12 +8369,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>345055</t>
+          <t>344432</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>87220</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8376,17 +8384,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TALAVERA</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PANIAGUA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8396,12 +8404,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5540308509</t>
+          <t>5515226715</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>C SUR 171</t>
+          <t>ALFREDIO</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8411,52 +8419,52 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>20-02-1963</t>
+          <t>23-08-1991</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>ANGELTALAVERAP63@GMAIL.COM</t>
+          <t>LIC.ALFREDO.91@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>19-02-2026 13:00:23</t>
+          <t>17-02-2026 09:59:28</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>19-02-2026 13:17:48</t>
+          <t>17-02-2026 10:14:17</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>19-02-2026 13:16:38</t>
+          <t>17-02-2026 10:13:36</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8466,7 +8474,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -8476,14 +8484,14 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26220522493820004335</t>
+          <t>26220522423710004040</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -8500,12 +8508,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>345063</t>
+          <t>345338</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>87228</t>
+          <t>87503</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8515,17 +8523,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MARIA DE LA LUZ</t>
+          <t xml:space="preserve">GUADALUPE </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>CARRANZA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8535,12 +8543,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5561186386</t>
+          <t>5615722096</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>C SUR 171</t>
+          <t xml:space="preserve">FRACC HACIENDA DE LAS PALMAS III </t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8550,52 +8558,52 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>15-04-1963</t>
+          <t>03-09-1981</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>LG.JACK63@GMAIL.COM</t>
+          <t>GUADALUPECARRANZA2830@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>19-02-2026 13:21:09</t>
+          <t>20-02-2026 16:38:08</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>19-02-2026 13:30:22</t>
+          <t>20-02-2026 16:51:02</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>19-02-2026 13:29:04</t>
+          <t>20-02-2026 16:49:11</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8615,36 +8623,36 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26220522494100004341</t>
+          <t>26220522530660004497</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>344432</t>
+          <t>344931</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8654,17 +8662,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>ANDRES JESUS</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8674,12 +8682,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5515226715</t>
+          <t>5537346724</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ALFREDIO</t>
+          <t>MZ H EDIF 2B</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8689,17 +8697,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>23-08-1991</t>
+          <t>10-11-1992</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>LIC.ALFREDO.91@GMAIL.COM</t>
+          <t>RAZIEL_FO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>17-02-2026 09:59:28</t>
+          <t>18-02-2026 18:46:57</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8724,17 +8732,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>17-02-2026 10:14:17</t>
+          <t>18-02-2026 18:54:43</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>17-02-2026 10:13:36</t>
+          <t>18-02-2026 18:52:58</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8754,7 +8762,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26220522423710004040</t>
+          <t>26220522473750004279</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
@@ -8778,12 +8786,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>344626</t>
+          <t>344934</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8793,17 +8801,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>IXCHEL YARELI</t>
+          <t xml:space="preserve">YENNIFER </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIN </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8813,12 +8821,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5579912763</t>
+          <t>5512992481</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>C DZILAM MZ 814 LT 4</t>
+          <t>TULTITLAM MEX</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8828,52 +8836,52 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>31-01-1989</t>
+          <t>17-09-1993</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>IXCHELMARIN@OUTLOOK.COM</t>
+          <t>YLOPEZFLORES17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>17-02-2026 17:48:58</t>
+          <t>18-02-2026 18:57:05</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>PLAN FAMILIAR RECURRENTE $999</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>17-02-2026 18:01:12</t>
+          <t>18-02-2026 19:01:48</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>17-02-2026 17:59:12</t>
+          <t>18-02-2026 19:00:57</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8883,7 +8891,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -8893,36 +8901,36 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26220522439570004122</t>
+          <t>26220522473980004280</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>344934</t>
+          <t>344900</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22751</t>
+          <t>22717</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8932,17 +8940,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">YENNIFER </t>
+          <t>ADRIAN BERENICE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8952,14 +8960,10 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>5512992481</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>TULTITLAM MEX</t>
-        </is>
-      </c>
+          <t>5540961768</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8967,24 +8971,20 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>17-09-1993</t>
+          <t>05-03-1999</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>YLOPEZFLORES17@GMAIL.COM</t>
+          <t>BEREADRY99@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>18-02-2026 18:57:05</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>18-02-2026 17:32:28</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>18-02-2026 19:01:48</t>
+          <t>18-02-2026 17:43:39</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>18-02-2026 19:00:57</t>
+          <t>18-02-2026 17:43:01</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26220522473980004280</t>
+          <t>26220522470070004245</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
@@ -9044,24 +9044,24 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>344931</t>
+          <t>345055</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>87220</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9071,17 +9071,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ANDRES JESUS</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>TALAVERA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>PANIAGUA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9091,12 +9091,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>5537346724</t>
+          <t>5540308509</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>MZ H EDIF 2B</t>
+          <t>C SUR 171</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9106,52 +9106,52 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>10-11-1992</t>
+          <t>20-02-1963</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>RAZIEL_FO@HOTMAIL.COM</t>
+          <t>ANGELTALAVERAP63@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>18-02-2026 18:46:57</t>
+          <t>19-02-2026 13:00:23</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>18-02-2026 18:54:43</t>
+          <t>19-02-2026 13:17:48</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>18-02-2026 18:52:58</t>
+          <t>19-02-2026 13:16:38</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -9171,14 +9171,14 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26220522473750004279</t>
+          <t>26220522493820004335</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -9195,12 +9195,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>345338</t>
+          <t>345063</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>87503</t>
+          <t>87228</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9210,17 +9210,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUADALUPE </t>
+          <t>MARIA DE LA LUZ</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CARRANZA</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>5615722096</t>
+          <t>5561186386</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRACC HACIENDA DE LAS PALMAS III </t>
+          <t>C SUR 171</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -9245,52 +9245,52 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>03-09-1981</t>
+          <t>15-04-1963</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>GUADALUPECARRANZA2830@GMAIL.COM</t>
+          <t>LG.JACK63@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>20-02-2026 16:38:08</t>
+          <t>19-02-2026 13:21:09</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>20-02-2026 16:51:02</t>
+          <t>19-02-2026 13:30:22</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>20-02-2026 16:49:11</t>
+          <t>19-02-2026 13:29:04</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9310,36 +9310,36 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26220522530660004497</t>
+          <t>26220522494100004341</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>344940</t>
+          <t>345074</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>87239</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRANDON </t>
+          <t>SANDRA ESTRELLA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MONTESINOS</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9369,79 +9369,67 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5613578379</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>C CIPRECES MZA 3</t>
-        </is>
-      </c>
+          <t>5545570437</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>08-03-1994</t>
+          <t>19-06-1974</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>BRANDON.FAMDA@GMAIL.COM</t>
+          <t>GARCIA_SANDRA98@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>18-02-2026 19:14:37</t>
+          <t>19-02-2026 14:14:15</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>18-02-2026 19:17:54</t>
+          <t>23-02-2026 14:12:47</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>18-02-2026 19:17:35</t>
-        </is>
-      </c>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9449,14 +9437,22 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26220522474720004282</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
+          <t>26220522581980004643</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>DIANA MADRID ORTIZ</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
@@ -9473,12 +9469,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>345129</t>
+          <t>345401</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>87294</t>
+          <t>87566</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9488,17 +9484,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KIMBERLY ABIGAIL</t>
+          <t>MELANY SAMANTHA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>ESPINOSA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9508,12 +9504,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>5619291534</t>
+          <t>5636743221</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>U HAB 4 VIENTOS</t>
+          <t>AV DE CANAL MZ 27</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9523,52 +9519,52 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>20-08-2007</t>
+          <t>03-09-2007</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>KKKIMBERLYY2@GMAIL.COM</t>
+          <t>MELANILOPES36@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>19-02-2026 16:52:09</t>
+          <t>20-02-2026 18:57:58</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>19-02-2026 17:04:47</t>
+          <t>24-02-2026 18:38:06</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>19-02-2026 17:03:32</t>
+          <t>24-02-2026 18:37:40</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -9578,7 +9574,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -9588,36 +9584,40 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26220522500320004391</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr"/>
+          <t>26220522632110004851</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>345130</t>
+          <t>345129</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>87295</t>
+          <t>87294</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9627,19 +9627,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MARISELA</t>
+          <t>KIMBERLY ABIGAIL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>VAZQUEZ</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>ENRIQUEZ</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>52</t>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>5538014107</t>
+          <t>5619291534</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -9662,17 +9662,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>02-12-1975</t>
+          <t>20-08-2007</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>KIMBERLY89@GMAIL.COM</t>
+          <t>KKKIMBERLYY2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>19-02-2026 16:54:23</t>
+          <t>19-02-2026 16:52:09</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>19-02-2026 17:08:32</t>
+          <t>19-02-2026 17:04:47</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>19-02-2026 17:08:01</t>
+          <t>19-02-2026 17:03:32</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26220522500550004392</t>
+          <t>26220522500320004391</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
@@ -9739,24 +9739,24 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>345074</t>
+          <t>345130</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>87239</t>
+          <t>87295</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9766,17 +9766,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SANDRA ESTRELLA</t>
+          <t>MARISELA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9786,10 +9786,14 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>5545570437</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>5538014107</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>U HAB 4 VIENTOS</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9797,56 +9801,64 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>19-06-1974</t>
+          <t>02-12-1975</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>GARCIA_SANDRA98@YAHOO.COM.MX</t>
+          <t>KIMBERLY89@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>19-02-2026 14:14:15</t>
+          <t>19-02-2026 16:54:23</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>23-02-2026 14:12:47</t>
+          <t>19-02-2026 17:08:32</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:08:01</t>
+        </is>
+      </c>
       <c r="U69" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9854,22 +9866,14 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26220522581980004643</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>DIANA MADRID ORTIZ</t>
-        </is>
-      </c>
+          <t>26220522500550004392</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -9886,12 +9890,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>345401</t>
+          <t>344940</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>87566</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9901,17 +9905,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>MELANY SAMANTHA</t>
+          <t xml:space="preserve">BRANDON </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ESPINOSA</t>
+          <t>MONTESINOS</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9921,67 +9925,67 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>5636743221</t>
+          <t>5613578379</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>AV DE CANAL MZ 27</t>
+          <t>C CIPRECES MZA 3</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>03-09-2007</t>
+          <t>08-03-1994</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>MELANILOPES36@GMAIL.COM</t>
+          <t>BRANDON.FAMDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>20-02-2026 18:57:58</t>
+          <t>18-02-2026 19:14:37</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>24-02-2026 18:38:06</t>
+          <t>18-02-2026 19:17:54</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>24-02-2026 18:37:40</t>
+          <t>18-02-2026 19:17:35</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -9991,7 +9995,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -10001,18 +10005,14 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26220522632110004851</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522474720004282</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -10029,12 +10029,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>346617</t>
+          <t>345977</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>88782</t>
+          <t>88142</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10044,17 +10044,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRISTIAN </t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MANRIQUEZ</t>
+          <t>PAYAN</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>5513431982</t>
+          <t>5586887467</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -10075,24 +10075,20 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>22-07-1992</t>
+          <t>01-11-1978</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CRISTIAN_@HOTMAIL.COM</t>
+          <t>JUANCARLOSLARAPAYAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>26-02-2026 04:30:59</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>23-02-2026 18:23:19</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -10100,22 +10096,22 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>26-02-2026 04:33:00</t>
+          <t>23-02-2026 18:25:30</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>23-03-2027 23:59:59</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -10132,36 +10128,36 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26220522669400004995</t>
+          <t>26220522595510004713</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>346215</t>
+          <t>346085</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>88380</t>
+          <t>88250</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10171,17 +10167,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NANCY IVONN</t>
+          <t xml:space="preserve">ARACELI </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">SALMORAN </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>VILLAGOMEZ</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -10191,12 +10187,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>5514373677</t>
+          <t>5539066958</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>IXTAPALIUUCA</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -10206,27 +10202,23 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>23-11-1977</t>
+          <t>16-11-1982</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>GONZALEZCASTILLONANCYIVONN@GMAIL.COM</t>
+          <t>ARACELI.TSGS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>24-02-2026 16:32:59</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>24-02-2026 08:14:04</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -10236,34 +10228,26 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>698</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>27-02-2026 07:54:16</t>
+          <t>24-02-2026 08:00:00</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>27-02-2026 07:53:55</t>
-        </is>
-      </c>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10271,40 +10255,36 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26220522705980005132</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220522612860004768</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>698</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>345977</t>
+          <t>346617</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>88142</t>
+          <t>88782</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10314,17 +10294,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t xml:space="preserve">CRISTIAN </t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PAYAN</t>
+          <t>MANRIQUEZ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10334,7 +10314,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>5586887467</t>
+          <t>5513431982</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10345,20 +10325,24 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>01-11-1978</t>
+          <t>22-07-1992</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>JUANCARLOSLARAPAYAN@GMAIL.COM</t>
+          <t>CRISTIAN_@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>23-02-2026 18:23:19</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>26-02-2026 04:30:59</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -10366,22 +10350,22 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>23-02-2026 18:25:30</t>
+          <t>26-02-2026 04:33:00</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>23-03-2027 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -10398,36 +10382,36 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26220522595510004713</t>
+          <t>26220522669400004995</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>346085</t>
+          <t>346215</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>88250</t>
+          <t>88380</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10437,17 +10421,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARACELI </t>
+          <t>NANCY IVONN</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALMORAN </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>VILLAGOMEZ</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10457,12 +10441,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>5539066958</t>
+          <t>5514373677</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ALFREDO</t>
+          <t>IXTAPALIUUCA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -10472,23 +10456,27 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>16-11-1982</t>
+          <t>23-11-1977</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ARACELI.TSGS@GMAIL.COM</t>
+          <t>GONZALEZCASTILLONANCYIVONN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>24-02-2026 08:14:04</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>24-02-2026 16:32:59</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -10498,26 +10486,34 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>24-02-2026 08:00:00</t>
+          <t>27-02-2026 07:54:16</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr"/>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>27-02-2026 07:53:55</t>
+        </is>
+      </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W74" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10525,24 +10521,28 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26220522612860004768</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr"/>
+          <t>26220522705980005132</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347541</t>
+          <t>272613</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89706</t>
+          <t>70115</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AYLIN</t>
+          <t>GIBRAN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JACALES</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VILLALPANDO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,32 +613,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5529573810</t>
+          <t>5599774035</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IXTAPALUCA CENTRO</t>
+          <t>FRACC LOS HEROES</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>05-12-2009</t>
+          <t>27-04-1991</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>AYLINVILLALPANDO20@GMAIL.COM</t>
+          <t>GIMATDK21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 12:36:05</t>
+          <t>08-01-2025 14:22:46</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 12:49:10</t>
+          <t>03-03-2026 14:39:08</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>02-03-2026 12:48:39</t>
+          <t>03-03-2026 14:38:16</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26220522791920005343</t>
+          <t>26220522842100005502</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -717,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347529</t>
+          <t>347541</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89694</t>
+          <t>89706</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FARID JORDAN</t>
+          <t>AYLIN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>JACALES</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>VILLALPANDO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,67 +752,79 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7291633215</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>5529573810</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA CENTRO</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>10-04-2001</t>
+          <t>05-12-2009</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>FARIDJORDAN01@GMAIL.COM</t>
+          <t>AYLINVILLALPANDO20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 12:07:58</t>
+          <t>02-03-2026 12:36:05</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 12:16:51</t>
+          <t>02-03-2026 12:49:10</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:48:39</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,14 +832,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26220522790720005338</t>
+          <t>26220522791920005343</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -844,12 +856,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347794</t>
+          <t>347529</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89959</t>
+          <t>89694</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MARIA GUADALUPE</t>
+          <t>FARID JORDAN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,79 +891,67 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5622303333</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>C SAN ENRIQUE COND MZ 6</t>
-        </is>
-      </c>
+          <t>7291633215</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>05-11-1986</t>
+          <t>10-04-2001</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>MARIAGONZALEZPE511@GMAIL.COM</t>
+          <t>FARIDJORDAN01@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 18:07:34</t>
+          <t>02-03-2026 12:07:58</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 19:48:43</t>
+          <t>02-03-2026 12:16:51</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:48:16</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -959,14 +959,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26220522817890005445</t>
+          <t>26220522790720005338</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1388,12 +1388,151 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>347794</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>89959</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MARIA GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5622303333</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>C SAN ENRIQUE COND MZ 6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>05-11-1986</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>MARIAGONZALEZPE511@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:07:34</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:48:43</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:48:16</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>26220522817890005445</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Svein  Peñaloza Lara</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347541</t>
+          <t>329826</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89706</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AYLIN</t>
+          <t xml:space="preserve">BRENDA AYLIN </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JACALES</t>
+          <t xml:space="preserve">CRUZ </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VILLALPANDO</t>
+          <t>ALATORRE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,32 +752,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5529573810</t>
+          <t>5559171999</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IXTAPALUCA CENTRO</t>
+          <t>SAN BUENAVENTURA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>05-12-2009</t>
+          <t>04-01-1998</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>AYLINVILLALPANDO20@GMAIL.COM</t>
+          <t>AYLIN.CIPRIANO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 12:36:05</t>
+          <t>22-12-2025 10:04:43</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 12:49:10</t>
+          <t>04-03-2026 17:11:25</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>02-03-2026 12:48:39</t>
+          <t>04-03-2026 17:10:47</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -832,11 +832,19 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26220522791920005343</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26220522889560005681</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>549</t>
@@ -844,12 +852,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Antonio  Chaparro Alonso</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1130,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347537</t>
+          <t>347794</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89702</t>
+          <t>89959</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1137,17 +1145,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MARIA DE LOURDES</t>
+          <t>MARIA GUADALUPE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLALPANDO </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1157,12 +1165,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5538981251</t>
+          <t>5622303333</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IXTAPALUCA CENTRO</t>
+          <t>C SAN ENRIQUE COND MZ 6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1172,17 +1180,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>21-06-1966</t>
+          <t>05-11-1986</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>LEDESMAL28@HOTMAIL.COM</t>
+          <t>MARIAGONZALEZPE511@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 12:32:36</t>
+          <t>02-03-2026 18:07:34</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1207,7 +1215,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 12:45:05</t>
+          <t>02-03-2026 19:48:43</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1217,7 +1225,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 12:44:30</t>
+          <t>02-03-2026 19:48:16</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1227,7 +1235,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1237,7 +1245,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26220522791710005342</t>
+          <t>26220522817890005445</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1249,24 +1257,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347543</t>
+          <t>347537</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89708</t>
+          <t>89702</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1284,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MELANI YATZIRI</t>
+          <t>MARIA DE LOURDES</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JACALES</t>
+          <t xml:space="preserve">VILLALPANDO </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VILLALPANDO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,7 +1304,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5666090456</t>
+          <t>5538981251</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1311,17 +1319,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>03-04-2007</t>
+          <t>21-06-1966</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MELANIYATZIRI02@GMAIL.COM</t>
+          <t>LEDESMAL28@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 12:39:46</t>
+          <t>02-03-2026 12:32:36</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 12:52:17</t>
+          <t>02-03-2026 12:45:05</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1356,7 +1364,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-03-2026 12:51:36</t>
+          <t>02-03-2026 12:44:30</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1376,7 +1384,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26220522792050005345</t>
+          <t>26220522791710005342</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1388,24 +1396,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347794</t>
+          <t>347543</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89959</t>
+          <t>89708</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1423,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MARIA GUADALUPE</t>
+          <t>MELANI YATZIRI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>JACALES</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>VILLALPANDO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,12 +1443,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5622303333</t>
+          <t>5666090456</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C SAN ENRIQUE COND MZ 6</t>
+          <t>IXTAPALUCA CENTRO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1450,17 +1458,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>05-11-1986</t>
+          <t>03-04-2007</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MARIAGONZALEZPE511@GMAIL.COM</t>
+          <t>MELANIYATZIRI02@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 18:07:34</t>
+          <t>02-03-2026 12:39:46</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1485,7 +1493,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 19:48:43</t>
+          <t>02-03-2026 12:52:17</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1495,7 +1503,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 19:48:16</t>
+          <t>02-03-2026 12:51:36</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1505,7 +1513,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1515,7 +1523,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26220522817890005445</t>
+          <t>26220522792050005345</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1527,12 +1535,429 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>348508</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>90673</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAMUEL </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ANTONIO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5531931335</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CDA ROBLE MZ 6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>23-02-1993</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>SAMY777_2302@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:08:41</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:16:01</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:15:31</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26220522889820005682</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Luis Antonio  Chaparro Alonso</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>347541</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>89706</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AYLIN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>JACALES</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VILLALPANDO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>5529573810</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA CENTRO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>05-12-2009</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>AYLINVILLALPANDO20@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:36:05</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:49:10</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:48:39</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26220522791920005343</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>David Guillermo  Fuentes Carrillo</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>348744</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90909</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ANGEL BRAYAN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BALTAZAR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5533602578</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IXTAPALUCA </t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>16-12-2001</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ANGELBRAYANGARCIABALTAZAR6@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:22:27</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:44:47</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:42:56</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26220522921920005803</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -864,12 +864,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347529</t>
+          <t>347520</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89694</t>
+          <t>89685</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FARID JORDAN</t>
+          <t>JULIETA CALINA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -899,67 +899,79 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7291633215</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>5534197614</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AV ACOZAC CENTRO</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>10-04-2001</t>
+          <t>17-04-1967</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>FARIDJORDAN01@GMAIL.COM</t>
+          <t>CALINASILVAG@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 12:07:58</t>
+          <t>02-03-2026 11:58:20</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 12:16:51</t>
+          <t>02-03-2026 12:11:05</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:10:11</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -967,14 +979,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26220522790720005338</t>
+          <t>26220522790470005335</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -991,12 +1003,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347520</t>
+          <t>347541</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89685</t>
+          <t>89706</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +1018,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JULIETA CALINA</t>
+          <t>AYLIN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>JACALES</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>VILLALPANDO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,12 +1038,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5534197614</t>
+          <t>5529573810</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AV ACOZAC CENTRO</t>
+          <t>IXTAPALUCA CENTRO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1041,17 +1053,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>17-04-1967</t>
+          <t>05-12-2009</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CALINASILVAG@YAHOO.COM.MX</t>
+          <t>AYLINVILLALPANDO20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 11:58:20</t>
+          <t>02-03-2026 12:36:05</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1076,17 +1088,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 12:11:05</t>
+          <t>02-03-2026 12:49:10</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 12:10:11</t>
+          <t>02-03-2026 12:48:39</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1096,7 +1108,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1106,7 +1118,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26220522790470005335</t>
+          <t>26220522791920005343</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1118,12 +1130,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1232,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1359,7 +1371,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1498,7 +1510,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1547,12 +1559,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>348508</t>
+          <t>347958</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90673</t>
+          <t>90123</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1562,17 +1574,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAMUEL </t>
+          <t>STEPAHANIE AREMI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t xml:space="preserve">BLANQUET </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>MONTERO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1582,79 +1594,63 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5531931335</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>CDA ROBLE MZ 6</t>
-        </is>
-      </c>
+          <t>5527947141</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>23-02-1993</t>
+          <t>01-08-1994</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>SAMY777_2302@OUTLOOK.COM</t>
+          <t>SBLANQUETMONTERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>04-03-2026 17:08:41</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>03-03-2026 07:51:58</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>04-03-2026 17:16:01</t>
+          <t>07-03-2026 07:48:26</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>04-03-2026 17:15:31</t>
-        </is>
-      </c>
+          <t>06-04-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1662,19 +1658,27 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26220522889820005682</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26220522969530005950</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1686,12 +1690,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347541</t>
+          <t>347529</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89706</t>
+          <t>89694</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1701,17 +1705,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AYLIN</t>
+          <t>FARID JORDAN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JACALES</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VILLALPANDO</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1721,79 +1725,67 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5529573810</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>IXTAPALUCA CENTRO</t>
-        </is>
-      </c>
+          <t>7291633215</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>05-12-2009</t>
+          <t>10-04-2001</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>AYLINVILLALPANDO20@GMAIL.COM</t>
+          <t>FARIDJORDAN01@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 12:36:05</t>
+          <t>02-03-2026 12:07:58</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 12:49:10</t>
+          <t>02-03-2026 12:16:51</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-03-2026 12:48:39</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1801,36 +1793,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26220522791920005343</t>
+          <t>26220522790720005338</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>David Guillermo  Fuentes Carrillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348744</t>
+          <t>348612</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90909</t>
+          <t>90777</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1840,17 +1832,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ANGEL BRAYAN</t>
+          <t xml:space="preserve">JOSUE </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BALTAZAR</t>
+          <t>FLORIN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1860,12 +1852,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5533602578</t>
+          <t>5544682303</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">IXTAPALUCA </t>
+          <t xml:space="preserve">C ALBATROS MZA 8 LT 6 </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1875,17 +1867,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>16-12-2001</t>
+          <t>15-01-1996</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ANGELBRAYANGARCIABALTAZAR6@GMAIL.COM</t>
+          <t>VARGASFLORINJOSUE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>05-03-2026 16:22:27</t>
+          <t>05-03-2026 05:24:03</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1910,17 +1902,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>05-03-2026 16:44:47</t>
+          <t>07-03-2026 05:52:55</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>06-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>05-03-2026 16:42:56</t>
+          <t>07-03-2026 05:52:13</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1940,7 +1932,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26220522921920005803</t>
+          <t>26220522963140005946</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1952,10 +1944,288 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>Brenda Anahi  Escamilla Mendez</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>348508</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90673</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAMUEL </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ANTONIO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5531931335</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CDA ROBLE MZ 6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>23-02-1993</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>SAMY777_2302@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:08:41</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:16:01</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:15:31</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26220522889820005682</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Luis Antonio  Chaparro Alonso</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>348744</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90909</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ANGEL BRAYAN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BALTAZAR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5533602578</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IXTAPALUCA </t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>16-12-2001</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ANGELBRAYANGARCIABALTAZAR6@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:22:27</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:44:47</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:42:56</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26220522921920005803</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>329826</t>
+          <t>307705</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRENDA AYLIN </t>
+          <t>JENIFER ADAMARIS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRUZ </t>
+          <t>ESPINOSA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ALATORRE</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,79 +752,67 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5559171999</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>SAN BUENAVENTURA</t>
-        </is>
-      </c>
+          <t>5574647817</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>04-01-1998</t>
+          <t>07-07-2004</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>AYLIN.CIPRIANO@GMAIL.COM</t>
+          <t>JENNESPINOSA604@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>22-12-2025 10:04:43</t>
+          <t>04-08-2025 19:02:00</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>04-03-2026 17:11:25</t>
+          <t>09-03-2026 14:25:57</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>04-03-2026 17:10:47</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -832,44 +820,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26220522889560005681</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220523008970006062</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347520</t>
+          <t>189290</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89685</t>
+          <t>86797</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -879,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JULIETA CALINA</t>
+          <t xml:space="preserve">JOEL OMAR </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t xml:space="preserve">OJEDA </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">CASASOLA </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -899,79 +879,67 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5534197614</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>AV ACOZAC CENTRO</t>
-        </is>
-      </c>
+          <t>5521402648</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>17-04-1967</t>
+          <t>17-07-1974</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CALINASILVAG@YAHOO.COM.MX</t>
+          <t>KARICOOR_17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 11:58:20</t>
+          <t>07-08-2023 08:58:50</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 12:11:05</t>
+          <t>09-03-2026 08:02:47</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-03-2026 12:10:11</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -979,14 +947,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26220522790470005335</t>
+          <t>26220522999810006027</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1003,12 +971,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347541</t>
+          <t>329826</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89706</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1018,17 +986,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AYLIN</t>
+          <t xml:space="preserve">BRENDA AYLIN </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JACALES</t>
+          <t xml:space="preserve">CRUZ </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VILLALPANDO</t>
+          <t>ALATORRE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1038,32 +1006,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5529573810</t>
+          <t>5559171999</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IXTAPALUCA CENTRO</t>
+          <t>SAN BUENAVENTURA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>05-12-2009</t>
+          <t>04-01-1998</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>AYLINVILLALPANDO20@GMAIL.COM</t>
+          <t>AYLIN.CIPRIANO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 12:36:05</t>
+          <t>22-12-2025 10:04:43</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1088,17 +1056,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 12:49:10</t>
+          <t>04-03-2026 17:11:25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 12:48:39</t>
+          <t>04-03-2026 17:10:47</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1118,11 +1086,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26220522791920005343</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26220522889560005681</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>549</t>
@@ -1130,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>David Guillermo  Fuentes Carrillo</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1142,12 +1118,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347794</t>
+          <t>345009</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89959</t>
+          <t>22826</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1157,19 +1133,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MARIA GUADALUPE</t>
+          <t>OSCAR KEVIN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>GONZALEZ</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>PEREZ</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>52</t>
@@ -1177,39 +1153,35 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5622303333</t>
+          <t>5525350886</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C SAN ENRIQUE COND MZ 6</t>
+          <t>IXTA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>05-11-1986</t>
+          <t>19-12-2001</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MARIAGONZALEZPE511@GMAIL.COM</t>
+          <t>OSCARKRG3@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:07:34</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>19-02-2026 08:57:14</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1222,22 +1194,22 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>699</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 19:48:43</t>
+          <t>09-03-2026 11:00:00</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 19:48:16</t>
+          <t>05-03-2026 06:00:30</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1257,36 +1229,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26220522817890005445</t>
+          <t>26220522999910006029</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>699</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347537</t>
+          <t>347541</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89702</t>
+          <t>89706</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1296,17 +1268,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MARIA DE LOURDES</t>
+          <t>AYLIN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLALPANDO </t>
+          <t>JACALES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>VILLALPANDO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1316,7 +1288,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5538981251</t>
+          <t>5529573810</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1331,17 +1303,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>21-06-1966</t>
+          <t>05-12-2009</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>LEDESMAL28@HOTMAIL.COM</t>
+          <t>AYLINVILLALPANDO20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 12:32:36</t>
+          <t>02-03-2026 12:36:05</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1366,7 +1338,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 12:45:05</t>
+          <t>02-03-2026 12:49:10</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1376,7 +1348,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-03-2026 12:44:30</t>
+          <t>02-03-2026 12:48:39</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1396,7 +1368,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26220522791710005342</t>
+          <t>26220522791920005343</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1408,24 +1380,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347543</t>
+          <t>347520</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89708</t>
+          <t>89685</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1435,17 +1407,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MELANI YATZIRI</t>
+          <t>JULIETA CALINA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JACALES</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VILLALPANDO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1455,12 +1427,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5666090456</t>
+          <t>5534197614</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IXTAPALUCA CENTRO</t>
+          <t>AV ACOZAC CENTRO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1470,17 +1442,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>03-04-2007</t>
+          <t>17-04-1967</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MELANIYATZIRI02@GMAIL.COM</t>
+          <t>CALINASILVAG@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 12:39:46</t>
+          <t>02-03-2026 11:58:20</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1505,7 +1477,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 12:52:17</t>
+          <t>02-03-2026 12:11:05</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1515,7 +1487,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 12:51:36</t>
+          <t>02-03-2026 12:10:11</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1525,7 +1497,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1535,7 +1507,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26220522792050005345</t>
+          <t>26220522790470005335</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1547,24 +1519,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>David Guillermo  Fuentes Carrillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347958</t>
+          <t>347537</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90123</t>
+          <t>89702</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1574,17 +1546,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>STEPAHANIE AREMI</t>
+          <t>MARIA DE LOURDES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLANQUET </t>
+          <t xml:space="preserve">VILLALPANDO </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MONTERO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1594,10 +1566,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5527947141</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>5538981251</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA CENTRO</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1605,52 +1581,64 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>01-08-1994</t>
+          <t>21-06-1966</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>SBLANQUETMONTERO@GMAIL.COM</t>
+          <t>LEDESMAL28@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-03-2026 07:51:58</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>02-03-2026 12:32:36</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>07-03-2026 07:48:26</t>
+          <t>02-03-2026 12:45:05</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>06-04-2027 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:44:30</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1658,44 +1646,36 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26220522969530005950</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522791710005342</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347529</t>
+          <t>347543</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89694</t>
+          <t>89708</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1705,17 +1685,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FARID JORDAN</t>
+          <t>MELANI YATZIRI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>JACALES</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>VILLALPANDO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1725,67 +1705,79 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7291633215</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>5666090456</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA CENTRO</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>10-04-2001</t>
+          <t>03-04-2007</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FARIDJORDAN01@GMAIL.COM</t>
+          <t>MELANIYATZIRI02@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 12:07:58</t>
+          <t>02-03-2026 12:39:46</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 12:16:51</t>
+          <t>02-03-2026 12:52:17</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:51:36</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1793,36 +1785,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26220522790720005338</t>
+          <t>26220522792050005345</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348612</t>
+          <t>347794</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90777</t>
+          <t>89959</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1832,17 +1824,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSUE </t>
+          <t>MARIA GUADALUPE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FLORIN</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1852,32 +1844,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5544682303</t>
+          <t>5622303333</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">C ALBATROS MZA 8 LT 6 </t>
+          <t>C SAN ENRIQUE COND MZ 6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15-01-1996</t>
+          <t>05-11-1986</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>VARGASFLORINJOSUE@GMAIL.COM</t>
+          <t>MARIAGONZALEZPE511@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>05-03-2026 05:24:03</t>
+          <t>02-03-2026 18:07:34</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1902,17 +1894,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>07-03-2026 05:52:55</t>
+          <t>02-03-2026 19:48:43</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>07-03-2026 05:52:13</t>
+          <t>02-03-2026 19:48:16</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1932,7 +1924,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26220522963140005946</t>
+          <t>26220522817890005445</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1944,7 +1936,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1956,12 +1948,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348508</t>
+          <t>347958</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90673</t>
+          <t>90123</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1971,17 +1963,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAMUEL </t>
+          <t>STEPAHANIE AREMI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANTONIO</t>
+          <t xml:space="preserve">BLANQUET </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>MONTERO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1991,79 +1983,63 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5531931335</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>CDA ROBLE MZ 6</t>
-        </is>
-      </c>
+          <t>5527947141</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>23-02-1993</t>
+          <t>01-08-1994</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>SAMY777_2302@OUTLOOK.COM</t>
+          <t>SBLANQUETMONTERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>04-03-2026 17:08:41</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>03-03-2026 07:51:58</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-03-2026 17:16:01</t>
+          <t>07-03-2026 07:48:26</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>04-03-2026 17:15:31</t>
-        </is>
-      </c>
+          <t>06-04-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2071,19 +2047,27 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26220522889820005682</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26220522969530005950</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Luis Antonio  Chaparro Alonso</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2095,12 +2079,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348744</t>
+          <t>347529</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90909</t>
+          <t>89694</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2110,17 +2094,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ANGEL BRAYAN</t>
+          <t>FARID JORDAN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BALTAZAR</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2130,14 +2114,10 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5533602578</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IXTAPALUCA </t>
-        </is>
-      </c>
+          <t>7291633215</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2145,64 +2125,56 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>16-12-2001</t>
+          <t>10-04-2001</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ANGELBRAYANGARCIABALTAZAR6@GMAIL.COM</t>
+          <t>FARIDJORDAN01@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>05-03-2026 16:22:27</t>
+          <t>02-03-2026 12:07:58</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>05-03-2026 16:44:47</t>
+          <t>02-03-2026 12:16:51</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>05-03-2026 16:42:56</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2210,24 +2182,3185 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26220522921920005803</t>
+          <t>26220522790720005338</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>348612</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90777</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSUE </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>VARGAS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>FLORIN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>5544682303</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C ALBATROS MZA 8 LT 6 </t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>15-01-1996</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>VARGASFLORINJOSUE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>05-03-2026 05:24:03</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>07-03-2026 05:52:55</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>07-03-2026 05:52:13</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26220522963140005946</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Brenda Anahi  Escamilla Mendez</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>348744</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90909</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ANGEL BRAYAN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>BALTAZAR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5533602578</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IXTAPALUCA </t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>16-12-2001</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ANGELBRAYANGARCIABALTAZAR6@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:22:27</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:44:47</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>05-03-2026 16:42:56</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26220522921920005803</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348508</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90673</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAMUEL </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ANTONIO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5531931335</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CDA ROBLE MZ 6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>23-02-1993</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>SAMY777_2302@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:08:41</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:16:01</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:15:31</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26220522889820005682</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Svein  Peñaloza Lara</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>349177</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>91342</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MARTHA PATRICIA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVA </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>5532672328</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>56530</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>15-06-1975</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>SILVA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>08-03-2026 09:42:53</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>09-03-2026 09:55:54</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>09-03-2026 09:55:10</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26220523002690006039</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>349389</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>91554</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>JULIO CESAR</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SANTOS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>FUENTES</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>7711791653</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>30-01-2002</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>JULIOCSFUENTES@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>09-03-2026 12:01:31</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>13-03-2026 19:11:14</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26280523162430009988</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>349313</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>91478</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRENDA </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OJEDA </t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5544222203</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>10-08-1995</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>KAR_PINK_ITO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:00:23</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:01:30</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26220522999740006026</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>349472</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>91637</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ARANO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>5562215116</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>01-06-2001</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>SANTIAGO.GTEZ.ARANA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>09-03-2026 15:16:07</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>09-03-2026 15:23:39</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26280523011210009167</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>349830</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>91995</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SANDRA PATRICIA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ARMENTA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>5576868600</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>C TEZOMPA MZA 29</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>04-08-1979</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PATYSANDY260@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>10-03-2026 12:58:39</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>10-03-2026 13:10:09</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>10-03-2026 13:09:03</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26220523050820006183</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Svein  Peñaloza Lara</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>349854</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>92019</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ALAM JOSHUA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MENDOZA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BALBUENA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>5531277809</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NARANJERAS 16</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>13-10-2005</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>ALAMJOSH05@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:27:51</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:42:38</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:39:57</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26280523053470009378</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Carlos Arturo Flores Alvarez</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>349959</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>92124</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ARTURO UZIEL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TOVAR</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>5526660967</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>02-10-2001</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>UZIELTOVAR4@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:41:41</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>18-03-2026 17:18:40</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>17-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26220523298560006931</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Svein  Peñaloza Lara</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>350090</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>92255</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>JAZMIN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CADENA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>GUZMAN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>5630838234</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SAN BUENA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>08-11-2002</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>JAZMINGUZMAN0193@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>11-03-2026 12:14:23</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>11-03-2026 12:19:30</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>11-03-2026 12:19:05</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26220523087450006310</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Svein  Peñaloza Lara</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>349996</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>92161</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MARIA CLAUDIA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PAREDES</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>5530629905</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>09-06-1988</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>GABY23PAREDEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:33:41</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:52:51</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:51:03</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26280523069900009474</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Carlos Arturo Flores Alvarez</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>350311</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>92475</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DANIEL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ALVARADO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>5535129659</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>18-07-1997</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ALXNHDZ29@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>12-03-2026 12:31:53</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>12-03-2026 12:35:52</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>12-03-2026 12:35:16</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26220523121490006428</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Brenda Anahi  Escamilla Mendez</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>349997</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>92162</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RAYMUNDO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAZ </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5521915315</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>11-06-1983</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>RAYO23ISMA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:34:46</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:58:16</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:57:47</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26280523070190009478</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Carlos Arturo Flores Alvarez</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>350786</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>92950</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>JOSE ANTONIO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PADILLA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5544804372</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>C MEXICO 10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>17-08-1977</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>PD_@YAHOO.COM.MX</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>14-03-2026 11:26:49</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:07:04</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:06:12</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26220523220750006713</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>350639</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>92803</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>GUSTAVO ADOLFO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ROJAS</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>5531163423</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TLALPAN</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>10-11-1983</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DR.GUSTAVO@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>13-03-2026 17:34:40</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>13-03-2026 17:45:29</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>13-03-2026 17:43:22</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26280523159280009967</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Christian Yair Peña Villa</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>351544</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>93708</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VICTOR MANUEL </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ANDRADE</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>5535839863</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>C CICLON MZ 32</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>23-12-1960</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>VICTORANDRADEHZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:37:37</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:45:29</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:44:32</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26220523257000006832</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>351029</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>93193</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDNA FABIOLA </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRUZ </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PICHARDO </t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>5520660002</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CDA DEL TRABAJO</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>19-05-1989</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>LEPFABYCRUZ@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>16-03-2026 09:28:20</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>16-03-2026 11:12:22</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>16-03-2026 11:11:44</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26280523216320010123</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>JOSE RAUL MARTINEZ AMADOR</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Christian Yair Peña Villa</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>351030</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>93194</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIEGO </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUTIERREZ </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES </t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>5580044828</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>28-04-1989</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>LAIDIEGOGUTIERREZ@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>16-03-2026 09:29:33</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>16-03-2026 11:17:55</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>16-03-2026 11:17:29</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26280523216600010124</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>JOSE RAUL MARTINEZ AMADOR</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Christian Yair Peña Villa</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>351285</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>93449</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>JOSE RODRIGO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NOGUERON</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>HENARES</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>5549364625</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>08-01-2008</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>ADEPLOKI2008@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:52:06</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:58:24</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26220523229830006742</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Svein  Peñaloza Lara</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>351537</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>93701</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ESCARCEGA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>GIL</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>5513677806</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>FRACC IZCALLI</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>04-07-2012</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DEREKCITO.ESKA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:12:47</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:18:46</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>17-03-2026 15:18:14</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26220523255860006829</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>351282</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>93446</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>INGRID</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NOGUERON</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>HENARES</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>5560862817</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>CDA PUENTE DE FIERRO MZ65</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>07-09-2001</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NOGUERONHENARESI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:49:37</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:58:24</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:56:23</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26220523229830006742</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Svein  Peñaloza Lara</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>352166</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>94330</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESTEPHANIA </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>5543625065</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>CAMINO A CANUTILLO 8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>22-02-1997</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>FANYCJ@LIVE.COM.MX</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>19-03-2026 18:03:43</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>19-03-2026 18:10:19</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>19-03-2026 18:09:34</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26220523337140007062</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Svein  Peñaloza Lara</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__IXTAPALUCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,12 +1253,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347541</t>
+          <t>347529</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89706</t>
+          <t>89694</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1268,17 +1268,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AYLIN</t>
+          <t>FARID JORDAN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JACALES</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VILLALPANDO</t>
+          <t>NAVARRO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,79 +1288,67 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5529573810</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>IXTAPALUCA CENTRO</t>
-        </is>
-      </c>
+          <t>7291633215</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>05-12-2009</t>
+          <t>10-04-2001</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>AYLINVILLALPANDO20@GMAIL.COM</t>
+          <t>FARIDJORDAN01@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 12:36:05</t>
+          <t>02-03-2026 12:07:58</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 12:49:10</t>
+          <t>02-03-2026 12:16:51</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>02-03-2026 12:48:39</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1368,36 +1356,36 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26220522791920005343</t>
+          <t>26220522790720005338</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>David Guillermo  Fuentes Carrillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347520</t>
+          <t>345444</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89685</t>
+          <t>87609</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1407,17 +1395,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JULIETA CALINA</t>
+          <t xml:space="preserve">CESAR ALDAIR </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t xml:space="preserve">LUNA </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1427,32 +1415,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5534197614</t>
+          <t>5621417499</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AV ACOZAC CENTRO</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>17-04-1967</t>
+          <t>30-03-2001</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CALINASILVAG@YAHOO.COM.MX</t>
+          <t>CESARLAIKA23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 11:58:20</t>
+          <t>21-02-2026 07:05:57</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1477,17 +1465,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 12:11:05</t>
+          <t>25-03-2026 16:56:16</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>24-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 12:10:11</t>
+          <t>25-03-2026 16:55:45</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1497,7 +1485,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1507,10 +1495,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26220522790470005335</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
+          <t>26220523506920007606</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1809,12 +1801,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347794</t>
+          <t>347520</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89959</t>
+          <t>89685</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1824,17 +1816,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MARIA GUADALUPE</t>
+          <t>JULIETA CALINA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1844,12 +1836,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5622303333</t>
+          <t>5534197614</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C SAN ENRIQUE COND MZ 6</t>
+          <t>AV ACOZAC CENTRO</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1859,17 +1851,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>05-11-1986</t>
+          <t>17-04-1967</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MARIAGONZALEZPE511@GMAIL.COM</t>
+          <t>CALINASILVAG@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 18:07:34</t>
+          <t>02-03-2026 11:58:20</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1894,7 +1886,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 19:48:43</t>
+          <t>02-03-2026 12:11:05</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1904,7 +1896,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>02-03-2026 19:48:16</t>
+          <t>02-03-2026 12:10:11</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1924,7 +1916,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26220522817890005445</t>
+          <t>26220522790470005335</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1936,24 +1928,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347958</t>
+          <t>347541</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90123</t>
+          <t>89706</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1963,17 +1955,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>STEPAHANIE AREMI</t>
+          <t>AYLIN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLANQUET </t>
+          <t>JACALES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MONTERO</t>
+          <t>VILLALPANDO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1983,10 +1975,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5527947141</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>5529573810</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA CENTRO</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1994,52 +1990,64 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>01-08-1994</t>
+          <t>05-12-2009</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>SBLANQUETMONTERO@GMAIL.COM</t>
+          <t>AYLINVILLALPANDO20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 07:51:58</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>02-03-2026 12:36:05</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>07-03-2026 07:48:26</t>
+          <t>02-03-2026 12:49:10</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>06-04-2027 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:48:39</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2047,27 +2055,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26220522969530005950</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522791920005343</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>David Guillermo  Fuentes Carrillo</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2079,12 +2079,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347529</t>
+          <t>347794</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89694</t>
+          <t>89959</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2094,17 +2094,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FARID JORDAN</t>
+          <t>MARIA GUADALUPE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2114,67 +2114,79 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7291633215</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>5622303333</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>C SAN ENRIQUE COND MZ 6</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10-04-2001</t>
+          <t>05-11-1986</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FARIDJORDAN01@GMAIL.COM</t>
+          <t>MARIAGONZALEZPE511@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 12:07:58</t>
+          <t>02-03-2026 18:07:34</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 12:16:51</t>
+          <t>02-03-2026 19:48:43</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:48:16</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2182,36 +2194,36 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26220522790720005338</t>
+          <t>26220522817890005445</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348612</t>
+          <t>347958</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90777</t>
+          <t>90123</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2221,17 +2233,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSUE </t>
+          <t>STEPAHANIE AREMI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t xml:space="preserve">BLANQUET </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FLORIN</t>
+          <t>MONTERO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2241,79 +2253,63 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5544682303</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C ALBATROS MZA 8 LT 6 </t>
-        </is>
-      </c>
+          <t>5527947141</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>15-01-1996</t>
+          <t>01-08-1994</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>VARGASFLORINJOSUE@GMAIL.COM</t>
+          <t>SBLANQUETMONTERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>05-03-2026 05:24:03</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>03-03-2026 07:51:58</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>07-03-2026 05:52:55</t>
+          <t>07-03-2026 07:48:26</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>07-03-2026 05:52:13</t>
-        </is>
-      </c>
+          <t>06-04-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2321,14 +2317,22 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26220522963140005946</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26220522969530005950</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2345,12 +2349,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348744</t>
+          <t>348612</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90909</t>
+          <t>90777</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2360,17 +2364,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ANGEL BRAYAN</t>
+          <t xml:space="preserve">JOSUE </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BALTAZAR</t>
+          <t>FLORIN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2380,12 +2384,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5533602578</t>
+          <t>5544682303</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">IXTAPALUCA </t>
+          <t xml:space="preserve">C ALBATROS MZA 8 LT 6 </t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2395,17 +2399,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>16-12-2001</t>
+          <t>15-01-1996</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ANGELBRAYANGARCIABALTAZAR6@GMAIL.COM</t>
+          <t>VARGASFLORINJOSUE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>05-03-2026 16:22:27</t>
+          <t>05-03-2026 05:24:03</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2430,17 +2434,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>05-03-2026 16:44:47</t>
+          <t>07-03-2026 05:52:55</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>06-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>05-03-2026 16:42:56</t>
+          <t>07-03-2026 05:52:13</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2460,7 +2464,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26220522921920005803</t>
+          <t>26220522963140005946</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2472,12 +2476,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -2623,12 +2627,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>349177</t>
+          <t>348744</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>91342</t>
+          <t>90909</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2638,17 +2642,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MARTHA PATRICIA</t>
+          <t>ANGEL BRAYAN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVA </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>BALTAZAR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2658,32 +2662,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5532672328</t>
+          <t>5533602578</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>56530</t>
+          <t xml:space="preserve">IXTAPALUCA </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>15-06-1975</t>
+          <t>16-12-2001</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>SILVA@GMAIL.COM</t>
+          <t>ANGELBRAYANGARCIABALTAZAR6@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>08-03-2026 09:42:53</t>
+          <t>05-03-2026 16:22:27</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2708,17 +2712,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>09-03-2026 09:55:54</t>
+          <t>05-03-2026 16:44:47</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>09-03-2026 09:55:10</t>
+          <t>05-03-2026 16:42:56</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2728,7 +2732,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2738,19 +2742,11 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26220523002690006039</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>DANIA ESTER CUBIAS GALLEGOS</t>
-        </is>
-      </c>
+          <t>26220522921920005803</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
           <t>549</t>
@@ -2770,12 +2766,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>349389</t>
+          <t>349177</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>91554</t>
+          <t>91342</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2785,17 +2781,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>MARTHA PATRICIA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t xml:space="preserve">SILVA </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FUENTES</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2805,43 +2801,47 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7711791653</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>5532672328</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>56530</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>30-01-2002</t>
+          <t>15-06-1975</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>JULIOCSFUENTES@GMAIL.COM</t>
+          <t>SILVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>09-03-2026 12:01:31</t>
+          <t>08-03-2026 09:42:53</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Tarifas 2026 HE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2851,21 +2851,29 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>13-03-2026 19:11:14</t>
+          <t>09-03-2026 09:55:54</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>12-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>09-03-2026 09:55:10</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2873,11 +2881,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26280523162430009988</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26220523002690006039</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>DANIA ESTER CUBIAS GALLEGOS</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>549</t>
@@ -2897,12 +2913,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>349313</t>
+          <t>349389</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>91478</t>
+          <t>91554</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2912,17 +2928,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRENDA </t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">OJEDA </t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>FUENTES</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2932,33 +2948,33 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5544222203</t>
+          <t>7711791653</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>10-08-1995</t>
+          <t>30-01-2002</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>KAR_PINK_ITO@GMAIL.COM</t>
+          <t>JULIOCSFUENTES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>09-03-2026 08:00:23</t>
+          <t>09-03-2026 12:01:31</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Tarifas 2026 HE</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2968,28 +2984,28 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>09-03-2026 08:01:30</t>
+          <t>13-03-2026 19:11:14</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>12-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -3000,14 +3016,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26220522999740006026</t>
+          <t>26280523162430009988</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3151,12 +3167,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>349830</t>
+          <t>349959</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>91995</t>
+          <t>92124</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3166,17 +3182,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SANDRA PATRICIA</t>
+          <t>ARTURO UZIEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ARMENTA</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3186,32 +3202,28 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5576868600</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>C TEZOMPA MZA 29</t>
-        </is>
-      </c>
+          <t>5526660967</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>04-08-1979</t>
+          <t>02-10-2001</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>PATYSANDY260@GMAIL.COM</t>
+          <t>UZIELTOVAR4@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>10-03-2026 12:58:39</t>
+          <t>10-03-2026 18:41:41</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3221,44 +3233,36 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>10-03-2026 13:10:09</t>
+          <t>18-03-2026 17:18:40</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>10-03-2026 13:09:03</t>
-        </is>
-      </c>
+          <t>17-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3266,14 +3270,18 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26220523050820006183</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
+          <t>26220523298560006931</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3290,12 +3298,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>349854</t>
+          <t>350786</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>92019</t>
+          <t>92950</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3305,17 +3313,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ALAM JOSHUA</t>
+          <t>JOSE ANTONIO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>PADILLA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BALBUENA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3325,12 +3333,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5531277809</t>
+          <t>5544804372</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NARANJERAS 16</t>
+          <t>C MEXICO 10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3340,52 +3348,52 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13-10-2005</t>
+          <t>17-08-1977</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ALAMJOSH05@GMAIL.COM</t>
+          <t>PD_@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>10-03-2026 14:27:51</t>
+          <t>14-03-2026 11:26:49</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Tarifas 2026 HE</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>10-03-2026 14:42:38</t>
+          <t>16-03-2026 13:07:04</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>10-03-2026 14:39:57</t>
+          <t>16-03-2026 13:06:12</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3405,36 +3413,40 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26280523053470009378</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
+          <t>26220523220750006713</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Carlos Arturo Flores Alvarez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>349959</t>
+          <t>350311</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>92124</t>
+          <t>92475</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3444,12 +3456,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ARTURO UZIEL</t>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3464,10 +3476,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5526660967</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>5535129659</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3475,56 +3491,64 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>02-10-2001</t>
+          <t>18-07-1997</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>UZIELTOVAR4@GMAIL.COM</t>
+          <t>ALXNHDZ29@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>10-03-2026 18:41:41</t>
+          <t>12-03-2026 12:31:53</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>18-03-2026 17:18:40</t>
+          <t>12-03-2026 12:35:52</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>17-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>12-03-2026 12:35:16</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3532,23 +3556,19 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26220523298560006931</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26220523121490006428</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3560,12 +3580,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>350090</t>
+          <t>351537</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>92255</t>
+          <t>93701</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3575,17 +3595,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>JAZMIN</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CADENA</t>
+          <t>ESCARCEGA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>GIL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3595,32 +3615,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5630838234</t>
+          <t>5513677806</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SAN BUENA</t>
+          <t>FRACC IZCALLI</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>08-11-2002</t>
+          <t>04-07-2012</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>JAZMINGUZMAN0193@GMAIL.COM</t>
+          <t>DEREKCITO.ESKA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>11-03-2026 12:14:23</t>
+          <t>17-03-2026 15:12:47</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3645,17 +3665,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>11-03-2026 12:19:30</t>
+          <t>17-03-2026 15:18:46</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>10-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>11-03-2026 12:19:05</t>
+          <t>17-03-2026 15:18:14</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3675,7 +3695,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26220523087450006310</t>
+          <t>26220523255860006829</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3687,12 +3707,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -3838,12 +3858,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>350311</t>
+          <t>351285</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>92475</t>
+          <t>93449</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3853,17 +3873,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DANIEL</t>
+          <t>JOSE RODRIGO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>NOGUERON</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>HENARES</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3873,14 +3893,10 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5535129659</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>IXTAPALUCA</t>
-        </is>
-      </c>
+          <t>5549364625</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3888,64 +3904,52 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18-07-1997</t>
+          <t>08-01-2008</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ALXNHDZ29@GMAIL.COM</t>
+          <t>ADEPLOKI2008@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>12-03-2026 12:31:53</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>16-03-2026 17:52:06</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>12-03-2026 12:35:52</t>
+          <t>16-03-2026 17:58:24</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>12-03-2026 12:35:16</t>
-        </is>
-      </c>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3953,19 +3957,19 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26220523121490006428</t>
+          <t>26220523229830006742</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Brenda Anahi  Escamilla Mendez</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3977,12 +3981,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>349997</t>
+          <t>351029</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>92162</t>
+          <t>93193</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3992,17 +3996,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t xml:space="preserve">EDNA FABIOLA </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAZ </t>
+          <t xml:space="preserve">CRUZ </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">PICHARDO </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4012,32 +4016,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5521915315</t>
+          <t>5520660002</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TLALPAN</t>
+          <t>CDA DEL TRABAJO</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>11-06-1983</t>
+          <t>19-05-1989</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>RAYO23ISMA@GMAIL.COM</t>
+          <t>LEPFABYCRUZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10-03-2026 19:34:46</t>
+          <t>16-03-2026 09:28:20</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4062,17 +4066,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>10-03-2026 19:58:16</t>
+          <t>16-03-2026 11:12:22</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>10-03-2026 19:57:47</t>
+          <t>16-03-2026 11:11:44</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4092,11 +4096,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26280523070190009478</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+          <t>26280523216320010123</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>JOSE RAUL MARTINEZ AMADOR</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>649</t>
@@ -4104,7 +4116,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Carlos Arturo Flores Alvarez</t>
+          <t>Christian Yair Peña Villa</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4116,12 +4128,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>350786</t>
+          <t>350639</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>92950</t>
+          <t>92803</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4131,17 +4143,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO</t>
+          <t>GUSTAVO ADOLFO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PADILLA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4151,12 +4163,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5544804372</t>
+          <t>5531163423</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C MEXICO 10</t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4166,22 +4178,22 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>17-08-1977</t>
+          <t>10-11-1983</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>PD_@YAHOO.COM.MX</t>
+          <t>DR.GUSTAVO@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>14-03-2026 11:26:49</t>
+          <t>13-03-2026 17:34:40</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Tarifas 2026 HE</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -4191,27 +4203,27 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>16-03-2026 13:07:04</t>
+          <t>13-03-2026 17:45:29</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
+          <t>12-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>16-03-2026 13:06:12</t>
+          <t>13-03-2026 17:43:22</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4231,40 +4243,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26220523220750006713</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26280523159280009967</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Yair Peña Villa</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>350639</t>
+          <t>351030</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>92803</t>
+          <t>93194</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4274,17 +4282,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GUSTAVO ADOLFO</t>
+          <t xml:space="preserve">DIEGO </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4294,14 +4302,10 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5531163423</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>TLALPAN</t>
-        </is>
-      </c>
+          <t>5580044828</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4309,17 +4313,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>10-11-1983</t>
+          <t>28-04-1989</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>DR.GUSTAVO@OUTLOOK.COM</t>
+          <t>LAIDIEGOGUTIERREZ@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>13-03-2026 17:34:40</t>
+          <t>16-03-2026 09:29:33</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4334,27 +4338,27 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>13-03-2026 17:45:29</t>
+          <t>16-03-2026 11:17:55</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>12-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>13-03-2026 17:43:22</t>
+          <t>16-03-2026 11:17:29</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4364,7 +4368,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4374,14 +4378,22 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26280523159280009967</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+          <t>26280523216600010124</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>JOSE RAUL MARTINEZ AMADOR</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4398,12 +4410,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>351544</t>
+          <t>351282</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>93446</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4413,17 +4425,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR MANUEL </t>
+          <t>INGRID</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>NOGUERON</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>HENARES</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4433,37 +4445,37 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5535839863</t>
+          <t>5560862817</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C CICLON MZ 32</t>
+          <t>CDA PUENTE DE FIERRO MZ65</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>23-12-1960</t>
+          <t>07-09-2001</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>VICTORANDRADEHZ@GMAIL.COM</t>
+          <t>NOGUERONHENARESI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>17-03-2026 15:37:37</t>
+          <t>16-03-2026 17:49:37</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -4473,27 +4485,27 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>17-03-2026 15:45:29</t>
+          <t>16-03-2026 17:58:24</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>17-03-2026 15:44:32</t>
+          <t>16-03-2026 17:56:23</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4503,7 +4515,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4513,36 +4525,36 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26220523257000006832</t>
+          <t>26220523229830006742</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>351029</t>
+          <t>351544</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>93193</t>
+          <t>93708</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4552,17 +4564,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDNA FABIOLA </t>
+          <t xml:space="preserve">VICTOR MANUEL </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRUZ </t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">PICHARDO </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4572,37 +4584,37 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5520660002</t>
+          <t>5535839863</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CDA DEL TRABAJO</t>
+          <t>C CICLON MZ 32</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19-05-1989</t>
+          <t>23-12-1960</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>LEPFABYCRUZ@HOTMAIL.COM</t>
+          <t>VICTORANDRADEHZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>16-03-2026 09:28:20</t>
+          <t>17-03-2026 15:37:37</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Tarifas 2026 HE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -4612,17 +4624,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>16-03-2026 11:12:22</t>
+          <t>17-03-2026 15:45:29</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4632,7 +4644,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>16-03-2026 11:11:44</t>
+          <t>17-03-2026 15:44:32</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4652,44 +4664,36 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26280523216320010123</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>JOSE RAUL MARTINEZ AMADOR</t>
-        </is>
-      </c>
+          <t>26220523257000006832</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Christian Yair Peña Villa</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>351030</t>
+          <t>352487</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>93194</t>
+          <t>94651</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4699,17 +4703,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIEGO </t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>MACEDO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4719,28 +4723,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5580044828</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>5517264326</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>INSURGENTES SUR</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>28-04-1989</t>
+          <t>10-06-1998</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>LAIDIEGOGUTIERREZ@OUTLOOK.COM</t>
+          <t>FEER_HIDE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>16-03-2026 09:29:33</t>
+          <t>21-03-2026 10:20:20</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4755,27 +4763,27 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $649 HE</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>16-03-2026 11:17:55</t>
+          <t>21-03-2026 12:54:28</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>21-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>16-03-2026 11:17:29</t>
+          <t>21-03-2026 12:52:31</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4785,7 +4793,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4795,7 +4803,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26280523216600010124</t>
+          <t>26280523395060011102</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4803,19 +4811,15 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>JOSE RAUL MARTINEZ AMADOR</t>
-        </is>
-      </c>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Christian Yair Peña Villa</t>
+          <t>Josue Radames Rosales Rojas</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4827,12 +4831,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>351285</t>
+          <t>352656</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>93449</t>
+          <t>94820</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4842,17 +4846,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JOSE RODRIGO</t>
+          <t xml:space="preserve">LILY </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NOGUERON</t>
+          <t xml:space="preserve"> LOO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HENARES</t>
+          <t>CERVERA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4862,63 +4866,79 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5549364625</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>5551581097</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>56530</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>08-01-2008</t>
+          <t>20-09-2004</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ADEPLOKI2008@GMAIL.COM</t>
+          <t>LOOLILY554@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>16-03-2026 17:52:06</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>23-03-2026 07:31:55</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>16-03-2026 17:58:24</t>
+          <t>23-03-2026 07:38:07</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>23-03-2026 07:34:10</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4926,19 +4946,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26220523229830006742</t>
+          <t>26220523417150007306</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>Brenda Anahi  Escamilla Mendez</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4950,12 +4970,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>351537</t>
+          <t>352627</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>93701</t>
+          <t>94791</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4965,17 +4985,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>YULEIMY YAEL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ESCARCEGA</t>
+          <t>BASTIDA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GIL</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4985,32 +5005,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5513677806</t>
+          <t>5535096104</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>FRACC IZCALLI</t>
+          <t>C CERRO DEL TLALPIPI MZ 10 C</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>04-07-2012</t>
+          <t>05-01-1994</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>DEREKCITO.ESKA@GMAIL.COM</t>
+          <t>E.YULY.BC.05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>17-03-2026 15:12:47</t>
+          <t>22-03-2026 19:29:09</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5035,17 +5055,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>17-03-2026 15:18:46</t>
+          <t>26-03-2026 14:03:16</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>25-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>17-03-2026 15:18:14</t>
+          <t>26-03-2026 14:02:35</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5055,7 +5075,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5065,7 +5085,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26220523255860006829</t>
+          <t>26220523534430007699</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5077,24 +5097,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>351282</t>
+          <t>349997</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>93446</t>
+          <t>92162</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5104,17 +5124,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>INGRID</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NOGUERON</t>
+          <t xml:space="preserve">DIAZ </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HENARES</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5124,37 +5144,37 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5560862817</t>
+          <t>5521915315</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CDA PUENTE DE FIERRO MZ65</t>
+          <t>TLALPAN</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>07-09-2001</t>
+          <t>11-06-1983</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>NOGUERONHENARESI@GMAIL.COM</t>
+          <t>RAYO23ISMA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>16-03-2026 17:49:37</t>
+          <t>10-03-2026 19:34:46</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Tarifas 2026 HE</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -5164,27 +5184,27 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>16-03-2026 17:58:24</t>
+          <t>10-03-2026 19:58:16</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>16-03-2026 17:56:23</t>
+          <t>10-03-2026 19:57:47</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5194,7 +5214,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5204,19 +5224,19 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26220523229830006742</t>
+          <t>26280523070190009478</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Svein  Peñaloza Lara</t>
+          <t>Carlos Arturo Flores Alvarez</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5228,12 +5248,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>352166</t>
+          <t>349313</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>94330</t>
+          <t>91478</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5243,17 +5263,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTEPHANIA </t>
+          <t xml:space="preserve">BRENDA </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">OJEDA </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5263,14 +5283,10 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5543625065</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>CAMINO A CANUTILLO 8</t>
-        </is>
-      </c>
+          <t>5544222203</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5278,17 +5294,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>22-02-1997</t>
+          <t>10-08-1995</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>FANYCJ@LIVE.COM.MX</t>
+          <t>KAR_PINK_ITO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19-03-2026 18:03:43</t>
+          <t>09-03-2026 08:00:23</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5298,44 +5314,36 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>19-03-2026 18:10:19</t>
+          <t>09-03-2026 08:01:30</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>19-03-2026 18:09:34</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5343,24 +5351,2740 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26220523337140007062</t>
+          <t>26220522999740006026</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>352499</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>94663</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DIEGO OCTAVIO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZUÑIGA </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ALCARAZ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>5524969672</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>INSURGENTES SUR</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>13-08-1992</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>DIEGOZUALD@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>21-03-2026 10:51:37</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>23-03-2026 10:08:26</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>23-03-2026 10:07:39</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26280523421380011190</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>JOSE RAUL MARTINEZ AMADOR</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>353284</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>95448</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIANA AIMEE </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MERINO </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOPEZ </t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>5621730933</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SAN MARCOS</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>30-03-1997</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>AIMEEKVN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>25-03-2026 09:06:15</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>25-03-2026 09:10:49</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>25-03-2026 09:09:42</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26220523496620007568</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
         <is>
           <t>Svein  Peñaloza Lara</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>353429</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>95593</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LUIS URIEL</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PAZ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SOTELO</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>5565646324</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>C 7 116</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>10-05-2000</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>PAZLUIZ105@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>25-03-2026 18:42:48</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>25-03-2026 18:49:37</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>25-03-2026 18:49:04</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26220523512880007632</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Svein  Peñaloza Lara</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>352813</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>94977</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ELVIA DANYRA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>MENDOZA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>9611758393</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>14-07-1990</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>BOGUIRA_66@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>23-03-2026 16:14:15</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3 MESES $2,099</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>699.67</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>23-03-2026 16:21:12</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>22-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26280523431770011268</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>353285</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>95449</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>JORGE ISAAC</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA </t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5560438709</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>09-02-1997</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>DEADBYDAYLIGHT13666@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>25-03-2026 09:07:40</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>25-03-2026 09:10:49</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26220523496620007568</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Brenda Anahi  Escamilla Mendez</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>353558</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>95722</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DENEFF</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ALONSO</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5514964095</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>CDA BOLINA MZA 16</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>01-06-2004</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>ALONSODENEFF@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>26-03-2026 14:09:29</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>26-03-2026 14:35:53</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>26-03-2026 14:25:46</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26220523535220007704</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>352739</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>94903</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>FELIPE DANIEL</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>5534456701</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>22-07-2010</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>BELLOFELIPEDANIEL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>23-03-2026 12:07:49</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>24-03-2026 12:28:07</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26280523465250011435</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>352876</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>95040</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>KARINA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CAMPOS</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DETTMER</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>5515213533</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INSURGENTES SUR </t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>01-02-1983</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>KARIYDETTMER@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>23-03-2026 17:54:58</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $649 HE</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>23-03-2026 18:05:41</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>23-03-2026 18:04:02</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26280523438510011305</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>353383</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>95547</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MARIANA ARACELI</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>VENEGAS</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ALBA</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5635504352</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>C PALMERA NEGRA MZA 29</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>01-08-1999</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>MVENEGAS746@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>25-03-2026 16:47:36</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>25-03-2026 16:52:55</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>25-03-2026 16:52:13</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26220523506740007604</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>353395</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>95559</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MONTSERRAT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SAUZA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5617947826</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>16-06-1994</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>MONTSERRAT.RODRIGUEZ.SUAZA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:14:36</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:20:27</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26220523507960007609</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>353791</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>95955</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>FERNANDA ZOE</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>VARGAS</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>BAUTISTA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>8999982366</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>15-07-2006</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>FERNANDAFBUATISTA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>27-03-2026 17:31:31</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>27-03-2026 17:36:35</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>26-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26220523570250007837</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Brenda Anahi  Escamilla Mendez</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>353393</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>95557</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ROGELIO MIGUEL</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SIGUENZA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>5513561284</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>C HIDALGO 40</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>09-09-1991</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>RUOCYR_UCRAE@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:13:03</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:20:27</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:18:47</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26220523507960007609</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>349830</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>91995</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SANDRA PATRICIA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ARMENTA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>5576868600</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>C TEZOMPA MZA 29</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>04-08-1979</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>PATYSANDY260@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>10-03-2026 12:58:39</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>10-03-2026 13:10:09</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>10-03-2026 13:09:03</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26220523050820006183</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Svein  Peñaloza Lara</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>349854</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>92019</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ALAM JOSHUA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>MENDOZA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BALBUENA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>5531277809</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>NARANJERAS 16</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>13-10-2005</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>ALAMJOSH05@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:27:51</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>CONVENIO DOMICILIADO $549</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:42:38</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:39:57</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26280523053470009378</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Carlos Arturo Flores Alvarez</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>350090</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>92255</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>JAZMIN</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>CADENA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>GUZMAN</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>5630838234</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>SAN BUENA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>08-11-2002</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>JAZMINGUZMAN0193@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>11-03-2026 12:14:23</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>11-03-2026 12:19:30</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>11-03-2026 12:19:05</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26220523087450006310</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Svein  Peñaloza Lara</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>352166</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>94330</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESTEPHANIA </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>5543625065</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>CAMINO A CANUTILLO 8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>22-02-1997</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>FANYCJ@LIVE.COM.MX</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>19-03-2026 18:03:43</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>19-03-2026 18:10:19</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>19-03-2026 18:09:34</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26220523337140007062</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Svein  Peñaloza Lara</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>352786</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>94950</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REBECA </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PADILLA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>VARGAS</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>5510706192</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INSURGENTES SUR </t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>03-01-1998</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>REBECAPV03@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>23-03-2026 15:16:29</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 HE</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,549 HE</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>23-03-2026 15:40:59</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>23-03-2026 15:39:57</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26280523430260011255</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Diana Itzel Martinez Colín</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>353789</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>95953</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ABIGAIL</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>NUÑEZ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>VERDEJA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>5551494036</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>COND MAGDALENA MZA 2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>17-04-2003</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>ABIGAILNUNEZBJA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>27-03-2026 17:30:06</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>27-03-2026 17:36:35</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>26-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>27-03-2026 17:35:58</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26220523570250007837</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>353406</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>95570</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>FABIOLA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ALFARO</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CASTILLO</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>5548767016</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>BLVD CUAUHTEMMOC PONIENTE SN</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>31-05-1969</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>FABIOLAALFAROCASTILLO@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:53:03</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:57:25</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:56:38</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26220523509990007621</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>353557</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>95721</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MARCO ANTONIO</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>MENA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>5652535403</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>CDA BOLINA MZA 16</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>27-10-1986</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>MARCOANTONIOLOPEZ@YAHOO.COM.MX</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>26-03-2026 14:07:22</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>26-03-2026 14:16:54</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>26-03-2026 14:15:52</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26220523534680007700</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
